--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="572">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>33</t>
+    <t>32</t>
   </si>
   <si>
     <t>1위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>590경 105조 2361억 5050만</t>
+    <t>602경 2808조 3209억 1039만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
@@ -101,36 +101,39 @@
     <t>혜영</t>
   </si>
   <si>
+    <t>2026.09.13</t>
+  </si>
+  <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>426경 4014조 630억 3459만</t>
+  </si>
+  <si>
+    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
     <t>2026.09.12</t>
   </si>
   <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>423경 5784조 1410억 7919만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
     <t>호러</t>
   </si>
   <si>
@@ -143,7 +146,7 @@
     <t>36</t>
   </si>
   <si>
-    <t>489경 1106조 8141억 5819만</t>
+    <t>490경 142조 9842억 9830만</t>
   </si>
   <si>
     <t>오래 하실분들 환영입니다</t>
@@ -167,7 +170,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>356경 8997조 6517억 710만</t>
+    <t>358경 322조 7357억 4279만</t>
   </si>
   <si>
     <t>월드아레나 대비 잘치는분들 위주로 와주세요. in50위 문의주세요! (목표보상:에디큐브 70개 확정보상:에디큐브 60개)</t>
@@ -185,439 +188,442 @@
     <t>Scania 50</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>650경 1938조 438억 2009만</t>
+  </si>
+  <si>
+    <t>노을승용</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>빔냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>228경 131조 6916억 361만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>58경 4001조 2779억 5325만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>53경 625조 5653억 3480만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>48경 1083조 794억 4056만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>40경 4809조 4569억 7661만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>23경 5452조 8627억 4888만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>22경 2897조 9622억 4868만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>22경 2364조 9461억 5527만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>12경 2879조 2905억 3861만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>9경 3208조 1900억 1331만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>8경 6293조 6296억 417만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>8경 5425조 4820억 9586만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>7경 8521조 7245억 5404만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>밉상b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
+  </si>
+  <si>
+    <t>7경 145조 793억 7358만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>6경 7507조 6793억 8682만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>6경 5572조 9054억 2021만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4885조 3111억 7395만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>5경 6355조 5541억 4319만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>4경 6208조 3978억 9628만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1경 5432조 1524억 327만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 5275조 752억 3008만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>1경 5042조 8838억 8041만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1경 2844조 9014억 2537만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>익맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 84조 5679억 4324만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>8944조 2540억 2789만</t>
+  </si>
+  <si>
     <t>28</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>650경 1747조 5815억 6999만</t>
-  </si>
-  <si>
-    <t>노을승용</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>228경 131조 6916억 361만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>56경 2380조 2927억 6127만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>51경 8875조 2162억 6967만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>48경 1083조 794억 4056만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>39경 4863조 5172억 8731만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>23경 5452조 8627억 4888만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>22경 2656조 5088억 3487만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>22경 2273조 5626억 5080만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>12경 2879조 2905억 3861만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>9경 2858조 7659억 4585만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8경 6293조 6296억 417만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>8경 5425조 4820억 9586만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>7경 7634조 1071억 4397만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>밉상b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
-  </si>
-  <si>
-    <t>7경 145조 793억 7358만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6경 5453조 148억 5508만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4885조 3111억 7395만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>6경 3278조 9460억 3057만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>5경 2700조 2571억 9886만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>4경 5847조 8701억 7698만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>4경 332조 8806억 8276만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 5275조 752억 3008만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 5210조 2553억 4869만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 5042조 8838억 8041만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 2844조 9014억 2537만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>익맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 58조 8286억 5389만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8944조 2540억 2789만</t>
-  </si>
-  <si>
     <t>루넨</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>8487조 8465억 6014만</t>
+    <t>8488조 7335억 2631만</t>
   </si>
   <si>
     <t>29</t>
@@ -629,10 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>8199조 9891억 1409만</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>8263조 3641억 1604만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -650,7 +653,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>90경 5190조 7370억 5330만</t>
+    <t>90경 5421조 6879억 5283만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -665,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>55경 9558조 3770억 2696만</t>
+    <t>56경 517조 3389억 4810만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -674,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>55경 4800조 1974억 7977만</t>
+    <t>55경 6705조 8607억 1783만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -701,7 +704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>25경 397조 7568억 2985만</t>
+    <t>25경 572조 2289억 9768만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -710,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>12경 1733조 2782억 9500만</t>
+    <t>12경 1860조 2754억 6623만</t>
   </si>
   <si>
     <t>악경</t>
@@ -719,7 +722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
   </si>
   <si>
-    <t>6경 8262조 1885억 6055만</t>
+    <t>7경 1546조 5179억 2533만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -758,7 +761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>3경 3608조 8530억 4041만</t>
+    <t>3경 3707조 8260억 2668만</t>
   </si>
   <si>
     <t>힐캐</t>
@@ -767,7 +770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
   </si>
   <si>
-    <t>3경 2650조 1466억 4218만</t>
+    <t>3경 2761조 7842억 3815만</t>
   </si>
   <si>
     <t>안리뿐</t>
@@ -785,7 +788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>2경 449조 7106억 4547만</t>
+    <t>2경 953조 9359억 4013만</t>
   </si>
   <si>
     <t>막내비숍</t>
@@ -803,7 +806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>1경 2528조 2290억 5124만</t>
+    <t>1경 2611조 9185억 6690만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -812,7 +815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>8591조 8265억 4479만</t>
+    <t>9391조 9163억 8294만</t>
   </si>
   <si>
     <t>charon</t>
@@ -821,7 +824,7 @@
     <t>https://mgf.gg/contents/character.php?n=charon</t>
   </si>
   <si>
-    <t>8571조 8955억 1516만</t>
+    <t>8589조 5193억 4087만</t>
   </si>
   <si>
     <t>뜨람프</t>
@@ -860,7 +863,16 @@
     <t>113</t>
   </si>
   <si>
-    <t>4217조 8381억 499만</t>
+    <t>4242조 1912억 767만</t>
+  </si>
+  <si>
+    <t>악갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>3740조 5336억 1426만</t>
   </si>
   <si>
     <t>힐나눔</t>
@@ -869,16 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%82%98%EB%88%94</t>
   </si>
   <si>
-    <t>3555조 5855억 6311만</t>
-  </si>
-  <si>
-    <t>악갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>3411조 9324억 7037만</t>
+    <t>3738조 6158억 3056만</t>
   </si>
   <si>
     <t>이웡삥</t>
@@ -929,7 +932,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1673억 4366만</t>
+    <t>1778억 3580만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
@@ -947,7 +950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>97경 3705조 3097억 4238만</t>
+    <t>103경 9343조 852억 7080만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -956,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>33경 9418조 1231억 3087만</t>
+    <t>33경 9441조 8855억 7628만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -977,7 +980,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>30경 2501조 8318억 3006만</t>
+    <t>30경 4356조 9490억 5074만</t>
+  </si>
+  <si>
+    <t>메키존망섭종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
+  </si>
+  <si>
+    <t>23경 8429조 9195억 4856만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -989,15 +1001,6 @@
     <t>23경 7221조 2621억 7072만</t>
   </si>
   <si>
-    <t>메키존망섭종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
-  </si>
-  <si>
-    <t>23경 2646조 2077억 8081만</t>
-  </si>
-  <si>
     <t>도당이</t>
   </si>
   <si>
@@ -1013,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>5경 2419조 3577억 1787만</t>
+    <t>5경 2435조 7227억 2031만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1031,7 +1034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
   </si>
   <si>
-    <t>4경 1093조 6725억 3734만</t>
+    <t>4경 4347조 9483억 3614만</t>
   </si>
   <si>
     <t>다이사</t>
@@ -1040,7 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>3경 8050조 7302억 97만</t>
+    <t>3경 8590조 8062억 5177만</t>
   </si>
   <si>
     <t>카지야</t>
@@ -1049,7 +1052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%A7%80%EC%95%BC</t>
   </si>
   <si>
-    <t>3경 2679조 1236억 7239만</t>
+    <t>3경 5553조 7678억 6483만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1067,7 +1070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A6%90%EC%B2%98%EB%93%9C%EC%85%88</t>
   </si>
   <si>
-    <t>1경 7110조 1659억 7060만</t>
+    <t>1경 7667조 3210억 5616만</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -1076,7 +1079,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>1경 952조 6045억 9114만</t>
+    <t>1경 1145조 7008억 3610만</t>
   </si>
   <si>
     <t>고래털</t>
@@ -1085,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%9E%98%ED%84%B8</t>
   </si>
   <si>
-    <t>1경 458조 3521억 5565만</t>
+    <t>1경 780조 3521억 3691만</t>
   </si>
   <si>
     <t>피타입</t>
@@ -1094,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%ED%83%80%EC%9E%85</t>
   </si>
   <si>
-    <t>1경 11조 7289억 9539만</t>
+    <t>1경 275조 7891억 929만</t>
   </si>
   <si>
     <t>YooU</t>
@@ -1157,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
   </si>
   <si>
-    <t>4257조 787억 6210만</t>
+    <t>4809조 5362억 1988만</t>
   </si>
   <si>
     <t>강띵띵</t>
@@ -1166,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>4242조 2161억 529만</t>
+    <t>4368조 6077억 1180만</t>
   </si>
   <si>
     <t>악전</t>
@@ -1187,228 +1190,228 @@
     <t>3976조 1105억 1204만</t>
   </si>
   <si>
+    <t>박미쯔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
+  </si>
+  <si>
+    <t>3322조 6600억 2558만</t>
+  </si>
+  <si>
     <t>앙음</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
   </si>
   <si>
+    <t>3194조 3135억 4268만</t>
+  </si>
+  <si>
+    <t>과금X환불O</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
+  </si>
+  <si>
+    <t>193경 9022조 2239억 7452만</t>
+  </si>
+  <si>
+    <t>환불존망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>44경 2774조 6465억 5898만</t>
+  </si>
+  <si>
+    <t>역삼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>36경 2853조 9795억 1472만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
+  </si>
+  <si>
+    <t>22경 3529조 9579억 2234만</t>
+  </si>
+  <si>
+    <t>아그리아스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17경 5872조 9942억 4977만</t>
+  </si>
+  <si>
+    <t>쏘쏘하네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
+  </si>
+  <si>
+    <t>8경 9178조 32억 4075만</t>
+  </si>
+  <si>
+    <t>꼬꼬대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>5경 8660조 4059억 7632만</t>
+  </si>
+  <si>
+    <t>참OI슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>4경 5229조 6295억 9430만</t>
+  </si>
+  <si>
+    <t>록현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
+  </si>
+  <si>
+    <t>3경 9690조 147억 8495만</t>
+  </si>
+  <si>
+    <t>유지애123</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
+  </si>
+  <si>
+    <t>3경 2758조 9056억 9499만</t>
+  </si>
+  <si>
+    <t>머스탱GT</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
+  </si>
+  <si>
+    <t>2경 1730조 5409억 9421만</t>
+  </si>
+  <si>
+    <t>아이츄크림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%B8%84%ED%81%AC%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>1경 8531조 3059억 7038만</t>
+  </si>
+  <si>
+    <t>강남무자본</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%82%A8%EB%AC%B4%EC%9E%90%EB%B3%B8</t>
+  </si>
+  <si>
+    <t>1경 6584조 1550억 1095만</t>
+  </si>
+  <si>
+    <t>응구7</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
+  </si>
+  <si>
+    <t>1경 4308조 8464억 4826만</t>
+  </si>
+  <si>
+    <t>할게없다고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>1경 4249조 5640억 4379만</t>
+  </si>
+  <si>
+    <t>웅선김</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
+  </si>
+  <si>
+    <t>1경 2720조 2817억 7518만</t>
+  </si>
+  <si>
+    <t>가루o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
+  </si>
+  <si>
+    <t>1경 1396조 7462억 2001만</t>
+  </si>
+  <si>
+    <t>정듄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
+  </si>
+  <si>
+    <t>1경 868조 1535억 9578만</t>
+  </si>
+  <si>
+    <t>반서님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9C%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1경 336조 9852억 3626만</t>
+  </si>
+  <si>
+    <t>정슌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
+  </si>
+  <si>
+    <t>8973조 131억 4136만</t>
+  </si>
+  <si>
+    <t>귀염둥이제제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>8301조 4843억 6289만</t>
+  </si>
+  <si>
+    <t>우유냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
+  </si>
+  <si>
+    <t>7808조 2533억 6118만</t>
+  </si>
+  <si>
+    <t>한도100</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84100</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>3168조 7115억 1645만</t>
-  </si>
-  <si>
-    <t>박미쯔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
-  </si>
-  <si>
-    <t>3117조 399억 4567만</t>
-  </si>
-  <si>
-    <t>과금X환불O</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
-  </si>
-  <si>
-    <t>193경 5252조 6509억 952만</t>
-  </si>
-  <si>
-    <t>환불존망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>44경 2774조 6465억 5898만</t>
-  </si>
-  <si>
-    <t>역삼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>36경 2714조 6453억 6979만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
-  </si>
-  <si>
-    <t>22경 3235조 6802억 4253만</t>
-  </si>
-  <si>
-    <t>아그리아스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17경 5872조 9942억 4977만</t>
-  </si>
-  <si>
-    <t>쏘쏘하네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
-  </si>
-  <si>
-    <t>8경 4549조 6726억 1610만</t>
-  </si>
-  <si>
-    <t>꼬꼬대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>5경 8638조 6253억 9220만</t>
-  </si>
-  <si>
-    <t>참OI슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>4경 5229조 6295억 9430만</t>
-  </si>
-  <si>
-    <t>록현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
-  </si>
-  <si>
-    <t>3경 9690조 147억 8495만</t>
-  </si>
-  <si>
-    <t>유지애123</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
-  </si>
-  <si>
-    <t>3경 2711조 7892억 4930만</t>
-  </si>
-  <si>
-    <t>머스탱GT</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
-  </si>
-  <si>
-    <t>1경 8276조 402억 1248만</t>
-  </si>
-  <si>
-    <t>아이츄크림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%B8%84%ED%81%AC%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1경 7408조 1965억 1763만</t>
-  </si>
-  <si>
-    <t>강남무자본</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%82%A8%EB%AC%B4%EC%9E%90%EB%B3%B8</t>
-  </si>
-  <si>
-    <t>1경 6541조 791억 4855만</t>
-  </si>
-  <si>
-    <t>할게없다고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>1경 4249조 5640억 4379만</t>
-  </si>
-  <si>
-    <t>응구7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
-  </si>
-  <si>
-    <t>1경 4210조 8258억 6319만</t>
-  </si>
-  <si>
-    <t>웅선김</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
-  </si>
-  <si>
-    <t>1경 2720조 2817억 7518만</t>
-  </si>
-  <si>
-    <t>가루o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
-  </si>
-  <si>
-    <t>1경 1396조 7462억 2001만</t>
-  </si>
-  <si>
-    <t>반서님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9C%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1경 336조 9852억 3626만</t>
-  </si>
-  <si>
-    <t>정듄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
-  </si>
-  <si>
-    <t>9353조 2286억 2438만</t>
-  </si>
-  <si>
-    <t>정슌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
-  </si>
-  <si>
-    <t>8691조 7994억 9115만</t>
-  </si>
-  <si>
-    <t>귀염둥이제제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>8301조 4843억 6289만</t>
-  </si>
-  <si>
-    <t>우유냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
-  </si>
-  <si>
-    <t>7803조 7185억 7949만</t>
-  </si>
-  <si>
-    <t>한도100</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84100</t>
-  </si>
-  <si>
     <t>7688조 2639억 2056만</t>
   </si>
   <si>
@@ -1418,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=zi%EC%A1%B4%EB%8F%99%EA%B8%B8</t>
   </si>
   <si>
-    <t>6134조 9704억 5125만</t>
+    <t>6358조 6572억 9133만</t>
   </si>
   <si>
     <t>꼼맹</t>
@@ -1427,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EB%A7%B9</t>
   </si>
   <si>
-    <t>5098조 3359억 7539만</t>
+    <t>5106조 5481억 4307만</t>
   </si>
   <si>
     <t>천닼나</t>
@@ -1445,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%81%90%EB%A5%98%EB%B0%94</t>
   </si>
   <si>
-    <t>2623조 6164억 396만</t>
+    <t>2625조 8261억 3038만</t>
   </si>
   <si>
     <t>백정Hero</t>
@@ -1499,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
   </si>
   <si>
-    <t>9126조 2127억 2812만</t>
+    <t>9327조 4672억 3457만</t>
   </si>
   <si>
     <t>아테나1</t>
@@ -1517,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>3606조 898억 9873만</t>
+    <t>3634조 6848억 3808만</t>
   </si>
   <si>
     <t>카엘다</t>
@@ -1526,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2692조 7109억 995만</t>
+    <t>2716조 4605억 1575만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
@@ -1541,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
   </si>
   <si>
-    <t>1626조 7280억 3537만</t>
+    <t>1653조 9452억 9209만</t>
   </si>
   <si>
     <t>노을새벽</t>
@@ -1580,7 +1583,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8B%9C%EC%95%84</t>
   </si>
   <si>
-    <t>920조 5247억 359만</t>
+    <t>1021조 9980억 6228만</t>
   </si>
   <si>
     <t>속초피바다</t>
@@ -1604,6 +1607,18 @@
     <t>630조 2955억 4217만</t>
   </si>
   <si>
+    <t>노을쁨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>471조 4362억 527만</t>
+  </si>
+  <si>
     <t>노을고래</t>
   </si>
   <si>
@@ -1619,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
   </si>
   <si>
-    <t>452조 6734억 3864만</t>
+    <t>452조 7772억 6635만</t>
   </si>
   <si>
     <t>노을비츠</t>
@@ -1628,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
   </si>
   <si>
-    <t>440조 7936억 6617만</t>
+    <t>441조 2474억 9819만</t>
   </si>
   <si>
     <t>노을밍</t>
@@ -1637,19 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
   </si>
   <si>
-    <t>433조 2685억 592만</t>
-  </si>
-  <si>
-    <t>노을쁨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>426조 9584억 736만</t>
+    <t>434조 8316억 6701만</t>
   </si>
   <si>
     <t>노을하온</t>
@@ -1658,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
   </si>
   <si>
-    <t>410조 3843억 8438만</t>
+    <t>413조 4231억 9095만</t>
   </si>
   <si>
     <t>햄숍</t>
@@ -1667,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
   </si>
   <si>
-    <t>371조 5380억 5780만</t>
+    <t>376조 1403억 3038만</t>
   </si>
   <si>
     <t>노을둥이</t>
@@ -1676,7 +1679,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%91%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>341조 328억 6808만</t>
+    <t>348조 9144억 1349만</t>
+  </si>
+  <si>
+    <t>노을막내</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
+  </si>
+  <si>
+    <t>313조 1687억 9027만</t>
   </si>
   <si>
     <t>사자탈</t>
@@ -1688,15 +1700,6 @@
     <t>310조 5275억 5074만</t>
   </si>
   <si>
-    <t>노을막내</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
-  </si>
-  <si>
-    <t>290조 7575억 5660만</t>
-  </si>
-  <si>
     <t>노을달빛</t>
   </si>
   <si>
@@ -1712,7 +1715,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
   </si>
   <si>
-    <t>266조 1441억 4509만</t>
+    <t>270조 9602억 4392만</t>
   </si>
   <si>
     <t>노을도아</t>
@@ -1721,7 +1724,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8F%84%EC%95%84</t>
   </si>
   <si>
-    <t>212조 313억 1885만</t>
+    <t>218조 2100억 9220만</t>
   </si>
   <si>
     <t>노을쿠키</t>
@@ -1739,7 +1742,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B2%B0%EB%B9%9B</t>
   </si>
   <si>
-    <t>149조 608억 3933만</t>
+    <t>149조 6902억 4298만</t>
   </si>
 </sst>
 </file>
@@ -2238,27 +2241,27 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -2270,36 +2273,36 @@
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>18</v>
@@ -2308,58 +2311,58 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2395,28 +2398,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2427,28 +2430,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2459,28 +2462,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2491,28 +2494,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2523,28 +2526,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2555,28 +2558,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2587,28 +2590,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2619,28 +2622,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2651,28 +2654,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2683,28 +2686,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2715,28 +2718,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2747,28 +2750,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2779,28 +2782,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2811,28 +2814,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2843,25 +2846,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>137</v>
@@ -2887,13 +2890,13 @@
         <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>141</v>
@@ -2919,16 +2922,16 @@
         <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2939,25 +2942,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>150</v>
@@ -2983,13 +2986,13 @@
         <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>154</v>
@@ -3015,10 +3018,10 @@
         <v>157</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>158</v>
@@ -3047,13 +3050,13 @@
         <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>163</v>
@@ -3079,13 +3082,13 @@
         <v>166</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>167</v>
@@ -3111,10 +3114,10 @@
         <v>170</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>158</v>
@@ -3143,10 +3146,10 @@
         <v>174</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>158</v>
@@ -3175,16 +3178,16 @@
         <v>178</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3195,28 +3198,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3227,28 +3230,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3259,7 +3262,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
@@ -3268,19 +3271,19 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3291,28 +3294,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3323,28 +3326,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3355,28 +3358,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3440,28 +3443,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3472,31 +3475,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3504,31 +3507,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3536,7 +3539,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>33</v>
@@ -3545,22 +3548,22 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3568,31 +3571,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3600,31 +3603,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3632,31 +3635,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3664,31 +3667,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3696,31 +3699,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3728,31 +3731,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3760,31 +3763,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3792,31 +3795,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3824,31 +3827,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3856,31 +3859,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3888,31 +3891,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3923,28 +3926,28 @@
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3955,28 +3958,28 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3984,31 +3987,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4019,28 +4022,28 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4051,28 +4054,28 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4083,28 +4086,28 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4115,28 +4118,28 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4147,28 +4150,28 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4179,28 +4182,28 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4211,28 +4214,28 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4240,31 +4243,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4272,31 +4275,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4304,31 +4307,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4336,31 +4339,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4368,31 +4371,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4400,31 +4403,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4485,28 +4488,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4514,938 +4517,938 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>388</v>
+        <v>277</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>390</v>
@@ -5457,19 +5460,19 @@
         <v>391</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5521,7 +5524,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5530,28 +5533,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5559,10 +5562,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>393</v>
@@ -5574,27 +5577,27 @@
         <v>394</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>395</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>396</v>
@@ -5606,27 +5609,27 @@
         <v>397</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>398</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>399</v>
@@ -5638,59 +5641,59 @@
         <v>400</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>402</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>403</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>404</v>
@@ -5702,27 +5705,27 @@
         <v>405</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>406</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>407</v>
@@ -5734,27 +5737,27 @@
         <v>408</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>409</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>410</v>
@@ -5766,27 +5769,27 @@
         <v>411</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>412</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>413</v>
@@ -5798,27 +5801,27 @@
         <v>414</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>415</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>416</v>
@@ -5830,27 +5833,27 @@
         <v>417</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>418</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>419</v>
@@ -5862,27 +5865,27 @@
         <v>420</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>421</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>422</v>
@@ -5894,27 +5897,27 @@
         <v>423</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>424</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>425</v>
@@ -5926,10 +5929,10 @@
         <v>426</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>158</v>
@@ -5938,15 +5941,15 @@
         <v>427</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>428</v>
@@ -5958,27 +5961,27 @@
         <v>429</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>430</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>431</v>
@@ -5990,24 +5993,24 @@
         <v>432</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>433</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
@@ -6022,24 +6025,24 @@
         <v>435</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>436</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
@@ -6054,27 +6057,27 @@
         <v>438</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>439</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>440</v>
@@ -6086,24 +6089,24 @@
         <v>441</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>442</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
@@ -6118,24 +6121,24 @@
         <v>444</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>445</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>155</v>
@@ -6150,24 +6153,24 @@
         <v>447</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>448</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
@@ -6182,24 +6185,24 @@
         <v>450</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>451</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
@@ -6214,24 +6217,24 @@
         <v>453</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>454</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
@@ -6246,10 +6249,10 @@
         <v>456</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>158</v>
@@ -6258,12 +6261,12 @@
         <v>457</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
@@ -6278,211 +6281,211 @@
         <v>459</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -6542,28 +6545,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6571,962 +6574,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>286</v>
+        <v>528</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>520</v>
+        <v>287</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>312</v>
+        <v>126</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>286</v>
+        <v>521</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>539</v>
+        <v>287</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>312</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>520</v>
+        <v>291</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>313</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>290</v>
+        <v>521</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>290</v>
+        <v>528</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -260,7 +260,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>58경 4001조 2779억 5325만</t>
+    <t>64경 4217조 575억 9009만</t>
   </si>
   <si>
     <t>3</t>
@@ -272,7 +272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>53경 625조 5653억 3480만</t>
+    <t>55경 4363조 3706억 9167만</t>
   </si>
   <si>
     <t>4</t>
@@ -284,376 +284,394 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>55경 2525조 6218억 1334만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>41경 7711조 7799억 3444만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>23경 6378조 9억 8238만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>23경 6194조 6186억 7365만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>23경 5452조 8627억 4888만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>12경 4509조 2134억 7835만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>10경 280조 6073억 2728만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>9경 7717조 5279억 6925만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>8경 6777조 8160억 7603만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>8경 32조 5919억 4407만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>밉상b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
+  </si>
+  <si>
+    <t>7경 6310조 4728억 1122만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 2264조 8746억 6831만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>6경 7680조 2331억 1997만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4885조 3111억 7395만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>5경 8342조 1557억 9929만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>4경 7757조 7936억 9566만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1경 7102조 8495억 2595만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>1경 5351조 1664억 8613만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 5275조 752억 3008만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1경 3944조 7727억 1715만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>익맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 2718조 2674억 5593만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 14조 9938억 1255만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>9468조 2895억 2411만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>8944조 2540억 2789만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>6665조 3780억 1797만</t>
+  </si>
+  <si>
+    <t>메키에바란다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>48경 1083조 794억 4056만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>40경 4809조 4569억 7661만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>23경 5452조 8627억 4888만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>22경 2897조 9622억 4868만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>22경 2364조 9461억 5527만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>12경 2879조 2905억 3861만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>9경 3208조 1900억 1331만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8경 6293조 6296억 417만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>8경 5425조 4820억 9586만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>7경 8521조 7245억 5404만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>밉상b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
-  </si>
-  <si>
-    <t>7경 145조 793억 7358만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>6경 7507조 6793억 8682만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6경 5572조 9054억 2021만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4885조 3111억 7395만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>5경 6355조 5541억 4319만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>5경 5228조 9003억 4099만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>4경 6208조 3978억 9628만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 5432조 1524억 327만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 5275조 752억 3008만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>1경 5042조 8838억 8041만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 2844조 9014억 2537만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>익맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 84조 5679억 4324만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8944조 2540억 2789만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>8488조 7335억 2631만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>8263조 3641억 1604만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>6665조 3780억 1797만</t>
-  </si>
-  <si>
-    <t>메키에바란다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>90경 5421조 6879억 5283만</t>
+    <t>91경 9465조 9827억 649만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
+  </si>
+  <si>
+    <t>60경 7045조 652억 325만</t>
+  </si>
+  <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Matter</t>
+  </si>
+  <si>
+    <t>60경 339조 6350억 2632만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -665,28 +683,13 @@
     <t>56경 8609조 8131억 5928만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
-  </si>
-  <si>
-    <t>56경 517조 3389억 4810만</t>
-  </si>
-  <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter</t>
-  </si>
-  <si>
-    <t>55경 6705조 8607억 1783만</t>
-  </si>
-  <si>
     <t>혁수킹</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>48경 1871조 6464억 4236만</t>
+    <t>54경 5852조 8098억 1207만</t>
   </si>
   <si>
     <t>셀문</t>
@@ -704,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>25경 572조 2289억 9768만</t>
+    <t>27경 2261조 2339억 2665만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -713,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>12경 1860조 2754억 6623만</t>
+    <t>12경 4643조 339억 9230만</t>
   </si>
   <si>
     <t>악경</t>
@@ -731,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>4경 7273조 8638억 6431만</t>
+    <t>4경 7799조 1263억 2384만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -746,31 +749,31 @@
     <t>3경 9345조 1748억 2777만</t>
   </si>
   <si>
-    <t>람보르7l니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%B4%EB%A5%B47l%EB%8B%88</t>
+    <t>히째히째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>3경 5889조 1978억 4877만</t>
+  </si>
+  <si>
+    <t>떠영아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%98%81%EC%95%84</t>
   </si>
   <si>
     <t>3경 4432조 1072억 1410만</t>
   </si>
   <si>
-    <t>히째히째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>3경 3707조 8260억 2668만</t>
-  </si>
-  <si>
     <t>힐캐</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
   </si>
   <si>
-    <t>3경 2761조 7842억 3815만</t>
+    <t>3경 4425조 2247억 5892만</t>
   </si>
   <si>
     <t>안리뿐</t>
@@ -806,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>1경 2611조 9185억 6690만</t>
+    <t>1경 3084조 3477억 1406만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -815,7 +818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>9391조 9163억 8294만</t>
+    <t>9840조 9184억 4426만</t>
   </si>
   <si>
     <t>charon</t>
@@ -824,7 +827,7 @@
     <t>https://mgf.gg/contents/character.php?n=charon</t>
   </si>
   <si>
-    <t>8589조 5193억 4087만</t>
+    <t>9662조 1109억 3741만</t>
   </si>
   <si>
     <t>뜨람프</t>
@@ -842,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%93%B0</t>
   </si>
   <si>
-    <t>5617조 8345억 2588만</t>
+    <t>5626조 742억 4534만</t>
   </si>
   <si>
     <t>미나별</t>
@@ -863,7 +866,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4242조 1912억 767만</t>
+    <t>5054조 6465억 1446만</t>
   </si>
   <si>
     <t>악갱</t>
@@ -872,7 +875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B0%B1</t>
   </si>
   <si>
-    <t>3740조 5336억 1426만</t>
+    <t>4367조 7714억 7311만</t>
   </si>
   <si>
     <t>힐나눔</t>
@@ -881,7 +884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%82%98%EB%88%94</t>
   </si>
   <si>
-    <t>3738조 6158억 3056만</t>
+    <t>3931조 6828억 1958만</t>
   </si>
   <si>
     <t>이웡삥</t>
@@ -893,7 +896,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>618조 6280억 4983만</t>
+    <t>1034조 8303억 5680만</t>
   </si>
   <si>
     <t>Matter2</t>
@@ -905,7 +908,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>184조 6512억 8047만</t>
+    <t>199조 5130억 5508만</t>
   </si>
   <si>
     <t>캐랑</t>
@@ -917,7 +920,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>31조 9690억 1779만</t>
+    <t>39조 2016억 1989만</t>
   </si>
   <si>
     <t>Matter3</t>
@@ -932,15 +935,12 @@
     <t>93</t>
   </si>
   <si>
-    <t>1778억 3580만</t>
+    <t>2392억 2701만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
     <t>202경 5365조 6847억 4286만</t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>103경 9343조 852억 7080만</t>
+    <t>109경 7862조 268억 2299만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -959,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>33경 9441조 8855억 7628만</t>
+    <t>35경 2940조 7310억 6211만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -971,7 +971,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>33경 7501조 2434억 9263만</t>
+    <t>35경 38조 6170억 4346만</t>
   </si>
   <si>
     <t>송곧</t>
@@ -980,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>30경 4356조 9490억 5074만</t>
+    <t>34경 1278조 5441억 3102만</t>
   </si>
   <si>
     <t>메키존망섭종</t>
@@ -989,7 +989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
   </si>
   <si>
-    <t>23경 8429조 9195억 4856만</t>
+    <t>24경 7526조 3190억 3581만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1016,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>5경 2435조 7227억 2031만</t>
+    <t>5경 3329조 3983억 9783만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1043,7 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>3경 8590조 8062억 5177만</t>
+    <t>4경 84조 1716억 8223만</t>
   </si>
   <si>
     <t>카지야</t>
@@ -1052,7 +1052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%A7%80%EC%95%BC</t>
   </si>
   <si>
-    <t>3경 5553조 7678억 6483만</t>
+    <t>3경 5611조 4308억 9296만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1061,7 +1061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 6176조 6422억 5370만</t>
+    <t>2경 8269조 1138억 6803만</t>
   </si>
   <si>
     <t>즐처드셈</t>
@@ -1070,7 +1070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A6%90%EC%B2%98%EB%93%9C%EC%85%88</t>
   </si>
   <si>
-    <t>1경 7667조 3210억 5616만</t>
+    <t>1경 8863조 9763억 9143만</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -1079,7 +1079,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>1경 1145조 7008억 3610만</t>
+    <t>1경 1937조 5718억 9003만</t>
   </si>
   <si>
     <t>고래털</t>
@@ -1088,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%9E%98%ED%84%B8</t>
   </si>
   <si>
-    <t>1경 780조 3521억 3691만</t>
+    <t>1경 1043조 468억 1279만</t>
   </si>
   <si>
     <t>피타입</t>
@@ -1097,7 +1097,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%ED%83%80%EC%9E%85</t>
   </si>
   <si>
-    <t>1경 275조 7891억 929만</t>
+    <t>1경 848조 3851억 4771만</t>
+  </si>
+  <si>
+    <t>원순철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>8090조 8880억 7485만</t>
   </si>
   <si>
     <t>YooU</t>
@@ -1109,15 +1118,6 @@
     <t>7873조 6623억 710만</t>
   </si>
   <si>
-    <t>원순철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>7703조 5571억 1292만</t>
-  </si>
-  <si>
     <t>대전월클</t>
   </si>
   <si>
@@ -1151,7 +1151,7 @@
     <t>https://mgf.gg/contents/character.php?n=RaguS</t>
   </si>
   <si>
-    <t>6022조 2472억 5192만</t>
+    <t>6382조 8879억 904만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1160,7 +1160,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
   </si>
   <si>
-    <t>4809조 5362억 1988만</t>
+    <t>5272조 3660억 832만</t>
+  </si>
+  <si>
+    <t>악전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
+  </si>
+  <si>
+    <t>4915조 2750억 5026만</t>
   </si>
   <si>
     <t>강띵띵</t>
@@ -1169,16 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>4368조 6077억 1180만</t>
-  </si>
-  <si>
-    <t>악전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
-  </si>
-  <si>
-    <t>4031조 1359억 714만</t>
+    <t>4379조 1845억 2994만</t>
   </si>
   <si>
     <t>끽코</t>
@@ -1187,7 +1187,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
   </si>
   <si>
-    <t>3976조 1105억 1204만</t>
+    <t>4200조 4114억 4325만</t>
+  </si>
+  <si>
+    <t>앙음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>3733조 1323억 2129만</t>
   </si>
   <si>
     <t>박미쯔</t>
@@ -1196,16 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
   </si>
   <si>
-    <t>3322조 6600억 2558만</t>
-  </si>
-  <si>
-    <t>앙음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>3194조 3135억 4268만</t>
+    <t>3378조 7663억 3397만</t>
   </si>
   <si>
     <t>과금X환불O</t>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
   </si>
   <si>
-    <t>193경 9022조 2239억 7452만</t>
+    <t>196경 2520조 1483억 6179만</t>
   </si>
   <si>
     <t>환불존망겜</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
   </si>
   <si>
-    <t>44경 2774조 6465억 5898만</t>
+    <t>44경 3845조 4866억 4750만</t>
   </si>
   <si>
     <t>역삼이</t>
@@ -1232,13 +1232,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>36경 2853조 9795억 1472만</t>
+    <t>38경 4102조 9598억 1650만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
   </si>
   <si>
-    <t>22경 3529조 9579억 2234만</t>
+    <t>24경 5419조 6267억 6546만</t>
   </si>
   <si>
     <t>아그리아스</t>
@@ -1247,7 +1247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>17경 5872조 9942억 4977만</t>
+    <t>17경 6716조 9928억 4335만</t>
   </si>
   <si>
     <t>쏘쏘하네</t>
@@ -1256,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
   </si>
   <si>
-    <t>8경 9178조 32억 4075만</t>
+    <t>9경 3237조 9342억 7629만</t>
   </si>
   <si>
     <t>꼬꼬대장</t>
@@ -1265,7 +1265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>5경 8660조 4059억 7632만</t>
+    <t>5경 9746조 9191억 7314만</t>
   </si>
   <si>
     <t>참OI슬</t>
@@ -1274,7 +1274,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
   </si>
   <si>
-    <t>4경 5229조 6295억 9430만</t>
+    <t>4경 9642조 1684억 2049만</t>
   </si>
   <si>
     <t>록현</t>
@@ -1283,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
   </si>
   <si>
-    <t>3경 9690조 147억 8495만</t>
+    <t>4경 2580조 7001억 6305만</t>
   </si>
   <si>
     <t>유지애123</t>
@@ -1292,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
   </si>
   <si>
-    <t>3경 2758조 9056억 9499만</t>
+    <t>3경 5245조 3472억 6074만</t>
   </si>
   <si>
     <t>머스탱GT</t>
@@ -1301,7 +1301,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
   </si>
   <si>
-    <t>2경 1730조 5409억 9421만</t>
+    <t>2경 2744조 4691억 3860만</t>
   </si>
   <si>
     <t>아이츄크림</t>
@@ -1319,7 +1319,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%82%A8%EB%AC%B4%EC%9E%90%EB%B3%B8</t>
   </si>
   <si>
-    <t>1경 6584조 1550억 1095만</t>
+    <t>1경 8259조 7876억 9729만</t>
   </si>
   <si>
     <t>응구7</t>
@@ -1328,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
   </si>
   <si>
-    <t>1경 4308조 8464억 4826만</t>
+    <t>1경 5511조 9850억 3950만</t>
   </si>
   <si>
     <t>할게없다고</t>
@@ -1337,7 +1337,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
   </si>
   <si>
-    <t>1경 4249조 5640억 4379만</t>
+    <t>1경 4584조 4424억 2782만</t>
   </si>
   <si>
     <t>웅선김</t>
@@ -1346,7 +1346,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
   </si>
   <si>
-    <t>1경 2720조 2817억 7518만</t>
+    <t>1경 3758조 2869억 1064만</t>
   </si>
   <si>
     <t>가루o</t>
@@ -1355,7 +1355,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
   </si>
   <si>
-    <t>1경 1396조 7462억 2001만</t>
+    <t>1경 3527조 1863억 5039만</t>
   </si>
   <si>
     <t>정듄</t>
@@ -1364,7 +1364,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
   </si>
   <si>
-    <t>1경 868조 1535억 9578만</t>
+    <t>1경 1421조 3190억 3529만</t>
   </si>
   <si>
     <t>반서님</t>
@@ -1376,13 +1376,22 @@
     <t>1경 336조 9852억 3626만</t>
   </si>
   <si>
+    <t>우유냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
+  </si>
+  <si>
+    <t>9796조 7681억 6815만</t>
+  </si>
+  <si>
     <t>정슌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
   </si>
   <si>
-    <t>8973조 131억 4136만</t>
+    <t>9344조 8246억 7760만</t>
   </si>
   <si>
     <t>귀염둥이제제</t>
@@ -1391,16 +1400,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
   </si>
   <si>
-    <t>8301조 4843억 6289만</t>
-  </si>
-  <si>
-    <t>우유냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
-  </si>
-  <si>
-    <t>7808조 2533억 6118만</t>
+    <t>8571조 6272억 9815만</t>
   </si>
   <si>
     <t>한도100</t>
@@ -1412,7 +1412,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>7688조 2639억 2056만</t>
+    <t>7853조 9914억 6717만</t>
   </si>
   <si>
     <t>zi존동길</t>
@@ -1421,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=zi%EC%A1%B4%EB%8F%99%EA%B8%B8</t>
   </si>
   <si>
-    <t>6358조 6572억 9133만</t>
+    <t>7056조 79억 8576만</t>
   </si>
   <si>
     <t>꼼맹</t>
@@ -1430,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EB%A7%B9</t>
   </si>
   <si>
-    <t>5106조 5481억 4307만</t>
+    <t>5123조 5283억 4134만</t>
   </si>
   <si>
     <t>천닼나</t>
@@ -1448,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%81%90%EB%A5%98%EB%B0%94</t>
   </si>
   <si>
-    <t>2625조 8261억 3038만</t>
+    <t>2690조 527억 7245만</t>
   </si>
   <si>
     <t>백정Hero</t>
@@ -1466,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%83%A5%EC%9E%89</t>
   </si>
   <si>
-    <t>1601조 108억 4997만</t>
+    <t>1692조 9992억 7032만</t>
   </si>
   <si>
     <t>노을준이</t>
@@ -1475,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>621경 4457조 5244억 3102만</t>
+    <t>637경 8249조 3544억 9865만</t>
   </si>
   <si>
     <t>노을뽀롱</t>
@@ -1487,6 +1487,15 @@
     <t>24경 2357조 755억 8065만</t>
   </si>
   <si>
+    <t>노을주의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
+  </si>
+  <si>
+    <t>1경 750조 7307억 8404만</t>
+  </si>
+  <si>
     <t>노을구름</t>
   </si>
   <si>
@@ -1496,22 +1505,13 @@
     <t>1경 160조 531억 125만</t>
   </si>
   <si>
-    <t>노을주의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
-  </si>
-  <si>
-    <t>9327조 4672억 3457만</t>
-  </si>
-  <si>
     <t>아테나1</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%85%8C%EB%82%981</t>
   </si>
   <si>
-    <t>4027조 7769억 7747만</t>
+    <t>4433조 8053억 4573만</t>
   </si>
   <si>
     <t>노을푸링</t>
@@ -1520,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>3634조 6848억 3808만</t>
+    <t>3906조 4210억 3380만</t>
   </si>
   <si>
     <t>카엘다</t>
@@ -1529,13 +1529,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2716조 4605억 1575만</t>
+    <t>2829조 9317억 6719만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
   </si>
   <si>
-    <t>2540조 5830억 1372만</t>
+    <t>2631조 8970억 3319만</t>
+  </si>
+  <si>
+    <t>노을새벽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1792조 354억 106만</t>
   </si>
   <si>
     <t>노을치누</t>
@@ -1544,19 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
   </si>
   <si>
-    <t>1653조 9452억 9209만</t>
-  </si>
-  <si>
-    <t>노을새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1351조 5749억 8281만</t>
+    <t>1727조 297억 4879만</t>
   </si>
   <si>
     <t>노을이즈</t>
@@ -1595,7 +1595,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>797조 8313억 6781만</t>
+    <t>858조 2920억 8263만</t>
   </si>
   <si>
     <t>노을주크</t>
@@ -1607,6 +1607,33 @@
     <t>630조 2955억 4217만</t>
   </si>
   <si>
+    <t>노을망령</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
+  </si>
+  <si>
+    <t>526조 3520억 9707만</t>
+  </si>
+  <si>
+    <t>노을고래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>510조 9103억 8808만</t>
+  </si>
+  <si>
+    <t>노을밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>504조 5890억 4114만</t>
+  </si>
+  <si>
     <t>노을쁨</t>
   </si>
   <si>
@@ -1616,25 +1643,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>471조 4362억 527만</t>
-  </si>
-  <si>
-    <t>노을고래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>457조 9905억 1021만</t>
-  </si>
-  <si>
-    <t>노을망령</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
-  </si>
-  <si>
-    <t>452조 7772억 6635만</t>
+    <t>494조 224억 8810만</t>
   </si>
   <si>
     <t>노을비츠</t>
@@ -1643,16 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
   </si>
   <si>
-    <t>441조 2474억 9819만</t>
-  </si>
-  <si>
-    <t>노을밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>434조 8316억 6701만</t>
+    <t>453조 4222억 8355만</t>
   </si>
   <si>
     <t>노을하온</t>
@@ -1661,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
   </si>
   <si>
-    <t>413조 4231억 9095만</t>
+    <t>427조 8237억 3929만</t>
   </si>
   <si>
     <t>햄숍</t>
@@ -1682,6 +1682,15 @@
     <t>348조 9144억 1349만</t>
   </si>
   <si>
+    <t>사자탈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
+  </si>
+  <si>
+    <t>341조 1692억 6421만</t>
+  </si>
+  <si>
     <t>노을막내</t>
   </si>
   <si>
@@ -1691,22 +1700,13 @@
     <t>313조 1687억 9027만</t>
   </si>
   <si>
-    <t>사자탈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
-  </si>
-  <si>
-    <t>310조 5275억 5074만</t>
-  </si>
-  <si>
     <t>노을달빛</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8B%AC%EB%B9%9B</t>
   </si>
   <si>
-    <t>275조 3784억 3637만</t>
+    <t>285조 4216억 7957만</t>
   </si>
   <si>
     <t>노을준홍</t>
@@ -1715,7 +1715,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
   </si>
   <si>
-    <t>270조 9602억 4392만</t>
+    <t>283조 5765억 6876만</t>
+  </si>
+  <si>
+    <t>노을쿠키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%BF%A0%ED%82%A4</t>
+  </si>
+  <si>
+    <t>257조 5503억 4943만</t>
   </si>
   <si>
     <t>노을도아</t>
@@ -1724,16 +1733,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8F%84%EC%95%84</t>
   </si>
   <si>
-    <t>218조 2100억 9220만</t>
-  </si>
-  <si>
-    <t>노을쿠키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%BF%A0%ED%82%A4</t>
-  </si>
-  <si>
-    <t>207조 5107억 1682만</t>
+    <t>218조 2452억 3470만</t>
   </si>
   <si>
     <t>노을결빛</t>
@@ -1742,7 +1742,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B2%B0%EB%B9%9B</t>
   </si>
   <si>
-    <t>149조 6902억 4298만</t>
+    <t>190조 7084억 3727만</t>
   </si>
 </sst>
 </file>
@@ -2701,7 +2701,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>111</v>
@@ -2768,7 +2768,7 @@
         <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>122</v>
@@ -2800,7 +2800,7 @@
         <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2861,13 +2861,13 @@
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2878,22 +2878,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>131</v>
@@ -2925,7 +2925,7 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>111</v>
@@ -2989,7 +2989,7 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>111</v>
@@ -3085,7 +3085,7 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>131</v>
@@ -3152,10 +3152,10 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3166,16 +3166,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -3184,7 +3184,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>180</v>
@@ -3213,7 +3213,7 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>158</v>
@@ -3265,25 +3265,25 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3294,16 +3294,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -3315,7 +3315,7 @@
         <v>158</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3326,25 +3326,25 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>202</v>
@@ -3490,13 +3490,13 @@
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -3510,19 +3510,19 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>76</v>
@@ -3542,25 +3542,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -3574,25 +3574,25 @@
         <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -3606,25 +3606,25 @@
         <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -3638,13 +3638,13 @@
         <v>91</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -3656,7 +3656,7 @@
         <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -3670,13 +3670,13 @@
         <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -3688,7 +3688,7 @@
         <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -3702,25 +3702,25 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -3734,25 +3734,25 @@
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -3766,13 +3766,13 @@
         <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -3784,7 +3784,7 @@
         <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -3798,25 +3798,25 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -3830,25 +3830,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -3862,25 +3862,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -3894,13 +3894,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -3912,7 +3912,7 @@
         <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -3923,28 +3923,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -3958,13 +3958,13 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -3976,7 +3976,7 @@
         <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -3990,13 +3990,13 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -4008,7 +4008,7 @@
         <v>188</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4022,13 +4022,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -4040,7 +4040,7 @@
         <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4054,25 +4054,25 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4086,13 +4086,13 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -4104,7 +4104,7 @@
         <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4118,13 +4118,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -4133,10 +4133,10 @@
         <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4150,13 +4150,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -4165,10 +4165,10 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4182,13 +4182,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -4197,10 +4197,10 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4211,16 +4211,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -4229,10 +4229,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4246,13 +4246,13 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -4261,10 +4261,10 @@
         <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4278,13 +4278,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -4293,10 +4293,10 @@
         <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4310,25 +4310,25 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4339,16 +4339,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -4357,10 +4357,10 @@
         <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4371,28 +4371,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -4406,25 +4406,25 @@
         <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -4529,16 +4529,16 @@
         <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>304</v>
@@ -4567,10 +4567,10 @@
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>307</v>
@@ -4762,7 +4762,7 @@
         <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>326</v>
@@ -4823,10 +4823,10 @@
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -4887,7 +4887,7 @@
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>131</v>
@@ -4922,7 +4922,7 @@
         <v>313</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -4954,7 +4954,7 @@
         <v>313</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>344</v>
@@ -4968,7 +4968,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>345</v>
@@ -5015,7 +5015,7 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>188</v>
@@ -5050,7 +5050,7 @@
         <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>353</v>
@@ -5079,7 +5079,7 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>188</v>
@@ -5111,10 +5111,10 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>359</v>
@@ -5143,10 +5143,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>362</v>
@@ -5175,10 +5175,10 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>365</v>
@@ -5207,10 +5207,10 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>368</v>
@@ -5242,7 +5242,7 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>371</v>
@@ -5256,7 +5256,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>372</v>
@@ -5274,7 +5274,7 @@
         <v>149</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>374</v>
@@ -5303,10 +5303,10 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>377</v>
@@ -5335,10 +5335,10 @@
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>380</v>
@@ -5367,10 +5367,10 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>383</v>
@@ -5384,7 +5384,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>384</v>
@@ -5402,7 +5402,7 @@
         <v>149</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>386</v>
@@ -5416,7 +5416,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>387</v>
@@ -5431,10 +5431,10 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
@@ -5463,10 +5463,10 @@
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
@@ -5580,10 +5580,10 @@
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>395</v>
@@ -5612,10 +5612,10 @@
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>398</v>
@@ -5647,7 +5647,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
@@ -5673,10 +5673,10 @@
         <v>402</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>95</v>
@@ -5708,10 +5708,10 @@
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>313</v>
+        <v>140</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>406</v>
@@ -5740,7 +5740,7 @@
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>111</v>
@@ -5804,7 +5804,7 @@
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>131</v>
@@ -5900,7 +5900,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>158</v>
@@ -5964,7 +5964,7 @@
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>188</v>
@@ -5996,7 +5996,7 @@
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>188</v>
@@ -6013,7 +6013,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>434</v>
@@ -6063,7 +6063,7 @@
         <v>313</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>439</v>
@@ -6124,10 +6124,10 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>445</v>
@@ -6156,7 +6156,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>188</v>
@@ -6188,10 +6188,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>451</v>
@@ -6220,10 +6220,10 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>454</v>
@@ -6252,10 +6252,10 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>457</v>
@@ -6284,7 +6284,7 @@
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>460</v>
@@ -6301,7 +6301,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>462</v>
@@ -6319,7 +6319,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>464</v>
@@ -6351,7 +6351,7 @@
         <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>460</v>
+        <v>278</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>467</v>
@@ -6380,10 +6380,10 @@
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>470</v>
@@ -6412,10 +6412,10 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>473</v>
@@ -6429,7 +6429,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>474</v>
@@ -6444,7 +6444,7 @@
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>460</v>
@@ -6461,7 +6461,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>477</v>
@@ -6595,7 +6595,7 @@
         <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>482</v>
@@ -6656,10 +6656,10 @@
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>488</v>
@@ -6688,10 +6688,10 @@
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>491</v>
@@ -6813,10 +6813,10 @@
         <v>501</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>460</v>
@@ -6848,13 +6848,13 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>287</v>
+        <v>505</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6868,22 +6868,22 @@
         <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>508</v>
+        <v>288</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>509</v>
@@ -6915,7 +6915,7 @@
         <v>149</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>512</v>
@@ -6947,7 +6947,7 @@
         <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>515</v>
@@ -6979,7 +6979,7 @@
         <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>518</v>
@@ -7025,7 +7025,7 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>523</v>
@@ -7040,10 +7040,10 @@
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>525</v>
@@ -7072,13 +7072,13 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7092,13 +7092,13 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -7107,10 +7107,10 @@
         <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7124,25 +7124,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7156,22 +7156,22 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>538</v>
@@ -7200,10 +7200,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>313</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>287</v>
+        <v>521</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>541</v>
@@ -7296,7 +7296,7 @@
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>521</v>
@@ -7313,7 +7313,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>551</v>
@@ -7328,10 +7328,10 @@
         <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>313</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>553</v>
@@ -7360,10 +7360,10 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>313</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>521</v>
+        <v>292</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>556</v>
@@ -7392,10 +7392,10 @@
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>559</v>
@@ -7424,10 +7424,10 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>562</v>
@@ -7441,7 +7441,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>563</v>
@@ -7456,10 +7456,10 @@
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>565</v>
@@ -7473,7 +7473,7 @@
         <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>566</v>
@@ -7488,10 +7488,10 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>568</v>
@@ -7520,10 +7520,10 @@
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>571</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -1475,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>637경 8249조 3544억 9865만</t>
+    <t>808경 4894조 7658억 7352만</t>
   </si>
   <si>
     <t>노을뽀롱</t>
@@ -1493,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
   </si>
   <si>
-    <t>1경 750조 7307억 8404만</t>
+    <t>1경 779조 5389억 9595만</t>
   </si>
   <si>
     <t>노을구름</t>
@@ -1511,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%85%8C%EB%82%981</t>
   </si>
   <si>
-    <t>4433조 8053억 4573만</t>
+    <t>4974조 4392억 583만</t>
   </si>
   <si>
     <t>노을푸링</t>
@@ -1520,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>3906조 4210억 3380만</t>
+    <t>3933조 7183억 779만</t>
   </si>
   <si>
     <t>카엘다</t>
@@ -1529,7 +1529,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2829조 9317억 6719만</t>
+    <t>2856조 818억 6677만</t>
+  </si>
+  <si>
+    <t>노을치누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2767조 386억 7305만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
@@ -1544,21 +1556,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>1792조 354억 106만</t>
   </si>
   <si>
-    <t>노을치누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
-  </si>
-  <si>
-    <t>1727조 297억 4879만</t>
-  </si>
-  <si>
     <t>노을이즈</t>
   </si>
   <si>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A7%AD%EC%8B%9D</t>
   </si>
   <si>
-    <t>1242조 852억 5727만</t>
+    <t>1252조 4153억 1024만</t>
   </si>
   <si>
     <t>노을시아</t>
@@ -1592,129 +1592,129 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8D%EC%B4%88%ED%94%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
+    <t>869조 6629억 3751만</t>
+  </si>
+  <si>
+    <t>노을주크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%ED%81%AC</t>
+  </si>
+  <si>
+    <t>630조 2955억 4217만</t>
+  </si>
+  <si>
+    <t>노을고래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>541조 8655억 3198만</t>
+  </si>
+  <si>
+    <t>노을밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>527조 1177억 9455만</t>
+  </si>
+  <si>
+    <t>노을망령</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
-    <t>858조 2920억 8263만</t>
-  </si>
-  <si>
-    <t>노을주크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%ED%81%AC</t>
-  </si>
-  <si>
-    <t>630조 2955억 4217만</t>
-  </si>
-  <si>
-    <t>노을망령</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
-  </si>
-  <si>
     <t>526조 3520억 9707만</t>
   </si>
   <si>
-    <t>노을고래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>510조 9103억 8808만</t>
-  </si>
-  <si>
-    <t>노을밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>504조 5890억 4114만</t>
-  </si>
-  <si>
     <t>노을쁨</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
   </si>
   <si>
+    <t>520조 6988억 5095만</t>
+  </si>
+  <si>
+    <t>노을비츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>454조 265억 8012만</t>
+  </si>
+  <si>
+    <t>노을하온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
+  </si>
+  <si>
+    <t>429조 4676억 9889만</t>
+  </si>
+  <si>
+    <t>사자탈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
+  </si>
+  <si>
+    <t>421조 1169억 8050만</t>
+  </si>
+  <si>
+    <t>햄숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>413조 7451억 8027만</t>
+  </si>
+  <si>
+    <t>노을막내</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
+  </si>
+  <si>
+    <t>366조 4137억 8848만</t>
+  </si>
+  <si>
+    <t>노을둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>348조 9144억 1349만</t>
+  </si>
+  <si>
+    <t>노을달빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8B%AC%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>285조 4216억 7957만</t>
+  </si>
+  <si>
+    <t>노을준홍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
+  </si>
+  <si>
     <t>108</t>
   </si>
   <si>
-    <t>494조 224억 8810만</t>
-  </si>
-  <si>
-    <t>노을비츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>453조 4222억 8355만</t>
-  </si>
-  <si>
-    <t>노을하온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
-  </si>
-  <si>
-    <t>427조 8237억 3929만</t>
-  </si>
-  <si>
-    <t>햄숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>376조 1403억 3038만</t>
-  </si>
-  <si>
-    <t>노을둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>348조 9144억 1349만</t>
-  </si>
-  <si>
-    <t>사자탈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
-  </si>
-  <si>
-    <t>341조 1692억 6421만</t>
-  </si>
-  <si>
-    <t>노을막내</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
-  </si>
-  <si>
-    <t>313조 1687억 9027만</t>
-  </si>
-  <si>
-    <t>노을달빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8B%AC%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>285조 4216억 7957만</t>
-  </si>
-  <si>
-    <t>노을준홍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
-  </si>
-  <si>
     <t>283조 5765억 6876만</t>
   </si>
   <si>
@@ -1733,7 +1733,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8F%84%EC%95%84</t>
   </si>
   <si>
-    <t>218조 2452억 3470만</t>
+    <t>232조 7707억 5633만</t>
   </si>
   <si>
     <t>노을결빛</t>
@@ -1742,7 +1742,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B2%B0%EB%B9%9B</t>
   </si>
   <si>
-    <t>190조 7084억 3727만</t>
+    <t>210조 4361억 9387만</t>
   </si>
 </sst>
 </file>
@@ -6804,25 +6804,25 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>501</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>501</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>200</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6836,22 +6836,22 @@
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>503</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>506</v>
@@ -6880,10 +6880,10 @@
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>288</v>
+        <v>503</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>509</v>
@@ -6915,7 +6915,7 @@
         <v>149</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>512</v>
@@ -6979,7 +6979,7 @@
         <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>518</v>
@@ -7011,10 +7011,10 @@
         <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7028,13 +7028,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -7046,7 +7046,7 @@
         <v>288</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7060,25 +7060,25 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7092,25 +7092,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7124,22 +7124,22 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>534</v>
@@ -7171,10 +7171,10 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7188,13 +7188,13 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -7203,10 +7203,10 @@
         <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7220,13 +7220,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -7235,10 +7235,10 @@
         <v>149</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7252,25 +7252,25 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7284,25 +7284,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7316,25 +7316,25 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7348,25 +7348,25 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7380,13 +7380,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -7395,10 +7395,10 @@
         <v>140</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7412,13 +7412,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
@@ -7427,7 +7427,7 @@
         <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>562</v>
@@ -7459,7 +7459,7 @@
         <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>565</v>
@@ -7491,7 +7491,7 @@
         <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>568</v>
@@ -7523,7 +7523,7 @@
         <v>106</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>571</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">노을이!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">리안!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">헤라클레스!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">헤라클레스!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">호러!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="569">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>32</t>
+    <t>31</t>
   </si>
   <si>
     <t>1위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>602경 2808조 3209억 1039만</t>
+    <t>642경 7481조 8460억 1870만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
@@ -101,7 +101,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.09.13</t>
+    <t>2026.09.16</t>
   </si>
   <si>
     <t>리안</t>
@@ -143,7 +143,7 @@
     <t>Scania 10</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>490경 142조 9842억 9830만</t>
@@ -188,463 +188,466 @@
     <t>Scania 50</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>896경 4322조 940억 5360만</t>
+  </si>
+  <si>
+    <t>노을승용</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>빔냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>228경 131조 6916억 361만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>67경 2705조 1001억 2336만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>56경 7588조 8796억 205만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>56경 4909조 216억 5226만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>43경 2523조 8528억 3452만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>26경 6603조 6785억 6620만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>24경 6324조 2509억 4408만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>23경 6378조 9억 8238만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>12경 5797조 5282억 3519만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>10경 3790조 2974억 300만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>9경 7717조 5279억 6925만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>9경 7134조 3747억 7858만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>8경 7873조 5334억 9992만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>밉상b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
+  </si>
+  <si>
+    <t>8경 3399조 1839억 9474만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 3342조 5921억 8584만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>7경 1027조 7063억 5237만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4885조 3111억 7395만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>5경 8774조 7748억 8940만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>5경 3594조 4156억 1520만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>1경 7878조 1123억 177만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>1경 6529조 5322억 4370만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 5275조 752억 3008만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1경 4618조 2500억 6149만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>익맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 2768조 6356억 4928만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 1613조 6754억 1930만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>9468조 2895억 2411만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>8944조 2540억 2789만</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>650경 1938조 438억 2009만</t>
-  </si>
-  <si>
-    <t>노을승용</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>228경 131조 6916억 361만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>64경 4217조 575억 9009만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>55경 4363조 3706억 9167만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>55경 2525조 6218억 1334만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>41경 7711조 7799억 3444만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>23경 6378조 9억 8238만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>23경 6194조 6186억 7365만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>23경 5452조 8627억 4888만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>12경 4509조 2134억 7835만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>10경 280조 6073억 2728만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>9경 7717조 5279억 6925만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8경 6777조 8160억 7603만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>8경 32조 5919억 4407만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>밉상b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
-  </si>
-  <si>
-    <t>7경 6310조 4728억 1122만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 2264조 8746억 6831만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6경 7680조 2331억 1997만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4885조 3111억 7395만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>5경 8342조 1557억 9929만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>5경 5228조 9003억 4099만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>4경 7757조 7936억 9566만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 7102조 8495억 2595만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>1경 5351조 1664억 8613만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 5275조 752억 3008만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 3944조 7727억 1715만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>익맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 2718조 2674억 5593만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 14조 9938억 1255만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>9468조 2895억 2411만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8944조 2540억 2789만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>6665조 3780억 1797만</t>
+    <t>7596조 3054억 8889만</t>
   </si>
   <si>
     <t>메키에바란다</t>
@@ -653,16 +656,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>91경 9465조 9827억 649만</t>
+    <t>94경 4078조 28억 5858만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>60경 7045조 652억 325만</t>
+    <t>62경 6714조 5769억 8548만</t>
+  </si>
+  <si>
+    <t>라온PB</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
+  </si>
+  <si>
+    <t>60경 3474조 3971억 9956만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -674,22 +683,13 @@
     <t>60경 339조 6350억 2632만</t>
   </si>
   <si>
-    <t>라온PB</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
-  </si>
-  <si>
-    <t>56경 8609조 8131억 5928만</t>
-  </si>
-  <si>
     <t>혁수킹</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>54경 5852조 8098억 1207만</t>
+    <t>55경 7881조 3223억 2425만</t>
   </si>
   <si>
     <t>셀문</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>27경 2261조 2339억 2665만</t>
+    <t>27경 2358조 9413억 6552만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>12경 4643조 339억 9230만</t>
+    <t>12경 4816조 8867억 7101만</t>
   </si>
   <si>
     <t>악경</t>
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
   </si>
   <si>
-    <t>7경 1546조 5179억 2533만</t>
+    <t>8경 509조 7204억 3601만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -734,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>4경 7799조 1263억 2384만</t>
+    <t>4경 8360조 419억 1969만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -755,7 +755,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>3경 5889조 1978억 4877만</t>
+    <t>3경 5918조 2339억 2336만</t>
+  </si>
+  <si>
+    <t>힐캐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
+  </si>
+  <si>
+    <t>3경 5171조 8261억 605만</t>
   </si>
   <si>
     <t>떠영아</t>
@@ -767,13 +776,13 @@
     <t>3경 4432조 1072억 1410만</t>
   </si>
   <si>
-    <t>힐캐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
-  </si>
-  <si>
-    <t>3경 4425조 2247억 5892만</t>
+    <t>바람의새벽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
+  </si>
+  <si>
+    <t>2경 9221조 4290억 1767만</t>
   </si>
   <si>
     <t>안리뿐</t>
@@ -785,15 +794,6 @@
     <t>2경 3213조 7183억 2529만</t>
   </si>
   <si>
-    <t>바람의새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>2경 953조 9359억 4013만</t>
-  </si>
-  <si>
     <t>막내비숍</t>
   </si>
   <si>
@@ -809,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>1경 3084조 3477억 1406만</t>
+    <t>1경 3161조 792억 5309만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -818,7 +818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
   </si>
   <si>
-    <t>9840조 9184억 4426만</t>
+    <t>1경 213조 1532억 2만</t>
   </si>
   <si>
     <t>charon</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%9E%8C%ED%94%84</t>
   </si>
   <si>
-    <t>6250조 872억 4763만</t>
+    <t>7655조 8140억 293만</t>
   </si>
   <si>
     <t>초쓰</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%93%B0</t>
   </si>
   <si>
-    <t>5626조 742억 4534만</t>
+    <t>6573조 124억 6648만</t>
   </si>
   <si>
     <t>미나별</t>
@@ -875,7 +875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B0%B1</t>
   </si>
   <si>
-    <t>4367조 7714억 7311만</t>
+    <t>4854조 8896억 3741만</t>
   </si>
   <si>
     <t>힐나눔</t>
@@ -905,787 +905,781 @@
     <t>https://mgf.gg/contents/character.php?n=Matter2</t>
   </si>
   <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>210조 6116억 5619만</t>
+  </si>
+  <si>
+    <t>캐랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EB%9E%91</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>43조 6432억 7914만</t>
+  </si>
+  <si>
+    <t>Matter3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Matter3</t>
+  </si>
+  <si>
+    <t>나이트워커</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>2663억 39만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
+  </si>
+  <si>
+    <t>202경 5365조 6847억 4286만</t>
+  </si>
+  <si>
+    <t>난풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
+  </si>
+  <si>
+    <t>110경 59조 5376억 8708만</t>
+  </si>
+  <si>
+    <t>누짜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
+  </si>
+  <si>
+    <t>35경 7270조 8046억 7490만</t>
+  </si>
+  <si>
+    <t>일월마녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>35경 38조 6170억 4346만</t>
+  </si>
+  <si>
+    <t>송곧</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
+  </si>
+  <si>
+    <t>34경 1454조 2108억 1632만</t>
+  </si>
+  <si>
+    <t>메키존망섭종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
+  </si>
+  <si>
+    <t>24경 7526조 3190억 3581만</t>
+  </si>
+  <si>
+    <t>로드숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
+  </si>
+  <si>
+    <t>23경 7221조 2621억 7072만</t>
+  </si>
+  <si>
+    <t>도당이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%8B%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>9경 8526조 5240억 8367만</t>
+  </si>
+  <si>
+    <t>둄이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5경 4801조 6008억 389만</t>
+  </si>
+  <si>
+    <t>태켱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
+  </si>
+  <si>
+    <t>5경 4조 3212억 1972만</t>
+  </si>
+  <si>
+    <t>진짜지존법사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>4경 4347조 9483억 3614만</t>
+  </si>
+  <si>
+    <t>다이사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>4경 137조 1556억 8457만</t>
+  </si>
+  <si>
+    <t>카지야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%A7%80%EC%95%BC</t>
+  </si>
+  <si>
+    <t>3경 6041조 28억 4272만</t>
+  </si>
+  <si>
+    <t>똥으리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2경 8269조 1138억 6803만</t>
+  </si>
+  <si>
+    <t>즐처드셈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%90%EC%B2%98%EB%93%9C%EC%85%88</t>
+  </si>
+  <si>
+    <t>1경 9159조 5572억 6947만</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
+  </si>
+  <si>
+    <t>1경 1970조 658억 393만</t>
+  </si>
+  <si>
+    <t>고래털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%9E%98%ED%84%B8</t>
+  </si>
+  <si>
+    <t>1경 1043조 468억 1279만</t>
+  </si>
+  <si>
+    <t>피타입</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%ED%83%80%EC%9E%85</t>
+  </si>
+  <si>
+    <t>1경 862조 7448억 7357만</t>
+  </si>
+  <si>
+    <t>원순철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>8258조 2829억 571만</t>
+  </si>
+  <si>
+    <t>YooU</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YooU</t>
+  </si>
+  <si>
+    <t>7873조 6623억 710만</t>
+  </si>
+  <si>
+    <t>대전월클</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A0%84%EC%9B%94%ED%81%B4</t>
+  </si>
+  <si>
+    <t>7385조 2122억 8055만</t>
+  </si>
+  <si>
+    <t>기요코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EC%BD%94</t>
+  </si>
+  <si>
+    <t>7146조 7736억 709만</t>
+  </si>
+  <si>
+    <t>OrOl유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=OrOl%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>6722조 8488억 8977만</t>
+  </si>
+  <si>
+    <t>RaguS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=RaguS</t>
+  </si>
+  <si>
+    <t>6679조 4984억 735만</t>
+  </si>
+  <si>
+    <t>유디티기찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>5299조 440억 2486만</t>
+  </si>
+  <si>
+    <t>악전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
+  </si>
+  <si>
+    <t>4915조 2750억 5026만</t>
+  </si>
+  <si>
+    <t>강띵띵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
+  </si>
+  <si>
+    <t>4379조 1845억 2994만</t>
+  </si>
+  <si>
+    <t>끽코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
+  </si>
+  <si>
+    <t>4309조 528억 743만</t>
+  </si>
+  <si>
+    <t>앙음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>3841조 2766억 5950만</t>
+  </si>
+  <si>
+    <t>박미쯔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
+  </si>
+  <si>
+    <t>3638조 832억 926만</t>
+  </si>
+  <si>
+    <t>과금X환불O</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
+  </si>
+  <si>
+    <t>201경 4542조 6272억 96만</t>
+  </si>
+  <si>
+    <t>환불존망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>44경 4065조 7332억 1255만</t>
+  </si>
+  <si>
+    <t>역삼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>38경 4102조 9598억 1650만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
+  </si>
+  <si>
+    <t>24경 5575조 5299억 4079만</t>
+  </si>
+  <si>
+    <t>아그리아스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17경 6716조 9928억 4335만</t>
+  </si>
+  <si>
+    <t>쏘쏘하네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
+  </si>
+  <si>
+    <t>9경 3265조 5326억 1053만</t>
+  </si>
+  <si>
+    <t>꼬꼬대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>6경 123조 3836억 5298만</t>
+  </si>
+  <si>
+    <t>참OI슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>4경 9985조 2655억 8212만</t>
+  </si>
+  <si>
+    <t>록현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
+  </si>
+  <si>
+    <t>4경 3330조 130억 7145만</t>
+  </si>
+  <si>
+    <t>유지애123</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
+  </si>
+  <si>
+    <t>3경 6252조 2588억 7685만</t>
+  </si>
+  <si>
+    <t>머스탱GT</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
+  </si>
+  <si>
+    <t>2경 2767조 3150억 6295만</t>
+  </si>
+  <si>
+    <t>강남무자본</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%82%A8%EB%AC%B4%EC%9E%90%EB%B3%B8</t>
+  </si>
+  <si>
+    <t>1경 9221조 5793억 981만</t>
+  </si>
+  <si>
+    <t>아이츄크림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%B8%84%ED%81%AC%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>1경 8629조 3152억 3131만</t>
+  </si>
+  <si>
+    <t>응구7</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
+  </si>
+  <si>
+    <t>1경 7596조 7078억 2117만</t>
+  </si>
+  <si>
+    <t>할게없다고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>1경 4828조 3325억 9987만</t>
+  </si>
+  <si>
+    <t>웅선김</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
+  </si>
+  <si>
+    <t>1경 3758조 2869억 1064만</t>
+  </si>
+  <si>
+    <t>가루o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
+  </si>
+  <si>
+    <t>1경 3573조 3087억 4957만</t>
+  </si>
+  <si>
+    <t>정듄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
+  </si>
+  <si>
+    <t>1경 1911조 8279억 7563만</t>
+  </si>
+  <si>
+    <t>반서님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9C%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1경 336조 9852억 3626만</t>
+  </si>
+  <si>
+    <t>정슌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
+  </si>
+  <si>
+    <t>1경 167조 9227억 9043만</t>
+  </si>
+  <si>
+    <t>우유냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
+  </si>
+  <si>
+    <t>9865조 6616억 7883만</t>
+  </si>
+  <si>
+    <t>귀염둥이제제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>8610조 2540억 389만</t>
+  </si>
+  <si>
+    <t>한도100</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84100</t>
+  </si>
+  <si>
+    <t>8221조 9844억 3515만</t>
+  </si>
+  <si>
+    <t>zi존동길</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zi%EC%A1%B4%EB%8F%99%EA%B8%B8</t>
+  </si>
+  <si>
+    <t>7183조 1169억 899만</t>
+  </si>
+  <si>
+    <t>꼼맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>5303조 2607억 4857만</t>
+  </si>
+  <si>
+    <t>천닼나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%BC%EB%82%98</t>
+  </si>
+  <si>
+    <t>3194조 9774억 392만</t>
+  </si>
+  <si>
+    <t>스큐류바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%81%90%EB%A5%98%EB%B0%94</t>
+  </si>
+  <si>
+    <t>2971조 1917억 30만</t>
+  </si>
+  <si>
+    <t>백정Hero</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%A0%95Hero</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2082조 4772억 3438만</t>
+  </si>
+  <si>
+    <t>노을준이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>867경 57조 6580억 1416만</t>
+  </si>
+  <si>
+    <t>노을뽀롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%BD%80%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>24경 2357조 755억 8065만</t>
+  </si>
+  <si>
+    <t>노을주의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
+  </si>
+  <si>
+    <t>1경 1540조 35억 5440만</t>
+  </si>
+  <si>
+    <t>노을구름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B5%AC%EB%A6%84</t>
+  </si>
+  <si>
+    <t>1경 160조 531억 125만</t>
+  </si>
+  <si>
+    <t>아테나1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%85%8C%EB%82%981</t>
+  </si>
+  <si>
+    <t>4974조 4392억 583만</t>
+  </si>
+  <si>
+    <t>노을푸링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
+  </si>
+  <si>
+    <t>3966조 1691억 7579만</t>
+  </si>
+  <si>
+    <t>카엘다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>3006조 6054억 2070만</t>
+  </si>
+  <si>
+    <t>노을치누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2767조 386억 7305만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>2713조 4614억 3657만</t>
+  </si>
+  <si>
+    <t>노을새벽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
+  </si>
+  <si>
+    <t>1792조 354억 106만</t>
+  </si>
+  <si>
+    <t>노을짭식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A7%AD%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>1316조 2597억 9578만</t>
+  </si>
+  <si>
+    <t>노을이즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%9D%B4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1299조 1551억 5606만</t>
+  </si>
+  <si>
+    <t>노을시아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8B%9C%EC%95%84</t>
+  </si>
+  <si>
+    <t>1021조 9980억 6228만</t>
+  </si>
+  <si>
+    <t>속초피바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8D%EC%B4%88%ED%94%BC%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>869조 6629억 3751만</t>
+  </si>
+  <si>
+    <t>노을주크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%ED%81%AC</t>
+  </si>
+  <si>
+    <t>630조 2955억 4217만</t>
+  </si>
+  <si>
+    <t>노을고래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>541조 8655억 3198만</t>
+  </si>
+  <si>
+    <t>노을밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>527조 1177억 9455만</t>
+  </si>
+  <si>
+    <t>노을망령</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>526조 3520억 9707만</t>
+  </si>
+  <si>
+    <t>노을쁨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
+  </si>
+  <si>
+    <t>521조 2031억 2334만</t>
+  </si>
+  <si>
+    <t>노을비츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>454조 6679억 1603만</t>
+  </si>
+  <si>
+    <t>햄숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>438조 2067억 1883만</t>
+  </si>
+  <si>
+    <t>노을하온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
+  </si>
+  <si>
+    <t>429조 4676억 9889만</t>
+  </si>
+  <si>
+    <t>사자탈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
+  </si>
+  <si>
+    <t>421조 1805억 9627만</t>
+  </si>
+  <si>
+    <t>노을막내</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
+  </si>
+  <si>
     <t>107</t>
   </si>
   <si>
-    <t>199조 5130억 5508만</t>
-  </si>
-  <si>
-    <t>캐랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EB%9E%91</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>39조 2016억 1989만</t>
-  </si>
-  <si>
-    <t>Matter3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter3</t>
-  </si>
-  <si>
-    <t>나이트워커</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>2392억 2701만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
-  </si>
-  <si>
-    <t>202경 5365조 6847억 4286만</t>
-  </si>
-  <si>
-    <t>난풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
-  </si>
-  <si>
-    <t>109경 7862조 268억 2299만</t>
-  </si>
-  <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>35경 2940조 7310억 6211만</t>
-  </si>
-  <si>
-    <t>일월마녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>35경 38조 6170억 4346만</t>
-  </si>
-  <si>
-    <t>송곧</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
-  </si>
-  <si>
-    <t>34경 1278조 5441억 3102만</t>
-  </si>
-  <si>
-    <t>메키존망섭종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
-  </si>
-  <si>
-    <t>24경 7526조 3190억 3581만</t>
-  </si>
-  <si>
-    <t>로드숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
-  </si>
-  <si>
-    <t>23경 7221조 2621억 7072만</t>
-  </si>
-  <si>
-    <t>도당이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%8B%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>9경 5040조 8995억 3956만</t>
-  </si>
-  <si>
-    <t>둄이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5경 3329조 3983억 9783만</t>
-  </si>
-  <si>
-    <t>태켱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
-  </si>
-  <si>
-    <t>5경 4조 3212억 1972만</t>
-  </si>
-  <si>
-    <t>진짜지존법사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>4경 4347조 9483억 3614만</t>
-  </si>
-  <si>
-    <t>다이사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>4경 84조 1716억 8223만</t>
-  </si>
-  <si>
-    <t>카지야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%A7%80%EC%95%BC</t>
-  </si>
-  <si>
-    <t>3경 5611조 4308억 9296만</t>
-  </si>
-  <si>
-    <t>똥으리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2경 8269조 1138억 6803만</t>
-  </si>
-  <si>
-    <t>즐처드셈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%90%EC%B2%98%EB%93%9C%EC%85%88</t>
-  </si>
-  <si>
-    <t>1경 8863조 9763억 9143만</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
-  </si>
-  <si>
-    <t>1경 1937조 5718억 9003만</t>
-  </si>
-  <si>
-    <t>고래털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%9E%98%ED%84%B8</t>
-  </si>
-  <si>
-    <t>1경 1043조 468억 1279만</t>
-  </si>
-  <si>
-    <t>피타입</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%ED%83%80%EC%9E%85</t>
-  </si>
-  <si>
-    <t>1경 848조 3851억 4771만</t>
-  </si>
-  <si>
-    <t>원순철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>8090조 8880억 7485만</t>
-  </si>
-  <si>
-    <t>YooU</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YooU</t>
-  </si>
-  <si>
-    <t>7873조 6623억 710만</t>
-  </si>
-  <si>
-    <t>대전월클</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A0%84%EC%9B%94%ED%81%B4</t>
-  </si>
-  <si>
-    <t>7385조 2122억 8055만</t>
-  </si>
-  <si>
-    <t>기요코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EC%BD%94</t>
-  </si>
-  <si>
-    <t>7146조 7736억 709만</t>
-  </si>
-  <si>
-    <t>OrOl유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=OrOl%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>6722조 8488억 8977만</t>
-  </si>
-  <si>
-    <t>RaguS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RaguS</t>
-  </si>
-  <si>
-    <t>6382조 8879억 904만</t>
-  </si>
-  <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>5272조 3660억 832만</t>
-  </si>
-  <si>
-    <t>악전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
-  </si>
-  <si>
-    <t>4915조 2750억 5026만</t>
-  </si>
-  <si>
-    <t>강띵띵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
-  </si>
-  <si>
-    <t>4379조 1845억 2994만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>4200조 4114억 4325만</t>
-  </si>
-  <si>
-    <t>앙음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>3733조 1323억 2129만</t>
-  </si>
-  <si>
-    <t>박미쯔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
-  </si>
-  <si>
-    <t>3378조 7663억 3397만</t>
-  </si>
-  <si>
-    <t>과금X환불O</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
-  </si>
-  <si>
-    <t>196경 2520조 1483억 6179만</t>
-  </si>
-  <si>
-    <t>환불존망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>44경 3845조 4866억 4750만</t>
-  </si>
-  <si>
-    <t>역삼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>38경 4102조 9598억 1650만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
-  </si>
-  <si>
-    <t>24경 5419조 6267억 6546만</t>
-  </si>
-  <si>
-    <t>아그리아스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17경 6716조 9928억 4335만</t>
-  </si>
-  <si>
-    <t>쏘쏘하네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
-  </si>
-  <si>
-    <t>9경 3237조 9342억 7629만</t>
-  </si>
-  <si>
-    <t>꼬꼬대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>5경 9746조 9191억 7314만</t>
-  </si>
-  <si>
-    <t>참OI슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>4경 9642조 1684억 2049만</t>
-  </si>
-  <si>
-    <t>록현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
-  </si>
-  <si>
-    <t>4경 2580조 7001억 6305만</t>
-  </si>
-  <si>
-    <t>유지애123</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
-  </si>
-  <si>
-    <t>3경 5245조 3472억 6074만</t>
-  </si>
-  <si>
-    <t>머스탱GT</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
-  </si>
-  <si>
-    <t>2경 2744조 4691억 3860만</t>
-  </si>
-  <si>
-    <t>아이츄크림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%B8%84%ED%81%AC%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1경 8531조 3059억 7038만</t>
-  </si>
-  <si>
-    <t>강남무자본</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%82%A8%EB%AC%B4%EC%9E%90%EB%B3%B8</t>
-  </si>
-  <si>
-    <t>1경 8259조 7876억 9729만</t>
-  </si>
-  <si>
-    <t>응구7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
-  </si>
-  <si>
-    <t>1경 5511조 9850억 3950만</t>
-  </si>
-  <si>
-    <t>할게없다고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>1경 4584조 4424억 2782만</t>
-  </si>
-  <si>
-    <t>웅선김</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
-  </si>
-  <si>
-    <t>1경 3758조 2869억 1064만</t>
-  </si>
-  <si>
-    <t>가루o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
-  </si>
-  <si>
-    <t>1경 3527조 1863억 5039만</t>
-  </si>
-  <si>
-    <t>정듄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
-  </si>
-  <si>
-    <t>1경 1421조 3190억 3529만</t>
-  </si>
-  <si>
-    <t>반서님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9C%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1경 336조 9852억 3626만</t>
-  </si>
-  <si>
-    <t>우유냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
-  </si>
-  <si>
-    <t>9796조 7681억 6815만</t>
-  </si>
-  <si>
-    <t>정슌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
-  </si>
-  <si>
-    <t>9344조 8246억 7760만</t>
-  </si>
-  <si>
-    <t>귀염둥이제제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>8571조 6272억 9815만</t>
-  </si>
-  <si>
-    <t>한도100</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84100</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>7853조 9914억 6717만</t>
-  </si>
-  <si>
-    <t>zi존동길</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zi%EC%A1%B4%EB%8F%99%EA%B8%B8</t>
-  </si>
-  <si>
-    <t>7056조 79억 8576만</t>
-  </si>
-  <si>
-    <t>꼼맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>5123조 5283억 4134만</t>
-  </si>
-  <si>
-    <t>천닼나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EB%8B%BC%EB%82%98</t>
-  </si>
-  <si>
-    <t>3194조 9774억 392만</t>
-  </si>
-  <si>
-    <t>스큐류바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%81%90%EB%A5%98%EB%B0%94</t>
-  </si>
-  <si>
-    <t>2690조 527억 7245만</t>
-  </si>
-  <si>
-    <t>백정Hero</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%A0%95Hero</t>
-  </si>
-  <si>
-    <t>2082조 4772억 3438만</t>
-  </si>
-  <si>
-    <t>묘냥잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%83%A5%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1692조 9992억 7032만</t>
-  </si>
-  <si>
-    <t>노을준이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>808경 4894조 7658억 7352만</t>
-  </si>
-  <si>
-    <t>노을뽀롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%BD%80%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>24경 2357조 755억 8065만</t>
-  </si>
-  <si>
-    <t>노을주의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
-  </si>
-  <si>
-    <t>1경 779조 5389억 9595만</t>
-  </si>
-  <si>
-    <t>노을구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>1경 160조 531억 125만</t>
-  </si>
-  <si>
-    <t>아테나1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%85%8C%EB%82%981</t>
-  </si>
-  <si>
-    <t>4974조 4392억 583만</t>
-  </si>
-  <si>
-    <t>노을푸링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>3933조 7183억 779만</t>
-  </si>
-  <si>
-    <t>카엘다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2856조 818억 6677만</t>
-  </si>
-  <si>
-    <t>노을치누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2767조 386억 7305만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>2631조 8970억 3319만</t>
-  </si>
-  <si>
-    <t>노을새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>1792조 354억 106만</t>
-  </si>
-  <si>
-    <t>노을이즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%9D%B4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1298조 8987억 6480만</t>
-  </si>
-  <si>
-    <t>노을짭식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A7%AD%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>1252조 4153억 1024만</t>
-  </si>
-  <si>
-    <t>노을시아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8B%9C%EC%95%84</t>
-  </si>
-  <si>
-    <t>1021조 9980억 6228만</t>
-  </si>
-  <si>
-    <t>속초피바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8D%EC%B4%88%ED%94%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>869조 6629억 3751만</t>
-  </si>
-  <si>
-    <t>노을주크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%ED%81%AC</t>
-  </si>
-  <si>
-    <t>630조 2955억 4217만</t>
-  </si>
-  <si>
-    <t>노을고래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>541조 8655억 3198만</t>
-  </si>
-  <si>
-    <t>노을밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>527조 1177억 9455만</t>
-  </si>
-  <si>
-    <t>노을망령</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>526조 3520억 9707만</t>
-  </si>
-  <si>
-    <t>노을쁨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
-  </si>
-  <si>
-    <t>520조 6988억 5095만</t>
-  </si>
-  <si>
-    <t>노을비츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>454조 265억 8012만</t>
-  </si>
-  <si>
-    <t>노을하온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
-  </si>
-  <si>
-    <t>429조 4676억 9889만</t>
-  </si>
-  <si>
-    <t>사자탈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
-  </si>
-  <si>
-    <t>421조 1169억 8050만</t>
-  </si>
-  <si>
-    <t>햄숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>413조 7451억 8027만</t>
-  </si>
-  <si>
-    <t>노을막내</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
-  </si>
-  <si>
-    <t>366조 4137억 8848만</t>
+    <t>370조 9011억 6074만</t>
   </si>
   <si>
     <t>노을둥이</t>
@@ -1712,9 +1706,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>283조 5765억 6876만</t>
   </si>
   <si>
@@ -1733,7 +1724,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8F%84%EC%95%84</t>
   </si>
   <si>
-    <t>232조 7707억 5633만</t>
+    <t>233조 308억 1694만</t>
   </si>
   <si>
     <t>노을결빛</t>
@@ -1742,7 +1733,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B2%B0%EB%B9%9B</t>
   </si>
   <si>
-    <t>210조 4361억 9387만</t>
+    <t>210조 7265억 3033만</t>
   </si>
 </sst>
 </file>
@@ -2362,7 +2353,7 @@
         <v>56</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2512,10 +2503,10 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2526,16 +2517,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -2544,10 +2535,10 @@
         <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2558,16 +2549,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -2576,10 +2567,10 @@
         <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2590,28 +2581,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2622,25 +2613,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>102</v>
@@ -2672,7 +2663,7 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>107</v>
@@ -2701,7 +2692,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>111</v>
@@ -2736,10 +2727,10 @@
         <v>116</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2750,28 +2741,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2782,28 +2773,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2814,28 +2805,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2846,16 +2837,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -2864,10 +2855,10 @@
         <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2878,25 +2869,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>141</v>
@@ -2925,13 +2916,13 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2942,28 +2933,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2974,28 +2965,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3006,16 +2997,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -3024,10 +3015,10 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3038,16 +3029,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -3056,10 +3047,10 @@
         <v>116</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3070,28 +3061,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3102,16 +3093,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -3120,10 +3111,10 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3134,16 +3125,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -3152,10 +3143,10 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3166,16 +3157,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -3184,10 +3175,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3198,7 +3189,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>182</v>
@@ -3213,10 +3204,10 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>184</v>
@@ -3280,7 +3271,7 @@
         <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>193</v>
@@ -3312,7 +3303,7 @@
         <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>197</v>
@@ -3358,16 +3349,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
@@ -3379,7 +3370,7 @@
         <v>188</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3478,22 +3469,22 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>209</v>
@@ -3522,10 +3513,10 @@
         <v>200</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>211</v>
@@ -3554,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>214</v>
@@ -3571,7 +3562,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>215</v>
@@ -3586,7 +3577,7 @@
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>76</v>
@@ -3603,7 +3594,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>218</v>
@@ -3618,10 +3609,10 @@
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>220</v>
@@ -3635,7 +3626,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>221</v>
@@ -3653,7 +3644,7 @@
         <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>223</v>
@@ -3667,7 +3658,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>224</v>
@@ -3685,7 +3676,7 @@
         <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>226</v>
@@ -3714,7 +3705,7 @@
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>111</v>
@@ -3746,10 +3737,10 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>232</v>
@@ -3781,7 +3772,7 @@
         <v>69</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>235</v>
@@ -3795,7 +3786,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>236</v>
@@ -3813,7 +3804,7 @@
         <v>238</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>239</v>
@@ -3827,7 +3818,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>240</v>
@@ -3842,10 +3833,10 @@
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>242</v>
@@ -3859,7 +3850,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>243</v>
@@ -3874,10 +3865,10 @@
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
@@ -3891,7 +3882,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>246</v>
@@ -3906,10 +3897,10 @@
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
@@ -3923,7 +3914,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>249</v>
@@ -3938,10 +3929,10 @@
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>251</v>
@@ -3970,10 +3961,10 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>254</v>
@@ -3987,7 +3978,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>255</v>
@@ -4019,7 +4010,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>258</v>
@@ -4037,7 +4028,7 @@
         <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>260</v>
@@ -4051,7 +4042,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>261</v>
@@ -4066,7 +4057,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>201</v>
@@ -4083,7 +4074,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>264</v>
@@ -4101,7 +4092,7 @@
         <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>266</v>
@@ -4115,7 +4106,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>267</v>
@@ -4147,7 +4138,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>270</v>
@@ -4165,7 +4156,7 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>272</v>
@@ -4179,7 +4170,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>273</v>
@@ -4211,7 +4202,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>276</v>
@@ -4243,7 +4234,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>280</v>
@@ -4322,7 +4313,7 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>288</v>
@@ -4386,7 +4377,7 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>296</v>
@@ -4403,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>298</v>
@@ -4538,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>304</v>
@@ -4567,10 +4558,10 @@
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>307</v>
@@ -4602,7 +4593,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>310</v>
@@ -4616,7 +4607,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>311</v>
@@ -4634,7 +4625,7 @@
         <v>313</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>314</v>
@@ -4648,7 +4639,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>315</v>
@@ -4666,7 +4657,7 @@
         <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>317</v>
@@ -4680,7 +4671,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>318</v>
@@ -4698,7 +4689,7 @@
         <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>320</v>
@@ -4712,7 +4703,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>321</v>
@@ -4762,7 +4753,7 @@
         <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>326</v>
@@ -4794,7 +4785,7 @@
         <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>329</v>
@@ -4823,10 +4814,10 @@
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -4840,7 +4831,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>333</v>
@@ -4872,7 +4863,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>336</v>
@@ -4887,10 +4878,10 @@
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>338</v>
@@ -4904,7 +4895,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>339</v>
@@ -4922,7 +4913,7 @@
         <v>313</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -4936,7 +4927,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>342</v>
@@ -4954,7 +4945,7 @@
         <v>313</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>344</v>
@@ -4968,7 +4959,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>345</v>
@@ -4986,7 +4977,7 @@
         <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>347</v>
@@ -5015,7 +5006,7 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>188</v>
@@ -5032,7 +5023,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>351</v>
@@ -5064,7 +5055,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>354</v>
@@ -5079,7 +5070,7 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>188</v>
@@ -5096,7 +5087,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>357</v>
@@ -5111,7 +5102,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>201</v>
@@ -5128,7 +5119,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>360</v>
@@ -5143,7 +5134,7 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>201</v>
@@ -5160,7 +5151,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>363</v>
@@ -5175,7 +5166,7 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>201</v>
@@ -5192,7 +5183,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>366</v>
@@ -5207,7 +5198,7 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>278</v>
@@ -5224,7 +5215,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>369</v>
@@ -5256,7 +5247,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>372</v>
@@ -5271,7 +5262,7 @@
         <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>278</v>
@@ -5288,7 +5279,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>375</v>
@@ -5303,7 +5294,7 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>201</v>
@@ -5367,7 +5358,7 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>278</v>
@@ -5399,7 +5390,7 @@
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>278</v>
@@ -5431,7 +5422,7 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>278</v>
@@ -5448,7 +5439,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>390</v>
@@ -5466,7 +5457,7 @@
         <v>75</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
@@ -5515,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5524,7 +5515,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5580,10 +5571,10 @@
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>395</v>
@@ -5612,10 +5603,10 @@
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>398</v>
@@ -5647,7 +5638,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
@@ -5661,7 +5652,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>49</v>
@@ -5676,10 +5667,10 @@
         <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>403</v>
@@ -5693,7 +5684,7 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>404</v>
@@ -5708,10 +5699,10 @@
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>406</v>
@@ -5725,7 +5716,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>407</v>
@@ -5740,7 +5731,7 @@
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>111</v>
@@ -5757,7 +5748,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>410</v>
@@ -5775,7 +5766,7 @@
         <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>412</v>
@@ -5804,10 +5795,10 @@
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>415</v>
@@ -5839,7 +5830,7 @@
         <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>418</v>
@@ -5871,7 +5862,7 @@
         <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>421</v>
@@ -5885,7 +5876,7 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>422</v>
@@ -5900,10 +5891,10 @@
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>424</v>
@@ -5917,7 +5908,7 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>425</v>
@@ -5932,10 +5923,10 @@
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>427</v>
@@ -5949,7 +5940,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>428</v>
@@ -5964,10 +5955,10 @@
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>430</v>
@@ -5981,7 +5972,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>431</v>
@@ -5996,10 +5987,10 @@
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>433</v>
@@ -6013,7 +6004,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>434</v>
@@ -6077,7 +6068,7 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>440</v>
@@ -6109,7 +6100,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>443</v>
@@ -6124,10 +6115,10 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>445</v>
@@ -6141,7 +6132,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>446</v>
@@ -6156,7 +6147,7 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>188</v>
@@ -6173,7 +6164,7 @@
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>449</v>
@@ -6188,10 +6179,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>451</v>
@@ -6205,7 +6196,7 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>452</v>
@@ -6220,10 +6211,10 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>454</v>
@@ -6237,7 +6228,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>455</v>
@@ -6252,7 +6243,7 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>188</v>
@@ -6269,7 +6260,7 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>458</v>
@@ -6284,13 +6275,13 @@
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6301,16 +6292,16 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -6322,7 +6313,7 @@
         <v>201</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6333,16 +6324,16 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -6354,7 +6345,7 @@
         <v>278</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6368,25 +6359,25 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6400,25 +6391,25 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>278</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6432,22 +6423,22 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>476</v>
@@ -6456,40 +6447,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6519,7 +6478,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6536,7 +6494,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6580,28 +6538,28 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6612,13 +6570,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -6627,13 +6585,13 @@
         <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6644,28 +6602,28 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>201</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6673,31 +6631,31 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>201</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6705,16 +6663,16 @@
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -6723,13 +6681,13 @@
         <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6737,16 +6695,16 @@
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -6755,13 +6713,13 @@
         <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6769,16 +6727,16 @@
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -6787,13 +6745,13 @@
         <v>313</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6804,28 +6762,28 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6842,22 +6800,22 @@
         <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6868,13 +6826,13 @@
         <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -6883,13 +6841,13 @@
         <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6897,31 +6855,31 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6929,31 +6887,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6961,16 +6919,16 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -6979,13 +6937,13 @@
         <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6993,16 +6951,16 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -7014,10 +6972,10 @@
         <v>288</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7025,31 +6983,31 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7060,13 +7018,13 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -7078,10 +7036,10 @@
         <v>288</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7089,16 +7047,16 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -7110,10 +7068,10 @@
         <v>288</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7121,31 +7079,31 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7153,16 +7111,16 @@
         <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -7171,13 +7129,13 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7185,31 +7143,31 @@
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7217,31 +7175,31 @@
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>533</v>
+        <v>288</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7249,31 +7207,31 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>313</v>
+        <v>150</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>288</v>
+        <v>530</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7281,31 +7239,31 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>533</v>
+        <v>288</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7313,31 +7271,31 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7345,31 +7303,31 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7380,28 +7338,28 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7412,28 +7370,28 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>562</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7444,28 +7402,28 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7476,13 +7434,13 @@
         <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
@@ -7491,13 +7449,13 @@
         <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7505,31 +7463,31 @@
         <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -8,26 +8,26 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="셀린느" sheetId="2" r:id="rId2"/>
-    <sheet name="리안" sheetId="3" r:id="rId3"/>
-    <sheet name="호러" sheetId="4" r:id="rId4"/>
-    <sheet name="헤라클레스" sheetId="5" r:id="rId5"/>
-    <sheet name="노을이" sheetId="6" r:id="rId6"/>
+    <sheet name="설묘" sheetId="2" r:id="rId2"/>
+    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
+    <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
+    <sheet name="TRIUMPH" sheetId="5" r:id="rId5"/>
+    <sheet name="promise" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">노을이!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">리안!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">헤라클레스!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">호러!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="578">
   <si>
     <t>guild_name</t>
   </si>
@@ -68,133 +68,130 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>설묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>1067경 905조 4945억 8899만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>2026.09.18</t>
+  </si>
+  <si>
     <t>셀린느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 2</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
     <t>Lv.9</t>
   </si>
   <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>642경 7481조 8460억 1870만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
+    <t>668경 6572조 6179억 6729만</t>
+  </si>
+  <si>
+    <t>문의 [혜영]</t>
   </si>
   <si>
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.09.16</t>
-  </si>
-  <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>459경 4007조 5761억 2920만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>호러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>543경 5289조 3961억 5059만</t>
-  </si>
-  <si>
-    <t>오래 하실분들 환영입니다</t>
-  </si>
-  <si>
-    <t>기요밋</t>
-  </si>
-  <si>
-    <t>헤라클레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%97%A4%EB%9D%BC%ED%81%B4%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>Scania 38</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>386경 6174조 6629억 9260만</t>
-  </si>
-  <si>
-    <t>월드아레나 대비 잘치는분들 위주로 와주세요. in50위 문의주세요! (목표보상:에디큐브 70개 확정보상:에디큐브 60개)</t>
-  </si>
-  <si>
-    <t>번펀</t>
-  </si>
-  <si>
-    <t>2026.09.17</t>
-  </si>
-  <si>
-    <t>노을이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%85%B8%EC%9D%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>Scania 50</t>
+    <t>별하나달하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>783경 6190조 5721억 6339만</t>
+  </si>
+  <si>
+    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
+  </si>
+  <si>
+    <t>Onyul</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>896경 9134조 2991억 7049만</t>
-  </si>
-  <si>
-    <t>노을승용</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>886경 2075조 5257억 6509만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>4557조 7409억 1869만</t>
+  </si>
+  <si>
+    <t>길컨미참여 2일미접 추방입니다</t>
+  </si>
+  <si>
+    <t>이랑b</t>
   </si>
   <si>
     <t>member_rank_in_guild</t>
@@ -224,15 +221,420 @@
     <t>1</t>
   </si>
   <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>231경 7865조 5718억 420만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>225경 1047조 968억 5458만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>151경 4609조 7545억 8786만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>62경 4188조 2543억 3793만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>52경 9932조 7914억 9061만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>45경 5109조 8480억 2031만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>39경 1509조 7156억 9977만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>39경 863조 8820억 7662만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>35경 5866조 3798억 7180만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>21경 5442조 4971억 3872만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>21경 4753조 3765억 8338만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>18경 7073조 8948억 5020만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>15경 3797조 2443억 3111만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>13경 2105조 4816억 1933만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>12경 7975조 8170억 5111만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>8경 1791조 1615억 2546만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 4972조 6974억 1981만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>7경 2382조 7642억 9212만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>5경 5478조 8492억 3032만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 4783조 8696억 6956만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>4경 8648조 589억 330만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>수상구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2경 5422조 8458억 5094만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 612조 7974억 7642만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 8681조 1008억 7785만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>1경 6876조 6915억 91만</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4405조 2903억 5532만</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>9288조 9444억 7420만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>9023조 9082억 1993만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>8781조 4022억 5235만</t>
+  </si>
+  <si>
     <t>빔냥이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>신궁</t>
   </si>
   <si>
@@ -242,25 +644,22 @@
     <t>228경 131조 6916억 361만</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>MNMMNMMNMMNM</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>67경 2705조 1001억 2336만</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>82경 4332조 2590억 2998만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>58경 828조 6734억 1419만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -269,28 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>56경 7588조 8796억 205만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>56경 4909조 216억 5226만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>56경 8251조 4948억 4872만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -299,10 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>43경 2523조 8528억 3452만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>44경 7429조 932억 1578만</t>
   </si>
   <si>
     <t>뽀리빠</t>
@@ -311,16 +686,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>26경 6603조 6785억 6620만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>26경 7842조 692억 1075만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>26경 4824조 3993억 8632만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -332,25 +707,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>24경 6324조 2509억 4408만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>23경 6378조 9억 8238만</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>24경 9930조 6612억 5723만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -359,13 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>12경 5797조 5282억 3519만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>13경 8586조 3568억 7252만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -374,16 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>10경 3790조 2974억 300만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>10경 4506조 7719억 7191만</t>
   </si>
   <si>
     <t>약어</t>
@@ -392,55 +734,43 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
     <t>9경 7717조 5279억 6925만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>천천히걸어가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
   </si>
   <si>
-    <t>118</t>
-  </si>
-  <si>
     <t>9경 7134조 3747억 7858만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>국의</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8경 7873조 5334억 9992만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>밉상b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
-  </si>
-  <si>
-    <t>8경 3399조 1839억 9474만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>9경 5132조 3135억 4804만</t>
+  </si>
+  <si>
+    <t>익맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8경 4785조 8773억 3366만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>7경 7727조 6633억 2044만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -449,10 +779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>7경 3342조 5921억 8584만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>7경 7689조 2024억 7915만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -461,30 +788,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>캡틴</t>
-  </si>
-  <si>
     <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>7경 1027조 7063억 5237만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
@@ -494,22 +800,22 @@
     <t>6경 4885조 3111억 7395만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>킹몬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
     <t>5경 8774조 7748억 8940만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>5경 7078조 5154억 5987만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -521,34 +827,13 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>5경 3594조 4156억 1520만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>세아수호지호</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>1경 7878조 1123억 177만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>1경 8800조 5458억 7439만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -557,10 +842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>1경 6529조 5322억 4370만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>1경 6550조 8025억 4362만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -572,9 +854,6 @@
     <t>1경 5275조 752억 3008만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>프리프리</t>
   </si>
   <si>
@@ -584,19 +863,19 @@
     <t>1경 4618조 2500억 6149만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>익맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 2768조 6356억 4928만</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>1경 2820조 5747억 3779만</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1경 2795조 2161억 6085만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -605,10 +884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1613조 6754억 1930만</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>1경 2199조 4890억 2250만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -617,1138 +893,874 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>9468조 2895억 2411만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>9914조 2000억 5682만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>7721조 4388억 5016만</t>
+  </si>
+  <si>
+    <t>껌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>300경 9676조 7164억 5367만</t>
+  </si>
+  <si>
+    <t>달하나별하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>223경 1874조 2497억 5686만</t>
+  </si>
+  <si>
+    <t>왕이된사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>84경 1조 1044억 968만</t>
+  </si>
+  <si>
+    <t>라온DK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
+  </si>
+  <si>
+    <t>77경 4323조 4875억 3094만</t>
+  </si>
+  <si>
+    <t>라온B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
+  </si>
+  <si>
+    <t>34경 6366조 9101억 3776만</t>
+  </si>
+  <si>
+    <t>라온Z</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
+  </si>
+  <si>
+    <t>22경 5556조 3066억 7866만</t>
+  </si>
+  <si>
+    <t>와츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5경 1031조 232억 5292만</t>
+  </si>
+  <si>
+    <t>스터디뱅크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
+  </si>
+  <si>
+    <t>4경 625조 9816억 9415만</t>
+  </si>
+  <si>
+    <t>상깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
+  </si>
+  <si>
+    <t>3경 331조 1265억 4185만</t>
+  </si>
+  <si>
+    <t>찍먹비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>2경 7088조 8412억 8766만</t>
+  </si>
+  <si>
+    <t>뾰쀼뾰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
+  </si>
+  <si>
+    <t>2경 6639조 8064억 7260만</t>
+  </si>
+  <si>
+    <t>StarLink</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
+  </si>
+  <si>
+    <t>2경 6384조 4873억 4507만</t>
+  </si>
+  <si>
+    <t>뚜뭉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2경 1696조 3168억 4846만</t>
+  </si>
+  <si>
+    <t>못함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
+  </si>
+  <si>
+    <t>2경 718조 8851억 7734만</t>
+  </si>
+  <si>
+    <t>오쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1경 9483조 1803억 1728만</t>
+  </si>
+  <si>
+    <t>금하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>1경 6865조 6744억 3142만</t>
+  </si>
+  <si>
+    <t>쵸비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1경 4773조 3232억 5495만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
+  </si>
+  <si>
+    <t>1경 4480조 2743억 8806만</t>
+  </si>
+  <si>
+    <t>준준챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>1경 4200조 9912억 9042만</t>
+  </si>
+  <si>
+    <t>뚝딱비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>1경 453조 8183억 4245만</t>
+  </si>
+  <si>
+    <t>서두희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>1경 98조 2390억 9178만</t>
+  </si>
+  <si>
+    <t>연이무사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>9337조 3662억 7305만</t>
+  </si>
+  <si>
+    <t>회귀함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EA%B7%80%ED%95%A8</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>8944조 2540억 2789만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>7596조 3054억 8889만</t>
-  </si>
-  <si>
-    <t>메키에바란다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>94경 4078조 28억 5858만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
-  </si>
-  <si>
-    <t>62경 8309조 1316억 4266만</t>
-  </si>
-  <si>
-    <t>라온PB</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
-  </si>
-  <si>
-    <t>60경 3474조 3971억 9956만</t>
-  </si>
-  <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter</t>
-  </si>
-  <si>
-    <t>60경 339조 6350억 2632만</t>
-  </si>
-  <si>
-    <t>혁수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>55경 7881조 3223억 2425만</t>
-  </si>
-  <si>
-    <t>셀문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>44경 4304조 3775억 7803만</t>
-  </si>
-  <si>
-    <t>파퍼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
-  </si>
-  <si>
-    <t>27경 3395조 9172억 3566만</t>
-  </si>
-  <si>
-    <t>이삼2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
-  </si>
-  <si>
-    <t>12경 4957조 2115억 8358만</t>
-  </si>
-  <si>
-    <t>악경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>8경 509조 7204억 3601만</t>
-  </si>
-  <si>
-    <t>고먀츠나나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>4경 8360조 419억 1969만</t>
-  </si>
-  <si>
-    <t>딤개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>3경 9345조 1748억 2777만</t>
-  </si>
-  <si>
-    <t>히째히째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>3경 6705조 6123억 7632만</t>
-  </si>
-  <si>
-    <t>힐캐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
-  </si>
-  <si>
-    <t>3경 5798조 3232억 8369만</t>
-  </si>
-  <si>
-    <t>떠영아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%98%81%EC%95%84</t>
-  </si>
-  <si>
-    <t>3경 4432조 1072억 1410만</t>
-  </si>
-  <si>
-    <t>바람의새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>2경 9221조 4290억 1767만</t>
-  </si>
-  <si>
-    <t>안리뿐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A6%AC%EB%BF%90</t>
-  </si>
-  <si>
-    <t>2경 3213조 7183억 2529만</t>
-  </si>
-  <si>
-    <t>막내비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%82%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>2경 736조 2308억 389만</t>
-  </si>
-  <si>
-    <t>이남선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
-  </si>
-  <si>
-    <t>1경 3201조 8659억 5615만</t>
-  </si>
-  <si>
-    <t>표창빌런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%B9%8C%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>1경 213조 1532억 2만</t>
-  </si>
-  <si>
-    <t>charon</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=charon</t>
-  </si>
-  <si>
-    <t>9662조 1109억 3741만</t>
-  </si>
-  <si>
-    <t>뜨람프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%9E%8C%ED%94%84</t>
-  </si>
-  <si>
-    <t>7655조 8140억 293만</t>
-  </si>
-  <si>
-    <t>초쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%93%B0</t>
-  </si>
-  <si>
-    <t>7163조 7612억 701만</t>
-  </si>
-  <si>
-    <t>미나별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EB%82%98%EB%B3%84</t>
-  </si>
-  <si>
-    <t>5826조 5093억 5130만</t>
-  </si>
-  <si>
-    <t>모르도아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%EB%8F%84%EC%95%84</t>
+    <t>9024조 7811억 8626만</t>
+  </si>
+  <si>
+    <t>희다차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>8893조 8717억 1835만</t>
+  </si>
+  <si>
+    <t>널꼬라봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
+  </si>
+  <si>
+    <t>8593조 2536억 2739만</t>
+  </si>
+  <si>
+    <t>신참치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>7243조 8271억 2621만</t>
+  </si>
+  <si>
+    <t>걸동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6317조 5640억 5211만</t>
+  </si>
+  <si>
+    <t>수영하는수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%98%81%ED%95%98%EB%8A%94%EC%88%98%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>5154조 9765억 3925만</t>
+  </si>
+  <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
   </si>
   <si>
     <t>113</t>
   </si>
   <si>
-    <t>5054조 6465억 1446만</t>
-  </si>
-  <si>
-    <t>악갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>4869조 4859억 3163만</t>
-  </si>
-  <si>
-    <t>힐나눔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%82%98%EB%88%94</t>
-  </si>
-  <si>
-    <t>4008조 549억 2960만</t>
-  </si>
-  <si>
-    <t>이웡삥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%A1%EC%82%A5</t>
+    <t>4776조 6629억 1855만</t>
+  </si>
+  <si>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>4177조 5240억 1807만</t>
+  </si>
+  <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>844경 9612조 4594억 781만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>32경 3920조 5622억 4687만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2경 6045조 2479억 642만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 9093조 9092억 6631만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 2695조 2875억 7879만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>7005조 1563억 660만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2868조 1940억 5032만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2698조 6805억 2581만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>1034조 8303억 5680만</t>
-  </si>
-  <si>
-    <t>Matter2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter2</t>
+    <t>2518조 1619억 3179만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2155조 443억 5090만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>2122조 1292억 2655만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2021조 5911억 2973만</t>
+  </si>
+  <si>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1485조 5840억 7215만</t>
+  </si>
+  <si>
+    <t>산과바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1173조 6985억 7512만</t>
+  </si>
+  <si>
+    <t>서전붕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
+  </si>
+  <si>
+    <t>1098조 7210억 19만</t>
+  </si>
+  <si>
+    <t>호야빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>1077조 6256억 8210만</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>960조 1640억 2583만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
     <t>108</t>
   </si>
   <si>
-    <t>210조 6116억 5619만</t>
-  </si>
-  <si>
-    <t>캐랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EB%9E%91</t>
+    <t>836조 8013억 5457만</t>
+  </si>
+  <si>
+    <t>루린츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
+  </si>
+  <si>
+    <t>525조 7616억 9510만</t>
+  </si>
+  <si>
+    <t>묘피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
+  </si>
+  <si>
+    <t>450조 2034억 4621만</t>
+  </si>
+  <si>
+    <t>뽀야츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>328조 629억 6465만</t>
+  </si>
+  <si>
+    <t>하치츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>286조 7407억 2949만</t>
+  </si>
+  <si>
+    <t>히히힣히힣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
+  </si>
+  <si>
+    <t>245조 7214억 8719만</t>
+  </si>
+  <si>
+    <t>도리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>209조 7743억 1108만</t>
+  </si>
+  <si>
+    <t>주냥츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
+  </si>
+  <si>
+    <t>194조 4121억 2176만</t>
+  </si>
+  <si>
+    <t>디나인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>154조 153억 4607만</t>
+  </si>
+  <si>
+    <t>새벽츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EC%B8%84</t>
+  </si>
+  <si>
+    <t>152조 3767억 9006만</t>
+  </si>
+  <si>
+    <t>우솝쁘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%81%98</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>64조 3332억 4836만</t>
+  </si>
+  <si>
+    <t>비먀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
+  </si>
+  <si>
+    <t>52조 9807억 6147만</t>
+  </si>
+  <si>
+    <t>피카츄십볼트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
   </si>
   <si>
     <t>105</t>
   </si>
   <si>
-    <t>44조 309억 6049만</t>
-  </si>
-  <si>
-    <t>Matter3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter3</t>
+    <t>20조 7055억 4432만</t>
+  </si>
+  <si>
+    <t>결기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>453조 1445억 2085만</t>
+  </si>
+  <si>
+    <t>온우사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>398조 5534억 4596만</t>
+  </si>
+  <si>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>385조 7861억 5418만</t>
+  </si>
+  <si>
+    <t>후추양조장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>340조 9115억 7451만</t>
+  </si>
+  <si>
+    <t>지존승준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
+  </si>
+  <si>
+    <t>325조 5858억 5659만</t>
+  </si>
+  <si>
+    <t>우댕이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>323조 9446억 4934만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>320조 7784억 8801만</t>
+  </si>
+  <si>
+    <t>규르트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%9C%EB%A5%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>276조 90억 5306만</t>
+  </si>
+  <si>
+    <t>말랑랑말이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>247조 4907억 2652만</t>
+  </si>
+  <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>240조 770억 3731만</t>
+  </si>
+  <si>
+    <t>눅이마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>182조 201억 3448만</t>
+  </si>
+  <si>
+    <t>성식대군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>145조 6860억 7595만</t>
+  </si>
+  <si>
+    <t>태환이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>133조 9945억 6561만</t>
+  </si>
+  <si>
+    <t>효깨비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>131조 2511억 3160만</t>
+  </si>
+  <si>
+    <t>에너지솔루션</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
+  </si>
+  <si>
+    <t>118조 7364억 9923만</t>
+  </si>
+  <si>
+    <t>벵글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
+  </si>
+  <si>
+    <t>112조 9092억 3143만</t>
+  </si>
+  <si>
+    <t>버미겨리0</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
+  </si>
+  <si>
+    <t>110조 9463억 395만</t>
+  </si>
+  <si>
+    <t>NSYN</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NSYN</t>
+  </si>
+  <si>
+    <t>95조 237억 6303만</t>
+  </si>
+  <si>
+    <t>무큼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>69조 1211억 4510만</t>
+  </si>
+  <si>
+    <t>꿀가족</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B0%80%EC%A1%B1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>52조 9393억 7842만</t>
+  </si>
+  <si>
+    <t>진흥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>25조 7718억 97만</t>
+  </si>
+  <si>
+    <t>파란달팽2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
+  </si>
+  <si>
+    <t>17조 1123억 2995만</t>
+  </si>
+  <si>
+    <t>짜도이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>13조 5946억 6915만</t>
+  </si>
+  <si>
+    <t>상혀닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>10조 2535억 8036만</t>
+  </si>
+  <si>
+    <t>개념독점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%85%90%EB%8F%85%EC%A0%90</t>
+  </si>
+  <si>
+    <t>9조 9941억 7310만</t>
+  </si>
+  <si>
+    <t>돼지띠최덕배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%80%EB%9D%A0%EC%B5%9C%EB%8D%95%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>9조 6602억 4970만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
+  </si>
+  <si>
+    <t>5조 847억 1973만</t>
+  </si>
+  <si>
+    <t>도현빠덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%98%84%EB%B9%A0%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 2804억 8869만</t>
+  </si>
+  <si>
+    <t>백송희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%86%A1%ED%9D%AC</t>
   </si>
   <si>
     <t>나이트워커</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>3474억 7196만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
-  </si>
-  <si>
-    <t>229경 4357조 2792억 6494만</t>
-  </si>
-  <si>
-    <t>난풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
-  </si>
-  <si>
-    <t>110경 9584조 8295억 323만</t>
-  </si>
-  <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>36경 5167조 3358억 777만</t>
-  </si>
-  <si>
-    <t>일월마녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>35경 1686조 8222억 1804만</t>
-  </si>
-  <si>
-    <t>송곧</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
-  </si>
-  <si>
-    <t>34경 1532조 2767억 2659만</t>
-  </si>
-  <si>
-    <t>메키존망섭종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%A1%B4%EB%A7%9D%EC%84%AD%EC%A2%85</t>
-  </si>
-  <si>
-    <t>25경 371조 1114억 5018만</t>
-  </si>
-  <si>
-    <t>로드숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
-  </si>
-  <si>
-    <t>23경 7221조 2621억 7072만</t>
-  </si>
-  <si>
-    <t>도당이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%8B%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>10경 264조 4680억 1217만</t>
-  </si>
-  <si>
-    <t>둄이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5경 6277조 7553억 6679만</t>
-  </si>
-  <si>
-    <t>태켱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
-  </si>
-  <si>
-    <t>5경 4조 3212억 1972만</t>
-  </si>
-  <si>
-    <t>진짜지존법사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>4경 4347조 9483억 3614만</t>
-  </si>
-  <si>
-    <t>다이사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>4경 214조 7053억 3240만</t>
-  </si>
-  <si>
-    <t>카지야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%A7%80%EC%95%BC</t>
-  </si>
-  <si>
-    <t>3경 7401조 5842억 2501만</t>
-  </si>
-  <si>
-    <t>똥으리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2경 8269조 1138억 6803만</t>
-  </si>
-  <si>
-    <t>즐처드셈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%90%EC%B2%98%EB%93%9C%EC%85%88</t>
-  </si>
-  <si>
-    <t>1경 9193조 9405억 4110만</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
-  </si>
-  <si>
-    <t>1경 2017조 6231억 5342만</t>
-  </si>
-  <si>
-    <t>피타입</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%ED%83%80%EC%9E%85</t>
-  </si>
-  <si>
-    <t>1경 1089조 2729억 3017만</t>
-  </si>
-  <si>
-    <t>고래털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%9E%98%ED%84%B8</t>
-  </si>
-  <si>
-    <t>1경 1043조 468억 1279만</t>
-  </si>
-  <si>
-    <t>대전월클</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A0%84%EC%9B%94%ED%81%B4</t>
-  </si>
-  <si>
-    <t>8667조 4778억 2318만</t>
-  </si>
-  <si>
-    <t>원순철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>8268조 3280억 1157만</t>
-  </si>
-  <si>
-    <t>OrOl유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=OrOl%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>8073조 6387억 8596만</t>
-  </si>
-  <si>
-    <t>YooU</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YooU</t>
-  </si>
-  <si>
-    <t>7873조 6623억 710만</t>
-  </si>
-  <si>
-    <t>기요코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EC%BD%94</t>
-  </si>
-  <si>
-    <t>7146조 7736억 709만</t>
-  </si>
-  <si>
-    <t>RaguS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RaguS</t>
-  </si>
-  <si>
-    <t>6682조 3954억 2551만</t>
-  </si>
-  <si>
-    <t>악전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
-  </si>
-  <si>
-    <t>5452조 9692억 8522만</t>
-  </si>
-  <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>5309조 7830억 3873만</t>
-  </si>
-  <si>
-    <t>강띵띵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
-  </si>
-  <si>
-    <t>5116조 9650억 1417만</t>
-  </si>
-  <si>
-    <t>앙음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>4674조 9709억 5567만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>4339조 6517억 4777만</t>
-  </si>
-  <si>
-    <t>박미쯔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
-  </si>
-  <si>
-    <t>3638조 832억 926만</t>
-  </si>
-  <si>
-    <t>과금X환불O</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%EA%B8%88X%ED%99%98%EB%B6%88O</t>
-  </si>
-  <si>
-    <t>201경 6240조 3323억 2172만</t>
-  </si>
-  <si>
-    <t>환불존망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%A1%B4%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>44경 4274조 258억 6942만</t>
-  </si>
-  <si>
-    <t>역삼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EC%82%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>38경 4102조 9598억 1650만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%88%ED%8E%80</t>
-  </si>
-  <si>
-    <t>25경 964조 6516억 1773만</t>
-  </si>
-  <si>
-    <t>아그리아스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B7%B8%EB%A6%AC%EC%95%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17경 6716조 9928억 4335만</t>
-  </si>
-  <si>
-    <t>쏘쏘하네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%98%EC%8F%98%ED%95%98%EB%84%A4</t>
-  </si>
-  <si>
-    <t>9경 4745조 8630억 756만</t>
-  </si>
-  <si>
-    <t>꼬꼬대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%BC%AC%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>6경 182조 4408억 4610만</t>
-  </si>
-  <si>
-    <t>또수요일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%88%98%EC%9A%94%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>5경 2600조 1148억 8098만</t>
-  </si>
-  <si>
-    <t>참OI슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%B8OI%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>5경 236조 646억 552만</t>
-  </si>
-  <si>
-    <t>방팀장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%ED%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>4경 5004조 2465억 8868만</t>
-  </si>
-  <si>
-    <t>록현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9D%ED%98%84</t>
-  </si>
-  <si>
-    <t>4경 4574조 6601억 3976만</t>
-  </si>
-  <si>
-    <t>유지애123</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A7%80%EC%95%A0123</t>
-  </si>
-  <si>
-    <t>3경 7163조 5986억 7271만</t>
-  </si>
-  <si>
-    <t>머스탱GT</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EC%8A%A4%ED%83%B1GT</t>
-  </si>
-  <si>
-    <t>2경 3918조 1097억 8937만</t>
-  </si>
-  <si>
-    <t>아랐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%9E%90</t>
-  </si>
-  <si>
-    <t>2경 1421조 7561억 3912만</t>
-  </si>
-  <si>
-    <t>응구7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%91%EA%B5%AC7</t>
-  </si>
-  <si>
-    <t>1경 8984조 9858억 2109만</t>
-  </si>
-  <si>
-    <t>아이츄크림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%B8%84%ED%81%AC%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1경 8699조 2219억 6776만</t>
-  </si>
-  <si>
-    <t>할게없다고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B2%8C%EC%97%86%EB%8B%A4%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>1경 4865조 3322억 3611만</t>
-  </si>
-  <si>
-    <t>웅선김</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%84%A0%EA%B9%80</t>
-  </si>
-  <si>
-    <t>1경 3758조 2869억 1064만</t>
-  </si>
-  <si>
-    <t>가루o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%A3%A8o</t>
-  </si>
-  <si>
-    <t>1경 3712조 6679억 9386만</t>
-  </si>
-  <si>
-    <t>정듄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%93%84</t>
-  </si>
-  <si>
-    <t>1경 1914조 7465억 5936만</t>
-  </si>
-  <si>
-    <t>한도100</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84100</t>
-  </si>
-  <si>
-    <t>1경 577조 7460억 2583만</t>
-  </si>
-  <si>
-    <t>반서님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%84%9C%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1경 336조 9852억 3626만</t>
-  </si>
-  <si>
-    <t>정슌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8A%8C</t>
-  </si>
-  <si>
-    <t>1경 228조 6678억 1890만</t>
-  </si>
-  <si>
-    <t>우유냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%83%A5</t>
-  </si>
-  <si>
-    <t>9865조 6616억 7883만</t>
-  </si>
-  <si>
-    <t>귀염둥이제제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%97%BC%EB%91%A5%EC%9D%B4%EC%A0%9C%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>8925조 2607억 2621만</t>
-  </si>
-  <si>
-    <t>zi존동길</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zi%EC%A1%B4%EB%8F%99%EA%B8%B8</t>
-  </si>
-  <si>
-    <t>7490조 7821억 148만</t>
-  </si>
-  <si>
-    <t>꼼맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>5917조 3261억 6493만</t>
-  </si>
-  <si>
-    <t>구름몽실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%84%EB%AA%BD%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>3364조 9732억 581만</t>
-  </si>
-  <si>
-    <t>스큐류바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%81%90%EB%A5%98%EB%B0%94</t>
-  </si>
-  <si>
-    <t>2979조 8758억 2072만</t>
-  </si>
-  <si>
-    <t>백정Hero</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%A0%95Hero</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2406조 3255억 8611만</t>
-  </si>
-  <si>
-    <t>노을준이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>867경 57조 6580억 1416만</t>
-  </si>
-  <si>
-    <t>노을뽀롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%BD%80%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>24경 2357조 755억 8065만</t>
-  </si>
-  <si>
-    <t>노을주의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%EC%9D%98</t>
-  </si>
-  <si>
-    <t>1경 3570조 5841억 5234만</t>
-  </si>
-  <si>
-    <t>노을구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>1경 2006조 5800억 5455만</t>
-  </si>
-  <si>
-    <t>아테나1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%85%8C%EB%82%981</t>
-  </si>
-  <si>
-    <t>4974조 4392억 583만</t>
-  </si>
-  <si>
-    <t>노을푸링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%91%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>3966조 1691억 7579만</t>
-  </si>
-  <si>
-    <t>카엘다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%B4%EC%97%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>3201조 5111억 5146만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8A%B9%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>2914조 4412억 9586만</t>
-  </si>
-  <si>
-    <t>노을치누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%B9%98%EB%88%84</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2767조 386억 7305만</t>
-  </si>
-  <si>
-    <t>노을새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>1964조 9445억 8574만</t>
-  </si>
-  <si>
-    <t>노을짭식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A7%AD%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>1331조 5725억 5976만</t>
-  </si>
-  <si>
-    <t>노을이즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%9D%B4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1326조 2553억 1494만</t>
-  </si>
-  <si>
-    <t>노을시아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%8B%9C%EC%95%84</t>
-  </si>
-  <si>
-    <t>1021조 9980억 6228만</t>
-  </si>
-  <si>
-    <t>속초피바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8D%EC%B4%88%ED%94%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>900조 2910억 8582만</t>
-  </si>
-  <si>
-    <t>노을주크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A3%BC%ED%81%AC</t>
-  </si>
-  <si>
-    <t>674조 4123억 5869만</t>
-  </si>
-  <si>
-    <t>노을쁨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%81%A8</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>546조 3660억 7935만</t>
-  </si>
-  <si>
-    <t>노을고래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B3%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>541조 8655억 3198만</t>
-  </si>
-  <si>
-    <t>햄숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>538조 449억 8619만</t>
-  </si>
-  <si>
-    <t>노을밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>532조 5168억 4079만</t>
-  </si>
-  <si>
-    <t>노을망령</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%9D%EB%A0%B9</t>
-  </si>
-  <si>
-    <t>526조 3520억 9707만</t>
-  </si>
-  <si>
-    <t>노을비츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%B9%84%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>455조 2759억 8543만</t>
-  </si>
-  <si>
-    <t>노을하온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%ED%95%98%EC%98%A8</t>
-  </si>
-  <si>
-    <t>443조 2023억 8749만</t>
-  </si>
-  <si>
-    <t>사자탈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9E%90%ED%83%88</t>
-  </si>
-  <si>
-    <t>432조 250억 8648만</t>
-  </si>
-  <si>
-    <t>노을둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>427조 4378억 6910만</t>
-  </si>
-  <si>
-    <t>노을막내</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%A7%89%EB%82%B4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>370조 9011억 6074만</t>
-  </si>
-  <si>
-    <t>노을준홍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%A4%80%ED%99%8D</t>
-  </si>
-  <si>
-    <t>293조 8643억 6821만</t>
-  </si>
-  <si>
-    <t>노을달빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8B%AC%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>285조 4216억 7957만</t>
-  </si>
-  <si>
-    <t>노을쿠키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EC%BF%A0%ED%82%A4</t>
-  </si>
-  <si>
-    <t>257조 5503억 4943만</t>
-  </si>
-  <si>
-    <t>노을도아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EB%8F%84%EC%95%84</t>
-  </si>
-  <si>
-    <t>233조 1654억 6639만</t>
-  </si>
-  <si>
-    <t>노을결빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%9D%84%EA%B2%B0%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>215조 3380억 1125만</t>
+    <t>90</t>
+  </si>
+  <si>
+    <t>748억 9315만</t>
+  </si>
+  <si>
+    <t>봐람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%90%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>윈드브레이커</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>42억 7861만</t>
   </si>
 </sst>
 </file>
@@ -2122,7 +2134,7 @@
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="24.7109375" customWidth="1"/>
-    <col min="11" max="11" width="50.7109375" customWidth="1"/>
+    <col min="11" max="11" width="47.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2229,22 +2241,22 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2252,40 +2264,40 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2293,28 +2305,28 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -2322,53 +2334,53 @@
       <c r="J5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2391,11 +2403,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2404,28 +2416,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2436,28 +2448,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2468,28 +2480,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2500,28 +2512,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2532,28 +2544,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2564,28 +2576,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2596,28 +2608,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2628,28 +2640,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2660,28 +2672,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2692,28 +2704,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2724,28 +2736,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2756,28 +2768,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2788,28 +2800,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2820,28 +2832,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2852,28 +2864,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2884,28 +2896,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2916,28 +2928,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2948,28 +2960,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2980,28 +2992,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3012,28 +3024,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3044,28 +3056,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3076,28 +3088,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3108,28 +3120,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3140,28 +3152,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3172,28 +3184,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3204,28 +3216,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3236,28 +3248,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3268,28 +3280,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3300,28 +3312,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3332,28 +3344,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3364,28 +3376,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3436,7 +3448,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -3449,28 +3461,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3481,28 +3493,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3513,28 +3525,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3545,28 +3557,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3577,28 +3589,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3609,28 +3621,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3641,28 +3653,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3673,28 +3685,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3705,28 +3717,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3737,28 +3749,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3769,28 +3781,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3801,28 +3813,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3833,28 +3845,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3865,28 +3877,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3897,28 +3909,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3929,28 +3941,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3961,28 +3973,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3993,28 +4005,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4025,28 +4037,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4057,28 +4069,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4089,28 +4101,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4121,28 +4133,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4153,28 +4165,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4185,28 +4197,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4217,28 +4229,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4249,28 +4261,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4281,28 +4293,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>179</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4313,28 +4325,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4345,28 +4357,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>291</v>
+        <v>173</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4377,28 +4389,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4409,28 +4421,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>300</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4494,28 +4506,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4523,31 +4535,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4555,31 +4567,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4587,31 +4599,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4619,31 +4631,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>312</v>
+        <v>225</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4651,31 +4663,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4683,31 +4695,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4715,31 +4727,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4747,31 +4759,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4779,31 +4791,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4811,31 +4823,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4843,31 +4855,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4875,31 +4887,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4907,31 +4919,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4939,31 +4951,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4971,31 +4983,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5003,31 +5015,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5035,31 +5047,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5067,31 +5079,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>353</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>353</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5099,31 +5111,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5131,31 +5143,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5163,31 +5175,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5195,31 +5207,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5227,31 +5239,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5259,31 +5271,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5291,31 +5303,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5323,31 +5335,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5355,31 +5367,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5387,31 +5399,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>277</v>
+        <v>179</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5419,31 +5431,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>379</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5451,31 +5463,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5530,7 +5542,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5539,28 +5551,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5568,962 +5580,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>394</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>379</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>110</v>
+        <v>404</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>360</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>411</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>171</v>
+        <v>404</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>411</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>394</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>424</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>411</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>404</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>404</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>188</v>
+        <v>411</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>312</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>200</v>
+        <v>440</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>188</v>
+        <v>440</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>188</v>
+        <v>424</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>277</v>
+        <v>424</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6575,7 +6587,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6584,28 +6596,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6613,266 +6625,266 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>502</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>502</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>503</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>504</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>505</v>
@@ -6884,475 +6896,475 @@
         <v>506</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>539</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>551</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>552</v>
@@ -7364,59 +7376,59 @@
         <v>553</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>558</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>559</v>
@@ -7428,91 +7440,91 @@
         <v>560</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>291</v>
+        <v>550</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>561</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>567</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>568</v>
@@ -7524,51 +7536,51 @@
         <v>569</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>74</v>
+        <v>570</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>291</v>
+        <v>571</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>100</v>
+        <v>575</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>291</v>
+        <v>576</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>1067경 905조 4945억 8899만</t>
+    <t>1073경 7739조 4056억 1700만</t>
   </si>
   <si>
     <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
@@ -101,7 +101,7 @@
     <t>설익은체리</t>
   </si>
   <si>
-    <t>2026.09.18</t>
+    <t>2026.09.19</t>
   </si>
   <si>
     <t>셀린느</t>
@@ -113,13 +113,13 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>33</t>
+    <t>34</t>
   </si>
   <si>
     <t>Lv.9</t>
   </si>
   <si>
-    <t>668경 6572조 6179억 6729만</t>
+    <t>673경 5292조 3781억 1219만</t>
   </si>
   <si>
     <t>문의 [혜영]</t>
@@ -140,7 +140,7 @@
     <t>28</t>
   </si>
   <si>
-    <t>783경 6190조 5721억 6339만</t>
+    <t>794경 8979조 6437억 9900만</t>
   </si>
   <si>
     <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
@@ -158,499 +158,499 @@
     <t>Scania 63</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>914경 1139조 6810억 8739만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>1432</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>4545조 5801억 7298만</t>
+  </si>
+  <si>
+    <t>길컨미참여 2일미접 추방입니다</t>
+  </si>
+  <si>
+    <t>이랑b</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>231경 7865조 5718억 420만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>229경 8495조 7258억 379만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>151경 4649조 5542억 9866만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>62경 4188조 2543억 3793만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>52경 9932조 7914억 9061만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>45경 5109조 8480억 2031만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>39경 1509조 7156억 9977만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>39경 863조 8820억 7662만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>35경 5866조 3798억 7180만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>22경 2514조 1356억 9157만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>21경 4753조 3765억 8338만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>18경 9870조 503억 9521만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>15경 5172조 196억 122만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>13경 2105조 4816억 1933만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>12경 7975조 8170억 5111만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>8경 1791조 1615억 2546만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 4972조 6974억 1981만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>7경 2382조 7642억 9212만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>5경 5478조 8492억 3032만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 4783조 8696억 6956만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>5경 90조 1569억 6839만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>수상구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2경 5422조 8458억 5094만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 3101조 7046억 6202만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 1802조 9715억 751만</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>1경 7395조 9535억 4782만</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>886경 2075조 5257억 6509만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
-    <t>promise</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>1422</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>4557조 7409억 1869만</t>
-  </si>
-  <si>
-    <t>길컨미참여 2일미접 추방입니다</t>
-  </si>
-  <si>
-    <t>이랑b</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>231경 7865조 5718억 420만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4405조 2903억 5532만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>9554조 6832억 9248만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>9288조 9444억 7420만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>8781조 4022억 5235만</t>
+  </si>
+  <si>
+    <t>빔냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>228경 131조 6916억 361만</t>
+  </si>
+  <si>
+    <t>MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
     <t>123</t>
   </si>
   <si>
-    <t>225경 1047조 968억 5458만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>151경 4609조 7545억 8786만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>62경 4188조 2543억 3793만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>52경 9932조 7914억 9061만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>39경 1509조 7156억 9977만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>39경 863조 8820억 7662만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>35경 5866조 3798억 7180만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>29경 7613조 5062억 2329만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>21경 5442조 4971억 3872만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>21경 4753조 3765억 8338만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>18경 7073조 8948억 5020만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>15경 3797조 2443억 3111만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>13경 2105조 4816억 1933만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>12경 7975조 8170억 5111만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>8경 1791조 1615억 2546만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>7경 4972조 6974억 1981만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>7경 2382조 7642억 9212만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>5경 5478조 8492억 3032만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 4783조 8696억 6956만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>4경 8648조 589억 330만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>수상구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>2경 5422조 8458억 5094만</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 612조 7974억 7642만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 8681조 1008억 7785만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>1경 6876조 6915억 91만</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4405조 2903억 5532만</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>9288조 9444억 7420만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9023조 9082억 1993만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>8781조 4022억 5235만</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>228경 131조 6916억 361만</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>82경 4332조 2590억 2998만</t>
+    <t>82경 5369조 9726억 1782만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -659,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>58경 828조 6734억 1419만</t>
+    <t>59경 8932조 8415억 8249만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>56경 8251조 4948억 4872만</t>
+    <t>57경 3507조 7593억 4456만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>44경 7429조 932억 1578만</t>
+    <t>45경 8209조 1749억 7786만</t>
   </si>
   <si>
     <t>뽀리빠</t>
@@ -686,7 +686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>26경 7842조 692억 1075만</t>
+    <t>26경 7923조 9367억 2199만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>13경 8586조 3568억 7252만</t>
+    <t>14경 9012조 3724억 7633만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>10경 4506조 7719억 7191만</t>
+    <t>10경 4572조 1841억 4875만</t>
   </si>
   <si>
     <t>약어</t>
@@ -752,7 +752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>9경 5132조 3135억 4804만</t>
+    <t>9경 5359조 4682억 7643만</t>
   </si>
   <si>
     <t>익맹이</t>
@@ -764,6 +764,15 @@
     <t>8경 4785조 8773억 3366만</t>
   </si>
   <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 8016조 2969억 4906만</t>
+  </si>
+  <si>
     <t>잼포즈</t>
   </si>
   <si>
@@ -773,15 +782,6 @@
     <t>7경 7727조 6633억 2044만</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 7689조 2024억 7915만</t>
-  </si>
-  <si>
     <t>니달리신</t>
   </si>
   <si>
@@ -815,7 +815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
   </si>
   <si>
-    <t>5경 7078조 5154억 5987만</t>
+    <t>5경 7118조 8624억 9362만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -833,7 +833,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 8800조 5458억 7439만</t>
+    <t>1경 9039조 4842억 7168만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -842,7 +842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>1경 6550조 8025억 4362만</t>
+    <t>1경 7314조 2207억 4772만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -866,7 +866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 2820조 5747억 3779만</t>
+    <t>1경 3148조 1561억 8499만</t>
   </si>
   <si>
     <t>아이스꾸임</t>
@@ -875,7 +875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>1경 2795조 2161억 6085만</t>
+    <t>1경 2802조 3487억 3746만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -884,7 +884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 2199조 4890억 2250만</t>
+    <t>1경 2301조 9332억 9820만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -893,7 +893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>9914조 2000억 5682만</t>
+    <t>1경 337조 3153억 1051만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -902,7 +902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>7721조 4388억 5016만</t>
+    <t>8232조 4493억 242만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -929,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>84경 1조 1044억 968만</t>
+    <t>90경 3185조 6632억 3331만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -947,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>34경 6366조 9101억 3776만</t>
+    <t>38경 2547조 725억 1408만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -974,7 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 625조 9816억 9415만</t>
+    <t>4경 682조 4926억 7612만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -983,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>3경 331조 1265억 4185만</t>
+    <t>3경 7501조 4810억 1910만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -992,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7088조 8412억 8766만</t>
+    <t>2경 7371조 6164억 9803만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -1001,7 +1001,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 6639조 8064억 7260만</t>
+    <t>2경 6643조 1644억 2769만</t>
+  </si>
+  <si>
+    <t>뚜뭉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2경 6457조 8392억 9501만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -1013,22 +1022,13 @@
     <t>2경 6384조 4873억 4507만</t>
   </si>
   <si>
-    <t>뚜뭉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2경 1696조 3168억 4846만</t>
-  </si>
-  <si>
     <t>못함</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 718조 8851억 7734만</t>
+    <t>2경 742조 2857억 4036만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -1037,7 +1037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
   </si>
   <si>
-    <t>1경 9483조 1803억 1728만</t>
+    <t>1경 9978조 6367억 977만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -1046,7 +1046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>1경 6865조 6744억 3142만</t>
+    <t>1경 6917조 3374억 106만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -1058,7 +1058,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1경 4773조 3232억 5495만</t>
+    <t>1경 4779조 306억 3189만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
@@ -1082,7 +1082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 453조 8183억 4245만</t>
+    <t>1경 635조 2650억 1514만</t>
   </si>
   <si>
     <t>서두희</t>
@@ -1100,7 +1100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>9337조 3662억 7305만</t>
+    <t>9513조 8454억 6327만</t>
   </si>
   <si>
     <t>회귀함</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>8893조 8717억 1835만</t>
+    <t>8909조 3670억 3402만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -1130,7 +1130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>8593조 2536억 2739만</t>
+    <t>8597조 9245억 476만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -1139,7 +1139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>7243조 8271억 2621만</t>
+    <t>7259조 2964억 6491만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -1148,7 +1148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>6317조 5640억 5211만</t>
+    <t>6318조 5165억 7942만</t>
   </si>
   <si>
     <t>수영하는수달</t>
@@ -1157,7 +1157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%98%81%ED%95%98%EB%8A%94%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>5154조 9765억 3925만</t>
+    <t>5324조 3153억 5702만</t>
   </si>
   <si>
     <t>빈수르</t>
@@ -1166,42 +1166,42 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
   </si>
   <si>
+    <t>4786조 4122억 4118만</t>
+  </si>
+  <si>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>4177조 5240억 1807만</t>
+  </si>
+  <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>871경 552조 7232억 3310만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>33경 9721조 7385억 4093만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>4776조 6629억 1855만</t>
-  </si>
-  <si>
-    <t>김보들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
-  </si>
-  <si>
-    <t>4177조 5240억 1807만</t>
-  </si>
-  <si>
-    <t>종리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>844경 9612조 4594억 781만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>32경 3920조 5622억 4687만</t>
-  </si>
-  <si>
-    <t>몰라츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
-  </si>
-  <si>
     <t>2경 6045조 2479억 642만</t>
   </si>
   <si>
@@ -1214,7 +1214,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 9093조 9092억 6631만</t>
+    <t>2경 440조 6317억 4970만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 2695조 2875억 7879만</t>
+    <t>1경 2729조 2891억 8769만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1244,7 +1244,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>2868조 1940억 5032만</t>
+    <t>3554조 1639억 2229만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1253,7 +1253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>2698조 6805억 2581만</t>
+    <t>2710조 8228억 7500만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1274,7 +1274,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>2155조 443억 5090만</t>
+    <t>2245조 6355억 8959만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1283,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>2122조 1292억 2655만</t>
+    <t>2212조 2512억 953만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1292,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>2021조 5911억 2973만</t>
+    <t>2024조 4348억 8577만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1313,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1173조 6985억 7512만</t>
+    <t>1189조 8336억 1449만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -1340,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>960조 1640억 2583만</t>
+    <t>974조 3283억 5846만</t>
   </si>
   <si>
     <t>푸들츄</t>
@@ -1379,7 +1379,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>328조 629억 6465만</t>
+    <t>333조 7361억 7776만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -1388,54 +1388,54 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
   </si>
   <si>
+    <t>286조 7407억 2949만</t>
+  </si>
+  <si>
+    <t>히히힣히힣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
+  </si>
+  <si>
+    <t>245조 7214억 8719만</t>
+  </si>
+  <si>
+    <t>주냥츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
+  </si>
+  <si>
+    <t>216조 9810억 9795만</t>
+  </si>
+  <si>
+    <t>도리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>209조 7743억 1108만</t>
+  </si>
+  <si>
+    <t>디나인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>154조 153억 4607만</t>
+  </si>
+  <si>
+    <t>새벽츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EC%B8%84</t>
+  </si>
+  <si>
     <t>107</t>
   </si>
   <si>
-    <t>286조 7407억 2949만</t>
-  </si>
-  <si>
-    <t>히히힣히힣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
-  </si>
-  <si>
-    <t>245조 7214억 8719만</t>
-  </si>
-  <si>
-    <t>도리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>209조 7743억 1108만</t>
-  </si>
-  <si>
-    <t>주냥츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
-  </si>
-  <si>
-    <t>194조 4121억 2176만</t>
-  </si>
-  <si>
-    <t>디나인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>154조 153억 4607만</t>
-  </si>
-  <si>
-    <t>새벽츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EC%B8%84</t>
-  </si>
-  <si>
     <t>152조 3767억 9006만</t>
   </si>
   <si>
@@ -1445,139 +1445,139 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%81%98</t>
   </si>
   <si>
+    <t>64조 3332억 4836만</t>
+  </si>
+  <si>
+    <t>비먀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
+  </si>
+  <si>
+    <t>52조 9807억 6147만</t>
+  </si>
+  <si>
+    <t>피카츄십볼트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>22조 4858억 9485만</t>
+  </si>
+  <si>
+    <t>결기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>453조 1445억 2085만</t>
+  </si>
+  <si>
+    <t>온우사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>401조 4910억 992만</t>
+  </si>
+  <si>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>388조 3356억 5423만</t>
+  </si>
+  <si>
+    <t>후추양조장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>340조 9115억 7451만</t>
+  </si>
+  <si>
+    <t>지존승준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
+  </si>
+  <si>
+    <t>325조 5858억 5659만</t>
+  </si>
+  <si>
+    <t>우댕이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>323조 9446억 4934만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>320조 7784억 8801만</t>
+  </si>
+  <si>
+    <t>말랑랑말이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>248조 8354억 6757만</t>
+  </si>
+  <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>240조 2358억 9713만</t>
+  </si>
+  <si>
+    <t>눅이마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>182조 4954억 1452만</t>
+  </si>
+  <si>
+    <t>성식대군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
-    <t>64조 3332억 4836만</t>
-  </si>
-  <si>
-    <t>비먀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
-  </si>
-  <si>
-    <t>52조 9807억 6147만</t>
-  </si>
-  <si>
-    <t>피카츄십볼트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>20조 7055억 4432만</t>
-  </si>
-  <si>
-    <t>결기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>453조 1445억 2085만</t>
-  </si>
-  <si>
-    <t>온우사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>398조 5534억 4596만</t>
-  </si>
-  <si>
-    <t>베르카암프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>385조 7861억 5418만</t>
-  </si>
-  <si>
-    <t>후추양조장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>340조 9115억 7451만</t>
-  </si>
-  <si>
-    <t>지존승준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
-  </si>
-  <si>
-    <t>325조 5858억 5659만</t>
-  </si>
-  <si>
-    <t>우댕이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>323조 9446억 4934만</t>
-  </si>
-  <si>
-    <t>썬콜원준띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>320조 7784억 8801만</t>
-  </si>
-  <si>
-    <t>규르트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%9C%EB%A5%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>276조 90억 5306만</t>
-  </si>
-  <si>
-    <t>말랑랑말이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>247조 4907억 2652만</t>
-  </si>
-  <si>
-    <t>날씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
-  </si>
-  <si>
-    <t>240조 770억 3731만</t>
-  </si>
-  <si>
-    <t>눅이마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>182조 201억 3448만</t>
-  </si>
-  <si>
-    <t>성식대군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>145조 6860억 7595만</t>
+    <t>161조 8864억 5487만</t>
+  </si>
+  <si>
+    <t>한로얘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
+  </si>
+  <si>
+    <t>151조 1623억 2787만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1586,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>133조 9945억 6561만</t>
+    <t>139조 9077억 5330만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>131조 2511억 3160만</t>
+    <t>133조 1121억 889만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1604,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>118조 7364억 9923만</t>
+    <t>118조 8267억 2860만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>112조 9092억 3143만</t>
+    <t>113조 6488억 5109만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
   </si>
   <si>
-    <t>110조 9463억 395만</t>
+    <t>111조 6057억 2348만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1631,7 +1631,16 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>95조 237억 6303만</t>
+    <t>95조 1677억 7312만</t>
+  </si>
+  <si>
+    <t>방제서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
+  </si>
+  <si>
+    <t>84조 6308억 8585만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1640,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>69조 1211억 4510만</t>
+    <t>72조 6018억 2359만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1652,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>52조 9393억 7842만</t>
+    <t>53조 1235억 4663만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1682,7 +1691,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>13조 5946억 6915만</t>
+    <t>14조 1291억 5727만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1706,19 +1715,10 @@
     <t>9조 9941억 7310만</t>
   </si>
   <si>
-    <t>돼지띠최덕배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%80%EB%9D%A0%EC%B5%9C%EB%8D%95%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>9조 6602억 4970만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>5조 847억 1973만</t>
+    <t>5조 1977억 4143만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1730,7 +1730,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>1조 2804억 8869만</t>
+    <t>1조 6057억 7688만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1745,7 +1745,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>748억 9315만</t>
+    <t>786억 464만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1760,7 +1760,7 @@
     <t>81</t>
   </si>
   <si>
-    <t>42억 7861만</t>
+    <t>44억 9831만</t>
   </si>
 </sst>
 </file>
@@ -2133,7 +2133,7 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" customWidth="1"/>
     <col min="11" max="11" width="47.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -2498,10 +2498,10 @@
         <v>67</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2512,28 +2512,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2544,28 +2544,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2576,28 +2576,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2608,28 +2608,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2640,28 +2640,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2672,28 +2672,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2704,28 +2704,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2736,28 +2736,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2768,28 +2768,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2800,28 +2800,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2832,28 +2832,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2864,28 +2864,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2896,28 +2896,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2928,28 +2928,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2960,28 +2960,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2992,28 +2992,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3024,28 +3024,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3056,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>23</v>
@@ -3065,19 +3065,19 @@
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3088,28 +3088,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3120,28 +3120,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3152,28 +3152,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3187,25 +3187,25 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3216,28 +3216,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3248,28 +3248,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3280,28 +3280,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3315,25 +3315,25 @@
         <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3344,28 +3344,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3376,28 +3376,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3496,25 +3496,25 @@
         <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3528,22 +3528,22 @@
         <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>207</v>
@@ -3557,7 +3557,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>208</v>
@@ -3572,10 +3572,10 @@
         <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>210</v>
@@ -3589,7 +3589,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>211</v>
@@ -3604,7 +3604,7 @@
         <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>68</v>
@@ -3621,7 +3621,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>214</v>
@@ -3636,10 +3636,10 @@
         <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>216</v>
@@ -3653,7 +3653,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>217</v>
@@ -3668,10 +3668,10 @@
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>219</v>
@@ -3685,7 +3685,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>220</v>
@@ -3700,10 +3700,10 @@
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>222</v>
@@ -3717,7 +3717,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>223</v>
@@ -3735,7 +3735,7 @@
         <v>225</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
@@ -3749,7 +3749,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>227</v>
@@ -3764,10 +3764,10 @@
         <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
@@ -3781,7 +3781,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>230</v>
@@ -3796,10 +3796,10 @@
         <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3813,7 +3813,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>233</v>
@@ -3828,10 +3828,10 @@
         <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3845,7 +3845,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>236</v>
@@ -3860,10 +3860,10 @@
         <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
@@ -3877,7 +3877,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>239</v>
@@ -3892,10 +3892,10 @@
         <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
@@ -3909,7 +3909,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
@@ -3924,10 +3924,10 @@
         <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3941,7 +3941,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3956,10 +3956,10 @@
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>247</v>
@@ -3973,7 +3973,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>248</v>
@@ -3988,10 +3988,10 @@
         <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>250</v>
@@ -4005,7 +4005,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>251</v>
@@ -4020,10 +4020,10 @@
         <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>253</v>
@@ -4037,7 +4037,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>254</v>
@@ -4055,7 +4055,7 @@
         <v>225</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>256</v>
@@ -4069,7 +4069,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>257</v>
@@ -4084,10 +4084,10 @@
         <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>259</v>
@@ -4101,7 +4101,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>260</v>
@@ -4116,10 +4116,10 @@
         <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>262</v>
@@ -4133,7 +4133,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -4148,10 +4148,10 @@
         <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>265</v>
@@ -4165,7 +4165,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>266</v>
@@ -4180,10 +4180,10 @@
         <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>268</v>
@@ -4197,7 +4197,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>269</v>
@@ -4212,10 +4212,10 @@
         <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>271</v>
@@ -4244,10 +4244,10 @@
         <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>274</v>
@@ -4261,7 +4261,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>275</v>
@@ -4276,10 +4276,10 @@
         <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>277</v>
@@ -4293,7 +4293,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>32</v>
@@ -4305,13 +4305,13 @@
         <v>278</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>279</v>
@@ -4325,7 +4325,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>280</v>
@@ -4340,10 +4340,10 @@
         <v>66</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4372,10 +4372,10 @@
         <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>285</v>
@@ -4389,7 +4389,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>286</v>
@@ -4404,10 +4404,10 @@
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>288</v>
@@ -4421,7 +4421,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>289</v>
@@ -4436,10 +4436,10 @@
         <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>291</v>
@@ -4553,7 +4553,7 @@
         <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>68</v>
@@ -4585,10 +4585,10 @@
         <v>66</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>297</v>
@@ -4602,7 +4602,7 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>298</v>
@@ -4617,10 +4617,10 @@
         <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>300</v>
@@ -4634,7 +4634,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>301</v>
@@ -4652,7 +4652,7 @@
         <v>225</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>303</v>
@@ -4666,7 +4666,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>304</v>
@@ -4681,10 +4681,10 @@
         <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>306</v>
@@ -4698,7 +4698,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>307</v>
@@ -4713,10 +4713,10 @@
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>309</v>
@@ -4730,7 +4730,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>310</v>
@@ -4745,10 +4745,10 @@
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>312</v>
@@ -4762,7 +4762,7 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>313</v>
@@ -4777,10 +4777,10 @@
         <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>315</v>
@@ -4794,7 +4794,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>316</v>
@@ -4809,10 +4809,10 @@
         <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>318</v>
@@ -4826,7 +4826,7 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>319</v>
@@ -4841,10 +4841,10 @@
         <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>321</v>
@@ -4858,7 +4858,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>322</v>
@@ -4876,7 +4876,7 @@
         <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>324</v>
@@ -4890,7 +4890,7 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>325</v>
@@ -4905,10 +4905,10 @@
         <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>327</v>
@@ -4922,7 +4922,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>328</v>
@@ -4937,10 +4937,10 @@
         <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>330</v>
@@ -4954,7 +4954,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>331</v>
@@ -4969,10 +4969,10 @@
         <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>333</v>
@@ -4986,7 +4986,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>334</v>
@@ -5004,7 +5004,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>336</v>
@@ -5018,7 +5018,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>337</v>
@@ -5033,10 +5033,10 @@
         <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>339</v>
@@ -5050,7 +5050,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>340</v>
@@ -5068,7 +5068,7 @@
         <v>342</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>343</v>
@@ -5082,7 +5082,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
@@ -5094,13 +5094,13 @@
         <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>345</v>
@@ -5114,7 +5114,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>346</v>
@@ -5129,10 +5129,10 @@
         <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>348</v>
@@ -5146,7 +5146,7 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>349</v>
@@ -5161,10 +5161,10 @@
         <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>351</v>
@@ -5178,7 +5178,7 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>352</v>
@@ -5193,10 +5193,10 @@
         <v>66</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>354</v>
@@ -5210,7 +5210,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>355</v>
@@ -5225,10 +5225,10 @@
         <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>357</v>
@@ -5242,7 +5242,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>358</v>
@@ -5257,7 +5257,7 @@
         <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>360</v>
@@ -5289,10 +5289,10 @@
         <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>364</v>
@@ -5306,7 +5306,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>365</v>
@@ -5321,10 +5321,10 @@
         <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>367</v>
@@ -5338,7 +5338,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>368</v>
@@ -5353,10 +5353,10 @@
         <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>370</v>
@@ -5370,7 +5370,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>371</v>
@@ -5385,7 +5385,7 @@
         <v>66</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>360</v>
@@ -5417,10 +5417,10 @@
         <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>376</v>
@@ -5434,7 +5434,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>377</v>
@@ -5449,13 +5449,13 @@
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5466,28 +5466,28 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="F31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5586,25 +5586,25 @@
         <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5624,19 +5624,19 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5647,16 +5647,16 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>66</v>
@@ -5665,7 +5665,7 @@
         <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>391</v>
@@ -5679,7 +5679,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>392</v>
@@ -5694,7 +5694,7 @@
         <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>394</v>
@@ -5711,7 +5711,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>396</v>
@@ -5726,10 +5726,10 @@
         <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>398</v>
@@ -5743,7 +5743,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>399</v>
@@ -5758,10 +5758,10 @@
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>401</v>
@@ -5775,7 +5775,7 @@
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>402</v>
@@ -5790,7 +5790,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>404</v>
@@ -5807,7 +5807,7 @@
         <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>406</v>
@@ -5822,7 +5822,7 @@
         <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>360</v>
@@ -5839,7 +5839,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>409</v>
@@ -5854,7 +5854,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>411</v>
@@ -5871,7 +5871,7 @@
         <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>413</v>
@@ -5886,7 +5886,7 @@
         <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>404</v>
@@ -5903,7 +5903,7 @@
         <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>416</v>
@@ -5935,7 +5935,7 @@
         <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>419</v>
@@ -5950,7 +5950,7 @@
         <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>394</v>
@@ -5967,7 +5967,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>422</v>
@@ -5982,7 +5982,7 @@
         <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>424</v>
@@ -5999,7 +5999,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>426</v>
@@ -6014,7 +6014,7 @@
         <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>411</v>
@@ -6031,7 +6031,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>429</v>
@@ -6046,7 +6046,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>404</v>
@@ -6063,7 +6063,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>432</v>
@@ -6078,7 +6078,7 @@
         <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>404</v>
@@ -6095,7 +6095,7 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>435</v>
@@ -6110,7 +6110,7 @@
         <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>411</v>
@@ -6127,7 +6127,7 @@
         <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>438</v>
@@ -6142,7 +6142,7 @@
         <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>440</v>
@@ -6159,7 +6159,7 @@
         <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>442</v>
@@ -6174,7 +6174,7 @@
         <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>440</v>
@@ -6191,7 +6191,7 @@
         <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>445</v>
@@ -6206,7 +6206,7 @@
         <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>424</v>
@@ -6223,7 +6223,7 @@
         <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>448</v>
@@ -6255,7 +6255,7 @@
         <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>451</v>
@@ -6270,13 +6270,13 @@
         <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6287,28 +6287,28 @@
         <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="F24" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6322,25 +6322,25 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6351,28 +6351,28 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6383,28 +6383,28 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6415,25 +6415,25 @@
         <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>469</v>
@@ -6462,13 +6462,13 @@
         <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6479,28 +6479,28 @@
         <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6511,28 +6511,28 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6631,25 +6631,25 @@
         <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6663,25 +6663,25 @@
         <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6692,28 +6692,28 @@
         <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6724,28 +6724,28 @@
         <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6756,16 +6756,16 @@
         <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>66</v>
@@ -6777,7 +6777,7 @@
         <v>440</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6788,28 +6788,28 @@
         <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6820,28 +6820,28 @@
         <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>424</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6852,28 +6852,28 @@
         <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6884,28 +6884,28 @@
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="F10" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>440</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6916,28 +6916,28 @@
         <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6948,25 +6948,25 @@
         <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>513</v>
@@ -6980,7 +6980,7 @@
         <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>514</v>
@@ -6995,10 +6995,10 @@
         <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>516</v>
@@ -7012,7 +7012,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>517</v>
@@ -7027,10 +7027,10 @@
         <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>519</v>
@@ -7044,7 +7044,7 @@
         <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>520</v>
@@ -7059,10 +7059,10 @@
         <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>522</v>
@@ -7076,7 +7076,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>523</v>
@@ -7091,10 +7091,10 @@
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>525</v>
@@ -7108,7 +7108,7 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>526</v>
@@ -7126,7 +7126,7 @@
         <v>67</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>528</v>
@@ -7140,7 +7140,7 @@
         <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>529</v>
@@ -7158,7 +7158,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>531</v>
@@ -7172,7 +7172,7 @@
         <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>532</v>
@@ -7187,10 +7187,10 @@
         <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>534</v>
@@ -7204,7 +7204,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>535</v>
@@ -7219,10 +7219,10 @@
         <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>537</v>
@@ -7236,7 +7236,7 @@
         <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>538</v>
@@ -7251,13 +7251,13 @@
         <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7268,25 +7268,25 @@
         <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>544</v>
@@ -7300,7 +7300,7 @@
         <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>545</v>
@@ -7315,10 +7315,10 @@
         <v>66</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>547</v>
@@ -7332,7 +7332,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>548</v>
@@ -7347,13 +7347,13 @@
         <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7367,25 +7367,25 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7396,25 +7396,25 @@
         <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>558</v>
@@ -7428,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>559</v>
@@ -7443,10 +7443,10 @@
         <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>561</v>
@@ -7460,7 +7460,7 @@
         <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>54</v>
@@ -7472,13 +7472,13 @@
         <v>562</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>563</v>
@@ -7507,7 +7507,7 @@
         <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>566</v>
@@ -7524,7 +7524,7 @@
         <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>568</v>
@@ -7556,7 +7556,7 @@
         <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>573</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="579">
   <si>
     <t>guild_name</t>
   </si>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>1073경 7739조 4056억 1700만</t>
+    <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
     <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
@@ -101,7 +101,7 @@
     <t>설익은체리</t>
   </si>
   <si>
-    <t>2026.09.19</t>
+    <t>2026.09.20</t>
   </si>
   <si>
     <t>셀린느</t>
@@ -113,13 +113,13 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>34</t>
+    <t>33</t>
   </si>
   <si>
     <t>Lv.9</t>
   </si>
   <si>
-    <t>673경 5292조 3781억 1219만</t>
+    <t>677경 9011조 3320억 5240만</t>
   </si>
   <si>
     <t>문의 [혜영]</t>
@@ -140,7 +140,7 @@
     <t>28</t>
   </si>
   <si>
-    <t>794경 8979조 6437억 9900만</t>
+    <t>795경 1983조 1944억 1870만</t>
   </si>
   <si>
     <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
@@ -164,7 +164,7 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>914경 1139조 6810억 8739만</t>
+    <t>914경 1847조 7200억 8300만</t>
   </si>
   <si>
     <t>퐁이츄</t>
@@ -179,13 +179,13 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>1432</t>
+    <t>1433</t>
   </si>
   <si>
     <t>30위</t>
   </si>
   <si>
-    <t>4545조 5801억 7298만</t>
+    <t>4616조 2781억 2722만</t>
   </si>
   <si>
     <t>길컨미참여 2일미접 추방입니다</t>
@@ -221,36 +221,36 @@
     <t>1</t>
   </si>
   <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>239경 3650조 664억 5621만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>해물만두야</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
     <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
-  </si>
-  <si>
-    <t>229경 8495조 7258억 379만</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -263,7 +263,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>151경 4649조 5542억 9866만</t>
+    <t>151경 5004조 4630억 4973만</t>
   </si>
   <si>
     <t>4</t>
@@ -323,7 +323,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>39경 1509조 7156억 9977만</t>
+    <t>39경 4856조 4335억 8984만</t>
   </si>
   <si>
     <t>8</t>
@@ -377,7 +377,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>22경 2514조 1356억 9157만</t>
+    <t>22경 2622조 1388억 6246만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,16 +410,28 @@
     <t>14</t>
   </si>
   <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>18경 3564조 735억 3511만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>졸귀탱이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>15경 5172조 196억 122만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>15경 5795조 8588억 6810만</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -431,18 +443,6 @@
     <t>13경 2105조 4816억 1933만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>12경 7975조 8170억 5111만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -521,7 +521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>5경 90조 1569억 6839만</t>
+    <t>5경 3005조 1147억 1318만</t>
   </si>
   <si>
     <t>23</t>
@@ -593,6 +593,18 @@
     <t>1경 4405조 2903억 5532만</t>
   </si>
   <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>9562조 1082억 7865만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>읏코츠</t>
   </si>
   <si>
@@ -602,18 +614,6 @@
     <t>9554조 6832억 9248만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>9288조 9444억 7420만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -635,291 +635,294 @@
     <t>신궁</t>
   </si>
   <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>230경 375조 6847억 3301만</t>
+  </si>
+  <si>
+    <t>MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>82경 6629조 1011억 3884만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>59경 8932조 8415억 8249만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>58경 2451조 9309억 7663만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>45경 9931조 1583억 3973만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>26경 7953조 6509억 6286만</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>26경 7923조 9367억 2199만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>25경 4823조 3360억 295만</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>15경 857조 7736억 9512만</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>10경 4931조 5654억 7685만</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>10경 421조 9052억 6144만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>9경 7717조 5279억 6925만</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>9경 7577조 4960억 8311만</t>
+  </si>
+  <si>
+    <t>익맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8경 5493조 5674억 6937만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>7경 8676조 4971억 4482만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 8132조 1663억 9724만</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4934조 151억 6468만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>5경 8774조 7748억 8940만</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>5경 7132조 4680억 8461만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1경 9039조 4842억 7168만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>1경 7944조 8437억 7238만</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 5275조 752억 3008만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1경 4618조 2500억 6149만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 3784조 6932억 6395만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>1경 3172조 192억 1384만</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1경 2961조 5558억 3160만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>1경 337조 3153억 1051만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>8232조 4493억 242만</t>
+  </si>
+  <si>
+    <t>껌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>300경 9676조 7164억 5367만</t>
+  </si>
+  <si>
+    <t>달하나별하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
-    <t>228경 131조 6916억 361만</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>82경 5369조 9726억 1782만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>59경 8932조 8415억 8249만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>57경 3507조 7593억 4456만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>45경 8209조 1749억 7786만</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>26경 7923조 9367억 2199만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>26경 4824조 3993억 8632만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>24경 9930조 6612억 5723만</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>14경 9012조 3724억 7633만</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>10경 4572조 1841억 4875만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>9경 7717조 5279억 6925만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>9경 7134조 3747억 7858만</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>9경 5359조 4682억 7643만</t>
-  </si>
-  <si>
-    <t>익맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8경 4785조 8773억 3366만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 8016조 2969억 4906만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>7경 7727조 6633억 2044만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4885조 3111억 7395만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>5경 8774조 7748억 8940만</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>5경 7118조 8624억 9362만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>5경 5228조 9003억 4099만</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 9039조 4842억 7168만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 7314조 2207억 4772만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 5275조 752억 3008만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 4618조 2500억 6149만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>1경 3148조 1561억 8499만</t>
-  </si>
-  <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1경 2802조 3487억 3746만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 2301조 9332억 9820만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>1경 337조 3153억 1051만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>8232조 4493억 242만</t>
-  </si>
-  <si>
-    <t>껌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>300경 9676조 7164억 5367만</t>
-  </si>
-  <si>
-    <t>달하나별하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
     <t>223경 1874조 2497억 5686만</t>
   </si>
   <si>
@@ -956,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 5556조 3066억 7866만</t>
+    <t>22경 6681조 2757억 8928만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -974,7 +977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 682조 4926억 7612만</t>
+    <t>4경 685조 7578억 9730만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -983,7 +986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>3경 7501조 4810억 1910만</t>
+    <t>3경 8203조 7807억 7240만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -992,7 +995,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7371조 6164억 9803만</t>
+    <t>2경 7459조 1601억 6637만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -1001,7 +1004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 6643조 1644억 2769만</t>
+    <t>2경 6665조 109억 335만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -1028,7 +1031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 742조 2857억 4036만</t>
+    <t>2경 780조 6603억 1331만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -1046,7 +1049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>1경 6917조 3374억 106만</t>
+    <t>1경 6935조 2825억 2842만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -1103,6 +1106,15 @@
     <t>9513조 8454억 6327만</t>
   </si>
   <si>
+    <t>희다차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>9178조 6185억 2422만</t>
+  </si>
+  <si>
     <t>회귀함</t>
   </si>
   <si>
@@ -1115,22 +1127,13 @@
     <t>9024조 7811억 8626만</t>
   </si>
   <si>
-    <t>희다차</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
-  </si>
-  <si>
-    <t>8909조 3670억 3402만</t>
-  </si>
-  <si>
     <t>널꼬라봐</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>8597조 9245억 476만</t>
+    <t>8602조 5959억 6037만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -1160,6 +1163,15 @@
     <t>5324조 3153억 5702만</t>
   </si>
   <si>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>4910조 9077억 6257만</t>
+  </si>
+  <si>
     <t>빈수르</t>
   </si>
   <si>
@@ -1169,15 +1181,6 @@
     <t>4786조 4122억 4118만</t>
   </si>
   <si>
-    <t>김보들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
-  </si>
-  <si>
-    <t>4177조 5240억 1807만</t>
-  </si>
-  <si>
     <t>종리츄</t>
   </si>
   <si>
@@ -1214,7 +1217,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2경 440조 6317억 4970만</t>
+    <t>2경 842조 7593억 4321만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1223,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 2729조 2891억 8769만</t>
+    <t>1경 2752조 8702억 8273만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1253,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>2710조 8228억 7500만</t>
+    <t>2761조 6694억 8911만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1274,7 +1277,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>2245조 6355억 8959만</t>
+    <t>2370조 8947억 8831만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1292,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>2024조 4348억 8577만</t>
+    <t>2029조 6208억 9762만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1313,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1189조 8336억 1449만</t>
+    <t>1218조 6963억 8867만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -1340,7 +1343,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>974조 3283억 5846만</t>
+    <t>985조 433억 9200만</t>
   </si>
   <si>
     <t>푸들츄</t>
@@ -1349,18 +1352,18 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
+    <t>856조 2452억 7572만</t>
+  </si>
+  <si>
+    <t>루린츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
+  </si>
+  <si>
     <t>108</t>
   </si>
   <si>
-    <t>836조 8013억 5457만</t>
-  </si>
-  <si>
-    <t>루린츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
-  </si>
-  <si>
     <t>525조 7616억 9510만</t>
   </si>
   <si>
@@ -1382,6 +1385,15 @@
     <t>333조 7361억 7776만</t>
   </si>
   <si>
+    <t>히히힣히힣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
+  </si>
+  <si>
+    <t>287조 4507억 9033만</t>
+  </si>
+  <si>
     <t>하치츄</t>
   </si>
   <si>
@@ -1391,15 +1403,6 @@
     <t>286조 7407억 2949만</t>
   </si>
   <si>
-    <t>히히힣히힣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
-  </si>
-  <si>
-    <t>245조 7214억 8719만</t>
-  </si>
-  <si>
     <t>주냥츄</t>
   </si>
   <si>
@@ -1466,7 +1469,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>22조 4858억 9485만</t>
+    <t>22조 4995억 1676만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1493,7 +1496,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
   </si>
   <si>
-    <t>388조 3356억 5423만</t>
+    <t>397조 7126억 7953만</t>
+  </si>
+  <si>
+    <t>우댕이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>347조 342억 4183만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1514,15 +1526,6 @@
     <t>325조 5858억 5659만</t>
   </si>
   <si>
-    <t>우댕이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>323조 9446억 4934만</t>
-  </si>
-  <si>
     <t>썬콜원준띠</t>
   </si>
   <si>
@@ -1538,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>248조 8354억 6757만</t>
+    <t>250조 3505억 7807만</t>
   </si>
   <si>
     <t>날씬</t>
@@ -1547,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>240조 2358억 9713만</t>
+    <t>248조 4862억 2013만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1556,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
   </si>
   <si>
-    <t>182조 4954억 1452만</t>
+    <t>182조 6335억 7631만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1568,7 +1571,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>161조 8864억 5487만</t>
+    <t>169조 2583억 4467만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1577,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
   </si>
   <si>
-    <t>151조 1623억 2787만</t>
+    <t>155조 5567억 5475만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1595,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>133조 1121억 889만</t>
+    <t>133조 4591억 1064만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1607,22 +1610,22 @@
     <t>118조 8267억 2860만</t>
   </si>
   <si>
+    <t>버미겨리0</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
+  </si>
+  <si>
+    <t>116조 4642억 5559만</t>
+  </si>
+  <si>
     <t>벵글</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>113조 6488억 5109만</t>
-  </si>
-  <si>
-    <t>버미겨리0</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
-  </si>
-  <si>
-    <t>111조 6057억 2348만</t>
+    <t>113조 8190억 3005만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1631,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>95조 1677억 7312만</t>
+    <t>103조 3846억 4513만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1640,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>84조 6308억 8585만</t>
+    <t>84조 9553억 6854만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1649,7 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>72조 6018억 2359만</t>
+    <t>72조 6579억 550만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1661,7 +1664,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>53조 1235억 4663만</t>
+    <t>53조 2514억 7734만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1688,37 +1691,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
   </si>
   <si>
+    <t>14조 1291억 5727만</t>
+  </si>
+  <si>
+    <t>개념독점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%85%90%EB%8F%85%EC%A0%90</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>12조 1853억 8318만</t>
+  </si>
+  <si>
+    <t>상혀닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
+  </si>
+  <si>
+    <t>10조 2535억 8036만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>14조 1291억 5727만</t>
-  </si>
-  <si>
-    <t>상혀닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>10조 2535억 8036만</t>
-  </si>
-  <si>
-    <t>개념독점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%85%90%EB%8F%85%EC%A0%90</t>
-  </si>
-  <si>
-    <t>9조 9941억 7310만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
-  </si>
-  <si>
-    <t>5조 1977억 4143만</t>
+    <t>5조 2162억 4583만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1727,10 +1730,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%98%84%EB%B9%A0%EB%8D%9C</t>
   </si>
   <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 6057억 7688만</t>
+    <t>98</t>
+  </si>
+  <si>
+    <t>1조 8541억 6059만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1742,10 +1745,10 @@
     <t>나이트워커</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>786억 464만</t>
+    <t>92</t>
+  </si>
+  <si>
+    <t>808억 5077만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -2818,7 +2821,7 @@
         <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>121</v>
@@ -2914,7 +2917,7 @@
         <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>133</v>
@@ -2946,7 +2949,7 @@
         <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>137</v>
@@ -3327,7 +3330,7 @@
         <v>66</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>178</v>
@@ -3359,7 +3362,7 @@
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>178</v>
@@ -3668,10 +3671,10 @@
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>219</v>
@@ -3700,7 +3703,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>111</v>
@@ -3828,10 +3831,10 @@
         <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3860,10 +3863,10 @@
         <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
@@ -3927,7 +3930,7 @@
         <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3956,7 +3959,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>147</v>
@@ -3988,7 +3991,7 @@
         <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>147</v>
@@ -4247,7 +4250,7 @@
         <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>274</v>
@@ -4296,25 +4299,25 @@
         <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>32</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4328,16 +4331,16 @@
         <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>280</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>281</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>77</v>
@@ -4375,7 +4378,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>285</v>
@@ -4588,10 +4591,10 @@
         <v>201</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4605,13 +4608,13 @@
         <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>66</v>
@@ -4623,7 +4626,7 @@
         <v>206</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4637,13 +4640,13 @@
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>66</v>
@@ -4655,7 +4658,7 @@
         <v>206</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4669,13 +4672,13 @@
         <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>66</v>
@@ -4687,7 +4690,7 @@
         <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4701,13 +4704,13 @@
         <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>66</v>
@@ -4719,7 +4722,7 @@
         <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4733,13 +4736,13 @@
         <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>66</v>
@@ -4751,7 +4754,7 @@
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4765,13 +4768,13 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>66</v>
@@ -4783,7 +4786,7 @@
         <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4797,13 +4800,13 @@
         <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>66</v>
@@ -4815,7 +4818,7 @@
         <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4829,13 +4832,13 @@
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>66</v>
@@ -4847,7 +4850,7 @@
         <v>172</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4861,13 +4864,13 @@
         <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>66</v>
@@ -4879,7 +4882,7 @@
         <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4893,13 +4896,13 @@
         <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>66</v>
@@ -4911,7 +4914,7 @@
         <v>168</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4925,13 +4928,13 @@
         <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>66</v>
@@ -4943,7 +4946,7 @@
         <v>172</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4957,13 +4960,13 @@
         <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>66</v>
@@ -4975,7 +4978,7 @@
         <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4989,13 +4992,13 @@
         <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
@@ -5007,7 +5010,7 @@
         <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5021,13 +5024,13 @@
         <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>66</v>
@@ -5039,7 +5042,7 @@
         <v>172</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5053,25 +5056,25 @@
         <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5091,7 +5094,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>155</v>
@@ -5103,7 +5106,7 @@
         <v>172</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5117,13 +5120,13 @@
         <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>66</v>
@@ -5135,7 +5138,7 @@
         <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5149,13 +5152,13 @@
         <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>66</v>
@@ -5167,7 +5170,7 @@
         <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5181,13 +5184,13 @@
         <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>66</v>
@@ -5199,7 +5202,7 @@
         <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5213,13 +5216,13 @@
         <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
@@ -5231,7 +5234,7 @@
         <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5245,22 +5248,22 @@
         <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>360</v>
+        <v>172</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>361</v>
@@ -5289,13 +5292,13 @@
         <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>172</v>
+        <v>364</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5309,13 +5312,13 @@
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>66</v>
@@ -5327,7 +5330,7 @@
         <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5341,13 +5344,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>66</v>
@@ -5359,7 +5362,7 @@
         <v>178</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5373,13 +5376,13 @@
         <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>66</v>
@@ -5388,10 +5391,10 @@
         <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5405,13 +5408,13 @@
         <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>66</v>
@@ -5423,7 +5426,7 @@
         <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5437,25 +5440,25 @@
         <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5469,25 +5472,25 @@
         <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5586,13 +5589,13 @@
         <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>66</v>
@@ -5604,7 +5607,7 @@
         <v>68</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5624,7 +5627,7 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>155</v>
@@ -5636,7 +5639,7 @@
         <v>142</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5650,13 +5653,13 @@
         <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>66</v>
@@ -5665,10 +5668,10 @@
         <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5682,13 +5685,13 @@
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>66</v>
@@ -5697,10 +5700,10 @@
         <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5714,13 +5717,13 @@
         <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>66</v>
@@ -5732,7 +5735,7 @@
         <v>178</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5746,13 +5749,13 @@
         <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>66</v>
@@ -5761,10 +5764,10 @@
         <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5778,13 +5781,13 @@
         <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>66</v>
@@ -5793,10 +5796,10 @@
         <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5810,13 +5813,13 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>66</v>
@@ -5825,10 +5828,10 @@
         <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5842,13 +5845,13 @@
         <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>66</v>
@@ -5857,10 +5860,10 @@
         <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5874,13 +5877,13 @@
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>66</v>
@@ -5889,10 +5892,10 @@
         <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5906,25 +5909,25 @@
         <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5938,13 +5941,13 @@
         <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>66</v>
@@ -5953,10 +5956,10 @@
         <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5970,13 +5973,13 @@
         <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>66</v>
@@ -5985,10 +5988,10 @@
         <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6002,13 +6005,13 @@
         <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>66</v>
@@ -6017,10 +6020,10 @@
         <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6034,13 +6037,13 @@
         <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
@@ -6049,10 +6052,10 @@
         <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6066,13 +6069,13 @@
         <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>66</v>
@@ -6081,10 +6084,10 @@
         <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6098,13 +6101,13 @@
         <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>66</v>
@@ -6113,10 +6116,10 @@
         <v>201</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6130,13 +6133,13 @@
         <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>66</v>
@@ -6145,7 +6148,7 @@
         <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>441</v>
@@ -6177,10 +6180,10 @@
         <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6194,13 +6197,13 @@
         <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>66</v>
@@ -6209,10 +6212,10 @@
         <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6226,13 +6229,13 @@
         <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>66</v>
@@ -6241,10 +6244,10 @@
         <v>225</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6258,13 +6261,13 @@
         <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
@@ -6273,10 +6276,10 @@
         <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6290,13 +6293,13 @@
         <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>66</v>
@@ -6305,10 +6308,10 @@
         <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6322,13 +6325,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
@@ -6337,10 +6340,10 @@
         <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6354,13 +6357,13 @@
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>66</v>
@@ -6369,10 +6372,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6386,13 +6389,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>66</v>
@@ -6401,10 +6404,10 @@
         <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6418,13 +6421,13 @@
         <v>183</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>66</v>
@@ -6433,10 +6436,10 @@
         <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6450,13 +6453,13 @@
         <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>66</v>
@@ -6465,10 +6468,10 @@
         <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6482,13 +6485,13 @@
         <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>66</v>
@@ -6497,10 +6500,10 @@
         <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6514,13 +6517,13 @@
         <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>66</v>
@@ -6529,10 +6532,10 @@
         <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6631,13 +6634,13 @@
         <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>66</v>
@@ -6646,10 +6649,10 @@
         <v>141</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6663,13 +6666,13 @@
         <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>66</v>
@@ -6678,10 +6681,10 @@
         <v>201</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6695,13 +6698,13 @@
         <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>66</v>
@@ -6710,10 +6713,10 @@
         <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6727,25 +6730,25 @@
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6759,25 +6762,25 @@
         <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6791,25 +6794,25 @@
         <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6823,13 +6826,13 @@
         <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>66</v>
@@ -6838,10 +6841,10 @@
         <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6855,13 +6858,13 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>66</v>
@@ -6870,10 +6873,10 @@
         <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6887,13 +6890,13 @@
         <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>66</v>
@@ -6902,10 +6905,10 @@
         <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6919,13 +6922,13 @@
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>66</v>
@@ -6934,10 +6937,10 @@
         <v>141</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6951,13 +6954,13 @@
         <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>66</v>
@@ -6966,10 +6969,10 @@
         <v>120</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6983,13 +6986,13 @@
         <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>66</v>
@@ -6998,10 +7001,10 @@
         <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7015,13 +7018,13 @@
         <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>66</v>
@@ -7030,10 +7033,10 @@
         <v>141</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7047,13 +7050,13 @@
         <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>66</v>
@@ -7062,10 +7065,10 @@
         <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7079,13 +7082,13 @@
         <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
@@ -7094,10 +7097,10 @@
         <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7111,13 +7114,13 @@
         <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>66</v>
@@ -7126,10 +7129,10 @@
         <v>67</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7143,13 +7146,13 @@
         <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>66</v>
@@ -7158,10 +7161,10 @@
         <v>67</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7175,13 +7178,13 @@
         <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>66</v>
@@ -7190,10 +7193,10 @@
         <v>141</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7207,13 +7210,13 @@
         <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>66</v>
@@ -7222,10 +7225,10 @@
         <v>177</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7239,13 +7242,13 @@
         <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>66</v>
@@ -7254,10 +7257,10 @@
         <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7271,13 +7274,13 @@
         <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>66</v>
@@ -7286,10 +7289,10 @@
         <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7303,13 +7306,13 @@
         <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>66</v>
@@ -7318,10 +7321,10 @@
         <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7335,13 +7338,13 @@
         <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>66</v>
@@ -7350,10 +7353,10 @@
         <v>67</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7367,13 +7370,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
@@ -7382,7 +7385,7 @@
         <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>554</v>
@@ -7411,7 +7414,7 @@
         <v>66</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>557</v>
@@ -7443,7 +7446,7 @@
         <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>557</v>
@@ -7478,10 +7481,10 @@
         <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7495,13 +7498,13 @@
         <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>66</v>
@@ -7510,10 +7513,10 @@
         <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7527,25 +7530,25 @@
         <v>191</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7559,25 +7562,25 @@
         <v>195</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="580">
   <si>
     <t>guild_name</t>
   </si>
@@ -113,13 +113,13 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>33</t>
+    <t>32</t>
   </si>
   <si>
     <t>Lv.9</t>
   </si>
   <si>
-    <t>677경 9011조 3320억 5240만</t>
+    <t>696경 7510조 7954억 5490만</t>
   </si>
   <si>
     <t>문의 [혜영]</t>
@@ -128,6 +128,9 @@
     <t>혜영</t>
   </si>
   <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
     <t>별하나달하나</t>
   </si>
   <si>
@@ -179,7 +182,7 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>1433</t>
+    <t>1440</t>
   </si>
   <si>
     <t>30위</t>
@@ -263,7 +266,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>151경 5004조 4630억 4973만</t>
+    <t>151경 5359조 252억 6874만</t>
   </si>
   <si>
     <t>4</t>
@@ -347,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>35경 5866조 3798억 7180만</t>
+    <t>36경 6511조 8988억 7340만</t>
   </si>
   <si>
     <t>10</t>
@@ -377,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>22경 2622조 1388억 6246만</t>
+    <t>23경 8604조 2602억 407만</t>
   </si>
   <si>
     <t>12</t>
@@ -392,7 +395,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>21경 4753조 3765억 8338만</t>
+    <t>22경 3669조 4484억 7448만</t>
   </si>
   <si>
     <t>13</t>
@@ -428,7 +431,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>15경 5795조 8588억 6810만</t>
+    <t>17경 4164조 9587억 8438만</t>
   </si>
   <si>
     <t>16</t>
@@ -440,7 +443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>13경 2105조 4816억 1933만</t>
+    <t>13경 5108조 2316억 6087만</t>
   </si>
   <si>
     <t>17</t>
@@ -473,7 +476,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>7경 4972조 6974억 1981만</t>
+    <t>8경 1537조 6375억 7393만</t>
   </si>
   <si>
     <t>19</t>
@@ -491,6 +494,18 @@
     <t>20</t>
   </si>
   <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 6937조 649억 4869만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
@@ -500,18 +515,6 @@
     <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 4783조 8696억 6956만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -521,7 +524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>5경 3005조 1147억 1318만</t>
+    <t>5경 3662조 5378억 2059만</t>
   </si>
   <si>
     <t>23</t>
@@ -533,49 +536,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
   </si>
   <si>
+    <t>2경 6159조 1196억 1911만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 4542조 9763억 7625만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>애봉얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 2774조 3837억 9059만</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
     <t>117</t>
   </si>
   <si>
-    <t>2경 5422조 8458억 5094만</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 3101조 7046억 6202만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2경 1802조 9715억 751만</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>1경 7395조 9535억 4782만</t>
+    <t>1경 7931조 5551억 2790만</t>
   </si>
   <si>
     <t>27</t>
@@ -593,25 +596,25 @@
     <t>1경 4405조 2903억 5532만</t>
   </si>
   <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 298조 7664억 4784만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>설콩순</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>9562조 1082억 7865만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9554조 6832억 9248만</t>
+    <t>9845조 8620억 2111만</t>
   </si>
   <si>
     <t>30</t>
@@ -638,7 +641,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>230경 375조 6847억 3301만</t>
+    <t>237경 3832조 9827억 3587만</t>
   </si>
   <si>
     <t>MNMMNMMNMMNM</t>
@@ -650,7 +653,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>82경 6629조 1011억 3884만</t>
+    <t>84경 6922조 3647억 3514만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -659,7 +662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>59경 8932조 8415억 8249만</t>
+    <t>62경 1946조 3217억 3306만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -668,7 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>58경 2451조 9309억 7663만</t>
+    <t>58경 3504조 9661억 1085만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -677,7 +680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>45경 9931조 1583억 3973만</t>
+    <t>46경 6681조 6977억 6438만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -686,7 +689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>26경 7953조 6509억 6286만</t>
+    <t>29경 3428조 9822억 7658만</t>
   </si>
   <si>
     <t>뽀리빠</t>
@@ -695,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>26경 7923조 9367억 2199만</t>
+    <t>26경 9454조 2047억 4223만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -716,7 +719,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>15경 857조 7736억 9512만</t>
+    <t>15경 918조 3225억 3682만</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>11경 307조 5408억 3327만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -725,16 +737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>10경 4931조 5654억 7685만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>10경 421조 9052억 6144만</t>
+    <t>10경 8625조 1248억 9229만</t>
   </si>
   <si>
     <t>약어</t>
@@ -743,7 +746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>9경 7717조 5279억 6925만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>국의</t>
@@ -752,7 +755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>9경 7577조 4960억 8311만</t>
+    <t>9경 8834조 8762억 2038만</t>
   </si>
   <si>
     <t>익맹이</t>
@@ -761,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
   </si>
   <si>
-    <t>8경 5493조 5674억 6937만</t>
+    <t>8경 6680조 2850억 6904만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -800,6 +803,15 @@
     <t>6경 4934조 151억 6468만</t>
   </si>
   <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>6경 1668조 7392억 2259만</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -809,15 +821,6 @@
     <t>5경 8774조 7748억 8940만</t>
   </si>
   <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>5경 7132조 4680억 8461만</t>
-  </si>
-  <si>
     <t>쾌감</t>
   </si>
   <si>
@@ -827,22 +830,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>2경 1572조 3177억 5090만</t>
+  </si>
+  <si>
     <t>세아수호지호</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 9039조 4842억 7168만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 7944조 8437억 7238만</t>
+    <t>1경 9146조 5243억 1253만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -851,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>1경 5275조 752억 3008만</t>
+    <t>1경 7599조 1897억 5828만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -869,13 +872,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 3784조 6932억 6395만</t>
+    <t>1경 4546조 517억 3867만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 3172조 192억 1384만</t>
+    <t>1경 3471조 2104억 2832만</t>
   </si>
   <si>
     <t>아이스꾸임</t>
@@ -884,7 +887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>1경 2961조 5558억 3160만</t>
+    <t>1경 2975조 3166억 7368만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -893,7 +896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 337조 3153억 1051만</t>
+    <t>1경 511조 753억 1132만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -902,7 +905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>8232조 4493억 242만</t>
+    <t>8523조 7574억 722만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -932,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>90경 3185조 6632억 3331만</t>
+    <t>90경 8422조 6035억 9893만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -941,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
   </si>
   <si>
-    <t>77경 4323조 4875억 3094만</t>
+    <t>77경 5093조 4467억 7106만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -977,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 685조 7578억 9730만</t>
+    <t>4경 1512조 7880억 3358만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -995,7 +998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7459조 1601억 6637만</t>
+    <t>3경 641조 8308억 7945만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -1004,7 +1007,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 6665조 109억 335만</t>
+    <t>2경 6922조 4232억 8878만</t>
+  </si>
+  <si>
+    <t>StarLink</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
+  </si>
+  <si>
+    <t>2경 6781조 6396억 5816만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -1016,22 +1028,13 @@
     <t>2경 6457조 8392억 9501만</t>
   </si>
   <si>
-    <t>StarLink</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
-  </si>
-  <si>
-    <t>2경 6384조 4873억 4507만</t>
-  </si>
-  <si>
     <t>못함</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 780조 6603억 1331만</t>
+    <t>2경 2102조 6785억 4104만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -1049,7 +1052,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>1경 6935조 2825억 2842만</t>
+    <t>1경 7465조 3799억 3542만</t>
+  </si>
+  <si>
+    <t>준준챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>1경 4943조 7431억 9792만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -1067,16 +1079,7 @@
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 4480조 2743억 8806만</t>
-  </si>
-  <si>
-    <t>준준챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>1경 4200조 9912억 9042만</t>
+    <t>1경 4532조 9756억 2778만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -1085,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 635조 2650억 1514만</t>
+    <t>1경 1756조 526억 35만</t>
   </si>
   <si>
     <t>서두희</t>
@@ -1094,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 98조 2390억 9178만</t>
+    <t>1경 593조 2751억 2283만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -1112,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>9178조 6185억 2422만</t>
+    <t>9220조 6674억 7408만</t>
   </si>
   <si>
     <t>회귀함</t>
@@ -1133,7 +1136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>8602조 5959억 6037만</t>
+    <t>8869조 2586억 3000만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -1142,7 +1145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>7259조 2964억 6491만</t>
+    <t>7792조 8382억 1147만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -1151,7 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>6318조 5165억 7942만</t>
+    <t>6822조 6111억 5868만</t>
   </si>
   <si>
     <t>수영하는수달</t>
@@ -1163,6 +1166,15 @@
     <t>5324조 3153억 5702만</t>
   </si>
   <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>5195조 3960억 6328만</t>
+  </si>
+  <si>
     <t>김보들</t>
   </si>
   <si>
@@ -1172,22 +1184,13 @@
     <t>4910조 9077억 6257만</t>
   </si>
   <si>
-    <t>빈수르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>4786조 4122억 4118만</t>
-  </si>
-  <si>
     <t>종리츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>871경 552조 7232억 3310만</t>
+    <t>1075경 3143조 5952억 8486만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
@@ -1205,7 +1208,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2경 6045조 2479억 642만</t>
+    <t>2경 8916조 1873억 8930만</t>
   </si>
   <si>
     <t>정육츄</t>
@@ -1226,7 +1229,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 2752조 8702억 8273만</t>
+    <t>1경 3334조 5789억 7855만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1244,49 +1247,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
+    <t>3690조 8751억 6661만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2875조 558억 2036만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2720조 1881억 6264만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>2625조 1648억 3488만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>3554조 1639억 2229만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2761조 6694억 8911만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2518조 1619억 3179만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2370조 8947억 8831만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>2212조 2512억 953만</t>
+    <t>2441조 4086억 156만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1295,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>2029조 6208억 9762만</t>
+    <t>2120조 3237억 2872만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1316,7 +1319,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1218조 6963억 8867만</t>
+    <t>1369조 4079억 2740만</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>1136조 6341억 5815만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1133조 4213억 4958만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -1337,24 +1358,6 @@
     <t>1077조 6256억 8210만</t>
   </si>
   <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>985조 433억 9200만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>856조 2452억 7572만</t>
-  </si>
-  <si>
     <t>루린츄</t>
   </si>
   <si>
@@ -1373,7 +1376,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
   </si>
   <si>
-    <t>450조 2034억 4621만</t>
+    <t>487조 7888억 3041만</t>
   </si>
   <si>
     <t>뽀야츄</t>
@@ -1382,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>333조 7361억 7776만</t>
+    <t>355조 2052억 1578만</t>
   </si>
   <si>
     <t>히히힣히힣</t>
@@ -1391,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
   </si>
   <si>
-    <t>287조 4507억 9033만</t>
+    <t>309조 2873억 2951만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -1403,22 +1406,22 @@
     <t>286조 7407억 2949만</t>
   </si>
   <si>
+    <t>도리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>254조 3963억 7456만</t>
+  </si>
+  <si>
     <t>주냥츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
   </si>
   <si>
-    <t>216조 9810억 9795만</t>
-  </si>
-  <si>
-    <t>도리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>209조 7743억 1108만</t>
+    <t>246조 5019억 2720만</t>
   </si>
   <si>
     <t>디나인</t>
@@ -1427,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
   </si>
   <si>
-    <t>154조 153억 4607만</t>
+    <t>196조 5175억 6062만</t>
   </si>
   <si>
     <t>새벽츄</t>
@@ -1457,7 +1460,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
   </si>
   <si>
-    <t>52조 9807억 6147만</t>
+    <t>59조 2286억 2223만</t>
   </si>
   <si>
     <t>피카츄십볼트</t>
@@ -1469,7 +1472,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>22조 4995억 1676만</t>
+    <t>22조 6452억 4938만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1481,6 +1484,15 @@
     <t>453조 1445억 2085만</t>
   </si>
   <si>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>447조 2226억 4441만</t>
+  </si>
+  <si>
     <t>온우사수</t>
   </si>
   <si>
@@ -1490,15 +1502,6 @@
     <t>401조 4910억 992만</t>
   </si>
   <si>
-    <t>베르카암프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>397조 7126억 7953만</t>
-  </si>
-  <si>
     <t>우댕이</t>
   </si>
   <si>
@@ -1541,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>250조 3505억 7807만</t>
+    <t>268조 2415억 716만</t>
   </si>
   <si>
     <t>날씬</t>
@@ -1550,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>248조 4862억 2013만</t>
+    <t>267조 6233억 9318만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1559,7 +1562,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
   </si>
   <si>
-    <t>182조 6335억 7631만</t>
+    <t>203조 2256억 2893만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1589,7 +1592,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>139조 9077억 5330만</t>
+    <t>144조 3413억 624만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1598,7 +1601,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>133조 4591억 1064만</t>
+    <t>136조 1926억 8015만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1607,7 +1610,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>118조 8267억 2860만</t>
+    <t>126조 272억 3654만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1616,7 +1619,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
   </si>
   <si>
-    <t>116조 4642억 5559만</t>
+    <t>119조 4074억 2810만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1625,7 +1628,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>113조 8190억 3005만</t>
+    <t>114조 3560억 2849만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1643,7 +1646,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>84조 9553억 6854만</t>
+    <t>86조 6044억 5040만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1664,7 +1667,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>53조 2514억 7734만</t>
+    <t>54조 239억 9051만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1673,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>25조 7718억 97만</t>
+    <t>26조 2754억 7961만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1682,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>17조 1123억 2995만</t>
+    <t>20조 8845억 2964만</t>
   </si>
   <si>
     <t>짜도이</t>
@@ -1691,7 +1694,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>14조 1291억 5727만</t>
+    <t>14조 6703억 9690만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1703,7 +1706,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>12조 1853억 8318만</t>
+    <t>13조 62억 3337만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1712,7 +1715,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
   </si>
   <si>
-    <t>10조 2535억 8036만</t>
+    <t>11조 6150억 3558만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
@@ -1721,7 +1724,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>5조 2162억 4583만</t>
+    <t>5조 5404억 4796만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1733,7 +1736,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>1조 8541억 6059만</t>
+    <t>2조 22억 5112만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1748,7 +1751,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>808억 5077만</t>
+    <t>928억 7595만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1763,7 +1766,7 @@
     <t>81</t>
   </si>
   <si>
-    <t>44억 9831만</t>
+    <t>80억 8692만</t>
   </si>
 </sst>
 </file>
@@ -2262,27 +2265,27 @@
         <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -2294,13 +2297,13 @@
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2308,38 +2311,38 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2347,25 +2350,25 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
@@ -2374,13 +2377,13 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2410,7 +2413,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2419,28 +2422,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2451,28 +2454,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2483,28 +2486,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2515,28 +2518,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2547,28 +2550,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2579,28 +2582,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2611,28 +2614,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2643,28 +2646,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2675,28 +2678,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2707,28 +2710,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2739,28 +2742,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2771,28 +2774,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2803,28 +2806,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2835,28 +2838,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2867,28 +2870,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2899,28 +2902,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2931,28 +2934,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2963,28 +2966,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2995,28 +2998,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3027,28 +3030,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3059,28 +3062,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3091,28 +3094,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3123,28 +3126,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3155,25 +3158,25 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>169</v>
@@ -3199,10 +3202,10 @@
         <v>171</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>172</v>
@@ -3231,7 +3234,7 @@
         <v>176</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>177</v>
@@ -3251,7 +3254,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>180</v>
@@ -3263,16 +3266,16 @@
         <v>181</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3283,28 +3286,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3315,28 +3318,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3347,28 +3350,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3379,28 +3382,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3455,7 +3458,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3464,28 +3467,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3496,31 +3499,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3528,31 +3531,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3560,31 +3563,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3592,31 +3595,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3624,31 +3627,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3656,31 +3659,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3688,31 +3691,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3720,31 +3723,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3752,31 +3755,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3784,31 +3787,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3816,31 +3819,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3848,31 +3851,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3880,31 +3883,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3912,31 +3915,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3944,31 +3947,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3976,31 +3979,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4008,31 +4011,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4040,31 +4043,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4072,31 +4075,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4104,31 +4107,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4136,31 +4139,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4168,31 +4171,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4200,31 +4203,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4235,28 +4238,28 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4267,28 +4270,28 @@
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4296,31 +4299,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4328,7 +4331,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>32</v>
@@ -4337,22 +4340,22 @@
         <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4360,31 +4363,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4392,31 +4395,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4424,31 +4427,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4509,28 +4512,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4538,31 +4541,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4570,31 +4573,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4602,31 +4605,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4634,31 +4637,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4666,31 +4669,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4698,31 +4701,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4730,31 +4733,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4762,31 +4765,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4794,31 +4797,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4826,31 +4829,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4858,31 +4861,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4890,31 +4893,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4922,31 +4925,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4954,31 +4957,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4986,31 +4989,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5018,31 +5021,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5050,28 +5053,28 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>343</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>344</v>
@@ -5082,31 +5085,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5114,31 +5117,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>347</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>347</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5146,31 +5149,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5178,31 +5181,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5210,31 +5213,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5242,31 +5245,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5274,31 +5277,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5306,31 +5309,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5338,31 +5341,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5370,31 +5373,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5402,31 +5405,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5434,31 +5437,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5466,31 +5469,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5545,7 +5548,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5554,28 +5557,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5583,31 +5586,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5615,31 +5618,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5647,31 +5650,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5679,31 +5682,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5711,31 +5714,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5743,31 +5746,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5775,28 +5778,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>406</v>
@@ -5807,10 +5810,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>407</v>
@@ -5822,13 +5825,13 @@
         <v>408</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>409</v>
@@ -5839,10 +5842,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>410</v>
@@ -5854,10 +5857,10 @@
         <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>412</v>
@@ -5871,10 +5874,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>414</v>
@@ -5886,13 +5889,13 @@
         <v>415</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>416</v>
@@ -5903,10 +5906,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>417</v>
@@ -5918,16 +5921,16 @@
         <v>418</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5935,31 +5938,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5967,31 +5970,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5999,22 +6002,22 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>177</v>
@@ -6023,7 +6026,7 @@
         <v>412</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6031,31 +6034,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6063,31 +6066,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6095,31 +6098,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6127,31 +6130,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6159,31 +6162,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6191,31 +6194,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6223,31 +6226,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6255,31 +6258,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6287,31 +6290,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6319,31 +6322,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6351,31 +6354,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6383,31 +6386,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6415,31 +6418,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6447,31 +6450,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6479,31 +6482,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6511,31 +6514,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6599,28 +6602,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6628,31 +6631,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6660,31 +6663,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6692,31 +6695,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6724,31 +6727,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6756,31 +6759,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6788,31 +6791,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6820,31 +6823,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6852,31 +6855,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6884,31 +6887,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6916,31 +6919,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6948,31 +6951,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6980,31 +6983,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7012,31 +7015,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7044,31 +7047,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7076,31 +7079,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7108,31 +7111,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7140,31 +7143,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7172,31 +7175,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7204,31 +7207,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>177</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7236,31 +7239,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7268,31 +7271,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7300,31 +7303,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7332,31 +7335,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>544</v>
+        <v>480</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7364,31 +7367,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7396,31 +7399,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7428,31 +7431,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7460,31 +7463,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7492,31 +7495,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7524,31 +7527,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7556,31 +7559,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="설묘" sheetId="2" r:id="rId2"/>
-    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
+    <sheet name="셀린느" sheetId="2" r:id="rId2"/>
+    <sheet name="설묘" sheetId="3" r:id="rId3"/>
     <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
     <sheet name="TRIUMPH" sheetId="5" r:id="rId5"/>
     <sheet name="promise" sheetId="6" r:id="rId6"/>
@@ -17,17 +17,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRIUMPH!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">설묘!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="581">
   <si>
     <t>guild_name</t>
   </si>
@@ -68,160 +68,586 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>697경 4931조 204억 2499만</t>
+  </si>
+  <si>
+    <t>문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
     <t>설묘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 25</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>1089경 6103조 5933억 8200만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>2026.09.20</t>
+  </si>
+  <si>
+    <t>별하나달하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>796경 1899조 7356억 4540만</t>
+  </si>
+  <si>
+    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
+  </si>
+  <si>
+    <t>Onyul</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>914경 1847조 7200억 8300만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>4842조 9452억 2908만</t>
+  </si>
+  <si>
+    <t>길컨미참여 2일미접 추방입니다</t>
+  </si>
+  <si>
+    <t>이랑b</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>빔냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>289경 1954조 3484억 8861만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>내가바로스타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EA%B0%80%EB%B0%94%EB%A1%9C%EC%8A%A4%ED%83%80</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>88경 1033조 7006억 1868만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>64경 2299조 7904억 696만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>61경 4578조 8767억 9585만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>47경 3722조 467억 3648만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>33경 1920조 9453억 26만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>28경 9454조 9622억 8234만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>25경 4823조 3360억 295만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>15경 8700조 1204억 3738만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>12경 7987조 5641억 8654만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>11경 7392조 2311억 7248만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>10경 8113조 7967억 409만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>10경 4738조 815억 6221만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>10경 3451조 2235억 7402만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>익맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8경 9595조 8839억 3700만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>8경 1023조 3955억 5020만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4934조 151억 6468만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>6경 3796조 6772억 320만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>5경 8774조 7748억 8940만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2경 3143조 636억 8761만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2경 1323조 7490억 7475만</t>
+  </si>
+  <si>
     <t>24</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>1089경 6103조 5933억 8200만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>2026.09.20</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>696경 7510조 7954억 5490만</t>
-  </si>
-  <si>
-    <t>문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
-    <t>별하나달하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2경 135조 6001억 797만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 9623조 9376억 5311만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 4715조 100억 8837만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1경 4547조 6297억 3758만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>795경 1983조 1944억 1870만</t>
-  </si>
-  <si>
-    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
-  </si>
-  <si>
-    <t>Onyul</t>
-  </si>
-  <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>914경 1847조 7200억 8300만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
-    <t>promise</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>1440</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>4616조 2781억 2722만</t>
-  </si>
-  <si>
-    <t>길컨미참여 2일미접 추방입니다</t>
-  </si>
-  <si>
-    <t>이랑b</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 3621조 6074억 839만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>1경 1478조 6628억 7792만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>9473조 1710억 1554만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -230,19 +656,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>보우마스터</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>239경 3650조 664억 5621만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>280경 3220조 6404억 6122만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -254,22 +671,22 @@
     <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>캐일리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>151경 5359조 252억 6874만</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>168경 2967조 9668억 5943만</t>
+  </si>
+  <si>
+    <t>설익은앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>105경 4731조 5416억 8730만</t>
   </si>
   <si>
     <t>킹규봉</t>
@@ -278,16 +695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>62경 4188조 2543억 3793만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>85경 8894조 1952억 8378만</t>
   </si>
   <si>
     <t>설함마</t>
@@ -296,10 +704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>52경 9932조 7914억 9061만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>54경 2229조 7961억 949만</t>
   </si>
   <si>
     <t>루델밍</t>
@@ -311,37 +716,22 @@
     <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>설봄a</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>39경 4856조 4335억 8984만</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>설묘묘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>39경 863조 8820억 7662만</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>39경 2693조 1453억 3379만</t>
   </si>
   <si>
     <t>너굴얌</t>
@@ -353,37 +743,22 @@
     <t>36경 6511조 8988억 7340만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>시드리안</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>싲프</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>23경 8604조 2602억 407만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>25경 4854조 8127억 3153만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -392,13 +767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>22경 3669조 4484억 7448만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>23경 4966조 6734억 3557만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -410,7 +779,13 @@
     <t>18경 9870조 503억 9521만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>18경 4100조 4845억 3688만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -422,31 +797,22 @@
     <t>18경 3564조 735억 3511만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>17경 4164조 9587억 8438만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>선콜은차가워</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>13경 5108조 2316억 6087만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>14경 8087조 6776억 1961만</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>11경 2907조 6억 1960만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -455,16 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>8경 1791조 1615억 2546만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>8경 7356조 9674억 8080만</t>
   </si>
   <si>
     <t>설름</t>
@@ -473,25 +830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>8경 1537조 6375억 7393만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>7경 2382조 7642억 9212만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>8경 2915조 2869억 7820만</t>
   </si>
   <si>
     <t>폰병</t>
@@ -503,97 +842,73 @@
     <t>5경 6937조 649억 4869만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>다다익숍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>5경 3662조 5378억 2059만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>수상구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+    <t>5경 3908조 6780억 4783만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2경 6307조 7429억 2523만</t>
+  </si>
+  <si>
+    <t>상구얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
     <t>2경 6159조 1196억 1911만</t>
   </si>
   <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 4542조 9763억 7625만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>애봉얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
     <t>2경 2774조 3837억 9059만</t>
   </si>
   <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>1경 7931조 5551억 2790만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>설치는정상인</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
   </si>
   <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4405조 2903억 5532만</t>
+    <t>1경 4573조 2571억 532만</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>1경 1050조 7102억 6148만</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1경 409조 3565억 6965만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -602,310 +917,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 298조 7664억 4784만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>9845조 8620억 2111만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>8781조 4022억 5235만</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>237경 3832조 9827억 3587만</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>84경 6922조 3647억 3514만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>62경 1946조 3217억 3306만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>58경 3504조 9661억 1085만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>46경 6681조 6977억 6438만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>29경 3428조 9822억 7658만</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>26경 9454조 2047억 4223만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>25경 4823조 3360억 295만</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>15경 918조 3225억 3682만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>11경 307조 5408억 3327만</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>10경 8625조 1248억 9229만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>10경 4738조 815억 6221만</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>9경 8834조 8762억 2038만</t>
-  </si>
-  <si>
-    <t>익맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8경 6680조 2850억 6904만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>7경 8676조 4971억 4482만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 8132조 1663억 9724만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4934조 151억 6468만</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>6경 1668조 7392억 2259만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>5경 8774조 7748억 8940만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>5경 5228조 9003억 4099만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>2경 1572조 3177억 5090만</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 9146조 5243억 1253만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 7599조 1897억 5828만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 4618조 2500억 6149만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 4546조 517억 3867만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>1경 3471조 2104억 2832만</t>
-  </si>
-  <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1경 2975조 3166억 7368만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>1경 511조 753억 1132만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>8523조 7574억 722만</t>
+    <t>1경 305조 1962억 4074만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -929,13 +941,22 @@
     <t>223경 1874조 2497억 5686만</t>
   </si>
   <si>
+    <t>라온MS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
+  </si>
+  <si>
+    <t>178경 6628조 7559억 4369만</t>
+  </si>
+  <si>
     <t>왕이된사나이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>90경 8422조 6035억 9893만</t>
+    <t>91경 4473조 7730억 660만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -944,7 +965,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
   </si>
   <si>
-    <t>77경 5093조 4467억 7106만</t>
+    <t>80경 4840조 2718억 2549만</t>
+  </si>
+  <si>
+    <t>라온PB</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
+  </si>
+  <si>
+    <t>64경 6782조 2788억 1062만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -953,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>38경 2547조 725억 1408만</t>
+    <t>41경 1905조 6743억 903만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -962,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 6681조 2757억 8928만</t>
+    <t>22경 7652조 2452억 2243만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -971,7 +1001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
   </si>
   <si>
-    <t>5경 1031조 232억 5292만</t>
+    <t>5경 5732조 8413억 3455만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -989,7 +1019,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>3경 8203조 7807억 7240만</t>
+    <t>3경 8621조 9090억 175만</t>
+  </si>
+  <si>
+    <t>뚜뭉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3경 3657조 3272억 2731만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -998,7 +1037,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>3경 641조 8308억 7945만</t>
+    <t>3경 691조 6922억 981만</t>
+  </si>
+  <si>
+    <t>StarLink</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
+  </si>
+  <si>
+    <t>2경 7502조 3758억 839만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -1010,31 +1058,13 @@
     <t>2경 6922조 4232억 8878만</t>
   </si>
   <si>
-    <t>StarLink</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
-  </si>
-  <si>
-    <t>2경 6781조 6396억 5816만</t>
-  </si>
-  <si>
-    <t>뚜뭉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2경 6457조 8392억 9501만</t>
-  </si>
-  <si>
     <t>못함</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 2102조 6785억 4104만</t>
+    <t>2경 4177조 7281억 3707만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -1052,7 +1082,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>1경 7465조 3799억 3542만</t>
+    <t>1경 9294조 2198억 8574만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
+  </si>
+  <si>
+    <t>1경 8074조 233억 1047만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -1061,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 4943조 7431억 9792만</t>
+    <t>1경 6453조 1530억 4121만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -1073,13 +1109,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1경 4779조 306억 3189만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
-  </si>
-  <si>
-    <t>1경 4532조 9756억 2778만</t>
+    <t>1경 5510조 2000억 1832만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -1097,7 +1127,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 593조 2751억 2283만</t>
+    <t>1경 614조 3027억 8999만</t>
+  </si>
+  <si>
+    <t>희다차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>1경 374조 9989억 909만</t>
+  </si>
+  <si>
+    <t>널꼬라봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
+  </si>
+  <si>
+    <t>1경 265조 9002억 2289만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -1106,73 +1154,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>9513조 8454억 6327만</t>
-  </si>
-  <si>
-    <t>희다차</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
-  </si>
-  <si>
-    <t>9220조 6674억 7408만</t>
-  </si>
-  <si>
-    <t>회귀함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EA%B7%80%ED%95%A8</t>
+    <t>9918조 9020억 4996만</t>
+  </si>
+  <si>
+    <t>신참치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>8027조 6419억 7252만</t>
+  </si>
+  <si>
+    <t>걸동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6900조 916억 5107만</t>
+  </si>
+  <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>9024조 7811억 8626만</t>
-  </si>
-  <si>
-    <t>널꼬라봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
-  </si>
-  <si>
-    <t>8869조 2586억 3000만</t>
-  </si>
-  <si>
-    <t>신참치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>7792조 8382억 1147만</t>
-  </si>
-  <si>
-    <t>걸동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6822조 6111억 5868만</t>
-  </si>
-  <si>
-    <t>수영하는수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%98%81%ED%95%98%EB%8A%94%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>5324조 3153억 5702만</t>
-  </si>
-  <si>
-    <t>빈수르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>5195조 3960억 6328만</t>
+    <t>5369조 7388억 7778만</t>
   </si>
   <si>
     <t>김보들</t>
@@ -1190,13 +1202,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1075경 3143조 5952억 8486만</t>
+    <t>1106경 5644조 9769억 2423만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>33경 9721조 7385억 4093만</t>
+    <t>38경 7551조 7562억 3732만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -1208,7 +1220,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2경 8916조 1873억 8930만</t>
+    <t>3경 442조 6040억 7853만</t>
   </si>
   <si>
     <t>정육츄</t>
@@ -1220,7 +1232,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2경 842조 7593억 4321만</t>
+    <t>2경 5030조 1787억 2281만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1229,7 +1241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 3334조 5789억 7855만</t>
+    <t>1경 5471조 1864억 4056만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1238,7 +1250,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>7005조 1563억 660만</t>
+    <t>7228조 5088억 7944만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>4177조 5012억 3319만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1247,7 +1271,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>3690조 8751억 6661만</t>
+    <t>3891조 8593억 8342만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3333조 6772억 2378만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1256,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>2875조 558억 2036만</t>
+    <t>2930조 6360억 7292만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1268,7 +1301,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>2720조 1881억 6264만</t>
+    <t>2895조 6195억 7892만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1277,28 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>2625조 1648억 3488만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2441조 4086억 156만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2120조 3237억 2872만</t>
+    <t>2764조 8243억 527만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1307,10 +1319,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
+    <t>2060조 9875억 4297만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
-    <t>1485조 5840억 7215만</t>
+    <t>1575조 4828억 3452만</t>
   </si>
   <si>
     <t>산과바다</t>
@@ -1328,25 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>1136조 6341억 5815만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1133조 4213억 4958만</t>
-  </si>
-  <si>
-    <t>서전붕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
-  </si>
-  <si>
-    <t>1098조 7210억 19만</t>
+    <t>1340조 611억 4068만</t>
   </si>
   <si>
     <t>호야빵</t>
@@ -1376,7 +1379,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
   </si>
   <si>
-    <t>487조 7888억 3041만</t>
+    <t>518조 9139억 1803만</t>
+  </si>
+  <si>
+    <t>히히힣히힣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
+  </si>
+  <si>
+    <t>371조 3749억 3822만</t>
   </si>
   <si>
     <t>뽀야츄</t>
@@ -1385,16 +1397,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>355조 2052억 1578만</t>
-  </si>
-  <si>
-    <t>히히힣히힣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
-  </si>
-  <si>
-    <t>309조 2873억 2951만</t>
+    <t>358조 2356억 592만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -1403,7 +1406,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
   </si>
   <si>
-    <t>286조 7407억 2949만</t>
+    <t>334조 8942억 3290만</t>
   </si>
   <si>
     <t>도리츄</t>
@@ -1412,7 +1415,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>254조 3963억 7456만</t>
+    <t>289조 6975억 498만</t>
   </si>
   <si>
     <t>주냥츄</t>
@@ -1421,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
   </si>
   <si>
-    <t>246조 5019억 2720만</t>
+    <t>256조 6301억 9738만</t>
   </si>
   <si>
     <t>디나인</t>
@@ -1430,7 +1433,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
   </si>
   <si>
-    <t>196조 5175억 6062만</t>
+    <t>221조 76억 7136만</t>
   </si>
   <si>
     <t>새벽츄</t>
@@ -1445,22 +1448,22 @@
     <t>152조 3767억 9006만</t>
   </si>
   <si>
+    <t>비먀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
+  </si>
+  <si>
+    <t>75조 4109억 181만</t>
+  </si>
+  <si>
     <t>우솝쁘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%81%98</t>
   </si>
   <si>
-    <t>64조 3332억 4836만</t>
-  </si>
-  <si>
-    <t>비먀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
-  </si>
-  <si>
-    <t>59조 2286억 2223만</t>
+    <t>71조 2033억 5002만</t>
   </si>
   <si>
     <t>피카츄십볼트</t>
@@ -1475,22 +1478,22 @@
     <t>22조 6452억 4938만</t>
   </si>
   <si>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>499조 2985억 8286만</t>
+  </si>
+  <si>
     <t>결기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>453조 1445억 2085만</t>
-  </si>
-  <si>
-    <t>베르카암프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>447조 2226억 4441만</t>
+    <t>478조 7864억 3460만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1499,7 +1502,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>401조 4910억 992만</t>
+    <t>419조 5399억 8694만</t>
+  </si>
+  <si>
+    <t>후추양조장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>347조 9363억 2470만</t>
   </si>
   <si>
     <t>우댕이</t>
@@ -1508,16 +1520,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>347조 342억 4183만</t>
-  </si>
-  <si>
-    <t>후추양조장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>340조 9115억 7451만</t>
+    <t>347조 940억 1911만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>346조 2082억 1765만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1529,22 +1541,13 @@
     <t>325조 5858억 5659만</t>
   </si>
   <si>
-    <t>썬콜원준띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>320조 7784억 8801만</t>
-  </si>
-  <si>
     <t>말랑랑말이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>268조 2415억 716만</t>
+    <t>273조 7748억 4105만</t>
   </si>
   <si>
     <t>날씬</t>
@@ -1562,7 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
   </si>
   <si>
-    <t>203조 2256억 2893만</t>
+    <t>204조 4230억 61만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1574,7 +1577,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>169조 2583억 4467만</t>
+    <t>177조 7709억 10만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1583,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
   </si>
   <si>
-    <t>155조 5567억 5475만</t>
+    <t>158조 6846억 164만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1610,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>126조 272억 3654만</t>
+    <t>126조 2444억 8684만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1619,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
   </si>
   <si>
-    <t>119조 4074억 2810만</t>
+    <t>123조 5051억 8330만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1637,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>103조 3846억 4513만</t>
+    <t>103조 4621억 1853만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1646,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>86조 6044억 5040만</t>
+    <t>91조 8476억 2371만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1655,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>72조 6579억 550만</t>
+    <t>72조 7843억 578만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1667,7 +1670,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>54조 239억 9051만</t>
+    <t>54조 8740억 4671만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1676,7 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>26조 2754억 7961만</t>
+    <t>27조 5191억 8447만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1694,7 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>14조 6703억 9690만</t>
+    <t>16조 2499억 2642만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1706,7 +1709,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>13조 62억 3337만</t>
+    <t>13조 1126억 2751만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1715,7 +1718,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
   </si>
   <si>
-    <t>11조 6150억 3558만</t>
+    <t>11조 7929억 1743만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
@@ -1736,7 +1739,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 22억 5112만</t>
+    <t>2조 735억 3679만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1751,7 +1754,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>928억 7595만</t>
+    <t>976억 3882만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -2247,146 +2250,146 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +2416,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2422,28 +2425,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2454,28 +2457,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2486,28 +2489,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2518,28 +2521,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2550,28 +2553,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2582,28 +2585,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2614,28 +2617,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2646,28 +2649,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2678,28 +2681,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2710,28 +2713,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2742,28 +2745,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2774,28 +2777,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2806,28 +2809,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2838,28 +2841,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2870,28 +2873,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2902,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2934,28 +2937,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2966,28 +2969,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2998,28 +3001,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3030,28 +3033,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3062,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3094,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3126,28 +3129,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3158,28 +3161,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3190,28 +3193,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3222,28 +3225,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3254,28 +3257,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3286,28 +3289,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3318,28 +3321,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3350,28 +3353,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3382,28 +3385,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3454,7 +3457,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -3467,28 +3470,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3499,31 +3502,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3531,31 +3534,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3563,31 +3566,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3595,31 +3598,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3627,31 +3630,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3659,31 +3662,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3691,31 +3694,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3723,31 +3726,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3755,31 +3758,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3787,31 +3790,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3819,31 +3822,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3851,31 +3854,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3883,31 +3886,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3915,31 +3918,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3947,31 +3950,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3979,31 +3982,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4011,31 +4014,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4043,31 +4046,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4075,31 +4078,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4107,31 +4110,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4139,31 +4142,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4171,31 +4174,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4203,31 +4206,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4235,31 +4238,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4267,31 +4270,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4299,31 +4302,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4331,31 +4334,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4363,31 +4366,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4395,31 +4398,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4427,31 +4430,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4512,28 +4515,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4541,962 +4544,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>209</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>365</v>
+        <v>198</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>365</v>
+        <v>198</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5539,7 +5542,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5557,28 +5560,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5586,966 +5589,934 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6576,7 +6547,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6602,28 +6572,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6631,962 +6601,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="셀린느" sheetId="2" r:id="rId2"/>
-    <sheet name="설묘" sheetId="3" r:id="rId3"/>
+    <sheet name="설묘" sheetId="2" r:id="rId2"/>
+    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
     <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
     <sheet name="TRIUMPH" sheetId="5" r:id="rId5"/>
     <sheet name="promise" sheetId="6" r:id="rId6"/>
@@ -19,15 +19,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRIUMPH!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">설묘!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="581">
   <si>
     <t>guild_name</t>
   </si>
@@ -68,19 +68,52 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>설묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>1089경 6103조 5933억 8200만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>2026.09.20</t>
+  </si>
+  <si>
     <t>셀린느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 2</t>
   </si>
   <si>
-    <t>38</t>
+    <t>62</t>
   </si>
   <si>
     <t>3위</t>
@@ -89,9 +122,6 @@
     <t>Lv.9</t>
   </si>
   <si>
-    <t>30명</t>
-  </si>
-  <si>
     <t>697경 4931조 204억 2499만</t>
   </si>
   <si>
@@ -104,133 +134,511 @@
     <t>2026.09.21</t>
   </si>
   <si>
-    <t>설묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
+    <t>별하나달하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>796경 1899조 7356억 4540만</t>
+  </si>
+  <si>
+    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
+  </si>
+  <si>
+    <t>Onyul</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>914경 1847조 7200억 8300만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>2762</t>
+  </si>
+  <si>
+    <t>151위</t>
+  </si>
+  <si>
+    <t>4842조 9452억 2908만</t>
+  </si>
+  <si>
+    <t>길컨미참여 2일미접 추방입니다</t>
+  </si>
+  <si>
+    <t>이랑b</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>280경 3220조 6404억 6122만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>231경 7865조 5718억 420만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>186경 6553조 4045억 5383만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>설익은앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>105경 4731조 5416억 8730만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>85경 8894조 1952억 8378만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>67경 752조 7750억 5951만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>45경 5109조 8480억 2031만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>43경 6096조 3908억 1286만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>42경 2574조 9676억 6152만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>40경 1838조 8770억 743만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>29경 5116조 6755억 7049만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>23경 9068조 8949억 9120만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>19경 7396조 2622억 1029만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19경 6115조 5909억 3806만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>18경 9870조 503억 9521만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>16경 3093조 6375억 2234만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>11경 2907조 6억 1960만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>8경 7356조 9674억 8080만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>8경 4614조 8057억 3683만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>6경 5564조 1888억 7889만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>5경 5478조 8492억 3032만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>5경 5316조 8872억 234만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>상구얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
+  </si>
+  <si>
+    <t>3경 293조 836억 9607만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>애봉얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 5397조 4334억 557만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>1089경 6103조 5933억 8200만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>2026.09.20</t>
-  </si>
-  <si>
-    <t>별하나달하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>796경 1899조 7356억 4540만</t>
-  </si>
-  <si>
-    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
-  </si>
-  <si>
-    <t>Onyul</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 4947조 4456억 1260만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 4777조 7815억 7357만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4592조 3595억 1013만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>914경 1847조 7200억 8300만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
-    <t>promise</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=promise</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>1634</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>4842조 9452억 2908만</t>
-  </si>
-  <si>
-    <t>길컨미참여 2일미접 추방입니다</t>
-  </si>
-  <si>
-    <t>이랑b</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
     <t>빔냥이</t>
@@ -239,19 +647,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>신궁</t>
   </si>
   <si>
     <t>126</t>
   </si>
   <si>
-    <t>289경 1954조 3484억 8861만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>301경 902조 9114억 8217만</t>
   </si>
   <si>
     <t>내가바로스타</t>
@@ -260,16 +662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EA%B0%80%EB%B0%94%EB%A1%9C%EC%8A%A4%ED%83%80</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>88경 1033조 7006억 1868만</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>91경 9740조 985억 8332만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -278,10 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>64경 2299조 7904억 696만</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>83경 3615조 386억 238만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -290,13 +680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>61경 4578조 8767억 9585만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>64경 1795조 6090억 1846만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -305,13 +689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>47경 3722조 467억 3648만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>50경 4173조 2145억 9205만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -320,13 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>33경 1920조 9453억 26만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>34경 6124조 6964억 5847만</t>
   </si>
   <si>
     <t>뽀리빠</t>
@@ -335,16 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>28경 9454조 9622억 8234만</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>32경 4173조 3842억 7684만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -359,22 +722,13 @@
     <t>25경 4823조 3360억 295만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>부엉이형</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>15경 8700조 1204억 3738만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>17경 1218조 674억 1252만</t>
   </si>
   <si>
     <t>천천히걸어가</t>
@@ -383,16 +737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>12경 7987조 5641억 8654만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>13경 6804조 8876억 1833만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -401,10 +746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>11경 7392조 2311억 7248만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>12경 4306조 3052억 4003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -413,13 +755,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>10경 8113조 7967억 409만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>11경 3994조 4731억 2872만</t>
+  </si>
+  <si>
+    <t>익맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>11경 1678조 151억 5811만</t>
   </si>
   <si>
     <t>약어</t>
@@ -428,18 +773,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
     <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>하후돈</t>
   </si>
   <si>
@@ -449,34 +785,31 @@
     <t>10경 3451조 2235억 7402만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>익맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8경 9595조 8839억 3700만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>잼포즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>8경 1023조 3955억 5020만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>9경 961조 2436억 2444만</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>7경 6739조 6040억 354만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>7경 5079조 6722억 2664만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -485,52 +818,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>캡틴</t>
-  </si>
-  <si>
     <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4934조 151억 6468만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>6경 3796조 6772억 320만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>킹몬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>5경 8774조 7748억 8940만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>117</t>
+  </si>
+  <si>
+    <t>6경 1227조 9270억 3232만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -542,22 +842,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>할룽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>2경 3143조 636억 8761만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>2경 3525조 9083억 7559만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2경 3200조 7613억 3554만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -569,28 +869,19 @@
     <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>2경 135조 6001억 797만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>핫잇</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>1경 9623조 9376억 5311만</t>
+    <t>2경 927조 1222억 8696만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>1경 6303조 4245억 5058만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -599,34 +890,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 4715조 100억 8837만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1경 4547조 6297억 3758만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 3621조 6074억 839만</t>
+    <t>1경 5844조 3478억 8299만</t>
+  </si>
+  <si>
+    <t>쌉새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
+  </si>
+  <si>
+    <t>1경 3037조 442억 6604만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -635,7 +908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 1478조 6628억 7792만</t>
+    <t>1경 2752조 370억 300만</t>
   </si>
   <si>
     <t>30</t>
@@ -647,277 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>9473조 1710억 1554만</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>280경 3220조 6404억 6122만</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>231경 7865조 5718억 420만</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>168경 2967조 9668억 5943만</t>
-  </si>
-  <si>
-    <t>설익은앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>105경 4731조 5416억 8730만</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>85경 8894조 1952억 8378만</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>54경 2229조 7961억 949만</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>39경 4856조 4335억 8984만</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>39경 2693조 1453억 3379만</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>36경 6511조 8988억 7340만</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>29경 7613조 5062억 2329만</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>25경 4854조 8127억 3153만</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>23경 4966조 6734억 3557만</t>
-  </si>
-  <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>18경 9870조 503억 9521만</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>18경 4100조 4845억 3688만</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>18경 3564조 735억 3511만</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>14경 8087조 6776억 1961만</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>11경 2907조 6억 1960만</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>8경 7356조 9674억 8080만</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>8경 2915조 2869억 7820만</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 6937조 649억 4869만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5경 5478조 8492억 3032만</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>5경 3908조 6780억 4783만</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2경 6307조 7429억 2523만</t>
-  </si>
-  <si>
-    <t>상구얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
-  </si>
-  <si>
-    <t>2경 6159조 1196억 1911만</t>
-  </si>
-  <si>
-    <t>애봉얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
-  </si>
-  <si>
-    <t>2경 2774조 3837억 9059만</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>1경 4573조 2571억 532만</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>1경 1050조 7102억 6148만</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>1경 409조 3565억 6965만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1경 305조 1962억 4074만</t>
+    <t>9836조 9463억 9713만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -926,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>300경 9676조 7164억 5367만</t>
+    <t>332경 809조 3742억 6821만</t>
   </si>
   <si>
     <t>달하나별하나</t>
@@ -935,10 +938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>223경 1874조 2497억 5686만</t>
+    <t>252경 3504조 554억 5589만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -956,7 +956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>91경 4473조 7730억 660만</t>
+    <t>94경 871조 8885억 5305만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -965,7 +965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
   </si>
   <si>
-    <t>80경 4840조 2718억 2549만</t>
+    <t>81경 393조 5887억 8702만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -1001,7 +1001,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
   </si>
   <si>
-    <t>5경 5732조 8413억 3455만</t>
+    <t>5경 8194조 3039억 3062만</t>
+  </si>
+  <si>
+    <t>상깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
+  </si>
+  <si>
+    <t>4경 7266조 3913억 1163만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -1010,16 +1019,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 1512조 7880억 3358만</t>
-  </si>
-  <si>
-    <t>상깅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
-  </si>
-  <si>
-    <t>3경 8621조 9090억 175만</t>
+    <t>4경 3029조 649억 4734만</t>
+  </si>
+  <si>
+    <t>찍먹비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>3경 4977조 1514억 5131만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -1031,22 +1040,13 @@
     <t>3경 3657조 3272억 2731만</t>
   </si>
   <si>
-    <t>찍먹비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>3경 691조 6922억 981만</t>
-  </si>
-  <si>
     <t>StarLink</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>2경 7502조 3758억 839만</t>
+    <t>2경 8824조 775억 3519만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -1055,7 +1055,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 6922조 4232억 8878만</t>
+    <t>2경 8397조 7328억 5339만</t>
+  </si>
+  <si>
+    <t>오쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
+  </si>
+  <si>
+    <t>2경 4434조 46억 2999만</t>
   </si>
   <si>
     <t>못함</t>
@@ -1067,28 +1076,31 @@
     <t>2경 4177조 7281억 3707만</t>
   </si>
   <si>
-    <t>오쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1경 9978조 6367억 977만</t>
-  </si>
-  <si>
     <t>금하나</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>1경 9294조 2198억 8574만</t>
+    <t>1경 9337조 3545억 8186만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 8074조 233억 1047만</t>
+    <t>1경 8488조 6346억 3768만</t>
+  </si>
+  <si>
+    <t>쵸비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1경 7791조 6302억 4935만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -1097,19 +1109,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 6453조 1530억 4121만</t>
-  </si>
-  <si>
-    <t>쵸비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1경 5510조 2000억 1832만</t>
+    <t>1경 6669조 9089억 6233만</t>
+  </si>
+  <si>
+    <t>서두희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>1경 1967조 9252억 4458만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -1118,16 +1127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 1756조 526억 35만</t>
-  </si>
-  <si>
-    <t>서두희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>1경 614조 3027억 8999만</t>
+    <t>1경 1795조 8296억 3783만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -1136,7 +1136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>1경 374조 9989억 909만</t>
+    <t>1경 937조 8369억 4859만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -1145,7 +1145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 265조 9002억 2289만</t>
+    <t>1경 438조 9014억 3803만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -1154,7 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>9918조 9020억 4996만</t>
+    <t>1경 345조 3706억 8929만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -1163,7 +1163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>8027조 6419억 7252만</t>
+    <t>8917조 6314억 1691만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -1172,7 +1172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>6900조 916억 5107만</t>
+    <t>7622조 3899억 1418만</t>
   </si>
   <si>
     <t>빈수르</t>
@@ -1184,7 +1184,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5369조 7388억 7778만</t>
+    <t>5497조 1301억 4107만</t>
   </si>
   <si>
     <t>김보들</t>
@@ -1202,13 +1202,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1106경 5644조 9769억 2423만</t>
+    <t>1141경 5826조 622억 4118만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>38경 7551조 7562억 3732만</t>
+    <t>41경 6897조 9928억 9193만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -1229,40 +1229,58 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
   </si>
   <si>
+    <t>2경 5047조 6740억 1185만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 6775조 698억 3190만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>7688조 1247억 9300만</t>
+  </si>
+  <si>
+    <t>꾸덕행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5501조 5848억 8198만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5918만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>2경 5030조 1787억 2281만</t>
-  </si>
-  <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 5471조 1864억 4056만</t>
-  </si>
-  <si>
-    <t>수달츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>7228조 5088억 7944만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>4177조 5012억 3319만</t>
+    <t>5001조 9074억 5704만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1271,16 +1289,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>3891조 8593억 8342만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3333조 6772억 2378만</t>
+    <t>4016조 3966억 4068만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3210조 5504억 71만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1289,19 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>2930조 6360억 7292만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2895조 6195억 7892만</t>
+    <t>2941조 7812억 6779만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1319,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
-    <t>2060조 9875억 4297만</t>
+    <t>2367조 729억 7956만</t>
   </si>
   <si>
     <t>푸들츄</t>
@@ -1331,7 +1340,16 @@
     <t>109</t>
   </si>
   <si>
-    <t>1575조 4828억 3452만</t>
+    <t>2142조 8887억 2585만</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>2064조 1071억 8482만</t>
   </si>
   <si>
     <t>산과바다</t>
@@ -1340,16 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1369조 4079억 2740만</t>
-  </si>
-  <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>1340조 611억 4068만</t>
+    <t>1593조 2985억 7905만</t>
   </si>
   <si>
     <t>호야빵</t>
@@ -1358,7 +1367,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
   </si>
   <si>
-    <t>1077조 6256억 8210만</t>
+    <t>1462조 9569억 6314만</t>
+  </si>
+  <si>
+    <t>서전붕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
+  </si>
+  <si>
+    <t>1153조 2178억 8567만</t>
   </si>
   <si>
     <t>루린츄</t>
@@ -1370,7 +1388,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>525조 7616억 9510만</t>
+    <t>549조 5329억 3684만</t>
   </si>
   <si>
     <t>묘피</t>
@@ -1388,7 +1406,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
   </si>
   <si>
-    <t>371조 3749억 3822만</t>
+    <t>434조 4195억 1364만</t>
+  </si>
+  <si>
+    <t>주냥츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
+  </si>
+  <si>
+    <t>409조 5538억 8907만</t>
   </si>
   <si>
     <t>뽀야츄</t>
@@ -1397,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>358조 2356억 592만</t>
+    <t>360조 5925억 9466만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -1415,25 +1442,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>289조 6975억 498만</t>
-  </si>
-  <si>
-    <t>주냥츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
-  </si>
-  <si>
-    <t>256조 6301억 9738만</t>
-  </si>
-  <si>
-    <t>디나인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>221조 76억 7136만</t>
+    <t>313조 6065억 4365만</t>
   </si>
   <si>
     <t>새벽츄</t>
@@ -1454,7 +1463,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
   </si>
   <si>
-    <t>75조 4109억 181만</t>
+    <t>80조 554억 3819만</t>
   </si>
   <si>
     <t>우솝쁘</t>
@@ -1466,106 +1475,97 @@
     <t>71조 2033억 5002만</t>
   </si>
   <si>
-    <t>피카츄십볼트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>525조 9863억 4925만</t>
+  </si>
+  <si>
+    <t>결기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>509조 1897억 5936만</t>
+  </si>
+  <si>
+    <t>온우사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>419조 5399억 8694만</t>
+  </si>
+  <si>
+    <t>우댕이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>399조 6484억 9953만</t>
+  </si>
+  <si>
+    <t>후추양조장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>362조 1131억 5634만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>346조 2082억 1765만</t>
+  </si>
+  <si>
+    <t>지존승준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
+  </si>
+  <si>
+    <t>336조 7783억 4223만</t>
+  </si>
+  <si>
+    <t>말랑랑말이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>278조 7185억 8389만</t>
+  </si>
+  <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>272조 3120억 2688만</t>
+  </si>
+  <si>
+    <t>눅이마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
   </si>
   <si>
     <t>105</t>
   </si>
   <si>
-    <t>22조 6452억 4938만</t>
-  </si>
-  <si>
-    <t>베르카암프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>499조 2985억 8286만</t>
-  </si>
-  <si>
-    <t>결기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>478조 7864억 3460만</t>
-  </si>
-  <si>
-    <t>온우사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>419조 5399억 8694만</t>
-  </si>
-  <si>
-    <t>후추양조장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>347조 9363억 2470만</t>
-  </si>
-  <si>
-    <t>우댕이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>347조 940억 1911만</t>
-  </si>
-  <si>
-    <t>썬콜원준띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>346조 2082억 1765만</t>
-  </si>
-  <si>
-    <t>지존승준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
-  </si>
-  <si>
-    <t>325조 5858억 5659만</t>
-  </si>
-  <si>
-    <t>말랑랑말이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>273조 7748억 4105만</t>
-  </si>
-  <si>
-    <t>날씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
-  </si>
-  <si>
-    <t>267조 6233억 9318만</t>
-  </si>
-  <si>
-    <t>눅이마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>204조 4230억 61만</t>
+    <t>211조 8253억 2618만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1577,7 +1577,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>177조 7709억 10만</t>
+    <t>184조 5133억 1640만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1586,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
   </si>
   <si>
-    <t>158조 6846억 164만</t>
+    <t>160조 7067억 9801만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>144조 3413억 624만</t>
+    <t>145조 5584억 2636만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1604,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>136조 1926억 8015만</t>
+    <t>137조 425억 9602만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>126조 2444억 8684만</t>
+    <t>127조 8393억 5575만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
   </si>
   <si>
-    <t>123조 5051억 8330만</t>
+    <t>126조 7033억 6964만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>114조 3560억 2849만</t>
+    <t>119조 5540억 221만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>103조 4621억 1853만</t>
+    <t>115조 7425억 9475만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>91조 8476억 2371만</t>
+    <t>95조 511억 2086만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1658,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>72조 7843억 578만</t>
+    <t>81조 6185억 1553만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1679,7 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>27조 5191억 8447만</t>
+    <t>31조 4415억 2522만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1697,7 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>16조 2499억 2642만</t>
+    <t>18조 8067억 1459만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1706,28 +1706,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%85%90%EB%8F%85%EC%A0%90</t>
   </si>
   <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>14조 1683억 1440만</t>
+  </si>
+  <si>
+    <t>상혀닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>13조 1126억 2751만</t>
-  </si>
-  <si>
-    <t>상혀닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>11조 7929억 1743만</t>
+    <t>12조 5181억 909만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>5조 5404억 4796만</t>
+    <t>6조 1382억 5847만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1739,7 +1739,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 735억 3679만</t>
+    <t>2조 761억 6312만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1754,7 +1754,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>976억 3882만</t>
+    <t>1191억 976만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1766,10 +1766,10 @@
     <t>윈드브레이커</t>
   </si>
   <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>80억 8692만</t>
+    <t>82</t>
+  </si>
+  <si>
+    <t>90억 5426만</t>
   </si>
 </sst>
 </file>
@@ -2291,105 +2291,105 @@
         <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2425,28 +2425,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2457,28 +2457,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2489,28 +2489,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2521,28 +2521,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2553,28 +2553,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2585,28 +2585,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2617,28 +2617,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2649,28 +2649,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2681,28 +2681,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2713,28 +2713,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2745,28 +2745,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2777,28 +2777,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2809,28 +2809,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2841,28 +2841,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2873,28 +2873,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2905,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2937,28 +2937,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2969,28 +2969,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3001,28 +3001,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3033,28 +3033,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3065,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3097,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3129,28 +3129,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3161,28 +3161,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3193,28 +3193,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3225,28 +3225,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3257,25 +3257,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>190</v>
@@ -3301,13 +3301,13 @@
         <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>194</v>
@@ -3324,22 +3324,22 @@
         <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>199</v>
@@ -3353,67 +3353,35 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3444,7 +3412,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3428,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3470,28 +3437,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3502,28 +3469,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -3534,28 +3501,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -3566,28 +3533,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -3598,28 +3565,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -3630,28 +3597,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -3662,28 +3629,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -3694,28 +3661,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -3726,28 +3693,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -3758,28 +3725,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -3790,28 +3757,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -3822,28 +3789,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -3854,28 +3821,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -3886,28 +3853,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -3918,28 +3885,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -3950,28 +3917,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -3982,28 +3949,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4014,28 +3981,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4046,28 +4013,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4078,28 +4045,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4110,25 +4077,25 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>267</v>
@@ -4142,7 +4109,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>268</v>
@@ -4154,13 +4121,13 @@
         <v>269</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>270</v>
@@ -4174,28 +4141,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4206,28 +4173,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4238,28 +4205,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4270,28 +4237,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4302,25 +4269,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>283</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>284</v>
@@ -4346,13 +4313,13 @@
         <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>287</v>
@@ -4378,13 +4345,13 @@
         <v>289</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>290</v>
@@ -4398,7 +4365,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>291</v>
@@ -4410,13 +4377,13 @@
         <v>292</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>293</v>
@@ -4430,28 +4397,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>203</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -4515,28 +4482,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4547,31 +4514,31 @@
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4579,31 +4546,31 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>302</v>
+        <v>207</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>303</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4611,7 +4578,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>304</v>
@@ -4623,19 +4590,19 @@
         <v>305</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>306</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4643,7 +4610,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>307</v>
@@ -4655,19 +4622,19 @@
         <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>309</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4675,7 +4642,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>310</v>
@@ -4687,19 +4654,19 @@
         <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>312</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4707,7 +4674,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>313</v>
@@ -4719,19 +4686,19 @@
         <v>314</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>315</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4739,7 +4706,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>316</v>
@@ -4751,19 +4718,19 @@
         <v>317</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>318</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4771,7 +4738,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>319</v>
@@ -4783,19 +4750,19 @@
         <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>321</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4803,7 +4770,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>322</v>
@@ -4815,19 +4782,19 @@
         <v>323</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>324</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4835,7 +4802,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>325</v>
@@ -4847,19 +4814,19 @@
         <v>326</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>327</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4867,7 +4834,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>328</v>
@@ -4879,19 +4846,19 @@
         <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>330</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4899,7 +4866,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>331</v>
@@ -4911,19 +4878,19 @@
         <v>332</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>333</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4931,7 +4898,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>334</v>
@@ -4943,19 +4910,19 @@
         <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>336</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4963,7 +4930,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>337</v>
@@ -4975,19 +4942,19 @@
         <v>338</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>339</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4995,7 +4962,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>340</v>
@@ -5007,19 +4974,19 @@
         <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>342</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5027,7 +4994,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>343</v>
@@ -5039,19 +5006,19 @@
         <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>345</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -5059,7 +5026,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>346</v>
@@ -5071,19 +5038,19 @@
         <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>348</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5091,7 +5058,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>349</v>
@@ -5103,19 +5070,19 @@
         <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>351</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5123,31 +5090,31 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>353</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5155,7 +5122,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>354</v>
@@ -5167,19 +5134,19 @@
         <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>133</v>
+        <v>356</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5187,31 +5154,31 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>359</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5219,7 +5186,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>361</v>
@@ -5231,19 +5198,19 @@
         <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5251,7 +5218,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>364</v>
@@ -5263,19 +5230,19 @@
         <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5283,7 +5250,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>367</v>
@@ -5295,19 +5262,19 @@
         <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5315,7 +5282,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>370</v>
@@ -5327,19 +5294,19 @@
         <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5347,7 +5314,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>373</v>
@@ -5359,19 +5326,19 @@
         <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5391,19 +5358,19 @@
         <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5423,19 +5390,19 @@
         <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5443,7 +5410,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>382</v>
@@ -5455,10 +5422,10 @@
         <v>383</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>384</v>
@@ -5467,7 +5434,7 @@
         <v>385</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5475,7 +5442,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>203</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>386</v>
@@ -5487,19 +5454,19 @@
         <v>387</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>388</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5551,7 +5518,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5560,28 +5527,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5589,10 +5556,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>389</v>
@@ -5604,59 +5571,59 @@
         <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>391</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>392</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>393</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>394</v>
@@ -5668,10 +5635,10 @@
         <v>395</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>396</v>
@@ -5680,15 +5647,15 @@
         <v>397</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>398</v>
@@ -5700,187 +5667,187 @@
         <v>399</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>396</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>417</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>418</v>
@@ -5892,27 +5859,27 @@
         <v>419</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>420</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>421</v>
@@ -5924,10 +5891,10 @@
         <v>422</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>423</v>
@@ -5936,15 +5903,15 @@
         <v>424</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>425</v>
@@ -5956,27 +5923,27 @@
         <v>426</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>423</v>
+        <v>384</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>427</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>428</v>
@@ -5988,10 +5955,10 @@
         <v>429</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>423</v>
@@ -6000,15 +5967,15 @@
         <v>430</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>431</v>
@@ -6020,59 +5987,59 @@
         <v>432</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>438</v>
@@ -6084,10 +6051,10 @@
         <v>439</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>423</v>
@@ -6096,15 +6063,15 @@
         <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>441</v>
@@ -6116,27 +6083,27 @@
         <v>442</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>444</v>
@@ -6148,91 +6115,91 @@
         <v>445</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>453</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>454</v>
@@ -6244,27 +6211,27 @@
         <v>455</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>456</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>457</v>
@@ -6276,27 +6243,27 @@
         <v>458</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>459</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>460</v>
@@ -6308,27 +6275,27 @@
         <v>461</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>462</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>463</v>
@@ -6340,27 +6307,27 @@
         <v>464</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>465</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>466</v>
@@ -6372,27 +6339,27 @@
         <v>467</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>468</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>469</v>
@@ -6404,56 +6371,56 @@
         <v>470</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>475</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>195</v>
@@ -6468,27 +6435,27 @@
         <v>477</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>478</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>479</v>
@@ -6500,19 +6467,19 @@
         <v>480</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6572,28 +6539,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6601,330 +6568,330 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>509</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>512</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>513</v>
@@ -6936,10 +6903,10 @@
         <v>514</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>515</v>
@@ -6948,15 +6915,15 @@
         <v>516</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>517</v>
@@ -6968,27 +6935,27 @@
         <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>520</v>
@@ -7000,10 +6967,10 @@
         <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>515</v>
@@ -7012,15 +6979,15 @@
         <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>523</v>
@@ -7032,27 +6999,27 @@
         <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>526</v>
@@ -7064,10 +7031,10 @@
         <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>515</v>
@@ -7076,15 +7043,15 @@
         <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>529</v>
@@ -7096,10 +7063,10 @@
         <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>515</v>
@@ -7108,15 +7075,15 @@
         <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>532</v>
@@ -7128,27 +7095,27 @@
         <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>535</v>
@@ -7160,27 +7127,27 @@
         <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>538</v>
@@ -7192,27 +7159,27 @@
         <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>541</v>
@@ -7224,27 +7191,27 @@
         <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>544</v>
@@ -7256,10 +7223,10 @@
         <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>546</v>
@@ -7268,15 +7235,15 @@
         <v>547</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>548</v>
@@ -7288,10 +7255,10 @@
         <v>549</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>546</v>
@@ -7300,15 +7267,15 @@
         <v>550</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>551</v>
@@ -7320,27 +7287,27 @@
         <v>552</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>553</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>554</v>
@@ -7352,10 +7319,10 @@
         <v>555</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>546</v>
@@ -7364,15 +7331,15 @@
         <v>556</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>557</v>
@@ -7384,10 +7351,10 @@
         <v>558</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>559</v>
@@ -7396,15 +7363,15 @@
         <v>560</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>561</v>
@@ -7416,56 +7383,56 @@
         <v>562</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>566</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>195</v>
@@ -7480,10 +7447,10 @@
         <v>568</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>569</v>
@@ -7492,15 +7459,15 @@
         <v>570</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>571</v>
@@ -7512,7 +7479,7 @@
         <v>572</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>573</v>
@@ -7524,15 +7491,15 @@
         <v>575</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>203</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>576</v>
@@ -7544,7 +7511,7 @@
         <v>577</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>578</v>
@@ -7556,7 +7523,7 @@
         <v>580</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="설묘" sheetId="2" r:id="rId2"/>
-    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
-    <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
-    <sheet name="TRIUMPH" sheetId="5" r:id="rId5"/>
+    <sheet name="별하나달하나" sheetId="3" r:id="rId3"/>
+    <sheet name="TRIUMPH" sheetId="4" r:id="rId4"/>
+    <sheet name="셀린느" sheetId="5" r:id="rId5"/>
     <sheet name="promise" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRIUMPH!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="578">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>47</t>
+    <t>44</t>
   </si>
   <si>
     <t>1위</t>
@@ -95,7 +95,7 @@
     <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+    <t>랭킹 98위권이내 용사를 상시 모집중  문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
   </si>
   <si>
     <t>설익은체리</t>
@@ -104,6 +104,60 @@
     <t>2026.09.20</t>
   </si>
   <si>
+    <t>별하나달하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>796경 1899조 7356억 4540만</t>
+  </si>
+  <si>
+    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
+  </si>
+  <si>
+    <t>Onyul</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>914경 1847조 7200억 8300만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
     <t>셀린느</t>
   </si>
   <si>
@@ -113,15 +167,12 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>62</t>
+    <t>57</t>
   </si>
   <si>
     <t>3위</t>
   </si>
   <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
     <t>697경 4931조 204억 2499만</t>
   </si>
   <si>
@@ -134,57 +185,6 @@
     <t>2026.09.21</t>
   </si>
   <si>
-    <t>별하나달하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>796경 1899조 7356억 4540만</t>
-  </si>
-  <si>
-    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
-  </si>
-  <si>
-    <t>Onyul</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>914경 1847조 7200억 8300만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
     <t>promise</t>
   </si>
   <si>
@@ -194,7 +194,7 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2762</t>
+    <t>2804</t>
   </si>
   <si>
     <t>151위</t>
@@ -251,7 +251,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>280경 3220조 6404억 6122만</t>
+    <t>280경 3220조 6,404억 6,122만</t>
   </si>
   <si>
     <t>2</t>
@@ -263,7 +263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>231경 7865조 5718억 420만</t>
+    <t>231경 7865조 5,718억 420만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>186경 6553조 4045억 5383만</t>
+    <t>186경 7071조 3,782억 8,079만</t>
   </si>
   <si>
     <t>4</t>
@@ -299,7 +299,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>105경 4731조 5416억 8730만</t>
+    <t>105경 4731조 5,416억 8,730만</t>
   </si>
   <si>
     <t>5</t>
@@ -314,7 +314,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>85경 8894조 1952억 8378만</t>
+    <t>85경 8894조 1,952억 8,378만</t>
   </si>
   <si>
     <t>6</t>
@@ -326,61 +326,61 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>67경 752조 7750억 5951만</t>
+    <t>68경 6411조 7,432억 2,421만</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>46경 1721조 8,958억 6,847만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>루델밍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>43경 6096조 3908억 1286만</t>
+    <t>45경 5109조 8,480억 2,031만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>43경 847조 2,572억 7,170만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>너굴얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 2574조 9676억 6152만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>40경 1838조 8770억 743만</t>
+    <t>42경 3138조 5,889억 4,039만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,7 +398,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>29경 7613조 5062억 2329만</t>
+    <t>29경 7613조 5,062억 2,329만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 5116조 6755억 7049만</t>
+    <t>29경 6216조 5,359억 3,679만</t>
   </si>
   <si>
     <t>13</t>
@@ -425,31 +425,31 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>23경 9068조 8949억 9120만</t>
+    <t>24경 3354조 9,527억 6,259만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>20경 5428조 7,775억 656만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>설딩</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
   </si>
   <si>
-    <t>19경 7396조 2622억 1029만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19경 6115조 5909억 3806만</t>
+    <t>19경 7396조 2,622억 1,029만</t>
   </si>
   <si>
     <t>16</t>
@@ -461,7 +461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9521만</t>
+    <t>18경 9870조 503억 9,521만</t>
   </si>
   <si>
     <t>17</t>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>16경 3093조 6375억 2234만</t>
+    <t>18경 5875조 8,151억 3,649만</t>
   </si>
   <si>
     <t>18</t>
@@ -488,7 +488,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1960만</t>
+    <t>11경 2907조 6억 1,960만</t>
   </si>
   <si>
     <t>19</t>
@@ -503,7 +503,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>8경 7356조 9674억 8080만</t>
+    <t>9경 1574조 1,762억 1,736만</t>
   </si>
   <si>
     <t>20</t>
@@ -515,7 +515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>8경 4614조 8057억 3683만</t>
+    <t>8경 5991조 208억 856만</t>
   </si>
   <si>
     <t>21</t>
@@ -530,184 +530,682 @@
     <t>118</t>
   </si>
   <si>
-    <t>6경 5564조 1888억 7889만</t>
+    <t>6경 5564조 1,888억 7,889만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>6경 1783조 4,474억 1,098만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>5경 5478조 8492억 3032만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>5경 5316조 8872억 234만</t>
+    <t>5경 5478조 8,492억 3,032만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>애봉얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>3경 4312조 1,092억 5,647만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>상구얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 293조 836억 9607만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>애봉얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
+    <t>3경 944조 1,885억 5,352만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1경 5307조 6,581억 7,894만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 5301조 1,854억 5,754만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4592조 3,595억 1,013만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>1경 1050조 7,102억 6,148만</t>
+  </si>
+  <si>
+    <t>껌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>400경 7671조 206억 8,592만</t>
+  </si>
+  <si>
+    <t>달하나별하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>278경 3626조 7,898억 1,199만</t>
+  </si>
+  <si>
+    <t>라온MS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
+  </si>
+  <si>
+    <t>178경 6628조 7,559억 4,369만</t>
+  </si>
+  <si>
+    <t>왕이된사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>94경 871조 8,885억 5,305만</t>
+  </si>
+  <si>
+    <t>라온DK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>81경 393조 5,887억 8,702만</t>
+  </si>
+  <si>
+    <t>라온PB</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
+  </si>
+  <si>
+    <t>64경 6782조 2,788억 1,062만</t>
+  </si>
+  <si>
+    <t>라온B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
+  </si>
+  <si>
+    <t>41경 1905조 6,743억 903만</t>
+  </si>
+  <si>
+    <t>라온Z</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
+  </si>
+  <si>
+    <t>22경 9361조 9,717억 7,223만</t>
+  </si>
+  <si>
+    <t>와츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5경 9571조 1,335억 7,726만</t>
+  </si>
+  <si>
+    <t>상깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
+  </si>
+  <si>
+    <t>4경 9304조 6,416억 3,411만</t>
+  </si>
+  <si>
+    <t>스터디뱅크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
+  </si>
+  <si>
+    <t>4경 6299조 7,270억 8,249만</t>
+  </si>
+  <si>
+    <t>뚜뭉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>4경 20조 8,028억 8,872만</t>
+  </si>
+  <si>
+    <t>찍먹비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>3경 4977조 1,514억 5,131만</t>
+  </si>
+  <si>
+    <t>StarLink</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
+  </si>
+  <si>
+    <t>3경 2289조 5,029억 5,012만</t>
+  </si>
+  <si>
+    <t>뾰쀼뾰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
+  </si>
+  <si>
+    <t>2경 8524조 8,834억 6,295만</t>
+  </si>
+  <si>
+    <t>오쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
+  </si>
+  <si>
+    <t>2경 6335조 3,243억 7,245만</t>
+  </si>
+  <si>
+    <t>못함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
+  </si>
+  <si>
+    <t>2경 4177조 7,281억 3,707만</t>
+  </si>
+  <si>
+    <t>금하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>2경 400조 2,278억 9,574만</t>
+  </si>
+  <si>
+    <t>쵸비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1경 9935조 5,126억 4,614만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
+  </si>
+  <si>
+    <t>1경 8724조 1,000억 9,409만</t>
+  </si>
+  <si>
+    <t>준준챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>1경 7945조 2,053억 8,538만</t>
+  </si>
+  <si>
+    <t>뚝딱비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>1경 3914조 4,654억 3,849만</t>
+  </si>
+  <si>
+    <t>희다차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>1경 2959조 4,760억 5,668만</t>
+  </si>
+  <si>
+    <t>서두희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>1경 2438조 3,899억 3,059만</t>
+  </si>
+  <si>
+    <t>연이무사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 1579조 6,334억 6,147만</t>
+  </si>
+  <si>
+    <t>널꼬라봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
+  </si>
+  <si>
+    <t>1경 837조 5,201억 2,986만</t>
+  </si>
+  <si>
+    <t>신참치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
     <t>115</t>
   </si>
   <si>
-    <t>2경 5397조 4334억 557만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 4947조 4456억 1260만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1경 4777조 7815억 7357만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4592조 3595억 1013만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>1경 1050조 7102억 6148만</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>301경 902조 9114억 8217만</t>
-  </si>
-  <si>
-    <t>내가바로스타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EA%B0%80%EB%B0%94%EB%A1%9C%EC%8A%A4%ED%83%80</t>
-  </si>
-  <si>
-    <t>91경 9740조 985억 8332만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>83경 3615조 386억 238만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>64경 1795조 6090억 1846만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>50경 4173조 2145억 9205만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>34경 6124조 6964억 5847만</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>32경 4173조 3842억 7684만</t>
+    <t>9262조 3,412억 2,839만</t>
+  </si>
+  <si>
+    <t>걸동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8854조 9,450억 4,226만</t>
+  </si>
+  <si>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>5840조 7,231억 2,937만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>5709조 6,081억 3,936만</t>
+  </si>
+  <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1374경 9967조 4,966억 4,046만</t>
+  </si>
+  <si>
+    <t>요쁘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
+  </si>
+  <si>
+    <t>146경 9210조 5,552억 2,224만</t>
+  </si>
+  <si>
+    <t>나야햄토리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>90경 5508조 2,719억 5,514만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>41경 6897조 9,928억 9,193만</t>
+  </si>
+  <si>
+    <t>딩느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
+  </si>
+  <si>
+    <t>11경 1394조 5,468억 1,937만</t>
+  </si>
+  <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>10경 2197조 1,821억 9,825만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3경 1732조 6,831억 2,430만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>2경 5047조 6,740억 1,185만</t>
+  </si>
+  <si>
+    <t>동작대교</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
+  </si>
+  <si>
+    <t>1경 8332조 1,425억 2,718만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 7475조 7,018억 3,841만</t>
+  </si>
+  <si>
+    <t>나야츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 1971조 6,929억 1,662만</t>
+  </si>
+  <si>
+    <t>날아라순자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 54조 9,994억 7,226만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>8199조 7,296억 9,107만</t>
+  </si>
+  <si>
+    <t>꾸덕행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>6827조 6,217억 3,831만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>5566조 6,120억 2,581만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5,918만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>5145조 1,415억 4,710만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5001조 9,074억 5,704만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>4302조 3,804억 7,260만</t>
+  </si>
+  <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>4197조 2,196억 4,458만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>3413조 2,055억 7,746만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3272조 1,723억 9,516만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3199조 8,996억 1,901만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3199조 3,306억 4,775만</t>
+  </si>
+  <si>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2827조 6,717억 8,583만</t>
+  </si>
+  <si>
+    <t>포이즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2692조 8,173억 3,981만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2632조 6,912억 5,153만</t>
+  </si>
+  <si>
+    <t>궁금증유발</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
+  </si>
+  <si>
+    <t>2280조 94억 3,832만</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>2064조 1,071억 8,482만</t>
+  </si>
+  <si>
+    <t>산과바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1652조 9,566억 8,362만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -716,10 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>25경 4823조 3360억 295만</t>
+    <t>25경 4823조 3,360억 295만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -728,16 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>17경 1218조 674억 1252만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>13경 6804조 8876억 1833만</t>
+    <t>19경 8464조 5,082억 5,270만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -746,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3052억 4003만</t>
+    <t>12경 4306조 3,052억 4,003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -755,16 +1241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 3994조 4731억 2872만</t>
-  </si>
-  <si>
-    <t>익맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>11경 1678조 151억 5811만</t>
+    <t>11경 4105조 7,960억 279만</t>
   </si>
   <si>
     <t>약어</t>
@@ -773,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>10경 4738조 815억 6221만</t>
+    <t>10경 4738조 815억 6,221만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -782,7 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>10경 3451조 2235억 7402만</t>
+    <t>10경 3451조 2,235억 7,402만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -791,16 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 961조 2436억 2444만</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>7경 6739조 6040억 354만</t>
+    <t>9경 3290조 8,758억 715만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -809,7 +1277,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 5079조 6722억 2664만</t>
+    <t>7경 6148조 2,651억 9,696만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -818,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>7경 3059조 933억 2511만</t>
+    <t>7경 3059조 933억 2,511만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -827,10 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>6경 1227조 9270억 3232만</t>
+    <t>6경 7083조 325억 1,634만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -839,7 +1304,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9003억 4099만</t>
+    <t>5경 5228조 9,003억 4,099만</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>2경 4504조 4,834억 827만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -848,7 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 3525조 9083억 7559만</t>
+    <t>2경 4130조 5,641억 7,043만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -857,7 +1331,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3200조 7613억 3554만</t>
+    <t>2경 3271조 2,021억 502만</t>
+  </si>
+  <si>
+    <t>오픈톡쌀숭E</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
+  </si>
+  <si>
+    <t>2경 2936조 4,015억 1,704만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -866,22 +1349,22 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 1323조 7490억 7475만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>2경 927조 1222억 8696만</t>
+    <t>2경 1323조 7,490억 7,475만</t>
+  </si>
+  <si>
+    <t>반가성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
+  </si>
+  <si>
+    <t>1경 9258조 3,650억 1,564만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 6303조 4245억 5058만</t>
+    <t>1경 7139조 5,691억 7,924만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -890,7 +1373,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5844조 3478억 8299만</t>
+    <t>1경 5876조 1,968억 392만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -899,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 3037조 442억 6604만</t>
+    <t>1경 5688조 4,374억 8,127만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -908,10 +1391,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 2752조 370억 300만</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>1경 3148조 5,412억 6,446만</t>
+  </si>
+  <si>
+    <t>니뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>1경 2312조 9,961억 3,717만</t>
+  </si>
+  <si>
+    <t>라똥삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
+  </si>
+  <si>
+    <t>1경 2085조 1,284억 3,396만</t>
+  </si>
+  <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 1856조 4,618억 6,137만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -920,682 +1427,175 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>9836조 9463억 9713만</t>
-  </si>
-  <si>
-    <t>껌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>332경 809조 3742억 6821만</t>
-  </si>
-  <si>
-    <t>달하나별하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>252경 3504조 554억 5589만</t>
-  </si>
-  <si>
-    <t>라온MS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
-  </si>
-  <si>
-    <t>178경 6628조 7559억 4369만</t>
-  </si>
-  <si>
-    <t>왕이된사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>94경 871조 8885억 5305만</t>
-  </si>
-  <si>
-    <t>라온DK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
-  </si>
-  <si>
-    <t>81경 393조 5887억 8702만</t>
-  </si>
-  <si>
-    <t>라온PB</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
-  </si>
-  <si>
-    <t>64경 6782조 2788억 1062만</t>
-  </si>
-  <si>
-    <t>라온B</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
-  </si>
-  <si>
-    <t>41경 1905조 6743억 903만</t>
-  </si>
-  <si>
-    <t>라온Z</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
-  </si>
-  <si>
-    <t>22경 7652조 2452억 2243만</t>
-  </si>
-  <si>
-    <t>와츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5경 8194조 3039억 3062만</t>
-  </si>
-  <si>
-    <t>상깅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
-  </si>
-  <si>
-    <t>4경 7266조 3913억 1163만</t>
-  </si>
-  <si>
-    <t>스터디뱅크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
-  </si>
-  <si>
-    <t>4경 3029조 649억 4734만</t>
-  </si>
-  <si>
-    <t>찍먹비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>3경 4977조 1514억 5131만</t>
-  </si>
-  <si>
-    <t>뚜뭉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3경 3657조 3272억 2731만</t>
-  </si>
-  <si>
-    <t>StarLink</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
-  </si>
-  <si>
-    <t>2경 8824조 775억 3519만</t>
-  </si>
-  <si>
-    <t>뾰쀼뾰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
-  </si>
-  <si>
-    <t>2경 8397조 7328억 5339만</t>
-  </si>
-  <si>
-    <t>오쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
-  </si>
-  <si>
-    <t>2경 4434조 46억 2999만</t>
-  </si>
-  <si>
-    <t>못함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
-  </si>
-  <si>
-    <t>2경 4177조 7281억 3707만</t>
-  </si>
-  <si>
-    <t>금하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>1경 9337조 3545억 8186만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
-  </si>
-  <si>
-    <t>1경 8488조 6346억 3768만</t>
-  </si>
-  <si>
-    <t>쵸비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1경 7791조 6302억 4935만</t>
-  </si>
-  <si>
-    <t>준준챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>1경 6669조 9089억 6233만</t>
-  </si>
-  <si>
-    <t>서두희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>1경 1967조 9252억 4458만</t>
-  </si>
-  <si>
-    <t>뚝딱비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>1경 1795조 8296억 3783만</t>
-  </si>
-  <si>
-    <t>희다차</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
-  </si>
-  <si>
-    <t>1경 937조 8369억 4859만</t>
-  </si>
-  <si>
-    <t>널꼬라봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
-  </si>
-  <si>
-    <t>1경 438조 9014억 3803만</t>
-  </si>
-  <si>
-    <t>연이무사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 345조 3706억 8929만</t>
-  </si>
-  <si>
-    <t>신참치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>8917조 6314억 1691만</t>
-  </si>
-  <si>
-    <t>걸동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7622조 3899억 1418만</t>
-  </si>
-  <si>
-    <t>빈수르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>5497조 1301억 4107만</t>
-  </si>
-  <si>
-    <t>김보들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
-  </si>
-  <si>
-    <t>4910조 9077억 6257만</t>
-  </si>
-  <si>
-    <t>종리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1141경 5826조 622억 4118만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>41경 6897조 9928억 9193만</t>
-  </si>
-  <si>
-    <t>몰라츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3경 442조 6040억 7853만</t>
-  </si>
-  <si>
-    <t>정육츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2경 5047조 6740억 1185만</t>
-  </si>
-  <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 6775조 698억 3190만</t>
-  </si>
-  <si>
-    <t>수달츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>7688조 1247억 9300만</t>
-  </si>
-  <si>
-    <t>꾸덕행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5501조 5848억 8198만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5471조 457억 5918만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>5001조 9074억 5704만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>4016조 3966억 4068만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>3210조 5504억 71만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2941조 7812억 6779만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>2764조 8243억 527만</t>
-  </si>
-  <si>
-    <t>화정츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2367조 729억 7956만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+    <t>1경 2,945억 9,039만</t>
+  </si>
+  <si>
+    <t>러너</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
+  </si>
+  <si>
+    <t>6443조 2,165억 2,470만</t>
+  </si>
+  <si>
+    <t>해찬나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>5796조 3,675억 8,873만</t>
+  </si>
+  <si>
+    <t>갓겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>341조 6,408억 9,657만</t>
+  </si>
+  <si>
+    <t>베르카암프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>528조 2,903억 8,564만</t>
+  </si>
+  <si>
+    <t>결기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
   </si>
   <si>
     <t>109</t>
   </si>
   <si>
-    <t>2142조 8887억 2585만</t>
-  </si>
-  <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>2064조 1071억 8482만</t>
-  </si>
-  <si>
-    <t>산과바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1593조 2985억 7905만</t>
-  </si>
-  <si>
-    <t>호야빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>1462조 9569억 6314만</t>
-  </si>
-  <si>
-    <t>서전붕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
-  </si>
-  <si>
-    <t>1153조 2178억 8567만</t>
-  </si>
-  <si>
-    <t>루린츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>549조 5329억 3684만</t>
-  </si>
-  <si>
-    <t>묘피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
-  </si>
-  <si>
-    <t>518조 9139억 1803만</t>
-  </si>
-  <si>
-    <t>히히힣히힣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
-  </si>
-  <si>
-    <t>434조 4195억 1364만</t>
-  </si>
-  <si>
-    <t>주냥츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
-  </si>
-  <si>
-    <t>409조 5538억 8907만</t>
-  </si>
-  <si>
-    <t>뽀야츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>360조 5925억 9466만</t>
-  </si>
-  <si>
-    <t>하치츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
-  </si>
-  <si>
-    <t>334조 8942억 3290만</t>
-  </si>
-  <si>
-    <t>도리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>313조 6065억 4365만</t>
-  </si>
-  <si>
-    <t>새벽츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EB%B2%BD%EC%B8%84</t>
+    <t>510조 8,522억 3,023만</t>
+  </si>
+  <si>
+    <t>후추양조장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>485조 6,946억 3,853만</t>
+  </si>
+  <si>
+    <t>온우사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>462조 6,492억 9,502만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>404조 5,216억 8,702만</t>
+  </si>
+  <si>
+    <t>지존승준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
+  </si>
+  <si>
+    <t>358조 5,526억 3,562만</t>
+  </si>
+  <si>
+    <t>말랑랑말이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>319조 6,634억 9,916만</t>
+  </si>
+  <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>281조 8,365억 8,619만</t>
+  </si>
+  <si>
+    <t>눅이마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>250조 8,464억 5,632만</t>
+  </si>
+  <si>
+    <t>성식대군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>185조 2,853억 5,484만</t>
+  </si>
+  <si>
+    <t>한로얘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>183조 8,405억 4,218만</t>
+  </si>
+  <si>
+    <t>태환이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>166조 3,857억 4,091만</t>
+  </si>
+  <si>
+    <t>버미겨리0</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
   </si>
   <si>
     <t>107</t>
   </si>
   <si>
-    <t>152조 3767억 9006만</t>
-  </si>
-  <si>
-    <t>비먀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
-  </si>
-  <si>
-    <t>80조 554억 3819만</t>
-  </si>
-  <si>
-    <t>우솝쁘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%81%98</t>
-  </si>
-  <si>
-    <t>71조 2033억 5002만</t>
-  </si>
-  <si>
-    <t>베르카암프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B4%EC%B9%B4%EC%95%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>525조 9863억 4925만</t>
-  </si>
-  <si>
-    <t>결기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>509조 1897억 5936만</t>
-  </si>
-  <si>
-    <t>온우사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>419조 5399억 8694만</t>
-  </si>
-  <si>
-    <t>우댕이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8C%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>399조 6484억 9953만</t>
-  </si>
-  <si>
-    <t>후추양조장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>362조 1131억 5634만</t>
-  </si>
-  <si>
-    <t>썬콜원준띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>346조 2082억 1765만</t>
-  </si>
-  <si>
-    <t>지존승준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
-  </si>
-  <si>
-    <t>336조 7783억 4223만</t>
-  </si>
-  <si>
-    <t>말랑랑말이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>278조 7185억 8389만</t>
-  </si>
-  <si>
-    <t>날씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
-  </si>
-  <si>
-    <t>272조 3120억 2688만</t>
-  </si>
-  <si>
-    <t>눅이마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%85%EC%9D%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>211조 8253억 2618만</t>
-  </si>
-  <si>
-    <t>성식대군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>184조 5133억 1640만</t>
-  </si>
-  <si>
-    <t>한로얘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
-  </si>
-  <si>
-    <t>160조 7067억 9801만</t>
-  </si>
-  <si>
-    <t>태환이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>145조 5584억 2636만</t>
+    <t>154조 7,346억 1,516만</t>
+  </si>
+  <si>
+    <t>멍뭉이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%AD%89%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>153조 5,425억 984만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1604,7 +1604,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>137조 425억 9602만</t>
+    <t>138조 6,113억 1,862만</t>
+  </si>
+  <si>
+    <t>벵글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
+  </si>
+  <si>
+    <t>134조 4,998억 5,770만</t>
+  </si>
+  <si>
+    <t>NSYN</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NSYN</t>
+  </si>
+  <si>
+    <t>130조 5,440억 9,674만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1613,34 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>127조 8393억 5575만</t>
-  </si>
-  <si>
-    <t>버미겨리0</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
-  </si>
-  <si>
-    <t>126조 7033억 6964만</t>
-  </si>
-  <si>
-    <t>벵글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
-  </si>
-  <si>
-    <t>119조 5540억 221만</t>
-  </si>
-  <si>
-    <t>NSYN</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=NSYN</t>
-  </si>
-  <si>
-    <t>115조 7425억 9475만</t>
+    <t>128조 1,033억 8,744만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1649,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>95조 511억 2086만</t>
+    <t>97조 5,494억 6,110만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1658,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>81조 6185억 1553만</t>
+    <t>82조 5,120억 1,455만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1670,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>54조 8740억 4671만</t>
+    <t>55조 296억 2,286만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1679,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>31조 4415억 2522만</t>
+    <t>31조 9,560억 6,444만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1688,16 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>20조 8845억 2964만</t>
-  </si>
-  <si>
-    <t>짜도이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%8F%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>18조 8067억 1459만</t>
+    <t>20조 8,845억 2,964만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1709,7 +1691,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>14조 1683억 1440만</t>
+    <t>14조 6,666억 5,274만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1721,13 +1703,22 @@
     <t>102</t>
   </si>
   <si>
-    <t>12조 5181억 909만</t>
+    <t>12조 8,251억 2,721만</t>
+  </si>
+  <si>
+    <t>이제명확찢</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A0%9C%EB%AA%85%ED%99%95%EC%B0%A2</t>
+  </si>
+  <si>
+    <t>10조 9,536억 4,351만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>6조 1382억 5847만</t>
+    <t>6조 4,425억 8,179만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1739,7 +1730,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 761억 6312만</t>
+    <t>2조 4,360억 4,592만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1754,7 +1745,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1191억 976만</t>
+    <t>1,456억 5,188만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1769,7 +1760,7 @@
     <t>82</t>
   </si>
   <si>
-    <t>90억 5426만</t>
+    <t>112억 5,433만</t>
   </si>
 </sst>
 </file>
@@ -2143,7 +2134,7 @@
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" customWidth="1"/>
-    <col min="11" max="11" width="47.7109375" customWidth="1"/>
+    <col min="11" max="11" width="48.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2256,99 +2247,99 @@
         <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2389,7 +2380,7 @@
         <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2407,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2667,7 +2658,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>103</v>
@@ -2699,7 +2690,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>107</v>
@@ -2728,13 +2719,13 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2745,25 +2736,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>117</v>
@@ -2891,7 +2882,7 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2923,7 +2914,7 @@
         <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -3083,7 +3074,7 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>162</v>
@@ -3112,7 +3103,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>166</v>
@@ -3132,22 +3123,22 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>171</v>
@@ -3164,16 +3155,16 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>82</v>
@@ -3208,13 +3199,13 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3225,25 +3216,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>185</v>
@@ -3275,10 +3266,10 @@
         <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3289,16 +3280,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -3307,10 +3298,10 @@
         <v>157</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3321,28 +3312,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3353,16 +3344,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -3371,10 +3362,10 @@
         <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3428,7 +3419,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3472,28 +3463,28 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3504,28 +3495,28 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3536,28 +3527,28 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3568,28 +3559,28 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3600,28 +3591,28 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3647,13 +3638,13 @@
         <v>157</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>223</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3676,16 +3667,16 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3708,16 +3699,16 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3728,13 +3719,13 @@
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -3743,13 +3734,13 @@
         <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3757,31 +3748,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3792,13 +3783,13 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -3807,13 +3798,13 @@
         <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3824,28 +3815,28 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>242</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3868,16 +3859,16 @@
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3900,16 +3891,16 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3932,16 +3923,16 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>251</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3964,16 +3955,16 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>254</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3996,16 +3987,16 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>257</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4028,16 +4019,16 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>260</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4060,16 +4051,16 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4080,28 +4071,28 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>265</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4112,28 +4103,28 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>166</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4144,13 +4135,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -4159,13 +4150,13 @@
         <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4176,13 +4167,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -4191,13 +4182,13 @@
         <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4208,28 +4199,28 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4237,16 +4228,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -4255,13 +4246,13 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4272,28 +4263,28 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
+        <v>282</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>33</v>
+        <v>282</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>283</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4301,7 +4292,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>285</v>
@@ -4316,16 +4307,16 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4333,16 +4324,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -4351,13 +4342,13 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4365,16 +4356,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -4383,13 +4374,13 @@
         <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4397,31 +4388,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4464,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4511,275 +4502,275 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>307</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>307</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -4788,126 +4779,126 @@
         <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>189</v>
+        <v>335</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -4916,126 +4907,126 @@
         <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5044,30 +5035,30 @@
         <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -5076,126 +5067,126 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>356</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>356</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>189</v>
+        <v>335</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>356</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>263</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -5204,30 +5195,30 @@
         <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>189</v>
+        <v>367</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -5236,30 +5227,30 @@
         <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
@@ -5268,126 +5259,126 @@
         <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>189</v>
+        <v>367</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
+        <v>367</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -5396,77 +5387,77 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>342</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>184</v>
+        <v>367</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -5509,7 +5500,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5518,7 +5509,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5556,307 +5547,307 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>396</v>
+        <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>396</v>
+        <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>396</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>409</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>409</v>
+        <v>112</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>416</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -5865,62 +5856,62 @@
         <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>416</v>
+        <v>241</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>423</v>
+        <v>166</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -5929,62 +5920,62 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>384</v>
+        <v>241</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>423</v>
+        <v>241</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -5993,50 +5984,50 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>423</v>
+        <v>241</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>436</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
@@ -6054,21 +6045,21 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>423</v>
+        <v>180</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>145</v>
@@ -6086,129 +6077,129 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>423</v>
+        <v>180</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>449</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>453</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -6217,126 +6208,126 @@
         <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>423</v>
+        <v>180</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -6345,30 +6336,30 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>452</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -6377,113 +6368,81 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>452</v>
+        <v>287</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>474</v>
+        <v>367</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6513,7 +6472,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6530,7 +6488,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6574,13 +6532,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
@@ -6589,13 +6547,13 @@
         <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6606,13 +6564,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -6621,13 +6579,13 @@
         <v>157</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6638,28 +6596,28 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6670,28 +6628,28 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6702,28 +6660,28 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6734,28 +6692,28 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6766,28 +6724,28 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6798,28 +6756,28 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6830,28 +6788,28 @@
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>452</v>
+        <v>504</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6859,31 +6817,31 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6894,28 +6852,28 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6926,28 +6884,28 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6958,28 +6916,28 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6990,28 +6948,28 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7022,13 +6980,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -7037,13 +6995,13 @@
         <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7054,13 +7012,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -7069,13 +7027,13 @@
         <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7086,28 +7044,28 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7118,28 +7076,28 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7150,28 +7108,28 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>511</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7182,13 +7140,13 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -7200,10 +7158,10 @@
         <v>511</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7214,13 +7172,13 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -7229,13 +7187,13 @@
         <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7246,13 +7204,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -7261,13 +7219,13 @@
         <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7278,13 +7236,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -7296,10 +7254,10 @@
         <v>511</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7310,28 +7268,28 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7339,31 +7297,31 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7374,28 +7332,28 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7403,7 +7361,7 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>59</v>
@@ -7412,22 +7370,22 @@
         <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7435,16 +7393,16 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -7453,13 +7411,13 @@
         <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7467,31 +7425,31 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7499,31 +7457,31 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>580</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -95,7 +95,7 @@
     <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중  문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
   </si>
   <si>
     <t>설익은체리</t>
@@ -251,7 +251,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>280경 3220조 6,404억 6,122만</t>
+    <t>280경 3220조 6404억 6122만</t>
   </si>
   <si>
     <t>2</t>
@@ -263,7 +263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>231경 7865조 5,718억 420만</t>
+    <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>186경 7071조 3,782억 8,079만</t>
+    <t>186경 7071조 3782억 8079만</t>
   </si>
   <si>
     <t>4</t>
@@ -299,7 +299,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>105경 4731조 5,416억 8,730만</t>
+    <t>105경 4731조 5416억 8730만</t>
   </si>
   <si>
     <t>5</t>
@@ -314,7 +314,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>85경 8894조 1,952억 8,378만</t>
+    <t>85경 8894조 1952억 8378만</t>
   </si>
   <si>
     <t>6</t>
@@ -326,7 +326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7,432억 2,421만</t>
+    <t>68경 6411조 7432억 2421만</t>
   </si>
   <si>
     <t>7</t>
@@ -338,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8,958억 6,847만</t>
+    <t>46경 1721조 8958억 6847만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>45경 5109조 8,480억 2,031만</t>
+    <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
     <t>9</t>
@@ -368,7 +368,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>43경 847조 2,572억 7,170만</t>
+    <t>43경 847조 2572억 7170만</t>
   </si>
   <si>
     <t>10</t>
@@ -380,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5,889억 4,039만</t>
+    <t>42경 3138조 5889억 4039만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,7 +398,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>29경 7613조 5,062억 2,329만</t>
+    <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 6216조 5,359억 3,679만</t>
+    <t>29경 6216조 5359억 3679만</t>
   </si>
   <si>
     <t>13</t>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>24경 3354조 9,527억 6,259만</t>
+    <t>24경 3354조 9527억 6259만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7,775억 656만</t>
+    <t>20경 5428조 7775억 656만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,7 +449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
   </si>
   <si>
-    <t>19경 7396조 2,622억 1,029만</t>
+    <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
     <t>16</t>
@@ -461,7 +461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9,521만</t>
+    <t>18경 9870조 503억 9521만</t>
   </si>
   <si>
     <t>17</t>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8,151억 3,649만</t>
+    <t>18경 5875조 8151억 3649만</t>
   </si>
   <si>
     <t>18</t>
@@ -488,7 +488,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1,960만</t>
+    <t>11경 2907조 6억 1960만</t>
   </si>
   <si>
     <t>19</t>
@@ -503,7 +503,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>9경 1574조 1,762억 1,736만</t>
+    <t>9경 1574조 1762억 1736만</t>
   </si>
   <si>
     <t>20</t>
@@ -530,7 +530,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>6경 5564조 1,888억 7,889만</t>
+    <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
     <t>22</t>
@@ -542,7 +542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4,474억 1,098만</t>
+    <t>6경 1783조 4474억 1098만</t>
   </si>
   <si>
     <t>23</t>
@@ -554,7 +554,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>5경 5478조 8,492억 3,032만</t>
+    <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
     <t>24</t>
@@ -572,7 +572,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>3경 4312조 1,092억 5,647만</t>
+    <t>3경 4312조 1092억 5647만</t>
   </si>
   <si>
     <t>25</t>
@@ -584,7 +584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1,885억 5,352만</t>
+    <t>3경 944조 1885억 5352만</t>
   </si>
   <si>
     <t>26</t>
@@ -596,7 +596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6,581억 7,894만</t>
+    <t>1경 5307조 6581억 7894만</t>
   </si>
   <si>
     <t>27</t>
@@ -608,7 +608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5301조 1,854억 5,754만</t>
+    <t>1경 5301조 1854억 5754만</t>
   </si>
   <si>
     <t>28</t>
@@ -623,7 +623,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>1경 4592조 3,595억 1,013만</t>
+    <t>1경 4592조 3595억 1013만</t>
   </si>
   <si>
     <t>29</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7,102억 6,148만</t>
+    <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -644,7 +644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>400경 7671조 206억 8,592만</t>
+    <t>400경 7671조 206억 8592만</t>
   </si>
   <si>
     <t>달하나별하나</t>
@@ -659,7 +659,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>278경 3626조 7,898억 1,199만</t>
+    <t>278경 3626조 7898억 1199만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
   </si>
   <si>
-    <t>178경 6628조 7,559억 4,369만</t>
+    <t>178경 6628조 7559억 4369만</t>
   </si>
   <si>
     <t>왕이된사나이</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>94경 871조 8,885억 5,305만</t>
+    <t>94경 871조 8885억 5305만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -689,7 +689,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>81경 393조 5,887억 8,702만</t>
+    <t>81경 393조 5887억 8702만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -698,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
   </si>
   <si>
-    <t>64경 6782조 2,788억 1,062만</t>
+    <t>64경 6782조 2788억 1062만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>41경 1905조 6,743억 903만</t>
+    <t>41경 1905조 6743억 903만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 9361조 9,717억 7,223만</t>
+    <t>22경 9361조 9717억 7223만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
   </si>
   <si>
-    <t>5경 9571조 1,335억 7,726만</t>
+    <t>5경 9571조 1335억 7726만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -734,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>4경 9304조 6,416억 3,411만</t>
+    <t>4경 9304조 6416억 3411만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -743,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 6299조 7,270억 8,249만</t>
+    <t>4경 6299조 7270억 8249만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -755,7 +755,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>4경 20조 8,028억 8,872만</t>
+    <t>4경 20조 8028억 8872만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -764,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>3경 4977조 1,514억 5,131만</t>
+    <t>3경 4977조 1514억 5131만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -773,7 +773,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 2289조 5,029억 5,012만</t>
+    <t>3경 2289조 5029억 5012만</t>
   </si>
   <si>
     <t>뾰쀼뾰</t>
@@ -782,7 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
   </si>
   <si>
-    <t>2경 8524조 8,834억 6,295만</t>
+    <t>2경 8524조 8834억 6295만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -791,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
   </si>
   <si>
-    <t>2경 6335조 3,243억 7,245만</t>
+    <t>2경 6335조 3243억 7245만</t>
   </si>
   <si>
     <t>못함</t>
@@ -800,7 +800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 4177조 7,281억 3,707만</t>
+    <t>2경 4177조 7281억 3707만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -809,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 400조 2,278억 9,574만</t>
+    <t>2경 400조 2278억 9574만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -821,13 +821,13 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1경 9935조 5,126억 4,614만</t>
+    <t>1경 9935조 5126억 4614만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 8724조 1,000억 9,409만</t>
+    <t>1경 8724조 1000억 9409만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 7945조 2,053억 8,538만</t>
+    <t>1경 7945조 2053억 8538만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 3914조 4,654억 3,849만</t>
+    <t>1경 3914조 4654억 3849만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -854,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>1경 2959조 4,760억 5,668만</t>
+    <t>1경 2959조 4760억 5668만</t>
   </si>
   <si>
     <t>서두희</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 2438조 3,899억 3,059만</t>
+    <t>1경 2438조 3899억 3059만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1579조 6,334억 6,147만</t>
+    <t>1경 1579조 6334억 6147만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 837조 5,201억 2,986만</t>
+    <t>1경 837조 5201억 2986만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -893,7 +893,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9262조 3,412억 2,839만</t>
+    <t>9262조 3412억 2839만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -902,7 +902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>8854조 9,450억 4,226만</t>
+    <t>8854조 9450억 4226만</t>
   </si>
   <si>
     <t>김보들</t>
@@ -911,7 +911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
   </si>
   <si>
-    <t>5840조 7,231억 2,937만</t>
+    <t>5840조 7231억 2937만</t>
   </si>
   <si>
     <t>30</t>
@@ -926,7 +926,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5709조 6,081억 3,936만</t>
+    <t>5709조 6081억 3936만</t>
   </si>
   <si>
     <t>종리츄</t>
@@ -935,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1374경 9967조 4,966억 4,046만</t>
+    <t>1374경 9967조 4966억 4046만</t>
   </si>
   <si>
     <t>요쁘</t>
@@ -944,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
   </si>
   <si>
-    <t>146경 9210조 5,552억 2,224만</t>
+    <t>146경 9210조 5552억 2224만</t>
   </si>
   <si>
     <t>나야햄토리</t>
@@ -953,13 +953,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>90경 5508조 2,719억 5,514만</t>
+    <t>90경 5508조 2719억 5514만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>41경 6897조 9,928억 9,193만</t>
+    <t>41경 6897조 9928억 9193만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -968,7 +968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
   </si>
   <si>
-    <t>11경 1394조 5,468억 1,937만</t>
+    <t>11경 1394조 5468억 1937만</t>
   </si>
   <si>
     <t>독고사수</t>
@@ -977,7 +977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>10경 2197조 1,821억 9,825만</t>
+    <t>10경 2197조 1821억 9825만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -986,7 +986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>3경 1732조 6,831억 2,430만</t>
+    <t>3경 1732조 6831억 2430만</t>
   </si>
   <si>
     <t>정육츄</t>
@@ -998,7 +998,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2경 5047조 6,740억 1,185만</t>
+    <t>2경 5047조 6740억 1185만</t>
   </si>
   <si>
     <t>동작대교</t>
@@ -1007,7 +1007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
   </si>
   <si>
-    <t>1경 8332조 1,425억 2,718만</t>
+    <t>1경 8332조 1425억 2718만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1016,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 7475조 7,018억 3,841만</t>
+    <t>1경 7475조 7018억 3841만</t>
   </si>
   <si>
     <t>나야츄</t>
@@ -1025,7 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 1971조 6,929억 1,662만</t>
+    <t>1경 1971조 6929억 1662만</t>
   </si>
   <si>
     <t>날아라순자</t>
@@ -1037,7 +1037,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 54조 9,994억 7,226만</t>
+    <t>1경 54조 9994억 7226만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1046,7 +1046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>8199조 7,296억 9,107만</t>
+    <t>8199조 7296억 9107만</t>
   </si>
   <si>
     <t>꾸덕행</t>
@@ -1058,7 +1058,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>6827조 6,217억 3,831만</t>
+    <t>6827조 6217억 3831만</t>
   </si>
   <si>
     <t>lNOVAl</t>
@@ -1067,7 +1067,7 @@
     <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
   </si>
   <si>
-    <t>5566조 6,120억 2,581만</t>
+    <t>5566조 6120억 2581만</t>
   </si>
   <si>
     <t>천상츄</t>
@@ -1076,7 +1076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>5471조 457억 5,918만</t>
+    <t>5471조 457억 5918만</t>
   </si>
   <si>
     <t>넹또</t>
@@ -1085,7 +1085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
   </si>
   <si>
-    <t>5145조 1,415억 4,710만</t>
+    <t>5145조 1415억 4710만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1094,7 +1094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>5001조 9,074억 5,704만</t>
+    <t>5001조 9074억 5704만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1103,7 +1103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>4302조 3,804억 7,260만</t>
+    <t>4302조 3804억 7260만</t>
   </si>
   <si>
     <t>직만</t>
@@ -1112,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>4197조 2,196억 4,458만</t>
+    <t>4197조 2196억 4458만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>3413조 2,055억 7,746만</t>
+    <t>3413조 2055억 7746만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1133,7 +1133,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>3272조 1,723억 9,516만</t>
+    <t>3272조 1723억 9516만</t>
   </si>
   <si>
     <t>나야김대장</t>
@@ -1142,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>3199조 8,996억 1,901만</t>
+    <t>3199조 8996억 1901만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1151,7 +1151,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>3199조 3,306억 4,775만</t>
+    <t>3199조 3306억 4775만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1160,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
-    <t>2827조 6,717억 8,583만</t>
+    <t>2827조 6717억 8583만</t>
   </si>
   <si>
     <t>포이즈</t>
@@ -1169,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
   </si>
   <si>
-    <t>2692조 8,173억 3,981만</t>
+    <t>2692조 8173억 3981만</t>
   </si>
   <si>
     <t>푸들츄</t>
@@ -1178,7 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>2632조 6,912억 5,153만</t>
+    <t>2632조 6912억 5153만</t>
   </si>
   <si>
     <t>궁금증유발</t>
@@ -1187,7 +1187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
   </si>
   <si>
-    <t>2280조 94억 3,832만</t>
+    <t>2280조 94억 3832만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -1196,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>2064조 1,071억 8,482만</t>
+    <t>2064조 1071억 8482만</t>
   </si>
   <si>
     <t>산과바다</t>
@@ -1205,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1652조 9,566억 8,362만</t>
+    <t>1652조 9566억 8362만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 4823조 3,360억 295만</t>
+    <t>25경 4823조 3360억 295만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5,082억 5,270만</t>
+    <t>19경 8464조 5082억 5270만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -1232,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3,052억 4,003만</t>
+    <t>12경 4306조 3052억 4003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1241,7 +1241,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7,960억 279만</t>
+    <t>11경 4105조 7960억 279만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>10경 6154조 8799억 4676만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1250,16 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>10경 4738조 815억 6,221만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>10경 3451조 2,235억 7,402만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1268,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3290조 8,758억 715만</t>
+    <t>9경 3423조 3510억 8891만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -1277,7 +1277,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2,651억 9,696만</t>
+    <t>7경 6148조 2651억 9696만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1286,16 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>7경 3059조 933억 2,511만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>6경 7083조 325억 1,634만</t>
+    <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1304,7 +1304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9,003억 4,099만</t>
+    <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1313,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4,834억 827만</t>
+    <t>2경 4504조 4834억 827만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -1322,7 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 4130조 5,641억 7,043만</t>
+    <t>2경 4130조 5641억 7043만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -1331,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2,021억 502만</t>
+    <t>2경 3271조 2021억 502만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1340,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
   </si>
   <si>
-    <t>2경 2936조 4,015억 1,704만</t>
+    <t>2경 2936조 4015억 1704만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1349,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 1323조 7,490억 7,475만</t>
+    <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -1358,13 +1358,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3,650억 1,564만</t>
+    <t>1경 9258조 3650억 1564만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5,691억 7,924만</t>
+    <t>1경 7139조 5691억 7924만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -1373,7 +1373,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1,968억 392만</t>
+    <t>1경 5876조 1968억 392만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -1382,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 5688조 4,374억 8,127만</t>
+    <t>1경 5688조 4374억 8127만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1391,7 +1391,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5,412억 6,446만</t>
+    <t>1경 3148조 5412억 6446만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -1400,7 +1400,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 2312조 9,961억 3,717만</t>
+    <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
     <t>라똥삐</t>
@@ -1409,7 +1409,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
   </si>
   <si>
-    <t>1경 2085조 1,284억 3,396만</t>
+    <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -1418,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
   </si>
   <si>
-    <t>1경 1856조 4,618억 6,137만</t>
+    <t>1경 1856조 4618억 6137만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -1427,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2,945억 9,039만</t>
+    <t>1경 2945억 9039만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1436,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2,165억 2,470만</t>
+    <t>6443조 2165억 2470만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -1445,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3,675억 8,873만</t>
+    <t>5796조 3675억 8873만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -1454,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>341조 6,408억 9,657만</t>
+    <t>341조 6408억 9657만</t>
   </si>
   <si>
     <t>베르카암프</t>
@@ -1466,7 +1466,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>528조 2,903억 8,564만</t>
+    <t>528조 2903억 8564만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1478,7 +1478,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>510조 8,522억 3,023만</t>
+    <t>510조 8522억 3023만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1487,7 +1487,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>485조 6,946억 3,853만</t>
+    <t>485조 6946억 3853만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1496,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EC%9A%B0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>462조 6,492억 9,502만</t>
+    <t>462조 6492억 9502만</t>
   </si>
   <si>
     <t>썬콜원준띠</t>
@@ -1505,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
   </si>
   <si>
-    <t>404조 5,216억 8,702만</t>
+    <t>404조 5216억 8702만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1514,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
   </si>
   <si>
-    <t>358조 5,526억 3,562만</t>
+    <t>358조 5526억 3562만</t>
   </si>
   <si>
     <t>말랑랑말이</t>
@@ -1523,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>319조 6,634억 9,916만</t>
+    <t>319조 6634억 9916만</t>
   </si>
   <si>
     <t>날씬</t>
@@ -1532,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>281조 8,365억 8,619만</t>
+    <t>281조 8365억 8619만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1544,7 +1544,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>250조 8,464억 5,632만</t>
+    <t>250조 8464억 5632만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1553,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
   </si>
   <si>
-    <t>185조 2,853억 5,484만</t>
+    <t>185조 2853억 5484만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1565,7 +1565,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>183조 8,405억 4,218만</t>
+    <t>183조 8405억 4218만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>166조 3,857억 4,091만</t>
+    <t>166조 3857억 4091만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1586,7 +1586,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>154조 7,346억 1,516만</t>
+    <t>154조 7346억 1516만</t>
   </si>
   <si>
     <t>멍뭉이다</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%AD%89%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>153조 5,425억 984만</t>
+    <t>153조 5425억 984만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1604,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
   </si>
   <si>
-    <t>138조 6,113억 1,862만</t>
+    <t>138조 6113억 1862만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>134조 4,998억 5,770만</t>
+    <t>134조 4998억 5770만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>130조 5,440억 9,674만</t>
+    <t>130조 5440억 9674만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>128조 1,033억 8,744만</t>
+    <t>128조 1033억 8744만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>97조 5,494억 6,110만</t>
+    <t>97조 5494억 6110만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>82조 5,120억 1,455만</t>
+    <t>82조 5120억 1455만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1661,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>55조 296억 2,286만</t>
+    <t>55조 296억 2286만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1670,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>31조 9,560억 6,444만</t>
+    <t>31조 9560억 6444만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1679,7 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>20조 8,845억 2,964만</t>
+    <t>20조 8845억 2964만</t>
   </si>
   <si>
     <t>개념독점</t>
@@ -1691,7 +1691,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>14조 6,666억 5,274만</t>
+    <t>14조 6666억 5274만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1703,7 +1703,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>12조 8,251억 2,721만</t>
+    <t>12조 8251억 2721만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1712,13 +1712,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A0%9C%EB%AA%85%ED%99%95%EC%B0%A2</t>
   </si>
   <si>
-    <t>10조 9,536억 4,351만</t>
+    <t>10조 9536억 4351만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>6조 4,425억 8,179만</t>
+    <t>6조 4425억 8179만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1730,7 +1730,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 4,360억 4,592만</t>
+    <t>2조 4360억 4592만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1745,7 +1745,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1,456억 5,188만</t>
+    <t>1456억 5188만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1760,7 +1760,7 @@
     <t>82</t>
   </si>
   <si>
-    <t>112억 5,433만</t>
+    <t>112억 5433만</t>
   </si>
 </sst>
 </file>
@@ -2134,7 +2134,7 @@
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" customWidth="1"/>
-    <col min="11" max="11" width="48.7109375" customWidth="1"/>
+    <col min="11" max="11" width="47.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2407,7 +2407,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3419,7 +3419,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4464,7 +4464,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5509,7 +5509,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5693,7 +5693,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>112</v>
@@ -5725,7 +5725,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>112</v>
@@ -5821,10 +5821,10 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>419</v>
@@ -5853,10 +5853,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>422</v>
@@ -6488,7 +6488,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -80,7 +80,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>44</t>
+    <t>45</t>
   </si>
   <si>
     <t>1위</t>
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>4위</t>
@@ -167,7 +167,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>57</t>
+    <t>59</t>
   </si>
   <si>
     <t>3위</t>
@@ -194,10 +194,10 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2804</t>
-  </si>
-  <si>
-    <t>151위</t>
+    <t>2833</t>
+  </si>
+  <si>
+    <t>153위</t>
   </si>
   <si>
     <t>4842조 9452억 2908만</t>
@@ -263,6 +263,9 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
+    <t>125</t>
+  </si>
+  <si>
     <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
@@ -278,10 +281,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>186경 7071조 3782억 8079만</t>
+    <t>186경 7791조 7180억 8576만</t>
   </si>
   <si>
     <t>4</t>
@@ -311,6 +311,9 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
   </si>
   <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
@@ -326,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7432억 2421만</t>
+    <t>70경 3411조 543억 9761만</t>
   </si>
   <si>
     <t>7</t>
@@ -338,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8958억 6847만</t>
+    <t>46경 5893조 4558억 8082만</t>
   </si>
   <si>
     <t>8</t>
@@ -380,7 +383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5889억 4039만</t>
+    <t>42경 3171조 6570억 2266만</t>
   </si>
   <si>
     <t>11</t>
@@ -392,25 +395,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>바이퍼</t>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>29경 7613조 5062억 2329만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>29경 6216조 5359억 3679만</t>
+    <t>29경 6457조 7252억 8350만</t>
   </si>
   <si>
     <t>13</t>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>24경 3354조 9527억 6259만</t>
+    <t>26경 304조 7942억 7478만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7775억 656만</t>
+    <t>20경 5726조 4261억 8056만</t>
   </si>
   <si>
     <t>15</t>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8151억 3649만</t>
+    <t>18경 9155조 2333억 8429만</t>
   </si>
   <si>
     <t>18</t>
@@ -515,7 +515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>8경 5991조 208억 856만</t>
+    <t>8경 6856조 4210억 2441만</t>
   </si>
   <si>
     <t>21</t>
@@ -542,7 +542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4474억 1098만</t>
+    <t>6경 1816조 4690억 8482만</t>
   </si>
   <si>
     <t>23</t>
@@ -584,31 +584,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1885억 5352만</t>
+    <t>3경 954조 4911억 7546만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 5656조 4416억 3248만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
     <t>설콩순</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6581억 7894만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1경 5301조 1854억 5754만</t>
+    <t>1경 5368조 6516억 4049만</t>
   </si>
   <si>
     <t>28</t>
@@ -698,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
   </si>
   <si>
-    <t>64경 6782조 2788억 1062만</t>
+    <t>68경 8923조 3781억 4276만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 9361조 9717억 7223만</t>
+    <t>22경 9403조 3418억 9373만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -734,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>4경 9304조 6416억 3411만</t>
+    <t>5경 1090조 1032억 7666만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -764,7 +764,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>3경 4977조 1514억 5131만</t>
+    <t>3경 8257조 4700억 1545만</t>
+  </si>
+  <si>
+    <t>뾰쀼뾰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
+  </si>
+  <si>
+    <t>3경 6359조 5733억 8430만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -773,16 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 2289조 5029억 5012만</t>
-  </si>
-  <si>
-    <t>뾰쀼뾰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
-  </si>
-  <si>
-    <t>2경 8524조 8834억 6295만</t>
+    <t>3경 2702조 2900억 8953만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -800,7 +800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 4177조 7281억 3707만</t>
+    <t>2경 4569조 7644억 2007만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -809,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 400조 2278억 9574만</t>
+    <t>2경 865조 3081억 1725만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -821,13 +821,13 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1경 9935조 5126억 4614만</t>
+    <t>2경 396조 7854억 3158만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 8724조 1000억 9409만</t>
+    <t>1경 8729조 8184억 5587만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 7945조 2053억 8538만</t>
+    <t>1경 8429조 8851억 9686만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 3914조 4654억 3849만</t>
+    <t>1경 4665조 199억 8565만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 2438조 3899억 3059만</t>
+    <t>1경 2452조 2537억 8973만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1579조 6334억 6147만</t>
+    <t>1경 1731조 1089억 6224만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +881,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 837조 5201억 2986만</t>
+    <t>1경 917조 8065억 3932만</t>
+  </si>
+  <si>
+    <t>걸동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 448조 656억 9808만</t>
   </si>
   <si>
     <t>신참치</t>
@@ -890,19 +902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>9262조 3412억 2839만</t>
-  </si>
-  <si>
-    <t>걸동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8854조 9450억 4226만</t>
+    <t>9715조 2331억 589만</t>
   </si>
   <si>
     <t>김보들</t>
@@ -926,7 +926,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5709조 6081억 3936만</t>
+    <t>5710조 4882억 8541만</t>
   </si>
   <si>
     <t>종리츄</t>
@@ -953,7 +953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>90경 5508조 2719억 5514만</t>
+    <t>96경 4458조 5761억 5942만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
@@ -962,6 +962,15 @@
     <t>41경 6897조 9928억 9193만</t>
   </si>
   <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>11경 1673조 7688억 4187만</t>
+  </si>
+  <si>
     <t>딩느</t>
   </si>
   <si>
@@ -971,13 +980,13 @@
     <t>11경 1394조 5468억 1937만</t>
   </si>
   <si>
-    <t>독고사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>10경 2197조 1821억 9825만</t>
+    <t>시든꽃에물을</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
+  </si>
+  <si>
+    <t>11경 1123조 616억 9366만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -1016,7 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 7475조 7018억 3841만</t>
+    <t>1경 8056조 278억 5726만</t>
   </si>
   <si>
     <t>나야츄</t>
@@ -1037,7 +1046,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 54조 9994억 7226만</t>
+    <t>1경 1520조 8565억 8068만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1046,7 +1055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>8199조 7296억 9107만</t>
+    <t>9471조 4067억 9854만</t>
   </si>
   <si>
     <t>꾸덕행</t>
@@ -1058,7 +1067,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>6827조 6217억 3831만</t>
+    <t>7070조 493억 5476만</t>
   </si>
   <si>
     <t>lNOVAl</t>
@@ -1085,7 +1094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
   </si>
   <si>
-    <t>5145조 1415억 4710만</t>
+    <t>5235조 7337억 1600만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1097,22 +1106,22 @@
     <t>5001조 9074억 5704만</t>
   </si>
   <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>4590조 8255억 616만</t>
+  </si>
+  <si>
     <t>딤츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>4302조 3804억 7260만</t>
-  </si>
-  <si>
-    <t>직만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4197조 2196억 4458만</t>
+    <t>4328조 6742억 5717만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1121,7 +1130,25 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>3413조 2055억 7746만</t>
+    <t>3767조 5742억 5267만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3356조 1840억 6499만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3323조 2601억 4498만</t>
   </si>
   <si>
     <t>조림츄</t>
@@ -1133,25 +1160,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>3272조 1723억 9516만</t>
-  </si>
-  <si>
-    <t>나야김대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3199조 8996억 1901만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3199조 3306억 4775만</t>
+    <t>3275조 564억 1948만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1187,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
   </si>
   <si>
-    <t>2280조 94억 3832만</t>
+    <t>2364조 6292억 9802만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -1199,15 +1208,6 @@
     <t>2064조 1071억 8482만</t>
   </si>
   <si>
-    <t>산과바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1652조 9566억 8362만</t>
-  </si>
-  <si>
     <t>말레이히어로</t>
   </si>
   <si>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5082억 5270만</t>
+    <t>21경 913조 6729억 9538만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -1232,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3052억 4003만</t>
+    <t>12경 6297조 3934억 1589만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1241,7 +1241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7960억 279만</t>
+    <t>12경 3858조 1172억 6063만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -1250,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>10경 6154조 8799억 4676만</t>
+    <t>10경 6184조 3457억 7322만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1268,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3423조 3510억 8891만</t>
+    <t>9경 3479조 369억 3638만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -1277,7 +1277,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2651억 9696만</t>
+    <t>8경 2706조 3135억 2808만</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>7경 5292조 4238억 2660만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1289,15 +1298,6 @@
     <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
     <t>쾌감</t>
   </si>
   <si>
@@ -1307,22 +1307,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>2경 5374조 9474억 3745만</t>
+  </si>
+  <si>
     <t>핫잇</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4834억 827만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>2경 4130조 5641억 7043만</t>
+    <t>2경 5181조 6388억 1979만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -1358,7 +1358,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3650억 1564만</t>
+    <t>2경 616조 9601억 9592만</t>
+  </si>
+  <si>
+    <t>쌉새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
+  </si>
+  <si>
+    <t>1경 7942조 150억 6859만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -1373,16 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1968억 392만</t>
-  </si>
-  <si>
-    <t>쌉새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
-  </si>
-  <si>
-    <t>1경 5688조 4374억 8127만</t>
+    <t>1경 6180조 1094억 5337만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1391,7 +1391,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5412억 6446만</t>
+    <t>1경 3352조 5107억 6670만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -1403,6 +1403,15 @@
     <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 2644조 7980억 538만</t>
+  </si>
+  <si>
     <t>라똥삐</t>
   </si>
   <si>
@@ -1412,22 +1421,13 @@
     <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
-    <t>오곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
-  </si>
-  <si>
-    <t>1경 1856조 4618억 6137만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2945억 9039만</t>
+    <t>1경 75조 3638억 2592만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1445,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3675억 8873만</t>
+    <t>5822조 9050억 2851만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -1454,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>341조 6408억 9657만</t>
+    <t>355조 4686억 5920만</t>
   </si>
   <si>
     <t>베르카암프</t>
@@ -1466,7 +1466,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>528조 2903억 8564만</t>
+    <t>530조 9713억 9599만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1478,7 +1478,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>510조 8522억 3023만</t>
+    <t>520조 1829억 7986만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1487,7 +1487,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>485조 6946억 3853만</t>
+    <t>485조 7656억 3797만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1517,22 +1517,22 @@
     <t>358조 5526억 3562만</t>
   </si>
   <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>346조 6476억 3515만</t>
+  </si>
+  <si>
     <t>말랑랑말이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>319조 6634억 9916만</t>
-  </si>
-  <si>
-    <t>날씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
-  </si>
-  <si>
-    <t>281조 8365억 8619만</t>
+    <t>323조 9373억 5450만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1544,7 +1544,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>250조 8464억 5632만</t>
+    <t>284조 2296억 9757만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1553,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
   </si>
   <si>
-    <t>185조 2853억 5484만</t>
+    <t>192조 5397억 1892만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1565,7 +1565,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>183조 8405억 4218만</t>
+    <t>191조 9727억 9291만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>166조 3857억 4091만</t>
+    <t>179조 5360억 1080만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>134조 4998억 5770만</t>
+    <t>136조 1130억 1164만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>130조 5440억 9674만</t>
+    <t>130조 8064억 950만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>128조 1033억 8744만</t>
+    <t>129조 4305억 6522만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>97조 5494억 6110만</t>
+    <t>98조 9331억 6438만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>82조 5120억 1455만</t>
+    <t>82조 8344억 5670만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1661,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>55조 296억 2286만</t>
+    <t>57조 5203억 1606만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1700,19 +1700,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
   </si>
   <si>
+    <t>14조 5432억 6339만</t>
+  </si>
+  <si>
+    <t>이제명확찢</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A0%9C%EB%AA%85%ED%99%95%EC%B0%A2</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>12조 8251억 2721만</t>
-  </si>
-  <si>
-    <t>이제명확찢</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A0%9C%EB%AA%85%ED%99%95%EC%B0%A2</t>
-  </si>
-  <si>
-    <t>10조 9536억 4351만</t>
+    <t>11조 59억 3638만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
@@ -1727,10 +1727,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%98%84%EB%B9%A0%EB%8D%9C</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>2조 4360억 4592만</t>
+    <t>99</t>
+  </si>
+  <si>
+    <t>2조 6573억 4758만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1745,7 +1745,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1456억 5188만</t>
+    <t>1485억 1704만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1757,10 +1757,10 @@
     <t>윈드브레이커</t>
   </si>
   <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>112억 5433만</t>
+    <t>83</t>
+  </si>
+  <si>
+    <t>114억 4703만</t>
   </si>
 </sst>
 </file>
@@ -2498,10 +2498,10 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2512,25 +2512,25 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>84</v>
@@ -2591,13 +2591,13 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2608,16 +2608,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -2626,10 +2626,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2640,28 +2640,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2672,28 +2672,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2704,28 +2704,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2736,16 +2736,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -2754,10 +2754,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2768,28 +2768,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2800,25 +2800,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2850,7 +2850,7 @@
         <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>132</v>
@@ -2879,10 +2879,10 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2911,10 +2911,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2946,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>144</v>
@@ -2975,10 +2975,10 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>148</v>
@@ -3007,7 +3007,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>152</v>
@@ -3074,7 +3074,7 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>162</v>
@@ -3103,7 +3103,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>166</v>
@@ -3135,7 +3135,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>152</v>
@@ -3167,7 +3167,7 @@
         <v>174</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>166</v>
@@ -3263,7 +3263,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>180</v>
@@ -3295,7 +3295,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>180</v>
@@ -3359,7 +3359,7 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>180</v>
@@ -3475,10 +3475,10 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>205</v>
@@ -3524,7 +3524,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>211</v>
@@ -3539,7 +3539,7 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>89</v>
@@ -3620,7 +3620,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>221</v>
@@ -3652,7 +3652,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>224</v>
@@ -3667,10 +3667,10 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>226</v>
@@ -3684,7 +3684,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>227</v>
@@ -3699,10 +3699,10 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>229</v>
@@ -3716,7 +3716,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>230</v>
@@ -3748,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>233</v>
@@ -3780,7 +3780,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>236</v>
@@ -3812,7 +3812,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>239</v>
@@ -3827,7 +3827,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>241</v>
@@ -3862,7 +3862,7 @@
         <v>157</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
@@ -3891,10 +3891,10 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
@@ -3923,10 +3923,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>208</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>251</v>
@@ -3987,7 +3987,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>180</v>
@@ -4019,7 +4019,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>241</v>
@@ -4115,7 +4115,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>166</v>
@@ -4147,7 +4147,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>180</v>
@@ -4179,7 +4179,7 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>180</v>
@@ -4211,7 +4211,7 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>180</v>
@@ -4243,7 +4243,7 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>180</v>
@@ -4307,7 +4307,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>287</v>
@@ -4339,7 +4339,7 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>287</v>
@@ -4371,7 +4371,7 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>287</v>
@@ -4523,7 +4523,7 @@
         <v>179</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>302</v>
@@ -4555,7 +4555,7 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>305</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>306</v>
@@ -4584,10 +4584,10 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>308</v>
@@ -4648,10 +4648,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>313</v>
@@ -4665,7 +4665,7 @@
         <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>314</v>
@@ -4680,10 +4680,10 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>316</v>
@@ -4697,7 +4697,7 @@
         <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>317</v>
@@ -4712,10 +4712,10 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>298</v>
+        <v>166</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>319</v>
@@ -4729,7 +4729,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>320</v>
@@ -4744,13 +4744,13 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4761,25 +4761,25 @@
         <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>326</v>
@@ -4793,7 +4793,7 @@
         <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>327</v>
@@ -4808,7 +4808,7 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>180</v>
@@ -4825,7 +4825,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>330</v>
@@ -4840,10 +4840,10 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>298</v>
+        <v>180</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>332</v>
@@ -4857,7 +4857,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>333</v>
@@ -4872,13 +4872,13 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4892,22 +4892,22 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>339</v>
@@ -4936,13 +4936,13 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4956,22 +4956,22 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>346</v>
@@ -5000,10 +5000,10 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>349</v>
@@ -5032,10 +5032,10 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>352</v>
@@ -5064,10 +5064,10 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>355</v>
@@ -5096,10 +5096,10 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>358</v>
@@ -5131,7 +5131,7 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5160,10 +5160,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>263</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5192,13 +5192,13 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5212,25 +5212,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5244,25 +5244,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5276,22 +5276,22 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>377</v>
@@ -5320,10 +5320,10 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>380</v>
@@ -5352,10 +5352,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>383</v>
@@ -5384,10 +5384,10 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>386</v>
@@ -5416,10 +5416,10 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
@@ -5448,10 +5448,10 @@
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
@@ -5568,7 +5568,7 @@
         <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>395</v>
@@ -5600,7 +5600,7 @@
         <v>157</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>398</v>
@@ -5614,7 +5614,7 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>399</v>
@@ -5632,7 +5632,7 @@
         <v>131</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
@@ -5664,7 +5664,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>404</v>
@@ -5696,7 +5696,7 @@
         <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>407</v>
@@ -5710,7 +5710,7 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>408</v>
@@ -5725,10 +5725,10 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>410</v>
@@ -5742,7 +5742,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>411</v>
@@ -5774,7 +5774,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>414</v>
@@ -5792,7 +5792,7 @@
         <v>219</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>416</v>
@@ -5806,7 +5806,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>417</v>
@@ -5821,10 +5821,10 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>419</v>
@@ -5838,7 +5838,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>420</v>
@@ -5853,10 +5853,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>422</v>
@@ -5870,7 +5870,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>423</v>
@@ -5902,7 +5902,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>426</v>
@@ -5917,7 +5917,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>241</v>
@@ -5949,7 +5949,7 @@
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>241</v>
@@ -5981,7 +5981,7 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>241</v>
@@ -6013,7 +6013,7 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>180</v>
@@ -6077,7 +6077,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>180</v>
@@ -6097,25 +6097,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>287</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>51</v>
@@ -6129,22 +6129,22 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>446</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>446</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>447</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>448</v>
@@ -6173,10 +6173,10 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>451</v>
@@ -6205,7 +6205,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>180</v>
@@ -6269,10 +6269,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>460</v>
@@ -6301,10 +6301,10 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>463</v>
@@ -6333,7 +6333,7 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>180</v>
@@ -6365,7 +6365,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>287</v>
@@ -6397,10 +6397,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>472</v>
@@ -6432,7 +6432,7 @@
         <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>475</v>
@@ -6544,7 +6544,7 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>478</v>
@@ -6593,7 +6593,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>484</v>
@@ -6608,7 +6608,7 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>482</v>
@@ -6672,7 +6672,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>482</v>
@@ -6689,7 +6689,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>493</v>
@@ -6721,7 +6721,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>496</v>
@@ -6736,10 +6736,10 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>498</v>
@@ -6753,7 +6753,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>499</v>
@@ -6768,10 +6768,10 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>501</v>
@@ -6785,7 +6785,7 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>502</v>
@@ -6817,7 +6817,7 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>506</v>
@@ -6849,7 +6849,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>509</v>
@@ -6864,7 +6864,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>511</v>
@@ -6881,7 +6881,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>513</v>
@@ -6992,7 +6992,7 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>518</v>
@@ -7088,7 +7088,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>504</v>
@@ -7152,7 +7152,7 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>511</v>
@@ -7184,7 +7184,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>543</v>
@@ -7216,7 +7216,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>543</v>
@@ -7315,10 +7315,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>35</v>
@@ -7332,22 +7332,22 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>561</v>
@@ -7408,7 +7408,7 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>566</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>53</t>
+    <t>54</t>
   </si>
   <si>
     <t>4위</t>
@@ -167,7 +167,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>59</t>
+    <t>62</t>
   </si>
   <si>
     <t>3위</t>
@@ -194,10 +194,10 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2833</t>
-  </si>
-  <si>
-    <t>153위</t>
+    <t>2855</t>
+  </si>
+  <si>
+    <t>154위</t>
   </si>
   <si>
     <t>4842조 9452억 2908만</t>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>70경 3411조 543억 9761만</t>
+    <t>70경 5202조 5289억 6005만</t>
   </si>
   <si>
     <t>7</t>
@@ -341,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 5893조 4558억 8082만</t>
+    <t>47경 490조 6765억 9738만</t>
   </si>
   <si>
     <t>8</t>
@@ -389,6 +389,21 @@
     <t>11</t>
   </si>
   <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>31경 3120조 4090억 8744만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>시드리안</t>
   </si>
   <si>
@@ -398,21 +413,6 @@
     <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>29경 6457조 7252억 8350만</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>26경 304조 7942억 7478만</t>
+    <t>26경 3393조 6831억 3749만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5726조 4261억 8056만</t>
+    <t>21경 4601조 3855억 149만</t>
   </si>
   <si>
     <t>15</t>
@@ -461,7 +461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9521만</t>
+    <t>19경 4410조 4980억 5909만</t>
   </si>
   <si>
     <t>17</t>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 9155조 2333억 8429만</t>
+    <t>19경 1787조 3571억 1968만</t>
   </si>
   <si>
     <t>18</t>
@@ -515,7 +515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>8경 6856조 4210억 2441만</t>
+    <t>9경 420조 3518억 4554만</t>
   </si>
   <si>
     <t>21</t>
@@ -527,33 +527,33 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
   </si>
   <si>
+    <t>6경 5564조 1888억 7889만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>6경 3605조 1616억 212만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
-    <t>6경 5564조 1888억 7889만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>6경 1816조 4690억 8482만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
@@ -584,7 +584,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 954조 4911억 7546만</t>
+    <t>3경 2981조 5907억 6449만</t>
   </si>
   <si>
     <t>26</t>
@@ -596,7 +596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5656조 4416억 3248만</t>
+    <t>1경 5849조 5535억 3532만</t>
   </si>
   <si>
     <t>27</t>
@@ -608,7 +608,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5368조 6516억 4049만</t>
+    <t>1경 5485조 9970억 1336만</t>
   </si>
   <si>
     <t>28</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7102억 6148만</t>
+    <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
     <t>껌쉬</t>
@@ -644,7 +644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>400경 7671조 206억 8592만</t>
+    <t>407경 4431조 9281억 9965만</t>
   </si>
   <si>
     <t>달하나별하나</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>94경 871조 8885억 5305만</t>
+    <t>95경 404조 7638억 4143만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -689,7 +689,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>81경 393조 5887억 8702만</t>
+    <t>81경 2026조 9445억 5460만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -698,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
   </si>
   <si>
-    <t>68경 8923조 3781억 4276만</t>
+    <t>69경 3013조 175억 5492만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>41경 1905조 6743억 903만</t>
+    <t>41경 9724조 2012억 1476만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>22경 9403조 3418억 9373만</t>
+    <t>25경 8750조 3608억 5632만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -734,7 +734,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>5경 1090조 1032억 7666만</t>
+    <t>5경 1605조 9303억 2226만</t>
+  </si>
+  <si>
+    <t>찍먹비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>4경 9066조 389억 7920만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -743,7 +755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>4경 6299조 7270억 8249만</t>
+    <t>4경 6438조 8802억 1526만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -752,21 +764,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
     <t>4경 20조 8028억 8872만</t>
   </si>
   <si>
-    <t>찍먹비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>3경 8257조 4700억 1545만</t>
-  </si>
-  <si>
     <t>뾰쀼뾰</t>
   </si>
   <si>
@@ -782,7 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 2702조 2900억 8953만</t>
+    <t>3경 2748조 907억 7752만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -791,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
   </si>
   <si>
-    <t>2경 6335조 3243억 7245만</t>
+    <t>2경 6887조 9215억 1543만</t>
   </si>
   <si>
     <t>못함</t>
@@ -800,7 +800,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 4569조 7644억 2007만</t>
+    <t>2경 4730조 1963억 4971만</t>
+  </si>
+  <si>
+    <t>쵸비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>2경 1097조 9667억 7668만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -809,25 +821,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 865조 3081억 1725만</t>
-  </si>
-  <si>
-    <t>쵸비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>2경 396조 7854억 3158만</t>
+    <t>2경 947조 1092억 4285만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>1경 8729조 8184억 5587만</t>
+    <t>1경 8865조 1892억 6814만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 8429조 8851억 9686만</t>
+    <t>1경 8553조 1624억 5633만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -854,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>1경 2959조 4760억 5668만</t>
+    <t>1경 3226조 7769억 3908만</t>
   </si>
   <si>
     <t>서두희</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 2452조 2537억 8973만</t>
+    <t>1경 2630조 5052억 5435만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1731조 1089억 6224만</t>
+    <t>1경 1753조 877억 6784만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 917조 8065억 3932만</t>
+    <t>1경 933조 419억 9047만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -953,13 +953,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>96경 4458조 5761억 5942만</t>
+    <t>101경 9703조 2913억 631만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>41경 6897조 9928억 9193만</t>
+    <t>44경 6319조 8919억 3757만</t>
+  </si>
+  <si>
+    <t>시든꽃에물을</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
+  </si>
+  <si>
+    <t>11경 8161조 4813억 4542만</t>
   </si>
   <si>
     <t>독고사수</t>
@@ -968,7 +977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>11경 1673조 7688억 4187만</t>
+    <t>11경 5422조 1567억 4724만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -980,15 +989,6 @@
     <t>11경 1394조 5468억 1937만</t>
   </si>
   <si>
-    <t>시든꽃에물을</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
-  </si>
-  <si>
-    <t>11경 1123조 616억 9366만</t>
-  </si>
-  <si>
     <t>몰라츄</t>
   </si>
   <si>
@@ -1034,7 +1034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 1971조 6929억 1662만</t>
+    <t>1경 2057조 2363억 8618만</t>
   </si>
   <si>
     <t>날아라순자</t>
@@ -1067,7 +1067,16 @@
     <t>111</t>
   </si>
   <si>
-    <t>7070조 493억 5476만</t>
+    <t>7189조 6952억 919만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6051조 1417억 7599만</t>
   </si>
   <si>
     <t>lNOVAl</t>
@@ -1097,13 +1106,13 @@
     <t>5235조 7337억 1600만</t>
   </si>
   <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5001조 9074억 5704만</t>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>4871조 996억 906만</t>
   </si>
   <si>
     <t>직만</t>
@@ -1112,16 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>4590조 8255억 616만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>4328조 6742억 5717만</t>
+    <t>4841조 9029억 1724만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1130,7 +1130,16 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>3767조 5742억 5267만</t>
+    <t>4171조 7934억 1773만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3414조 1764억 9443만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1139,7 +1148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>3356조 1840억 6499만</t>
+    <t>3357조 9102억 6954만</t>
   </si>
   <si>
     <t>나야김대장</t>
@@ -1151,25 +1160,25 @@
     <t>3323조 2601억 4498만</t>
   </si>
   <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>3275조 564억 1948만</t>
-  </si>
-  <si>
-    <t>화정츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2827조 6717억 8583만</t>
+    <t>3238조 4811억 8014만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2847조 8449억 4871만</t>
   </si>
   <si>
     <t>포이즈</t>
@@ -1181,15 +1190,6 @@
     <t>2692조 8173억 3981만</t>
   </si>
   <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2632조 6912억 5153만</t>
-  </si>
-  <si>
     <t>궁금증유발</t>
   </si>
   <si>
@@ -1226,6 +1226,24 @@
     <t>21경 913조 6729억 9538만</t>
   </si>
   <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>12경 7805조 791억 5905만</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>12경 7170조 9223억 583만</t>
+  </si>
+  <si>
     <t>걸음</t>
   </si>
   <si>
@@ -1235,13 +1253,13 @@
     <t>12경 6297조 3934억 1589만</t>
   </si>
   <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>12경 3858조 1172억 6063만</t>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>10경 7475조 5883억 7689만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -1250,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>10경 6184조 3457억 7322만</t>
+    <t>10경 6741조 2066억 6237만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1268,25 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3479조 369억 3638만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>8경 2706조 3135억 2808만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 5292조 4238억 2660만</t>
+    <t>9경 8900조 2461억 1026만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1295,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>7경 3381조 2238억 1561만</t>
+    <t>8경 889조 8820억 3333만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1307,22 +1307,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>2경 5674조 8497억 6042만</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 5374조 9474억 3745만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>2경 5181조 6388억 1979만</t>
+    <t>2경 5389조 5126억 3656만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -1331,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2021억 502만</t>
+    <t>2경 3490조 8557억 971만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1358,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 616조 9601억 9592만</t>
+    <t>2경 1051조 6678억 8223만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -1367,22 +1367,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 7942조 150억 6859만</t>
+    <t>1경 8946조 4328억 6990만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 7975조 2343억 1795만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5691억 7924만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 6180조 1094억 5337만</t>
+    <t>1경 7967조 8531억 1276만</t>
+  </si>
+  <si>
+    <t>니뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>1경 3466조 9661억 2553만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1394,13 +1403,13 @@
     <t>1경 3352조 5107억 6670만</t>
   </si>
   <si>
-    <t>니뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>1경 2819조 4851억 9770만</t>
+    <t>라똥삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
+  </si>
+  <si>
+    <t>1경 3335조 5943억 5779만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -1412,22 +1421,13 @@
     <t>1경 2644조 7980억 538만</t>
   </si>
   <si>
-    <t>라똥삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
-  </si>
-  <si>
-    <t>1경 2085조 1284억 3396만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 75조 3638억 2592만</t>
+    <t>1경 81조 8065억 59만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1436,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2165억 2470만</t>
+    <t>6503조 8983억 4302만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -1466,7 +1466,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>530조 9713억 9599만</t>
+    <t>558조 2538억 1727만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1478,7 +1478,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>520조 1829억 7986만</t>
+    <t>533조 9907억 9511만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1523,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>346조 6476억 3515만</t>
+    <t>354조 1216억 3546만</t>
   </si>
   <si>
     <t>말랑랑말이</t>
@@ -1532,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>323조 9373억 5450만</t>
+    <t>335조 5588억 9795만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1544,7 +1544,19 @@
     <t>106</t>
   </si>
   <si>
-    <t>284조 2296억 9757만</t>
+    <t>286조 3484억 2897만</t>
+  </si>
+  <si>
+    <t>한로얘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>204조 9706억 9593만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1553,19 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
   </si>
   <si>
-    <t>192조 5397억 1892만</t>
-  </si>
-  <si>
-    <t>한로얘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>191조 9727억 9291만</t>
+    <t>200조 4730억 4168만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>179조 5360억 1080만</t>
+    <t>180조 9473억 2096만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1586,7 +1586,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>154조 7346억 1516만</t>
+    <t>158조 9993억 322만</t>
   </si>
   <si>
     <t>멍뭉이다</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>136조 1130억 1164만</t>
+    <t>138조 4672억 2558만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>130조 8064억 950만</t>
+    <t>134조 3173억 8304만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>98조 9331억 6438만</t>
+    <t>100조 6585억 7077만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1661,7 +1661,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>57조 5203억 1606만</t>
+    <t>57조 8484억 2750만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1670,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>31조 9560억 6444만</t>
+    <t>32조 5217억 4610만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1700,7 +1700,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
   </si>
   <si>
-    <t>14조 5432억 6339만</t>
+    <t>14조 5467억 7542만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1712,7 +1712,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>11조 59억 3638만</t>
+    <t>11조 6147억 3677만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
@@ -1730,7 +1730,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>2조 6573억 4758만</t>
+    <t>3조 1140억 4952만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1742,10 +1742,10 @@
     <t>나이트워커</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>1485억 1704만</t>
+    <t>93</t>
+  </si>
+  <si>
+    <t>1653억 6758만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1760,7 +1760,7 @@
     <t>83</t>
   </si>
   <si>
-    <t>114억 4703만</t>
+    <t>127억 3938만</t>
   </si>
 </sst>
 </file>
@@ -2783,13 +2783,13 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2800,25 +2800,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2850,7 +2850,7 @@
         <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>132</v>
@@ -2882,7 +2882,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2914,7 +2914,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2946,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>144</v>
@@ -2978,7 +2978,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>148</v>
@@ -3106,10 +3106,10 @@
         <v>112</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3120,16 +3120,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -3141,7 +3141,7 @@
         <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3152,7 +3152,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>23</v>
@@ -3161,16 +3161,16 @@
         <v>23</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3234,7 +3234,7 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>185</v>
@@ -3542,7 +3542,7 @@
         <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>213</v>
@@ -3702,7 +3702,7 @@
         <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>229</v>
@@ -3734,7 +3734,7 @@
         <v>157</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>232</v>
@@ -3795,13 +3795,13 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>35</v>
@@ -3812,25 +3812,25 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>242</v>
@@ -3859,10 +3859,10 @@
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
@@ -3894,7 +3894,7 @@
         <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
@@ -3958,7 +3958,7 @@
         <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>254</v>
@@ -4019,13 +4019,13 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>35</v>
@@ -4039,22 +4039,22 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>263</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>264</v>
@@ -4080,7 +4080,7 @@
         <v>265</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>208</v>
@@ -4118,7 +4118,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>269</v>
@@ -4132,7 +4132,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>270</v>
@@ -4164,7 +4164,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>273</v>
@@ -4555,7 +4555,7 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>305</v>
@@ -4587,7 +4587,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>308</v>
@@ -4613,13 +4613,13 @@
         <v>309</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>310</v>
@@ -4648,10 +4648,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>313</v>
@@ -4680,10 +4680,10 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>316</v>
@@ -4712,10 +4712,10 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>319</v>
@@ -4857,7 +4857,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>333</v>
@@ -5003,7 +5003,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>349</v>
@@ -5035,7 +5035,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>352</v>
@@ -5067,7 +5067,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>355</v>
@@ -5099,7 +5099,7 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>358</v>
@@ -5128,10 +5128,10 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5160,10 +5160,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5177,7 +5177,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>365</v>
@@ -5192,7 +5192,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>345</v>
@@ -5209,7 +5209,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>368</v>
@@ -5227,7 +5227,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5259,7 +5259,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>373</v>
@@ -5291,10 +5291,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5308,13 +5308,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -5323,7 +5323,7 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>380</v>
@@ -5352,10 +5352,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>383</v>
@@ -5384,10 +5384,10 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>386</v>
@@ -5448,7 +5448,7 @@
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>345</v>
@@ -5629,10 +5629,10 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
@@ -5664,7 +5664,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>404</v>
@@ -5693,7 +5693,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>113</v>
@@ -5725,7 +5725,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>113</v>
@@ -5757,10 +5757,10 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>413</v>
@@ -5789,7 +5789,7 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>113</v>
@@ -5821,7 +5821,7 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>152</v>
@@ -5856,7 +5856,7 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>422</v>
@@ -5888,7 +5888,7 @@
         <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>425</v>
@@ -5902,7 +5902,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>426</v>
@@ -5920,7 +5920,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>428</v>
@@ -5952,7 +5952,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>431</v>
@@ -5984,7 +5984,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>434</v>
@@ -6129,25 +6129,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>447</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>447</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>51</v>
@@ -6161,22 +6161,22 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>449</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>449</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>450</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>451</v>
@@ -6205,7 +6205,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>180</v>
@@ -6222,7 +6222,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>455</v>
@@ -6237,10 +6237,10 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>457</v>
@@ -6254,7 +6254,7 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>458</v>
@@ -6269,10 +6269,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>460</v>
@@ -6301,10 +6301,10 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>463</v>
@@ -6432,7 +6432,7 @@
         <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>475</v>
@@ -6832,13 +6832,13 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -6852,22 +6852,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>512</v>
@@ -6881,7 +6881,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>513</v>
@@ -7123,7 +7123,7 @@
         <v>179</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>537</v>
@@ -7155,7 +7155,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>540</v>
@@ -7201,7 +7201,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>545</v>
@@ -7233,7 +7233,7 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>548</v>
@@ -7251,7 +7251,7 @@
         <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>550</v>
@@ -7373,7 +7373,7 @@
         <v>562</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>208</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -194,7 +194,7 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2855</t>
+    <t>2858</t>
   </si>
   <si>
     <t>154위</t>
@@ -962,22 +962,22 @@
     <t>44경 6319조 8919억 3757만</t>
   </si>
   <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>11경 8522조 8998억 4569만</t>
+  </si>
+  <si>
     <t>시든꽃에물을</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
   </si>
   <si>
-    <t>11경 8161조 4813억 4542만</t>
-  </si>
-  <si>
-    <t>독고사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>11경 5422조 1567억 4724만</t>
+    <t>11경 8194조 6927억 6358만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -1010,6 +1010,15 @@
     <t>2경 5047조 6740억 1185만</t>
   </si>
   <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 9281조 1467억 3386만</t>
+  </si>
+  <si>
     <t>동작대교</t>
   </si>
   <si>
@@ -1019,22 +1028,13 @@
     <t>1경 8332조 1425억 2718만</t>
   </si>
   <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 8056조 278억 5726만</t>
-  </si>
-  <si>
     <t>나야츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 2057조 2363억 8618만</t>
+    <t>1경 4393조 6778억 3625만</t>
   </si>
   <si>
     <t>날아라순자</t>
@@ -1064,46 +1064,55 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
   </si>
   <si>
+    <t>7189조 6952억 919만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6051조 1417억 7599만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>5566조 6120억 2581만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5918만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>5235조 7337억 1600만</t>
+  </si>
+  <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>7189조 6952억 919만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6051조 1417억 7599만</t>
-  </si>
-  <si>
-    <t>lNOVAl</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
-  </si>
-  <si>
-    <t>5566조 6120억 2581만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5471조 457억 5918만</t>
-  </si>
-  <si>
-    <t>넹또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
-  </si>
-  <si>
-    <t>5235조 7337억 1600만</t>
+    <t>4964조 8365억 8281만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -1115,15 +1124,6 @@
     <t>4871조 996억 906만</t>
   </si>
   <si>
-    <t>직만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4841조 9029억 1724만</t>
-  </si>
-  <si>
     <t>Dollmeng2</t>
   </si>
   <si>
@@ -1133,22 +1133,22 @@
     <t>4171조 7934억 1773만</t>
   </si>
   <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3453조 2261억 2721만</t>
+  </si>
+  <si>
     <t>조림츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>3414조 1764억 9443만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3357조 9102억 6954만</t>
+    <t>3438조 7426억 835만</t>
   </si>
   <si>
     <t>나야김대장</t>
@@ -1157,7 +1157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>3323조 2601억 4498만</t>
+    <t>3387조 2396억 6749만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1196,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
   </si>
   <si>
-    <t>2364조 6292억 9802만</t>
+    <t>2644조 2846억 1124만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -4648,10 +4648,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>313</v>
@@ -4680,10 +4680,10 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>316</v>
@@ -4808,7 +4808,7 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>180</v>
@@ -4840,7 +4840,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>180</v>
@@ -4971,10 +4971,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4988,13 +4988,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -5003,10 +5003,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5020,13 +5020,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5038,7 +5038,7 @@
         <v>325</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5052,13 +5052,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -5070,7 +5070,7 @@
         <v>338</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5084,13 +5084,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -5102,7 +5102,7 @@
         <v>325</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5116,22 +5116,22 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5160,10 +5160,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5195,7 +5195,7 @@
         <v>260</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5227,7 +5227,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5259,7 +5259,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>373</v>
@@ -5291,7 +5291,7 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -5419,7 +5419,7 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
@@ -5451,7 +5451,7 @@
         <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -20,14 +20,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="580">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>45</t>
+    <t>46</t>
   </si>
   <si>
     <t>1위</t>
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>4위</t>
@@ -146,7 +146,7 @@
     <t>Scania 63</t>
   </si>
   <si>
-    <t>48</t>
+    <t>49</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -167,7 +167,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>62</t>
+    <t>64</t>
   </si>
   <si>
     <t>3위</t>
@@ -194,10 +194,10 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2858</t>
-  </si>
-  <si>
-    <t>154위</t>
+    <t>2889</t>
+  </si>
+  <si>
+    <t>159위</t>
   </si>
   <si>
     <t>4842조 9452억 2908만</t>
@@ -266,7 +266,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>231경 7865조 5718억 420만</t>
+    <t>270경 7618조 922억 2211만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>186경 7791조 7180억 8576만</t>
+    <t>191경 2058조 3901억 1862만</t>
   </si>
   <si>
     <t>4</t>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>70경 5202조 5289억 6005만</t>
+    <t>74경 3866조 7469억 4439만</t>
   </si>
   <si>
     <t>7</t>
@@ -341,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>47경 490조 6765억 9738만</t>
+    <t>48경 834조 2237억 8543만</t>
   </si>
   <si>
     <t>8</t>
@@ -371,7 +371,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>43경 847조 2572억 7170만</t>
+    <t>45경 1339조 4074억 6761만</t>
   </si>
   <si>
     <t>10</t>
@@ -383,7 +383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3171조 6570억 2266만</t>
+    <t>43경 1581조 3006억 376만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,7 +398,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>31경 3120조 4090억 8744만</t>
+    <t>36경 9418조 7315억 5162만</t>
   </si>
   <si>
     <t>12</t>
@@ -437,12 +437,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>21경 4601조 3855억 149만</t>
+    <t>24경 1488조 7361억 7301만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>20경 2140조 5598억 6840만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>설딩</t>
   </si>
   <si>
@@ -452,18 +464,6 @@
     <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>19경 4410조 4980억 5909만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -473,7 +473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>19경 1787조 3571억 1968만</t>
+    <t>19경 2997조 2320억 2150만</t>
   </si>
   <si>
     <t>18</t>
@@ -485,42 +485,54 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
   </si>
   <si>
+    <t>11경 2907조 6억 1960만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>10경 1397조 804억 329만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
     <t>119</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1960만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
     <t>9경 1574조 1762억 1736만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>9경 420조 3518억 4554만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>6경 8871조 9348억 2549만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>폰병</t>
   </si>
   <si>
@@ -530,18 +542,6 @@
     <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>6경 3605조 1616억 212만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -572,7 +572,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>3경 4312조 1092억 5647만</t>
+    <t>4경 3134조 5060억 9315만</t>
   </si>
   <si>
     <t>25</t>
@@ -584,31 +584,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 2981조 5907억 6449만</t>
+    <t>3경 6630조 3879억 9954만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1경 6721조 8484억 2590만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
     <t>읏코츠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5849조 5535억 3532만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>1경 5485조 9970억 1336만</t>
+    <t>1경 6320조 3647억 4463만</t>
   </si>
   <si>
     <t>28</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>95경 404조 7638억 4143만</t>
+    <t>98경 5605조 561억 6808만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>41경 9724조 2012억 1476만</t>
+    <t>42경 40조 2497억 8777만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>25경 8750조 3608억 5632만</t>
+    <t>25경 8963조 8558억 7602만</t>
   </si>
   <si>
     <t>와츄</t>
@@ -728,13 +728,22 @@
     <t>5경 9571조 1335억 7726만</t>
   </si>
   <si>
+    <t>스터디뱅크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
+  </si>
+  <si>
+    <t>5경 2386조 1501억 9374만</t>
+  </si>
+  <si>
     <t>상깅</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>5경 1605조 9303억 2226만</t>
+    <t>5경 1622조 1730억 1908만</t>
   </si>
   <si>
     <t>찍먹비숍</t>
@@ -746,16 +755,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>4경 9066조 389억 7920만</t>
-  </si>
-  <si>
-    <t>스터디뱅크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
-  </si>
-  <si>
-    <t>4경 6438조 8802억 1526만</t>
+    <t>5경 128조 2126억 5074만</t>
   </si>
   <si>
     <t>뚜뭉이</t>
@@ -782,7 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 2748조 907억 7752만</t>
+    <t>3경 5352조 1555억 8999만</t>
   </si>
   <si>
     <t>오쉬</t>
@@ -791,7 +791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
   </si>
   <si>
-    <t>2경 6887조 9215억 1543만</t>
+    <t>2경 9176조 4466억 2022만</t>
   </si>
   <si>
     <t>못함</t>
@@ -800,7 +800,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>2경 4730조 1963억 4971만</t>
+    <t>2경 7853조 7862억 2233만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
+  </si>
+  <si>
+    <t>2경 6517조 1038억 8309만</t>
+  </si>
+  <si>
+    <t>금하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>2경 1348조 201억 9707만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -812,22 +827,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>2경 1097조 9667억 7668만</t>
-  </si>
-  <si>
-    <t>금하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>2경 947조 1092억 4285만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
-  </si>
-  <si>
-    <t>1경 8865조 1892억 6814만</t>
+    <t>2경 1281조 6453억 4837만</t>
   </si>
   <si>
     <t>준준챠</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
   </si>
   <si>
-    <t>1경 8553조 1624억 5633만</t>
+    <t>1경 9087조 7464억 9311만</t>
   </si>
   <si>
     <t>뚝딱비숍</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 4665조 199억 8565만</t>
+    <t>1경 5832조 5976억 1885만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
   </si>
   <si>
-    <t>1경 2630조 5052억 5435만</t>
+    <t>1경 3081조 2756억 3267만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 1753조 877억 6784만</t>
+    <t>1경 2016조 9110억 2771만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 933조 419억 9047만</t>
+    <t>1경 984조 7083억 6234만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -902,7 +902,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>9715조 2331억 589만</t>
+    <t>1경 444조 9657억 1311만</t>
+  </si>
+  <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>5913조 5400억 9898만</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>김보들</t>
@@ -914,28 +929,13 @@
     <t>5840조 7231억 2937만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>빈수르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>5710조 4882억 8541만</t>
-  </si>
-  <si>
     <t>종리츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1374경 9967조 4966억 4046만</t>
+    <t>1469경 8904조 2504억 6218만</t>
   </si>
   <si>
     <t>요쁘</t>
@@ -959,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>44경 6319조 8919억 3757만</t>
+    <t>44경 6915조 2326억 6632만</t>
   </si>
   <si>
     <t>독고사수</t>
@@ -968,7 +968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>11경 8522조 8998억 4569만</t>
+    <t>14경 8360조 2756억 5764만</t>
   </si>
   <si>
     <t>시든꽃에물을</t>
@@ -977,7 +977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
   </si>
   <si>
-    <t>11경 8194조 6927억 6358만</t>
+    <t>12경 6359조 2823억 9054만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -989,6 +989,18 @@
     <t>11경 1394조 5468억 1937만</t>
   </si>
   <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3경 2612조 2604억 9866만</t>
+  </si>
+  <si>
     <t>몰라츄</t>
   </si>
   <si>
@@ -998,16 +1010,13 @@
     <t>3경 1732조 6831억 2430만</t>
   </si>
   <si>
-    <t>정육츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>2경 5047조 6740억 1185만</t>
+    <t>동작대교</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
+  </si>
+  <si>
+    <t>2경 2501조 3242억 4169만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -1016,16 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 9281조 1467억 3386만</t>
-  </si>
-  <si>
-    <t>동작대교</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
-  </si>
-  <si>
-    <t>1경 8332조 1425억 2718만</t>
+    <t>2경 1893조 2780억 5524만</t>
   </si>
   <si>
     <t>나야츄</t>
@@ -1046,7 +1046,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 1520조 8565억 8068만</t>
+    <t>1경 2076조 4816억 9769만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -1064,7 +1064,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
   </si>
   <si>
-    <t>7189조 6952억 919만</t>
+    <t>7599조 782억 4473만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>7207조 6496억 50만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>6061조 6988억 3369만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -1076,15 +1094,6 @@
     <t>6051조 1417억 7599만</t>
   </si>
   <si>
-    <t>lNOVAl</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
-  </si>
-  <si>
-    <t>5566조 6120억 2581만</t>
-  </si>
-  <si>
     <t>천상츄</t>
   </si>
   <si>
@@ -1094,13 +1103,13 @@
     <t>5471조 457억 5918만</t>
   </si>
   <si>
-    <t>넹또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
-  </si>
-  <si>
-    <t>5235조 7337억 1600만</t>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5360조 3020억 1006만</t>
   </si>
   <si>
     <t>직만</t>
@@ -1112,16 +1121,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>4964조 8365억 8281만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>4871조 996억 906만</t>
+    <t>5173조 9211억 4312만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -1130,7 +1130,37 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>4171조 7934억 1773만</t>
+    <t>4392조 589억 1333만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3807조 9058억 253만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>3670조 4003억 4907만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3554조 7208억 4048만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -1139,25 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>3453조 2261억 2721만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3438조 7426억 835만</t>
-  </si>
-  <si>
-    <t>나야김대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3387조 2396억 6749만</t>
+    <t>3554조 6058억 5264만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -1166,19 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>3238조 4811억 8014만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2847조 8449억 4871만</t>
+    <t>3364조 9653억 6386만</t>
   </si>
   <si>
     <t>포이즈</t>
@@ -1205,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>2064조 1071억 8482만</t>
+    <t>2211조 5762억 834만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 4823조 3360억 295만</t>
+    <t>25경 5968조 5279억 8792만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -1223,7 +1223,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 913조 6729억 9538만</t>
+    <t>21경 3830조 9069억 3101만</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>15경 2682조 6704억 9270만</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>12경 9636조 105억 4675만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1235,22 +1253,22 @@
     <t>12경 7805조 791억 5905만</t>
   </si>
   <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>12경 7170조 9223억 583만</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>12경 6297조 3934억 1589만</t>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>11경 4318조 9260억 2021만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>11경 291조 4675억 896만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -1262,31 +1280,13 @@
     <t>10경 7475조 5883억 7689만</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>10경 6741조 2066억 6237만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>10경 4738조 815억 6221만</t>
-  </si>
-  <si>
     <t>잼포즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 8900조 2461억 1026만</t>
+    <t>10경 4273조 612억 9717만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1295,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>8경 889조 8820억 3333만</t>
+    <t>8경 3545조 3307억 6722만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1307,22 +1307,31 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>2경 7925조 8043억 3035만</t>
+  </si>
+  <si>
     <t>핫잇</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 5674조 8497억 6042만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>2경 5389조 5126억 3656만</t>
+    <t>2경 7756조 2579억 7515만</t>
+  </si>
+  <si>
+    <t>오픈톡쌀숭E</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
+  </si>
+  <si>
+    <t>2경 6890조 4852억 886만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -1334,13 +1343,13 @@
     <t>2경 3490조 8557억 971만</t>
   </si>
   <si>
-    <t>오픈톡쌀숭E</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
-  </si>
-  <si>
-    <t>2경 2936조 4015억 1704만</t>
+    <t>반가성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
+  </si>
+  <si>
+    <t>2경 3019조 5691억 5455만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1352,22 +1361,13 @@
     <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
-    <t>반가성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
-  </si>
-  <si>
-    <t>2경 1051조 6678억 8223만</t>
-  </si>
-  <si>
     <t>쌉새</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 8946조 4328억 6990만</t>
+    <t>2경 679조 9420억 5073만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -1376,13 +1376,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 7975조 2343억 1795만</t>
+    <t>1경 9568조 5677억 2556만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7967조 8531억 1276만</t>
+    <t>1경 8123조 8491억 9227만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -1403,10 +1403,10 @@
     <t>1경 3352조 5107억 6670만</t>
   </si>
   <si>
-    <t>라똥삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
+    <t>라똥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%9D%B4</t>
   </si>
   <si>
     <t>1경 3335조 5943억 5779만</t>
@@ -1418,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
   </si>
   <si>
-    <t>1경 2644조 7980억 538만</t>
+    <t>1경 2805조 1072억 4398만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -1427,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 81조 8065억 59만</t>
+    <t>1경 501조 4529억 6137만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1436,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6503조 8983억 4302만</t>
+    <t>7189조 6942억 6343만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -1445,7 +1445,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5822조 9050억 2851만</t>
+    <t>6773조 8889억 3186만</t>
+  </si>
+  <si>
+    <t>라라라온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%9D%BC%EB%9D%BC%EC%98%A8</t>
+  </si>
+  <si>
+    <t>1887조 978억 6719만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -1454,7 +1463,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>355조 4686억 5920만</t>
+    <t>412조 3890억 3560만</t>
+  </si>
+  <si>
+    <t>쿠크쿠쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%ED%81%AC%EC%BF%A0%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>1115조 3245억 2782만</t>
   </si>
   <si>
     <t>베르카암프</t>
@@ -1466,7 +1484,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>558조 2538억 1727만</t>
+    <t>567조 6706억 4070만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1487,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>485조 7656억 3797만</t>
+    <t>488조 6936억 1098만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1505,7 +1523,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
   </si>
   <si>
-    <t>404조 5216억 8702만</t>
+    <t>420조 915억 4392만</t>
+  </si>
+  <si>
+    <t>날씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
+  </si>
+  <si>
+    <t>370조 8748억 3980만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1517,22 +1544,13 @@
     <t>358조 5526억 3562만</t>
   </si>
   <si>
-    <t>날씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
-  </si>
-  <si>
-    <t>354조 1216억 3546만</t>
-  </si>
-  <si>
     <t>말랑랑말이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>335조 5588억 9795만</t>
+    <t>339조 5963억 9111만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1544,7 +1562,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>286조 3484억 2897만</t>
+    <t>316조 970억 3170만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1556,7 +1574,19 @@
     <t>105</t>
   </si>
   <si>
-    <t>204조 9706억 9593만</t>
+    <t>225조 1841억 9766만</t>
+  </si>
+  <si>
+    <t>버미겨리0</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>209조 4772억 5837만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1577,25 +1607,22 @@
     <t>180조 9473억 2096만</t>
   </si>
   <si>
-    <t>버미겨리0</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>158조 9993억 322만</t>
-  </si>
-  <si>
-    <t>멍뭉이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%AD%89%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>153조 5425억 984만</t>
+    <t>박상사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%83%81%EC%82%AC</t>
+  </si>
+  <si>
+    <t>148조 4553억 4079만</t>
+  </si>
+  <si>
+    <t>벵글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
+  </si>
+  <si>
+    <t>138조 8110억 9665만</t>
   </si>
   <si>
     <t>효깨비</t>
@@ -1607,22 +1634,13 @@
     <t>138조 6113억 1862만</t>
   </si>
   <si>
-    <t>벵글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
-  </si>
-  <si>
-    <t>138조 4672억 2558만</t>
-  </si>
-  <si>
     <t>NSYN</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>134조 3173억 8304만</t>
+    <t>135조 583억 4942만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1649,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>82조 8344억 5670만</t>
+    <t>86조 8704억 907만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1658,10 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B0%80%EC%A1%B1</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>57조 8484억 2750만</t>
+    <t>69조 3240억 9638만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1670,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>32조 5217억 4610만</t>
+    <t>38조 6698억 6068만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1679,28 +1694,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>20조 8845억 2964만</t>
-  </si>
-  <si>
-    <t>개념독점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%85%90%EB%8F%85%EC%A0%90</t>
+    <t>21조 2495억 8332만</t>
+  </si>
+  <si>
+    <t>상혀닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
   </si>
   <si>
     <t>103</t>
   </si>
   <si>
-    <t>14조 6666억 5274만</t>
-  </si>
-  <si>
-    <t>상혀닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%80%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>14조 5467억 7542만</t>
+    <t>15조 1852억 38만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1718,7 +1724,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>6조 4425억 8179만</t>
+    <t>7조 9154억 851만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1730,7 +1736,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>3조 1140억 4952만</t>
+    <t>3조 5767억 9049만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1745,7 +1751,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1653억 6758만</t>
+    <t>1655억 4143만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -2911,7 +2917,7 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>122</v>
@@ -2943,7 +2949,7 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>122</v>
@@ -2978,7 +2984,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>148</v>
@@ -3010,10 +3016,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3024,28 +3030,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3056,25 +3062,25 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>162</v>
@@ -3103,10 +3109,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>166</v>
@@ -3135,10 +3141,10 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>170</v>
@@ -3263,7 +3269,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>180</v>
@@ -3295,7 +3301,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>180</v>
@@ -3635,7 +3641,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>89</v>
@@ -3670,7 +3676,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>226</v>
@@ -3702,7 +3708,7 @@
         <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>229</v>
@@ -3731,7 +3737,7 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>174</v>
@@ -3763,10 +3769,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>235</v>
@@ -3795,13 +3801,13 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>35</v>
@@ -3815,22 +3821,22 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>242</v>
@@ -3862,7 +3868,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>245</v>
@@ -3894,7 +3900,7 @@
         <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
@@ -3990,7 +3996,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>257</v>
@@ -4007,25 +4013,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>35</v>
@@ -4036,16 +4042,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -4054,10 +4060,10 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>35</v>
@@ -4068,22 +4074,22 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>180</v>
@@ -4342,7 +4348,7 @@
         <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>291</v>
@@ -4371,13 +4377,13 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>35</v>
@@ -4388,25 +4394,25 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>299</v>
@@ -4619,7 +4625,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>310</v>
@@ -4715,7 +4721,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>319</v>
@@ -4744,13 +4750,13 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4764,22 +4770,22 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>326</v>
@@ -4808,7 +4814,7 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>180</v>
@@ -4840,7 +4846,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>180</v>
@@ -4875,7 +4881,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>335</v>
@@ -4939,7 +4945,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>342</v>
@@ -5003,7 +5009,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>348</v>
@@ -5035,7 +5041,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>351</v>
@@ -5067,7 +5073,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>354</v>
@@ -5081,7 +5087,7 @@
         <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>355</v>
@@ -5099,7 +5105,7 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>357</v>
@@ -5113,7 +5119,7 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>358</v>
@@ -5128,13 +5134,13 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5148,22 +5154,22 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5192,10 +5198,10 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5227,7 +5233,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5256,13 +5262,13 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5276,13 +5282,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -5291,10 +5297,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5308,13 +5314,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -5323,7 +5329,7 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>380</v>
@@ -5352,10 +5358,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>383</v>
@@ -5419,7 +5425,7 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>389</v>
@@ -5433,7 +5439,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>390</v>
@@ -5451,7 +5457,7 @@
         <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>392</v>
@@ -5500,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5597,7 +5603,7 @@
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>113</v>
@@ -5629,10 +5635,10 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>401</v>
@@ -5661,10 +5667,10 @@
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>404</v>
@@ -5693,10 +5699,10 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>407</v>
@@ -5725,7 +5731,7 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>113</v>
@@ -5757,7 +5763,7 @@
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>113</v>
@@ -5789,7 +5795,7 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>113</v>
@@ -5824,7 +5830,7 @@
         <v>179</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>419</v>
@@ -5856,7 +5862,7 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>422</v>
@@ -5888,7 +5894,7 @@
         <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>425</v>
@@ -5920,7 +5926,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>428</v>
@@ -5952,7 +5958,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>431</v>
@@ -5984,7 +5990,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>434</v>
@@ -6016,7 +6022,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>437</v>
@@ -6045,7 +6051,7 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>180</v>
@@ -6077,10 +6083,10 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
@@ -6126,7 +6132,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>447</v>
@@ -6158,7 +6164,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>50</v>
@@ -6240,7 +6246,7 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>457</v>
@@ -6400,7 +6406,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>472</v>
@@ -6429,10 +6435,10 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>475</v>
@@ -6441,8 +6447,40 @@
         <v>51</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6472,6 +6510,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6488,7 +6527,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6532,25 +6571,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>478</v>
+        <v>363</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>35</v>
@@ -6564,25 +6603,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>35</v>
@@ -6596,25 +6635,25 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>35</v>
@@ -6628,25 +6667,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>35</v>
@@ -6660,25 +6699,25 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>35</v>
@@ -6692,25 +6731,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>35</v>
@@ -6724,13 +6763,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -6739,10 +6778,10 @@
         <v>112</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>35</v>
@@ -6756,25 +6795,25 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>35</v>
@@ -6788,25 +6827,25 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>35</v>
@@ -6820,25 +6859,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -6852,25 +6891,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>35</v>
@@ -6884,25 +6923,25 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>35</v>
@@ -6916,25 +6955,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>35</v>
@@ -6948,25 +6987,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>35</v>
@@ -6980,25 +7019,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>35</v>
@@ -7012,13 +7051,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -7030,7 +7069,7 @@
         <v>518</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>35</v>
@@ -7044,25 +7083,25 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>35</v>
@@ -7076,25 +7115,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>35</v>
@@ -7105,28 +7144,28 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>35</v>
@@ -7137,28 +7176,28 @@
         <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>35</v>
@@ -7172,13 +7211,13 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -7187,10 +7226,10 @@
         <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>543</v>
+        <v>510</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>35</v>
@@ -7204,13 +7243,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -7219,10 +7258,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>35</v>
@@ -7236,25 +7275,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>35</v>
@@ -7268,25 +7307,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>553</v>
+        <v>514</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>35</v>
@@ -7300,13 +7339,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -7315,10 +7354,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>35</v>
@@ -7332,13 +7371,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -7347,10 +7386,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>35</v>
@@ -7370,7 +7409,7 @@
         <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>173</v>
@@ -7379,10 +7418,10 @@
         <v>208</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>35</v>
@@ -7396,13 +7435,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -7411,10 +7450,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>35</v>
@@ -7428,25 +7467,25 @@
         <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>35</v>
@@ -7457,28 +7496,28 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>35</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -18,16 +18,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="571">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>46</t>
+    <t>47</t>
   </si>
   <si>
     <t>1위</t>
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>55</t>
+    <t>57</t>
   </si>
   <si>
     <t>4위</t>
@@ -146,7 +146,7 @@
     <t>Scania 63</t>
   </si>
   <si>
-    <t>49</t>
+    <t>50</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -167,7 +167,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>64</t>
+    <t>65</t>
   </si>
   <si>
     <t>3위</t>
@@ -194,10 +194,10 @@
     <t>Scania 12</t>
   </si>
   <si>
-    <t>2889</t>
-  </si>
-  <si>
-    <t>159위</t>
+    <t>2899</t>
+  </si>
+  <si>
+    <t>162위</t>
   </si>
   <si>
     <t>4842조 9452억 2908만</t>
@@ -236,37 +236,37 @@
     <t>1</t>
   </si>
   <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>297경 2867조 5488억 4785만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>마옥지</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
-    <t>280경 3220조 6404억 6122만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>270경 7618조 922억 2211만</t>
+    <t>289경 6454조 4742억 1360만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>191경 2058조 3901억 1862만</t>
+    <t>206경 7530조 1038억 2497만</t>
   </si>
   <si>
     <t>4</t>
@@ -311,105 +311,105 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>85경 8894조 1952억 8378만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>76경 7872조 6949억 9142만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>48경 834조 2237억 8543만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>45경 5109조 8480억 2031만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>45경 1339조 4074억 6761만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>43경 1581조 3006억 376만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>37경 8186조 166억 18만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
     <t>바이퍼</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>85경 8894조 1952억 8378만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>74경 3866조 7469억 4439만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>48경 834조 2237억 8543만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>45경 1339조 4074억 6761만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>43경 1581조 3006억 376만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>36경 9418조 7315억 5162만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
     <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>26경 3393조 6831억 3749만</t>
+    <t>28경 2514조 7004억 9852만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 1488조 7361억 7301만</t>
+    <t>24경 6036조 6491억 3235만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,12 +449,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>20경 2140조 5598억 6840만</t>
+    <t>21경 127조 2151억 9086만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>20경 5514조 8976억 7519만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>설딩</t>
   </si>
   <si>
@@ -464,18 +476,6 @@
     <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>19경 2997조 2320억 2150만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -497,7 +497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>10경 1397조 804억 329만</t>
+    <t>10경 5928조 6370억 6895만</t>
   </si>
   <si>
     <t>20</t>
@@ -515,7 +515,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>9경 1574조 1762억 1736만</t>
+    <t>10경 491조 6226억 4381만</t>
   </si>
   <si>
     <t>21</t>
@@ -527,12 +527,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 8871조 9348억 2549만</t>
+    <t>7경 4318조 3235억 2661만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>7경 2830조 3342억 6906만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>폰병</t>
   </si>
   <si>
@@ -542,24 +557,21 @@
     <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>5경 5478조 8492억 3032만</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
+    <t>상구얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
+  </si>
+  <si>
+    <t>5경 4800조 2727억 5361만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>애봉얌</t>
   </si>
   <si>
@@ -575,31 +587,37 @@
     <t>4경 3134조 5060억 9315만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>상구얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
-  </si>
-  <si>
-    <t>3경 6630조 3879억 9954만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2경 420조 1374억 5167만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
     <t>설콩순</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 6721조 8484억 2590만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>1경 8428조 4809억 2430만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -608,22 +626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 6320조 3647억 4463만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4592조 3595억 1013만</t>
+    <t>1경 6393조 9171억 9294만</t>
   </si>
   <si>
     <t>29</t>
@@ -638,15 +641,6 @@
     <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
-    <t>껌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>407경 4431조 9281억 9965만</t>
-  </si>
-  <si>
     <t>달하나별하나</t>
   </si>
   <si>
@@ -668,7 +662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
   </si>
   <si>
-    <t>178경 6628조 7559억 4369만</t>
+    <t>180경 1277조 7508억 9771만</t>
   </si>
   <si>
     <t>왕이된사나이</t>
@@ -707,7 +701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
   </si>
   <si>
-    <t>42경 40조 2497억 8777만</t>
+    <t>42경 137조 9477억 2491만</t>
   </si>
   <si>
     <t>라온Z</t>
@@ -716,16 +710,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
   </si>
   <si>
-    <t>25경 8963조 8558억 7602만</t>
-  </si>
-  <si>
-    <t>와츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5경 9571조 1335억 7726만</t>
+    <t>26경 1263조 8269억 2063만</t>
   </si>
   <si>
     <t>스터디뱅크</t>
@@ -734,7 +719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
   </si>
   <si>
-    <t>5경 2386조 1501억 9374만</t>
+    <t>5경 2684조 7425억 7862만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -743,37 +728,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>5경 1622조 1730억 1908만</t>
-  </si>
-  <si>
-    <t>찍먹비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8D%EB%A8%B9%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>5경 128조 2126억 5074만</t>
-  </si>
-  <si>
-    <t>뚜뭉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EB%AD%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4경 20조 8028억 8872만</t>
-  </si>
-  <si>
-    <t>뾰쀼뾰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BE%B0%EC%80%BC%EB%BE%B0</t>
-  </si>
-  <si>
-    <t>3경 6359조 5733억 8430만</t>
+    <t>5경 1636조 4516억 3545만</t>
+  </si>
+  <si>
+    <t>못함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
+  </si>
+  <si>
+    <t>3경 6375조 1012억 407만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -782,25 +746,7 @@
     <t>https://mgf.gg/contents/character.php?n=StarLink</t>
   </si>
   <si>
-    <t>3경 5352조 1555억 8999만</t>
-  </si>
-  <si>
-    <t>오쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%89%AC</t>
-  </si>
-  <si>
-    <t>2경 9176조 4466억 2022만</t>
-  </si>
-  <si>
-    <t>못함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
-  </si>
-  <si>
-    <t>2경 7853조 7862억 2233만</t>
+    <t>3경 6127조 720억 4912만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
@@ -815,7 +761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 1348조 201억 9707만</t>
+    <t>2경 2196조 5606억 4882만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -830,15 +776,6 @@
     <t>2경 1281조 6453억 4837만</t>
   </si>
   <si>
-    <t>준준챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%80%EC%A4%80%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>1경 9087조 7464억 9311만</t>
-  </si>
-  <si>
     <t>뚝딱비숍</t>
   </si>
   <si>
@@ -857,22 +794,13 @@
     <t>1경 3226조 7769억 3908만</t>
   </si>
   <si>
-    <t>서두희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%91%90%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>1경 3081조 2756억 3267만</t>
-  </si>
-  <si>
     <t>연이무사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 2016조 9110억 2771만</t>
+    <t>1경 2142조 9837억 5812만</t>
   </si>
   <si>
     <t>널꼬라봐</t>
@@ -881,7 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
   </si>
   <si>
-    <t>1경 984조 7083억 6234만</t>
+    <t>1경 1985조 432억 6670만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -896,13 +824,25 @@
     <t>1경 448조 656억 9808만</t>
   </si>
   <si>
-    <t>신참치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1경 444조 9657억 1311만</t>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>7310조 6501억 3270만</t>
+  </si>
+  <si>
+    <t>치전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A0%84</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>7094조 239억 475만</t>
   </si>
   <si>
     <t>빈수르</t>
@@ -911,301 +851,325 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>5913조 5400억 9898만</t>
   </si>
   <si>
+    <t>잉규우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B7%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3283조 3780억 8600만</t>
+  </si>
+  <si>
+    <t>삼성며언</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%84%B1%EB%A9%B0%EC%96%B8</t>
+  </si>
+  <si>
+    <t>2887조 7959억 1916만</t>
+  </si>
+  <si>
+    <t>무과금재능충</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%EA%B8%88%EC%9E%AC%EB%8A%A5%EC%B6%A9</t>
+  </si>
+  <si>
+    <t>2831조 5908억 1563만</t>
+  </si>
+  <si>
+    <t>심겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>252조 7757억 2583만</t>
+  </si>
+  <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1475경 7871조 886억 679만</t>
+  </si>
+  <si>
+    <t>요쁘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
+  </si>
+  <si>
+    <t>146경 9210조 5552억 2224만</t>
+  </si>
+  <si>
+    <t>나야햄토리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>101경 9703조 2913억 631만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>44경 6915조 2326억 6632만</t>
+  </si>
+  <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>14경 8360조 2756억 5764만</t>
+  </si>
+  <si>
+    <t>딩느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
+  </si>
+  <si>
+    <t>13경 8069조 4405억 5425만</t>
+  </si>
+  <si>
+    <t>시든꽃에물을</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
+  </si>
+  <si>
+    <t>13경 2370조 3366억 7953만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3경 3961조 3345억 679만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3경 2612조 2604억 9866만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2경 4687조 3476억 8061만</t>
+  </si>
+  <si>
+    <t>동작대교</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
+  </si>
+  <si>
+    <t>2경 2501조 3242억 4169만</t>
+  </si>
+  <si>
+    <t>나야츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 4393조 6778억 3625만</t>
+  </si>
+  <si>
+    <t>날아라순자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 2076조 4816억 9769만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>9896조 7673억 7398만</t>
+  </si>
+  <si>
+    <t>꾸덕행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
+  </si>
+  <si>
+    <t>9799조 1968억 6913만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>7207조 6496억 50만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>6061조 6988억 3369만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6051조 1417억 7599만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5918만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5360조 3020억 1006만</t>
+  </si>
+  <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5356조 2989억 2814만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>4392조 589억 1333만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>4289조 6428억 6705만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>4268조 7828억 8180만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3654조 9529억 8383만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3599조 2680억 8561만</t>
+  </si>
+  <si>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3364조 9653억 6386만</t>
+  </si>
+  <si>
+    <t>포이즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2692조 8173억 3981만</t>
+  </si>
+  <si>
+    <t>궁금증유발</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
+  </si>
+  <si>
+    <t>2644조 2846억 1124만</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>김보들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
-  </si>
-  <si>
-    <t>5840조 7231억 2937만</t>
-  </si>
-  <si>
-    <t>종리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1469경 8904조 2504억 6218만</t>
-  </si>
-  <si>
-    <t>요쁘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
-  </si>
-  <si>
-    <t>146경 9210조 5552억 2224만</t>
-  </si>
-  <si>
-    <t>나야햄토리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>101경 9703조 2913억 631만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>44경 6915조 2326억 6632만</t>
-  </si>
-  <si>
-    <t>독고사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>14경 8360조 2756억 5764만</t>
-  </si>
-  <si>
-    <t>시든꽃에물을</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
-  </si>
-  <si>
-    <t>12경 6359조 2823억 9054만</t>
-  </si>
-  <si>
-    <t>딩느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
-  </si>
-  <si>
-    <t>11경 1394조 5468억 1937만</t>
-  </si>
-  <si>
-    <t>정육츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3경 2612조 2604억 9866만</t>
-  </si>
-  <si>
-    <t>몰라츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3경 1732조 6831억 2430만</t>
-  </si>
-  <si>
-    <t>동작대교</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
-  </si>
-  <si>
-    <t>2경 2501조 3242억 4169만</t>
-  </si>
-  <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2경 1893조 2780억 5524만</t>
-  </si>
-  <si>
-    <t>나야츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 4393조 6778억 3625만</t>
-  </si>
-  <si>
-    <t>날아라순자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 2076조 4816억 9769만</t>
-  </si>
-  <si>
-    <t>수달츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>9471조 4067억 9854만</t>
-  </si>
-  <si>
-    <t>꾸덕행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
-  </si>
-  <si>
-    <t>7599조 782억 4473만</t>
-  </si>
-  <si>
-    <t>lNOVAl</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
-  </si>
-  <si>
-    <t>7207조 6496억 50만</t>
-  </si>
-  <si>
-    <t>넹또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
-  </si>
-  <si>
-    <t>6061조 6988억 3369만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6051조 1417억 7599만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5471조 457억 5918만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5360조 3020억 1006만</t>
-  </si>
-  <si>
-    <t>직만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5173조 9211억 4312만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>4392조 589억 1333만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3807조 9058억 253만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>3670조 4003억 4907만</t>
-  </si>
-  <si>
-    <t>나야김대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3554조 7208억 4048만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3554조 6058억 5264만</t>
-  </si>
-  <si>
-    <t>화정츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3364조 9653억 6386만</t>
-  </si>
-  <si>
-    <t>포이즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2692조 8173억 3981만</t>
-  </si>
-  <si>
-    <t>궁금증유발</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
-  </si>
-  <si>
-    <t>2644조 2846억 1124만</t>
-  </si>
-  <si>
     <t>현유수</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>2211조 5762억 834만</t>
+    <t>2298조 8312억 7453만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1214,7 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 5968조 5279억 8792만</t>
+    <t>26경 4852조 2614억 1968만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -1223,7 +1187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 3830조 9069억 3101만</t>
+    <t>21경 4363조 7782억 2245만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1241,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 9636조 105억 4675만</t>
+    <t>13경 1932조 6330억 1482만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1259,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 4318조 9260억 2021만</t>
+    <t>11경 4765조 3141억 9866만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1286,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>10경 4273조 612억 9717만</t>
+    <t>10경 5815조 2768억 8824만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1295,7 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>8경 3545조 3307억 6722만</t>
+    <t>8경 8180조 3418억 7758만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1304,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9003억 4099만</t>
+    <t>6경 9105조 2843억 3125만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -1313,7 +1277,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 7925조 8043억 3035만</t>
+    <t>2경 8241조 5079억 1888만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1322,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 7756조 2579억 7515만</t>
+    <t>2경 7759조 6503억 7144만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1340,7 +1304,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3490조 8557억 971만</t>
+    <t>2경 5490조 5466억 3494만</t>
+  </si>
+  <si>
+    <t>관리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2경 5040조 3923억 9599만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -1367,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>2경 679조 9420억 5073만</t>
+    <t>2경 1101조 5163억 3714만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -1376,13 +1349,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9568조 5677억 2556만</t>
+    <t>1경 9583조 9296억 6627만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 8123조 8491억 9227만</t>
+    <t>1경 9206조 5759억 431만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>1경 3924조 4290억 8656만</t>
+  </si>
+  <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 3778조 4071억 622만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -1391,16 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 3466조 9661억 2553만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>1경 3352조 5107억 6670만</t>
+    <t>1경 3657조 3032억 2557만</t>
   </si>
   <si>
     <t>라똥이</t>
@@ -1412,22 +1394,22 @@
     <t>1경 3335조 5943억 5779만</t>
   </si>
   <si>
-    <t>오곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
-  </si>
-  <si>
-    <t>1경 2805조 1072억 4398만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 501조 4529억 6137만</t>
+    <t>1경 863조 343억 2047만</t>
+  </si>
+  <si>
+    <t>초식왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
+  </si>
+  <si>
+    <t>8154조 2007억 5516만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1454,25 +1436,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%9D%BC%EB%9D%BC%EC%98%A8</t>
   </si>
   <si>
-    <t>1887조 978억 6719만</t>
-  </si>
-  <si>
-    <t>갓겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>412조 3890억 3560만</t>
-  </si>
-  <si>
-    <t>쿠크쿠쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%ED%81%AC%EC%BF%A0%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>1115조 3245억 2782만</t>
+    <t>2209조 1036억 14만</t>
+  </si>
+  <si>
+    <t>결기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>705조 9790억 9898만</t>
   </si>
   <si>
     <t>베르카암프</t>
@@ -1484,19 +1460,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>567조 6706억 4070만</t>
-  </si>
-  <si>
-    <t>결기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>533조 9907억 9511만</t>
+    <t>650조 2456억 3546만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1505,7 +1469,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>488조 6936억 1098만</t>
+    <t>561조 6384억 8827만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1532,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>370조 8748억 3980만</t>
+    <t>394조 8388억 3838만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1541,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
   </si>
   <si>
-    <t>358조 5526억 3562만</t>
+    <t>375조 6038억 5225만</t>
   </si>
   <si>
     <t>말랑랑말이</t>
@@ -1550,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>339조 5963억 9111만</t>
+    <t>343조 466억 2758만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1562,7 +1526,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>316조 970억 3170만</t>
+    <t>321조 6915억 7558만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1574,7 +1538,16 @@
     <t>105</t>
   </si>
   <si>
-    <t>225조 1841억 9766만</t>
+    <t>243조 1169억 9907만</t>
+  </si>
+  <si>
+    <t>성식대군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>222조 5512억 2910만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1589,22 +1562,31 @@
     <t>209조 4772억 5837만</t>
   </si>
   <si>
-    <t>성식대군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>200조 4730억 4168만</t>
-  </si>
-  <si>
     <t>태환이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>180조 9473억 2096만</t>
+    <t>187조 2499억 2626만</t>
+  </si>
+  <si>
+    <t>효깨비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>155조 2862억 92만</t>
+  </si>
+  <si>
+    <t>벵글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
+  </si>
+  <si>
+    <t>150조 6104억 8451만</t>
   </si>
   <si>
     <t>박상사</t>
@@ -1613,25 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%83%81%EC%82%AC</t>
   </si>
   <si>
-    <t>148조 4553억 4079만</t>
-  </si>
-  <si>
-    <t>벵글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
-  </si>
-  <si>
-    <t>138조 8110억 9665만</t>
-  </si>
-  <si>
-    <t>효깨비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>138조 6113억 1862만</t>
+    <t>150조 3135억 5276만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1640,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>135조 583억 4942만</t>
+    <t>139조 2795억 9411만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1649,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>129조 4305억 6522만</t>
+    <t>131조 1647억 3394만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1658,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
   </si>
   <si>
-    <t>100조 6585억 7077만</t>
+    <t>107조 3005억 2454만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1667,7 +1631,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>86조 8704억 907만</t>
+    <t>95조 6673억 6395만</t>
+  </si>
+  <si>
+    <t>피읕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%9D%95</t>
+  </si>
+  <si>
+    <t>95조 3657억 64만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1676,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B0%80%EC%A1%B1</t>
   </si>
   <si>
-    <t>69조 3240억 9638만</t>
+    <t>72조 7173억 9926만</t>
   </si>
   <si>
     <t>진흥이</t>
@@ -1685,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%9D%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>38조 6698억 6068만</t>
+    <t>51조 8043억 13만</t>
   </si>
   <si>
     <t>파란달팽2</t>
@@ -1694,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%9E%80%EB%8B%AC%ED%8C%BD2</t>
   </si>
   <si>
-    <t>21조 2495억 8332만</t>
+    <t>22조 4212억 7788만</t>
   </si>
   <si>
     <t>상혀닝</t>
@@ -1706,7 +1679,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 1852억 38만</t>
+    <t>16조 1273억 5394만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1718,13 +1691,13 @@
     <t>102</t>
   </si>
   <si>
-    <t>11조 6147억 3677만</t>
+    <t>15조 7363억 9572만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>7조 9154억 851만</t>
+    <t>8조 3444억 1401만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1736,7 +1709,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>3조 5767억 9049만</t>
+    <t>4조 646억 600만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1751,7 +1724,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1655억 4143만</t>
+    <t>1987억 1878만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1766,7 +1739,7 @@
     <t>83</t>
   </si>
   <si>
-    <t>127억 3938만</t>
+    <t>149억 6773만</t>
   </si>
 </sst>
 </file>
@@ -2536,7 +2509,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>84</v>
@@ -2597,13 +2570,13 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2614,16 +2587,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -2632,10 +2605,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2646,16 +2619,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -2667,7 +2640,7 @@
         <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2678,16 +2651,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -2696,10 +2669,10 @@
         <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2710,28 +2683,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2742,16 +2715,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -2760,10 +2733,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2774,16 +2747,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -2792,10 +2765,10 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2806,25 +2779,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2856,7 +2829,7 @@
         <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>132</v>
@@ -2888,7 +2861,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2920,7 +2893,7 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2952,7 +2925,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>144</v>
@@ -2984,7 +2957,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>148</v>
@@ -3016,7 +2989,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>152</v>
@@ -3048,7 +3021,7 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>156</v>
@@ -3129,25 +3102,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3158,25 +3131,25 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3205,13 +3178,13 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3222,25 +3195,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>185</v>
@@ -3269,13 +3242,13 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3286,28 +3259,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3318,28 +3291,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3350,16 +3323,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -3368,10 +3341,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3416,7 +3389,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3469,25 +3442,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>35</v>
@@ -3501,25 +3474,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>35</v>
@@ -3533,25 +3506,25 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>35</v>
@@ -3565,25 +3538,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>35</v>
@@ -3597,25 +3570,25 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>35</v>
@@ -3626,28 +3599,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>35</v>
@@ -3658,28 +3631,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>35</v>
@@ -3690,28 +3663,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>35</v>
@@ -3722,28 +3695,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>35</v>
@@ -3754,28 +3727,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -3786,28 +3759,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>35</v>
@@ -3818,28 +3791,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>35</v>
@@ -3853,13 +3826,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -3868,10 +3841,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>35</v>
@@ -3885,22 +3858,22 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>248</v>
@@ -3929,10 +3902,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>251</v>
@@ -3961,10 +3934,10 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>254</v>
@@ -3996,7 +3969,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>257</v>
@@ -4013,25 +3986,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>35</v>
@@ -4045,25 +4018,25 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>35</v>
@@ -4077,25 +4050,25 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>35</v>
@@ -4109,25 +4082,25 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>174</v>
+        <v>270</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>35</v>
@@ -4141,25 +4114,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>35</v>
@@ -4170,28 +4143,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>35</v>
@@ -4205,25 +4178,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>35</v>
@@ -4234,28 +4207,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>35</v>
@@ -4269,160 +4242,32 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J27"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4450,10 +4295,6 @@
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4470,7 +4311,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4514,25 +4355,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4546,13 +4387,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -4564,7 +4405,7 @@
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4578,13 +4419,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -4593,10 +4434,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4616,10 +4457,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>88</v>
@@ -4628,7 +4469,7 @@
         <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4642,13 +4483,13 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -4657,10 +4498,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4671,28 +4512,28 @@
         <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4703,28 +4544,28 @@
         <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4735,28 +4576,28 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4767,28 +4608,28 @@
         <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4799,28 +4640,28 @@
         <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4831,28 +4672,28 @@
         <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4863,16 +4704,16 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -4881,10 +4722,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4898,13 +4739,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -4913,10 +4754,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4930,13 +4771,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -4945,10 +4786,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4962,13 +4803,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -4977,10 +4818,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4994,13 +4835,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -5009,10 +4850,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5026,13 +4867,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5041,10 +4882,10 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5058,13 +4899,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -5073,10 +4914,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5090,13 +4931,13 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -5105,10 +4946,10 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5122,13 +4963,13 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -5137,10 +4978,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5154,13 +4995,13 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -5169,10 +5010,10 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5186,25 +5027,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5215,16 +5056,16 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -5233,10 +5074,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5250,25 +5091,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>373</v>
+        <v>287</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5279,16 +5120,16 @@
         <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -5297,10 +5138,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5314,13 +5155,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -5329,10 +5170,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5343,16 +5184,16 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -5361,10 +5202,10 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5375,16 +5216,16 @@
         <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -5393,10 +5234,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5407,16 +5248,16 @@
         <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -5425,10 +5266,10 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5439,28 +5280,28 @@
         <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>377</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5506,7 +5347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5559,25 +5400,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>51</v>
@@ -5591,13 +5432,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -5606,10 +5447,10 @@
         <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>51</v>
@@ -5623,13 +5464,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -5638,10 +5479,10 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>51</v>
@@ -5655,13 +5496,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -5670,10 +5511,10 @@
         <v>131</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>51</v>
@@ -5687,25 +5528,25 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>51</v>
@@ -5716,16 +5557,16 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -5734,10 +5575,10 @@
         <v>160</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>51</v>
@@ -5748,28 +5589,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>51</v>
@@ -5780,28 +5621,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>51</v>
@@ -5812,28 +5653,28 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>51</v>
@@ -5844,16 +5685,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -5862,10 +5703,10 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>51</v>
@@ -5876,16 +5717,16 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -5897,7 +5738,7 @@
         <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>51</v>
@@ -5908,16 +5749,16 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -5926,10 +5767,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -5943,13 +5784,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -5958,10 +5799,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>51</v>
@@ -5975,13 +5816,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -5990,10 +5831,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>51</v>
@@ -6007,13 +5848,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -6022,10 +5863,10 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>51</v>
@@ -6039,13 +5880,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -6054,10 +5895,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>51</v>
@@ -6071,25 +5912,25 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>51</v>
@@ -6103,25 +5944,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>287</v>
+        <v>190</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>51</v>
@@ -6135,25 +5976,25 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>51</v>
@@ -6167,25 +6008,25 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>173</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>51</v>
@@ -6199,25 +6040,25 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>452</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>452</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>51</v>
@@ -6231,13 +6072,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -6246,10 +6087,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>51</v>
@@ -6260,28 +6101,28 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>51</v>
@@ -6295,25 +6136,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>51</v>
@@ -6324,28 +6165,28 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>51</v>
@@ -6359,13 +6200,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -6374,10 +6215,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>287</v>
+        <v>184</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>51</v>
@@ -6388,16 +6229,16 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -6406,10 +6247,10 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>51</v>
@@ -6420,28 +6261,28 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>51</v>
@@ -6452,35 +6293,67 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6511,6 +6384,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6527,7 +6401,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6571,25 +6445,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>363</v>
+        <v>472</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>35</v>
@@ -6603,25 +6477,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>35</v>
@@ -6635,25 +6509,25 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>35</v>
@@ -6667,25 +6541,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>35</v>
@@ -6699,25 +6573,25 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>35</v>
@@ -6728,28 +6602,28 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>35</v>
@@ -6760,28 +6634,28 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>35</v>
@@ -6792,28 +6666,28 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>35</v>
@@ -6824,28 +6698,28 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>35</v>
@@ -6856,28 +6730,28 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>35</v>
@@ -6888,28 +6762,28 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>35</v>
@@ -6920,16 +6794,16 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -6938,10 +6812,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>35</v>
@@ -6955,25 +6829,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>35</v>
@@ -6987,25 +6861,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>35</v>
@@ -7019,25 +6893,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>35</v>
@@ -7051,25 +6925,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>35</v>
@@ -7083,25 +6957,25 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>35</v>
@@ -7115,25 +6989,25 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>35</v>
@@ -7147,25 +7021,25 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>35</v>
@@ -7179,25 +7053,25 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>35</v>
@@ -7211,25 +7085,25 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>35</v>
@@ -7243,13 +7117,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -7258,10 +7132,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>35</v>
@@ -7272,16 +7146,16 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -7290,10 +7164,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>35</v>
@@ -7307,13 +7181,13 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
@@ -7322,10 +7196,10 @@
         <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>35</v>
@@ -7336,16 +7210,16 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -7354,10 +7228,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>35</v>
@@ -7371,13 +7245,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -7386,10 +7260,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>35</v>
@@ -7400,7 +7274,7 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>59</v>
@@ -7409,19 +7283,19 @@
         <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>35</v>
@@ -7432,16 +7306,16 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -7450,10 +7324,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>35</v>
@@ -7464,28 +7338,28 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>35</v>
@@ -7496,28 +7370,28 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>377</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>35</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,16 +9,16 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="설묘" sheetId="2" r:id="rId2"/>
-    <sheet name="별하나달하나" sheetId="3" r:id="rId3"/>
-    <sheet name="TRIUMPH" sheetId="4" r:id="rId4"/>
+    <sheet name="TRIUMPH" sheetId="3" r:id="rId3"/>
+    <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
     <sheet name="셀린느" sheetId="5" r:id="rId5"/>
     <sheet name="promise" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="575">
   <si>
     <t>guild_name</t>
   </si>
@@ -104,6 +104,27 @@
     <t>2026.09.20</t>
   </si>
   <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>914경 1847조 7200억 8300만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
     <t>별하나달하나</t>
   </si>
   <si>
@@ -137,27 +158,6 @@
     <t>2026.09.22</t>
   </si>
   <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>914경 1847조 7200억 8300만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
     <t>셀린느</t>
   </si>
   <si>
@@ -251,7 +251,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>297경 2867조 5488억 4785만</t>
+    <t>308경 5775조 8635억 934만</t>
   </si>
   <si>
     <t>2</t>
@@ -266,7 +266,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>289경 6454조 4742억 1360만</t>
+    <t>296경 225조 5202억 8461만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>206경 7530조 1038억 2497만</t>
+    <t>210경 3232조 1464억 2197만</t>
   </si>
   <si>
     <t>4</t>
@@ -326,7 +326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>76경 7872조 6949억 9142만</t>
+    <t>78경 3943조 4780억 2568만</t>
   </si>
   <si>
     <t>7</t>
@@ -344,6 +344,24 @@
     <t>8</t>
   </si>
   <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>46경 2528조 6129억 7820만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>루델밍</t>
   </si>
   <si>
@@ -353,24 +371,6 @@
     <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>45경 1339조 4074억 6761만</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>43경 1581조 3006억 376만</t>
+    <t>44경 6683조 9426억 1397만</t>
   </si>
   <si>
     <t>11</t>
@@ -395,7 +395,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>37경 8186조 166억 18만</t>
+    <t>37경 8729조 5286억 2732만</t>
   </si>
   <si>
     <t>12</t>
@@ -437,12 +437,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 6036조 6491억 3235만</t>
+    <t>24경 9067조 3518억 5만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>21경 148조 2647억 9744만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>마덕칠</t>
   </si>
   <si>
@@ -452,18 +464,6 @@
     <t>21경 127조 2151억 9086만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>20경 5514조 8976억 7519만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -497,7 +497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>10경 5928조 6370억 6895만</t>
+    <t>10경 6016조 364억 6115만</t>
   </si>
   <si>
     <t>20</t>
@@ -521,6 +521,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>7경 4772조 1310억 7065만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>다다익숍</t>
   </si>
   <si>
@@ -530,7 +542,7 @@
     <t>7경 4318조 3235억 2661만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
@@ -545,18 +557,6 @@
     <t>7경 2830조 3342억 6906만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>6경 5564조 1888억 7889만</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
@@ -614,7 +614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 8428조 4809억 2430만</t>
+    <t>1경 8768조 6008억 6927만</t>
   </si>
   <si>
     <t>28</t>
@@ -626,7 +626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 6393조 9171억 9294만</t>
+    <t>1경 6685조 4095억 6058만</t>
   </si>
   <si>
     <t>29</t>
@@ -641,19 +641,310 @@
     <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1734경 8665조 4259억 3571만</t>
+  </si>
+  <si>
+    <t>요쁘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
+  </si>
+  <si>
+    <t>146경 9210조 5552억 2224만</t>
+  </si>
+  <si>
+    <t>나야햄토리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>101경 9703조 2913억 631만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>44경 6915조 2326억 6632만</t>
+  </si>
+  <si>
+    <t>독고사수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
+  </si>
+  <si>
+    <t>14경 8360조 2756억 5764만</t>
+  </si>
+  <si>
+    <t>딩느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
+  </si>
+  <si>
+    <t>13경 8069조 4405억 5425만</t>
+  </si>
+  <si>
+    <t>시든꽃에물을</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
+  </si>
+  <si>
+    <t>13경 2370조 3366억 7953만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>3경 4989조 190억 4940만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3경 2612조 2604억 9866만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2경 5908조 9044억 2056만</t>
+  </si>
+  <si>
+    <t>동작대교</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
+  </si>
+  <si>
+    <t>2경 2501조 3242억 4169만</t>
+  </si>
+  <si>
+    <t>나야츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 4393조 6778억 3625만</t>
+  </si>
+  <si>
+    <t>날아라순자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 2076조 4816억 9769만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 30조 6030억 7881만</t>
+  </si>
+  <si>
+    <t>꾸덕행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
+  </si>
+  <si>
+    <t>9799조 1968억 6913만</t>
+  </si>
+  <si>
+    <t>넹또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
+  </si>
+  <si>
+    <t>7348조 755억 2314만</t>
+  </si>
+  <si>
+    <t>lNOVAl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
+  </si>
+  <si>
+    <t>7207조 6496억 50만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6417조 6558억 9398만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6051조 1417억 7599만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5471조 457억 5918만</t>
+  </si>
+  <si>
+    <t>직만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5356조 2989억 2814만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>5051조 7256억 2807만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>4289조 6428억 6705만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>4268조 7828억 8180만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3894조 7432억 4175만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3711조 293억 5772만</t>
+  </si>
+  <si>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
+  </si>
+  <si>
+    <t>3389조 3873억 2601만</t>
+  </si>
+  <si>
+    <t>궁금증유발</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
+  </si>
+  <si>
+    <t>2734조 8634억 6484만</t>
+  </si>
+  <si>
+    <t>포이즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2692조 8173억 3981만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>2329조 8194억 1497만</t>
+  </si>
+  <si>
     <t>달하나별하나</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>신궁</t>
-  </si>
-  <si>
     <t>126</t>
   </si>
   <si>
-    <t>278경 3626조 7898억 1199만</t>
+    <t>279경 4954조 9082억 1944만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -671,7 +962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>98경 5605조 561억 6808만</t>
+    <t>98경 6693조 9283억 9486만</t>
   </si>
   <si>
     <t>라온DK</t>
@@ -680,9 +971,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
     <t>81경 2026조 9445억 5460만</t>
   </si>
   <si>
@@ -692,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
   </si>
   <si>
-    <t>69경 3013조 175억 5492만</t>
+    <t>71경 308조 3942억 8949만</t>
   </si>
   <si>
     <t>라온B</t>
@@ -728,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>5경 1636조 4516억 3545만</t>
+    <t>5경 1650조 7124억 1325만</t>
   </si>
   <si>
     <t>못함</t>
@@ -737,7 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
   </si>
   <si>
-    <t>3경 6375조 1012억 407만</t>
+    <t>3경 8221조 9534억 218만</t>
   </si>
   <si>
     <t>StarLink</t>
@@ -752,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=Onyul</t>
   </si>
   <si>
-    <t>2경 6517조 1038억 8309만</t>
+    <t>2경 7530조 4082억 2527만</t>
   </si>
   <si>
     <t>금하나</t>
@@ -761,7 +1049,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
   </si>
   <si>
-    <t>2경 2196조 5606억 4882만</t>
+    <t>2경 2668조 5652억 6269만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>2경 2480조 5534억 5129만</t>
   </si>
   <si>
     <t>쵸비다</t>
@@ -770,19 +1067,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
   </si>
   <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
     <t>2경 1281조 6453억 4837만</t>
   </si>
   <si>
-    <t>뚝딱비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9D%EB%94%B1%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>1경 5832조 5976억 1885만</t>
+    <t>널꼬라봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
+  </si>
+  <si>
+    <t>1경 6027조 4749억 8865만</t>
   </si>
   <si>
     <t>희다차</t>
@@ -791,7 +1085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
   </si>
   <si>
-    <t>1경 3226조 7769억 3908만</t>
+    <t>1경 4481조 7180억 3929만</t>
   </si>
   <si>
     <t>연이무사</t>
@@ -800,16 +1094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 2142조 9837억 5812만</t>
-  </si>
-  <si>
-    <t>널꼬라봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
-  </si>
-  <si>
-    <t>1경 1985조 432억 6670만</t>
+    <t>1경 2564조 3792억 1980만</t>
   </si>
   <si>
     <t>걸동이</t>
@@ -839,10 +1124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A0%84</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>7094조 239억 475만</t>
+    <t>7096조 2974억 7032만</t>
   </si>
   <si>
     <t>빈수르</t>
@@ -851,7 +1133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
   </si>
   <si>
-    <t>5913조 5400억 9898만</t>
+    <t>6256조 9615억 5505만</t>
   </si>
   <si>
     <t>잉규우</t>
@@ -860,9 +1142,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B7%9C%EC%9A%B0</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>3283조 3780억 8600만</t>
   </si>
   <si>
@@ -890,286 +1169,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B2%9C</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>252조 7757억 2583만</t>
-  </si>
-  <si>
-    <t>종리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1475경 7871조 886억 679만</t>
-  </si>
-  <si>
-    <t>요쁘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
-  </si>
-  <si>
-    <t>146경 9210조 5552억 2224만</t>
-  </si>
-  <si>
-    <t>나야햄토리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>101경 9703조 2913억 631만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>44경 6915조 2326억 6632만</t>
-  </si>
-  <si>
-    <t>독고사수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
-  </si>
-  <si>
-    <t>14경 8360조 2756억 5764만</t>
-  </si>
-  <si>
-    <t>딩느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
-  </si>
-  <si>
-    <t>13경 8069조 4405억 5425만</t>
-  </si>
-  <si>
-    <t>시든꽃에물을</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
-  </si>
-  <si>
-    <t>13경 2370조 3366억 7953만</t>
-  </si>
-  <si>
-    <t>몰라츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3경 3961조 3345억 679만</t>
-  </si>
-  <si>
-    <t>정육츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3경 2612조 2604억 9866만</t>
-  </si>
-  <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2경 4687조 3476억 8061만</t>
-  </si>
-  <si>
-    <t>동작대교</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
-  </si>
-  <si>
-    <t>2경 2501조 3242억 4169만</t>
-  </si>
-  <si>
-    <t>나야츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 4393조 6778억 3625만</t>
-  </si>
-  <si>
-    <t>날아라순자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 2076조 4816억 9769만</t>
-  </si>
-  <si>
-    <t>수달츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>9896조 7673억 7398만</t>
-  </si>
-  <si>
-    <t>꾸덕행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
-  </si>
-  <si>
-    <t>9799조 1968억 6913만</t>
-  </si>
-  <si>
-    <t>lNOVAl</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=lNOVAl</t>
-  </si>
-  <si>
-    <t>7207조 6496억 50만</t>
-  </si>
-  <si>
-    <t>넹또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%B9%EB%98%90</t>
-  </si>
-  <si>
-    <t>6061조 6988억 3369만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6051조 1417억 7599만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5471조 457억 5918만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>5360조 3020억 1006만</t>
-  </si>
-  <si>
-    <t>직만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5356조 2989억 2814만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>4392조 589억 1333만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>4289조 6428억 6705만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>4268조 7828억 8180만</t>
-  </si>
-  <si>
-    <t>나야김대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3654조 9529억 8383만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3599조 2680억 8561만</t>
-  </si>
-  <si>
-    <t>화정츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
-  </si>
-  <si>
-    <t>3364조 9653억 6386만</t>
-  </si>
-  <si>
-    <t>포이즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2692조 8173억 3981만</t>
-  </si>
-  <si>
-    <t>궁금증유발</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%EA%B8%88%EC%A6%9D%EC%9C%A0%EB%B0%9C</t>
-  </si>
-  <si>
-    <t>2644조 2846억 1124만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>2298조 8312억 7453만</t>
+    <t>253조 3301억 3088만</t>
+  </si>
+  <si>
+    <t>김바들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B0%94%EB%93%A4</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>4억 1781만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1187,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 4363조 7782억 2245만</t>
+    <t>21경 4602조 2880억 4838만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1205,7 +1217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>13경 1932조 6330억 1482만</t>
+    <t>13경 7587조 3965억 6582만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1223,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 4765조 3141억 9866만</t>
+    <t>11경 4888조 1019억 6279만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1250,7 +1262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>10경 5815조 2768억 8824만</t>
+    <t>10경 7242조 7937억 8721만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1259,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>8경 8180조 3418억 7758만</t>
+    <t>9경 3317조 4001억 9160만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1277,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 8241조 5079억 1888만</t>
+    <t>2경 9699조 1981억 6015만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1286,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 7759조 6503억 7144만</t>
+    <t>2경 7903조 5183억 9816만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1304,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 5490조 5466억 3494만</t>
+    <t>2경 5712조 7806억 9494만</t>
   </si>
   <si>
     <t>관리</t>
@@ -1322,7 +1334,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 3019조 5691억 5455만</t>
+    <t>2경 3508조 3251억 6396만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1349,13 +1361,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9583조 9296억 6627만</t>
+    <t>1경 9797조 8732억 636만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 9206조 5759억 431만</t>
+    <t>1경 9793조 2926억 2205만</t>
+  </si>
+  <si>
+    <t>니뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>1경 4316조 7438억 6414만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1364,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3924조 4290억 8656만</t>
+    <t>1경 4044조 2010억 4291만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -1376,15 +1397,6 @@
     <t>1경 3778조 4071억 622만</t>
   </si>
   <si>
-    <t>니뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>1경 3657조 3032억 2557만</t>
-  </si>
-  <si>
     <t>라똥이</t>
   </si>
   <si>
@@ -1400,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 863조 343억 2047만</t>
+    <t>1경 1347조 2778억 8822만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -1436,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%9D%BC%EB%9D%BC%EC%98%A8</t>
   </si>
   <si>
-    <t>2209조 1036억 14만</t>
+    <t>2291조 6804억 2795만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1460,7 +1472,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>650조 2456억 3546만</t>
+    <t>652조 6436억 3867만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1469,7 +1481,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%B6%94%EC%96%91%EC%A1%B0%EC%9E%A5</t>
   </si>
   <si>
-    <t>561조 6384억 8827만</t>
+    <t>598조 9089억 1619만</t>
+  </si>
+  <si>
+    <t>썬콜원준띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>572조 5374억 7343만</t>
   </si>
   <si>
     <t>온우사수</t>
@@ -1481,22 +1502,13 @@
     <t>462조 6492억 9502만</t>
   </si>
   <si>
-    <t>썬콜원준띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EC%9B%90%EC%A4%80%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>420조 915억 4392만</t>
-  </si>
-  <si>
     <t>날씬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%94%AC</t>
   </si>
   <si>
-    <t>394조 8388억 3838만</t>
+    <t>400조 3497억 7235만</t>
   </si>
   <si>
     <t>지존승준</t>
@@ -1505,7 +1517,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%8A%B9%EC%A4%80</t>
   </si>
   <si>
-    <t>375조 6038억 5225만</t>
+    <t>377조 9362억 3025만</t>
   </si>
   <si>
     <t>말랑랑말이</t>
@@ -1514,7 +1526,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EB%9E%91%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>343조 466억 2758만</t>
+    <t>345조 2663억 4984만</t>
   </si>
   <si>
     <t>눅이마</t>
@@ -1526,7 +1538,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>321조 6915억 7558만</t>
+    <t>323조 9819억 969만</t>
   </si>
   <si>
     <t>한로얘</t>
@@ -1535,94 +1547,94 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
   </si>
   <si>
+    <t>250조 2125억 2104만</t>
+  </si>
+  <si>
+    <t>성식대군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>228조 146억 808만</t>
+  </si>
+  <si>
+    <t>버미겨리0</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>209조 4772억 5837만</t>
+  </si>
+  <si>
+    <t>태환이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>195조 7056억 7752만</t>
+  </si>
+  <si>
+    <t>효깨비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>155조 2862억 92만</t>
+  </si>
+  <si>
+    <t>박상사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%83%81%EC%82%AC</t>
+  </si>
+  <si>
+    <t>152조 2230억 5936만</t>
+  </si>
+  <si>
+    <t>벵글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
+  </si>
+  <si>
+    <t>150조 6855억 4467만</t>
+  </si>
+  <si>
+    <t>NSYN</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=NSYN</t>
+  </si>
+  <si>
+    <t>142조 5792억 8033만</t>
+  </si>
+  <si>
+    <t>에너지솔루션</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
+  </si>
+  <si>
+    <t>131조 2936억 7103만</t>
+  </si>
+  <si>
+    <t>방제서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
-    <t>243조 1169억 9907만</t>
-  </si>
-  <si>
-    <t>성식대군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>222조 5512억 2910만</t>
-  </si>
-  <si>
-    <t>버미겨리0</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%84%EB%AF%B8%EA%B2%A8%EB%A6%AC0</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>209조 4772억 5837만</t>
-  </si>
-  <si>
-    <t>태환이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%99%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>187조 2499억 2626만</t>
-  </si>
-  <si>
-    <t>효깨비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EA%B9%A8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>155조 2862억 92만</t>
-  </si>
-  <si>
-    <t>벵글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
-  </si>
-  <si>
-    <t>150조 6104억 8451만</t>
-  </si>
-  <si>
-    <t>박상사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%83%81%EC%82%AC</t>
-  </si>
-  <si>
-    <t>150조 3135억 5276만</t>
-  </si>
-  <si>
-    <t>NSYN</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=NSYN</t>
-  </si>
-  <si>
-    <t>139조 2795억 9411만</t>
-  </si>
-  <si>
-    <t>에너지솔루션</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
-  </si>
-  <si>
-    <t>131조 1647억 3394만</t>
-  </si>
-  <si>
-    <t>방제서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%A9%EC%A0%9C%EC%84%9C</t>
-  </si>
-  <si>
-    <t>107조 3005억 2454만</t>
+    <t>107조 3459억 6343만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1631,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>95조 6673억 6395만</t>
+    <t>102조 7538억 3535만</t>
   </si>
   <si>
     <t>피읕</t>
@@ -1679,7 +1691,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>16조 1273억 5394만</t>
+    <t>16조 3348억 8107만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1697,7 +1709,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9E%91b</t>
   </si>
   <si>
-    <t>8조 3444억 1401만</t>
+    <t>8조 8103억 675만</t>
   </si>
   <si>
     <t>도현빠덜</t>
@@ -1709,7 +1721,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 646억 600만</t>
+    <t>4조 1913억 6466만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1724,7 +1736,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1987억 1878만</t>
+    <t>2025억 9410만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -1739,7 +1751,7 @@
     <t>83</t>
   </si>
   <si>
-    <t>149억 6773만</t>
+    <t>171억 2112만</t>
   </si>
 </sst>
 </file>
@@ -2220,64 +2232,64 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2303,7 +2315,7 @@
         <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -2344,7 +2356,7 @@
         <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -2359,7 +2371,7 @@
         <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2666,13 +2678,13 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2683,25 +2695,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>113</v>
@@ -2890,10 +2902,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2922,10 +2934,10 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>144</v>
@@ -2989,7 +3001,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>152</v>
@@ -3021,7 +3033,7 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>156</v>
@@ -3082,7 +3094,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>161</v>
@@ -3102,25 +3114,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3131,25 +3143,25 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="G24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3181,7 +3193,7 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>179</v>
@@ -3389,919 +3401,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J27"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4311,7 +3410,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4349,31 +3448,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>290</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>291</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4381,19 +3480,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>292</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>292</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>293</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -4405,7 +3504,7 @@
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>294</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4413,19 +3512,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -4437,7 +3536,7 @@
         <v>94</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4445,22 +3544,22 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>298</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>88</v>
@@ -4469,7 +3568,7 @@
         <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>299</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4477,19 +3576,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>301</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -4498,10 +3597,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4509,19 +3608,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>303</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>303</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>304</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -4530,10 +3629,10 @@
         <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4541,19 +3640,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>307</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -4562,10 +3661,10 @@
         <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4573,31 +3672,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4605,19 +3704,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -4626,10 +3725,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4637,19 +3736,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>316</v>
+        <v>234</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -4661,7 +3760,7 @@
         <v>184</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>317</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4669,19 +3768,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>318</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>318</v>
+        <v>236</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -4693,7 +3792,7 @@
         <v>184</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4701,19 +3800,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -4722,10 +3821,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>323</v>
+        <v>241</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4733,19 +3832,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -4754,10 +3853,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>327</v>
+        <v>245</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4765,19 +3864,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>329</v>
+        <v>247</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -4786,10 +3885,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4797,19 +3896,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>332</v>
+        <v>250</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -4818,10 +3917,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>333</v>
+        <v>251</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4829,19 +3928,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>335</v>
+        <v>253</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -4850,10 +3949,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>336</v>
+        <v>254</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4861,19 +3960,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -4882,10 +3981,10 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4893,19 +3992,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>340</v>
+        <v>258</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>340</v>
+        <v>258</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>341</v>
+        <v>259</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -4914,10 +4013,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>342</v>
+        <v>260</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4925,19 +4024,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>343</v>
+        <v>261</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>343</v>
+        <v>261</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -4946,10 +4045,10 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>345</v>
+        <v>263</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4957,19 +4056,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -4978,10 +4077,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>348</v>
+        <v>266</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4989,19 +4088,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>350</v>
+        <v>268</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -5010,10 +4109,10 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>352</v>
+        <v>270</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5021,31 +4120,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>355</v>
+        <v>274</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5053,19 +4152,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>357</v>
+        <v>276</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -5074,10 +4173,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5085,31 +4184,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>361</v>
+        <v>281</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5117,19 +4216,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>362</v>
+        <v>282</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>362</v>
+        <v>282</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>363</v>
+        <v>283</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -5138,10 +4237,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>351</v>
+        <v>227</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5149,19 +4248,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>365</v>
+        <v>285</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>365</v>
+        <v>285</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>366</v>
+        <v>286</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -5170,10 +4269,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>367</v>
+        <v>287</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5181,19 +4280,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>368</v>
+        <v>288</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>368</v>
+        <v>288</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>369</v>
+        <v>289</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -5202,10 +4301,10 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5213,31 +4312,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>371</v>
+        <v>291</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>371</v>
+        <v>291</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>372</v>
+        <v>292</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>326</v>
+        <v>269</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5245,31 +4344,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5277,31 +4376,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>378</v>
+        <v>298</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>378</v>
+        <v>298</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>379</v>
+        <v>299</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5345,6 +4444,952 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J28"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5400,25 +5445,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>51</v>
@@ -5432,13 +5477,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -5447,10 +5492,10 @@
         <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>51</v>
@@ -5464,13 +5509,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -5482,7 +5527,7 @@
         <v>121</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>51</v>
@@ -5496,13 +5541,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -5514,7 +5559,7 @@
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>51</v>
@@ -5528,13 +5573,13 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -5546,7 +5591,7 @@
         <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>51</v>
@@ -5560,13 +5605,13 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -5575,10 +5620,10 @@
         <v>160</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>51</v>
@@ -5592,13 +5637,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -5607,10 +5652,10 @@
         <v>126</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>51</v>
@@ -5624,25 +5669,25 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>51</v>
@@ -5653,16 +5698,16 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -5671,10 +5716,10 @@
         <v>183</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>51</v>
@@ -5688,13 +5733,13 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -5706,7 +5751,7 @@
         <v>190</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>51</v>
@@ -5720,13 +5765,13 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -5738,7 +5783,7 @@
         <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>51</v>
@@ -5752,13 +5797,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -5767,10 +5812,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -5784,13 +5829,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -5802,7 +5847,7 @@
         <v>190</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>51</v>
@@ -5816,13 +5861,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -5831,10 +5876,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>51</v>
@@ -5848,13 +5893,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -5866,7 +5911,7 @@
         <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>51</v>
@@ -5880,13 +5925,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -5898,7 +5943,7 @@
         <v>190</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>51</v>
@@ -5912,13 +5957,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5930,7 +5975,7 @@
         <v>184</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>51</v>
@@ -5944,13 +5989,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -5962,7 +6007,7 @@
         <v>190</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>51</v>
@@ -5976,13 +6021,13 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -5991,10 +6036,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>51</v>
@@ -6008,13 +6053,13 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -6023,10 +6068,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>51</v>
@@ -6046,19 +6091,19 @@
         <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>51</v>
@@ -6072,25 +6117,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>51</v>
@@ -6101,28 +6146,28 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>51</v>
@@ -6136,25 +6181,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>184</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>51</v>
@@ -6168,25 +6213,25 @@
         <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>51</v>
@@ -6200,13 +6245,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -6218,7 +6263,7 @@
         <v>184</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>51</v>
@@ -6232,13 +6277,13 @@
         <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -6247,10 +6292,10 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>51</v>
@@ -6264,13 +6309,13 @@
         <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -6279,10 +6324,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>263</v>
+        <v>358</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>51</v>
@@ -6296,13 +6341,13 @@
         <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -6311,10 +6356,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>51</v>
@@ -6325,16 +6370,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
@@ -6343,10 +6388,10 @@
         <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>51</v>
@@ -6445,13 +6490,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
@@ -6460,13 +6505,13 @@
         <v>160</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6477,13 +6522,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -6492,13 +6537,13 @@
         <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6509,13 +6554,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -6524,13 +6569,13 @@
         <v>126</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6541,28 +6586,28 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>476</v>
+        <v>280</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6573,28 +6618,28 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6605,28 +6650,28 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6637,13 +6682,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -6655,10 +6700,10 @@
         <v>476</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6669,13 +6714,13 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -6684,13 +6729,13 @@
         <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6698,16 +6743,16 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -6716,13 +6761,13 @@
         <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6733,13 +6778,13 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -6751,10 +6796,10 @@
         <v>502</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6765,13 +6810,13 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -6780,13 +6825,13 @@
         <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6797,13 +6842,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -6812,13 +6857,13 @@
         <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6829,13 +6874,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -6844,13 +6889,13 @@
         <v>160</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6861,13 +6906,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -6876,13 +6921,13 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6893,28 +6938,28 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6925,28 +6970,28 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6957,13 +7002,13 @@
         <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -6972,13 +7017,13 @@
         <v>160</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6989,13 +7034,13 @@
         <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -7004,13 +7049,13 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7021,13 +7066,13 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -7036,13 +7081,13 @@
         <v>183</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7053,13 +7098,13 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -7068,13 +7113,13 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7085,13 +7130,13 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -7100,13 +7145,13 @@
         <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7117,13 +7162,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -7132,13 +7177,13 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7146,16 +7191,16 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -7164,13 +7209,13 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7181,13 +7226,13 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
@@ -7196,13 +7241,13 @@
         <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7213,13 +7258,13 @@
         <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -7228,13 +7273,13 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7245,13 +7290,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -7260,13 +7305,13 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7283,22 +7328,22 @@
         <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7309,13 +7354,13 @@
         <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -7324,13 +7369,13 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7341,28 +7386,28 @@
         <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7370,31 +7415,31 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,16 +9,16 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="설묘" sheetId="2" r:id="rId2"/>
-    <sheet name="TRIUMPH" sheetId="3" r:id="rId3"/>
-    <sheet name="별하나달하나" sheetId="4" r:id="rId4"/>
+    <sheet name="별하나달하나" sheetId="3" r:id="rId3"/>
+    <sheet name="TRIUMPH" sheetId="4" r:id="rId4"/>
     <sheet name="셀린느" sheetId="5" r:id="rId5"/>
     <sheet name="promise" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">promise!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별하나달하나!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별하나달하나!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="574">
   <si>
     <t>guild_name</t>
   </si>
@@ -104,6 +104,39 @@
     <t>2026.09.20</t>
   </si>
   <si>
+    <t>별하나달하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>796경 1899조 7356억 4540만</t>
+  </si>
+  <si>
+    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
+  </si>
+  <si>
+    <t>Onyul</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
     <t>TRIUMPH</t>
   </si>
   <si>
@@ -125,39 +158,6 @@
     <t>퐁이츄</t>
   </si>
   <si>
-    <t>별하나달하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%ED%95%98%EB%82%98%EB%8B%AC%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>796경 1899조 7356억 4540만</t>
-  </si>
-  <si>
-    <t>길드컨텐츠 필수 / 단톡참여 / 문의: Onyul, 금하나, 빈수르, 김보들</t>
-  </si>
-  <si>
-    <t>Onyul</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
     <t>셀린느</t>
   </si>
   <si>
@@ -251,7 +251,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>308경 5775조 8635억 934만</t>
+    <t>308경 7498조 5371억 8363만</t>
   </si>
   <si>
     <t>2</t>
@@ -266,7 +266,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>296경 225조 5202억 8461만</t>
+    <t>302경 3995조 3295억 7935만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,7 +281,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>210경 3232조 1464억 2197만</t>
+    <t>210경 4058조 3294억 9261만</t>
   </si>
   <si>
     <t>4</t>
@@ -296,91 +296,91 @@
     <t>팔라딘</t>
   </si>
   <si>
+    <t>105경 4731조 5416억 8730만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>105경 4731조 5416억 8730만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+    <t>85경 8894조 1952억 8378만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>81경 1380조 9531억 7826만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>48경 834조 2237억 8543만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>47경 6048조 4947억 5487만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>46경 8028조 2449억 5700만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
     <t>122</t>
   </si>
   <si>
-    <t>85경 8894조 1952억 8378만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>78경 3943조 4780억 2568만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>48경 834조 2237억 8543만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>46경 2528조 6129억 7820만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>44경 6683조 9426억 1397만</t>
+    <t>44경 9169조 3146억 906만</t>
   </si>
   <si>
     <t>11</t>
@@ -395,7 +395,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>37경 8729조 5286억 2732만</t>
+    <t>42경 752조 5877억 8211만</t>
   </si>
   <si>
     <t>12</t>
@@ -425,7 +425,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>28경 2514조 7004억 9852만</t>
+    <t>29경 4933조 8598억 7698만</t>
   </si>
   <si>
     <t>14</t>
@@ -437,7 +437,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 9067조 3518억 5만</t>
+    <t>25경 284조 3598억 3895만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,7 +449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>21경 148조 2647억 9744만</t>
+    <t>21경 436조 3705억 8354만</t>
   </si>
   <si>
     <t>16</t>
@@ -485,7 +485,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1960만</t>
+    <t>13경 5408조 677억 8062만</t>
   </si>
   <si>
     <t>19</t>
@@ -497,7 +497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>10경 6016조 364억 6115만</t>
+    <t>10경 8305조 4880억 3327만</t>
   </si>
   <si>
     <t>20</t>
@@ -521,6 +521,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>7경 4948조 4629억 103만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>폰병</t>
   </si>
   <si>
@@ -530,18 +542,6 @@
     <t>7경 4772조 1310억 7065만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>7경 4318조 3235억 2661만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -614,7 +614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 8768조 6008억 6927만</t>
+    <t>1경 8903조 4165억 5232만</t>
   </si>
   <si>
     <t>28</t>
@@ -626,7 +626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 6685조 4095억 6058만</t>
+    <t>1경 6732조 697억 2331만</t>
   </si>
   <si>
     <t>29</t>
@@ -641,13 +641,277 @@
     <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
+    <t>달하나별하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>279경 4954조 9082억 1944만</t>
+  </si>
+  <si>
+    <t>라온MS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>181경 8204조 6499억 8457만</t>
+  </si>
+  <si>
+    <t>왕이된사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>101경 7009조 401억 1927만</t>
+  </si>
+  <si>
+    <t>라온DK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
+  </si>
+  <si>
+    <t>81경 2026조 9445억 5460만</t>
+  </si>
+  <si>
+    <t>라온PB</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
+  </si>
+  <si>
+    <t>71경 308조 3942억 8949만</t>
+  </si>
+  <si>
+    <t>라온B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
+  </si>
+  <si>
+    <t>42경 571조 2197억 2306만</t>
+  </si>
+  <si>
+    <t>라온Z</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
+  </si>
+  <si>
+    <t>26경 1263조 8269억 2063만</t>
+  </si>
+  <si>
+    <t>스터디뱅크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
+  </si>
+  <si>
+    <t>5경 7698조 9233억 351만</t>
+  </si>
+  <si>
+    <t>상깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
+  </si>
+  <si>
+    <t>5경 1666조 9730억 2201만</t>
+  </si>
+  <si>
+    <t>StarLink</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
+  </si>
+  <si>
+    <t>3경 9092조 1079억 4347만</t>
+  </si>
+  <si>
+    <t>못함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
+  </si>
+  <si>
+    <t>3경 8617조 6869억 744만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
+  </si>
+  <si>
+    <t>3경 134조 4471억 3855만</t>
+  </si>
+  <si>
+    <t>금하나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>2경 2871조 8290억 9777만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>2경 2480조 5534억 5129만</t>
+  </si>
+  <si>
+    <t>쵸비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>2경 1281조 6453억 4837만</t>
+  </si>
+  <si>
+    <t>널꼬라봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
+  </si>
+  <si>
+    <t>1경 6027조 4749억 8865만</t>
+  </si>
+  <si>
+    <t>희다차</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
+  </si>
+  <si>
+    <t>1경 5106조 6231억 493만</t>
+  </si>
+  <si>
+    <t>연이무사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 2593조 6751억 9343만</t>
+  </si>
+  <si>
+    <t>걸동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 448조 656억 9808만</t>
+  </si>
+  <si>
+    <t>작업반장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EB%B0%98%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>7457조 1186억 5600만</t>
+  </si>
+  <si>
+    <t>김보들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
+  </si>
+  <si>
+    <t>7310조 6501억 3270만</t>
+  </si>
+  <si>
+    <t>치전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A0%84</t>
+  </si>
+  <si>
+    <t>7123조 6916억 299만</t>
+  </si>
+  <si>
+    <t>빈수르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>6520조 9182억 5850만</t>
+  </si>
+  <si>
+    <t>잉규우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B7%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3283조 3780억 8600만</t>
+  </si>
+  <si>
+    <t>무과금재능충</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%EA%B8%88%EC%9E%AC%EB%8A%A5%EC%B6%A9</t>
+  </si>
+  <si>
+    <t>2994조 2344억 4330만</t>
+  </si>
+  <si>
+    <t>삼성며언</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%84%B1%EB%A9%B0%EC%96%B8</t>
+  </si>
+  <si>
+    <t>2887조 7959억 1916만</t>
+  </si>
+  <si>
+    <t>심겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>253조 3301억 3088만</t>
+  </si>
+  <si>
     <t>종리츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1734경 8665조 4259억 3571만</t>
+    <t>1772경 2554조 1477억 941만</t>
   </si>
   <si>
     <t>요쁘</t>
@@ -656,7 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%81%98</t>
   </si>
   <si>
-    <t>146경 9210조 5552억 2224만</t>
+    <t>157경 6660조 8767억 1836만</t>
   </si>
   <si>
     <t>나야햄토리</t>
@@ -665,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%ED%96%84%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>101경 9703조 2913억 631만</t>
+    <t>133경 234조 1831억 2371만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
@@ -680,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%EC%82%AC%EC%88%98</t>
   </si>
   <si>
-    <t>14경 8360조 2756억 5764만</t>
+    <t>15경 5402조 854억 1760만</t>
   </si>
   <si>
     <t>딩느</t>
@@ -689,7 +953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A9%EB%8A%90</t>
   </si>
   <si>
-    <t>13경 8069조 4405억 5425만</t>
+    <t>14경 9209조 4659억 4616만</t>
   </si>
   <si>
     <t>시든꽃에물을</t>
@@ -698,7 +962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%A0%EA%BD%83%EC%97%90%EB%AC%BC%EC%9D%84</t>
   </si>
   <si>
-    <t>13경 2370조 3366억 7953만</t>
+    <t>13경 9999조 2139억 8076만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -707,12 +971,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>3경 4989조 190억 4940만</t>
   </si>
   <si>
@@ -722,9 +980,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>3경 2612조 2604억 9866만</t>
   </si>
   <si>
@@ -734,7 +989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>2경 5908조 9044억 2056만</t>
+    <t>2경 6556조 6410억 7424만</t>
   </si>
   <si>
     <t>동작대교</t>
@@ -743,7 +998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EC%9E%91%EB%8C%80%EA%B5%90</t>
   </si>
   <si>
-    <t>2경 2501조 3242억 4169만</t>
+    <t>2경 3567조 9163억 9213만</t>
   </si>
   <si>
     <t>나야츄</t>
@@ -755,15 +1010,24 @@
     <t>1경 4393조 6778억 3625만</t>
   </si>
   <si>
+    <t>깝츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 2943조 3444억 2631만</t>
+  </si>
+  <si>
     <t>날아라순자</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A0%EC%95%84%EB%9D%BC%EC%88%9C%EC%9E%90</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>1경 2076조 4816억 9769만</t>
   </si>
   <si>
@@ -773,16 +1037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 30조 6030억 7881만</t>
-  </si>
-  <si>
-    <t>꾸덕행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%8D%95%ED%96%89</t>
-  </si>
-  <si>
-    <t>9799조 1968억 6913만</t>
+    <t>1경 163조 1861억 4937만</t>
   </si>
   <si>
     <t>넹또</t>
@@ -821,6 +1076,15 @@
     <t>6051조 1417억 7599만</t>
   </si>
   <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>5904조 3079억 2089만</t>
+  </si>
+  <si>
     <t>천상츄</t>
   </si>
   <si>
@@ -848,9 +1112,6 @@
     <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
   </si>
   <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
     <t>5051조 7256억 2807만</t>
   </si>
   <si>
@@ -860,19 +1121,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>4289조 6428억 6705만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>4268조 7828억 8180만</t>
+    <t>4676조 6780억 2191만</t>
+  </si>
+  <si>
+    <t>나야김대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>4118조 9015억 5595만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -881,16 +1139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>3894조 7432억 4175만</t>
-  </si>
-  <si>
-    <t>나야김대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%95%BC%EA%B9%80%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3711조 293억 5772만</t>
+    <t>4111조 1477억 3481만</t>
   </si>
   <si>
     <t>화정츄</t>
@@ -902,6 +1151,15 @@
     <t>3389조 3873억 2601만</t>
   </si>
   <si>
+    <t>포이즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2763조 4451억 147만</t>
+  </si>
+  <si>
     <t>궁금증유발</t>
   </si>
   <si>
@@ -911,15 +1169,6 @@
     <t>2734조 8634억 6484만</t>
   </si>
   <si>
-    <t>포이즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%9D%B4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2692조 8173억 3981만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -929,259 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
   </si>
   <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>2329조 8194억 1497만</t>
-  </si>
-  <si>
-    <t>달하나별하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%ED%95%98%EB%82%98%EB%B3%84%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>279경 4954조 9082억 1944만</t>
-  </si>
-  <si>
-    <t>라온MS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
-  </si>
-  <si>
-    <t>180경 1277조 7508억 9771만</t>
-  </si>
-  <si>
-    <t>왕이된사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>98경 6693조 9283억 9486만</t>
-  </si>
-  <si>
-    <t>라온DK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8DK</t>
-  </si>
-  <si>
-    <t>81경 2026조 9445억 5460만</t>
-  </si>
-  <si>
-    <t>라온PB</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8PB</t>
-  </si>
-  <si>
-    <t>71경 308조 3942억 8949만</t>
-  </si>
-  <si>
-    <t>라온B</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8B</t>
-  </si>
-  <si>
-    <t>42경 137조 9477억 2491만</t>
-  </si>
-  <si>
-    <t>라온Z</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8Z</t>
-  </si>
-  <si>
-    <t>26경 1263조 8269억 2063만</t>
-  </si>
-  <si>
-    <t>스터디뱅크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%84%B0%EB%94%94%EB%B1%85%ED%81%AC</t>
-  </si>
-  <si>
-    <t>5경 2684조 7425억 7862만</t>
-  </si>
-  <si>
-    <t>상깅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
-  </si>
-  <si>
-    <t>5경 1650조 7124억 1325만</t>
-  </si>
-  <si>
-    <t>못함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BB%ED%95%A8</t>
-  </si>
-  <si>
-    <t>3경 8221조 9534억 218만</t>
-  </si>
-  <si>
-    <t>StarLink</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=StarLink</t>
-  </si>
-  <si>
-    <t>3경 6127조 720억 4912만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Onyul</t>
-  </si>
-  <si>
-    <t>2경 7530조 4082억 2527만</t>
-  </si>
-  <si>
-    <t>금하나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%ED%95%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>2경 2668조 5652억 6269만</t>
-  </si>
-  <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>2경 2480조 5534억 5129만</t>
-  </si>
-  <si>
-    <t>쵸비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2경 1281조 6453억 4837만</t>
-  </si>
-  <si>
-    <t>널꼬라봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%90%EA%BC%AC%EB%9D%BC%EB%B4%90</t>
-  </si>
-  <si>
-    <t>1경 6027조 4749억 8865만</t>
-  </si>
-  <si>
-    <t>희다차</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EB%8B%A4%EC%B0%A8</t>
-  </si>
-  <si>
-    <t>1경 4481조 7180억 3929만</t>
-  </si>
-  <si>
-    <t>연이무사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%9D%B4%EB%AC%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 2564조 3792억 1980만</t>
-  </si>
-  <si>
-    <t>걸동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 448조 656억 9808만</t>
-  </si>
-  <si>
-    <t>김보들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B3%B4%EB%93%A4</t>
-  </si>
-  <si>
-    <t>7310조 6501억 3270만</t>
-  </si>
-  <si>
-    <t>치전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A0%84</t>
-  </si>
-  <si>
-    <t>7096조 2974억 7032만</t>
-  </si>
-  <si>
-    <t>빈수르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%88%EC%88%98%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>6256조 9615억 5505만</t>
-  </si>
-  <si>
-    <t>잉규우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B7%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>3283조 3780억 8600만</t>
-  </si>
-  <si>
-    <t>삼성며언</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%84%B1%EB%A9%B0%EC%96%B8</t>
-  </si>
-  <si>
-    <t>2887조 7959억 1916만</t>
-  </si>
-  <si>
-    <t>무과금재능충</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%EA%B8%88%EC%9E%AC%EB%8A%A5%EC%B6%A9</t>
-  </si>
-  <si>
-    <t>2831조 5908억 1563만</t>
-  </si>
-  <si>
-    <t>심겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>253조 3301억 3088만</t>
-  </si>
-  <si>
-    <t>김바들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%B0%94%EB%93%A4</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>4억 1781만</t>
+    <t>2407조 2493억 8056만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1217,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>13경 7587조 3965억 6582만</t>
+    <t>13경 7601조 2024억 355만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -1229,6 +1226,15 @@
     <t>12경 7805조 791억 5905만</t>
   </si>
   <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>11경 6279조 9856억 8196만</t>
+  </si>
+  <si>
     <t>하후돈</t>
   </si>
   <si>
@@ -1253,16 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>10경 7475조 5883억 7689만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>10경 7242조 7937억 8721만</t>
+    <t>10경 8325조 7043억 8844만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -1271,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>9경 3317조 4001억 9160만</t>
+    <t>10경 5819조 998억 2162만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -1289,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 9699조 1981억 6015만</t>
+    <t>3경 3178조 9781억 8699만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1298,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 7903조 5183억 9816만</t>
+    <t>2경 8127조 9067억 203만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -1337,6 +1334,15 @@
     <t>2경 3508조 3251억 6396만</t>
   </si>
   <si>
+    <t>쌉새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
+  </si>
+  <si>
+    <t>2경 1927조 1440억 1308만</t>
+  </si>
+  <si>
     <t>프리프리</t>
   </si>
   <si>
@@ -1346,22 +1352,13 @@
     <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
-    <t>쌉새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
-  </si>
-  <si>
-    <t>2경 1101조 5163억 3714만</t>
-  </si>
-  <si>
     <t>망겜감별사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9797조 8732억 636만</t>
+    <t>1경 9979조 9674억 5590만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -1376,7 +1373,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 4316조 7438억 6414만</t>
+    <t>1경 5669조 3241억 5407만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1385,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 4044조 2010억 4291만</t>
+    <t>1경 4122조 3481억 9881만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -1412,7 +1409,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 1347조 2778억 8822만</t>
+    <t>1경 1353조 1986억 6676만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -1421,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>8154조 2007억 5516만</t>
+    <t>8180조 6118억 3210만</t>
   </si>
   <si>
     <t>러너</t>
@@ -1448,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%9D%BC%EB%9D%BC%EC%98%A8</t>
   </si>
   <si>
-    <t>2291조 6804억 2795만</t>
+    <t>2292조 5167억 1606만</t>
   </si>
   <si>
     <t>결기</t>
@@ -1472,7 +1469,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>652조 6436억 3867만</t>
+    <t>652조 7748억 4510만</t>
   </si>
   <si>
     <t>후추양조장</t>
@@ -1547,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A1%9C%EC%96%98</t>
   </si>
   <si>
-    <t>250조 2125억 2104만</t>
+    <t>250조 4251억 1610만</t>
   </si>
   <si>
     <t>성식대군</t>
@@ -1556,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%8B%9D%EB%8C%80%EA%B5%B0</t>
   </si>
   <si>
-    <t>228조 146억 808만</t>
+    <t>234조 7600억 5579만</t>
   </si>
   <si>
     <t>버미겨리0</t>
@@ -1568,7 +1565,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>209조 4772억 5837만</t>
+    <t>211조 8466억 9067만</t>
   </si>
   <si>
     <t>태환이</t>
@@ -1595,7 +1592,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%83%81%EC%82%AC</t>
   </si>
   <si>
-    <t>152조 2230억 5936만</t>
+    <t>155조 2701억 9992만</t>
   </si>
   <si>
     <t>벵글</t>
@@ -1604,7 +1601,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%B5%EA%B8%80</t>
   </si>
   <si>
-    <t>150조 6855억 4467만</t>
+    <t>151조 2026억 8593만</t>
   </si>
   <si>
     <t>NSYN</t>
@@ -1613,7 +1610,7 @@
     <t>https://mgf.gg/contents/character.php?n=NSYN</t>
   </si>
   <si>
-    <t>142조 5792억 8033만</t>
+    <t>145조 1129억 4966만</t>
   </si>
   <si>
     <t>에너지솔루션</t>
@@ -1622,7 +1619,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%84%88%EC%A7%80%EC%86%94%EB%A3%A8%EC%85%98</t>
   </si>
   <si>
-    <t>131조 2936억 7103만</t>
+    <t>139조 3768억 1186만</t>
   </si>
   <si>
     <t>방제서</t>
@@ -1634,7 +1631,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>107조 3459억 6343만</t>
+    <t>108조 6426억 8359만</t>
   </si>
   <si>
     <t>무큼이</t>
@@ -1643,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%81%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>102조 7538억 3535만</t>
+    <t>103조 381억 8380만</t>
   </si>
   <si>
     <t>피읕</t>
@@ -1652,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%9D%95</t>
   </si>
   <si>
-    <t>95조 3657억 64만</t>
+    <t>101조 3115억 3152만</t>
   </si>
   <si>
     <t>꿀가족</t>
@@ -1691,7 +1688,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>16조 3348억 8107만</t>
+    <t>16조 7820억 339만</t>
   </si>
   <si>
     <t>이제명확찢</t>
@@ -1721,7 +1718,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 1913억 6466만</t>
+    <t>4조 2003억 2826만</t>
   </si>
   <si>
     <t>백송희</t>
@@ -1736,7 +1733,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>2025억 9410만</t>
+    <t>2152억 4345만</t>
   </si>
   <si>
     <t>봐람</t>
@@ -2232,64 +2229,64 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2315,7 +2312,7 @@
         <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -2356,7 +2353,7 @@
         <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -2371,7 +2368,7 @@
         <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2553,10 +2550,10 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2567,16 +2564,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -2585,10 +2582,10 @@
         <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2599,16 +2596,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -2617,10 +2614,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2631,16 +2628,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -2649,10 +2646,10 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2663,28 +2660,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2695,28 +2692,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2727,16 +2724,16 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -2745,7 +2742,7 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>117</v>
@@ -2809,7 +2806,7 @@
         <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>127</v>
@@ -2905,7 +2902,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -3001,7 +2998,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>152</v>
@@ -3033,7 +3030,7 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>156</v>
@@ -3094,7 +3091,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>161</v>
@@ -3126,7 +3123,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>161</v>
@@ -3401,6 +3398,952 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>219</v>
+  